--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -1311,49 +1311,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128100827</v>
+        <v>128108655</v>
       </c>
       <c r="B8" t="n">
-        <v>98467</v>
+        <v>92640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533406</v>
+        <v>533673</v>
       </c>
       <c r="R8" t="n">
-        <v>6962317</v>
+        <v>6962211</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1408,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128101860</v>
+        <v>128108619</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1443,19 +1439,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533601</v>
+        <v>533675</v>
       </c>
       <c r="R9" t="n">
-        <v>6962344</v>
+        <v>6962244</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1519,10 +1515,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128109460</v>
+        <v>128110972</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1530,21 +1526,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1554,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533498</v>
+        <v>533997</v>
       </c>
       <c r="R10" t="n">
-        <v>6962158</v>
+        <v>6962746</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,6 +1586,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1616,45 +1617,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128110802</v>
+        <v>128101860</v>
       </c>
       <c r="B11" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533461</v>
+        <v>533601</v>
       </c>
       <c r="R11" t="n">
-        <v>6962171</v>
+        <v>6962344</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1691,7 +1697,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,10 +1724,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128110972</v>
+        <v>128109460</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,21 +1735,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1753,10 +1759,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533997</v>
+        <v>533498</v>
       </c>
       <c r="R12" t="n">
-        <v>6962746</v>
+        <v>6962158</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1789,11 +1795,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,50 +1821,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128108619</v>
+        <v>128110802</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533675</v>
+        <v>533461</v>
       </c>
       <c r="R13" t="n">
-        <v>6962244</v>
+        <v>6962171</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,7 +1896,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,45 +1923,49 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128108655</v>
+        <v>128100827</v>
       </c>
       <c r="B14" t="n">
-        <v>92639</v>
+        <v>98468</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533673</v>
+        <v>533406</v>
       </c>
       <c r="R14" t="n">
-        <v>6962211</v>
+        <v>6962317</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,37 +2131,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128100321</v>
+        <v>128109367</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2170,10 +2171,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533537</v>
+        <v>533550</v>
       </c>
       <c r="R16" t="n">
-        <v>6962358</v>
+        <v>6962157</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,6 +2207,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2232,10 +2238,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128100131</v>
+        <v>128110818</v>
       </c>
       <c r="B17" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,21 +2266,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533496</v>
+        <v>533766</v>
       </c>
       <c r="R17" t="n">
-        <v>6962335</v>
+        <v>6962317</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,6 +2309,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>10stycken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2430,50 +2437,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128109367</v>
+        <v>128110833</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533550</v>
+        <v>533768</v>
       </c>
       <c r="R19" t="n">
-        <v>6962157</v>
+        <v>6962318</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2506,11 +2508,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2537,45 +2534,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128110833</v>
+        <v>128100321</v>
       </c>
       <c r="B20" t="n">
-        <v>98384</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533768</v>
+        <v>533537</v>
       </c>
       <c r="R20" t="n">
-        <v>6962318</v>
+        <v>6962358</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,10 +2635,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128110818</v>
+        <v>128100131</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2662,17 +2663,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533766</v>
+        <v>533496</v>
       </c>
       <c r="R21" t="n">
-        <v>6962317</v>
+        <v>6962335</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,11 +2710,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>10stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2736,7 +2736,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128099395</v>
+        <v>128110771</v>
       </c>
       <c r="B22" t="n">
         <v>57672</v>
@@ -2765,21 +2765,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533356</v>
+        <v>533583</v>
       </c>
       <c r="R22" t="n">
-        <v>6962190</v>
+        <v>6962697</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2816,7 +2811,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
+          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2843,49 +2838,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128101601</v>
+        <v>128109293</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533496</v>
+        <v>533638</v>
       </c>
       <c r="R23" t="n">
-        <v>6962407</v>
+        <v>6962157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,6 +2914,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2944,10 +2945,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128108218</v>
+        <v>128101601</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2974,19 +2975,19 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533789</v>
+        <v>533496</v>
       </c>
       <c r="R24" t="n">
-        <v>6962263</v>
+        <v>6962407</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,38 +3046,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128109293</v>
+        <v>128108218</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533638</v>
+        <v>533789</v>
       </c>
       <c r="R25" t="n">
-        <v>6962157</v>
+        <v>6962263</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3121,11 +3121,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3152,7 +3147,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128110771</v>
+        <v>128099395</v>
       </c>
       <c r="B26" t="n">
         <v>57672</v>
@@ -3181,16 +3176,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533583</v>
+        <v>533356</v>
       </c>
       <c r="R26" t="n">
-        <v>6962697</v>
+        <v>6962190</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
+          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,10 +3254,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128110832</v>
+        <v>128108592</v>
       </c>
       <c r="B27" t="n">
-        <v>98384</v>
+        <v>80036</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,34 +3265,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>219790</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533652</v>
+        <v>533675</v>
       </c>
       <c r="R27" t="n">
-        <v>6962264</v>
+        <v>6962244</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,10 +3351,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128108592</v>
+        <v>128110832</v>
       </c>
       <c r="B28" t="n">
-        <v>80036</v>
+        <v>98385</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3362,34 +3362,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533675</v>
+        <v>533652</v>
       </c>
       <c r="R28" t="n">
-        <v>6962244</v>
+        <v>6962264</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,37 +3448,38 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128100230</v>
+        <v>128099402</v>
       </c>
       <c r="B29" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>55</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3487,10 +3488,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533506</v>
+        <v>533474</v>
       </c>
       <c r="R29" t="n">
-        <v>6962358</v>
+        <v>6962267</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3523,6 +3524,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3549,50 +3555,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128099402</v>
+        <v>128110780</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>91122</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533474</v>
+        <v>533670</v>
       </c>
       <c r="R30" t="n">
-        <v>6962267</v>
+        <v>6962552</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3625,11 +3626,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3656,54 +3652,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128099830</v>
+        <v>128110981</v>
       </c>
       <c r="B31" t="n">
-        <v>92639</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533353</v>
+        <v>533689</v>
       </c>
       <c r="R31" t="n">
-        <v>6962231</v>
+        <v>6962405</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3740,7 +3727,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3767,10 +3754,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128102143</v>
+        <v>128109875</v>
       </c>
       <c r="B32" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3797,7 +3784,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3806,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533615</v>
+        <v>533436</v>
       </c>
       <c r="R32" t="n">
-        <v>6962423</v>
+        <v>6962158</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3868,10 +3855,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128109875</v>
+        <v>128102143</v>
       </c>
       <c r="B33" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3898,7 +3885,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3907,10 +3894,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533436</v>
+        <v>533615</v>
       </c>
       <c r="R33" t="n">
-        <v>6962158</v>
+        <v>6962423</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3969,10 +3956,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128110803</v>
+        <v>128100230</v>
       </c>
       <c r="B34" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3997,17 +3984,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533524</v>
+        <v>533506</v>
       </c>
       <c r="R34" t="n">
-        <v>6962153</v>
+        <v>6962358</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4040,11 +4031,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4071,45 +4057,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128110981</v>
+        <v>128099830</v>
       </c>
       <c r="B35" t="n">
-        <v>98467</v>
+        <v>92640</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533689</v>
+        <v>533353</v>
       </c>
       <c r="R35" t="n">
-        <v>6962405</v>
+        <v>6962231</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4146,7 +4141,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4173,10 +4168,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128110780</v>
+        <v>128110790</v>
       </c>
       <c r="B36" t="n">
-        <v>91121</v>
+        <v>98502</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4184,21 +4179,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4208,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533670</v>
+        <v>533822</v>
       </c>
       <c r="R36" t="n">
-        <v>6962552</v>
+        <v>6962344</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4244,6 +4239,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4270,32 +4270,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128110790</v>
+        <v>128110803</v>
       </c>
       <c r="B37" t="n">
-        <v>98501</v>
+        <v>98468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4305,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533822</v>
+        <v>533524</v>
       </c>
       <c r="R37" t="n">
-        <v>6962344</v>
+        <v>6962153</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4372,7 +4372,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128101831</v>
+        <v>128110968</v>
       </c>
       <c r="B38" t="n">
         <v>57672</v>
@@ -4401,21 +4401,16 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533513</v>
+        <v>533634</v>
       </c>
       <c r="R38" t="n">
-        <v>6962442</v>
+        <v>6962526</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4452,7 +4447,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4479,45 +4474,50 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128108150</v>
+        <v>128102724</v>
       </c>
       <c r="B39" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533800</v>
+        <v>533659</v>
       </c>
       <c r="R39" t="n">
-        <v>6962306</v>
+        <v>6962512</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4550,6 +4550,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4576,7 +4581,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128102724</v>
+        <v>128101831</v>
       </c>
       <c r="B40" t="n">
         <v>57672</v>
@@ -4607,7 +4612,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4616,10 +4621,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533659</v>
+        <v>533513</v>
       </c>
       <c r="R40" t="n">
-        <v>6962512</v>
+        <v>6962442</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4656,7 +4661,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4683,32 +4688,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128099282</v>
+        <v>128110767</v>
       </c>
       <c r="B41" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4718,10 +4723,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533452</v>
+        <v>533794</v>
       </c>
       <c r="R41" t="n">
-        <v>6962232</v>
+        <v>6962411</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4754,6 +4759,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4780,10 +4790,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128110978</v>
+        <v>128110788</v>
       </c>
       <c r="B42" t="n">
-        <v>98501</v>
+        <v>98502</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4815,10 +4825,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533708</v>
+        <v>533590</v>
       </c>
       <c r="R42" t="n">
-        <v>6962645</v>
+        <v>6962592</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4877,32 +4887,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128110788</v>
+        <v>128110824</v>
       </c>
       <c r="B43" t="n">
-        <v>98501</v>
+        <v>98468</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4912,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533590</v>
+        <v>533712</v>
       </c>
       <c r="R43" t="n">
-        <v>6962592</v>
+        <v>6962628</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4948,6 +4958,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4974,45 +4989,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128110968</v>
+        <v>128108150</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533634</v>
+        <v>533800</v>
       </c>
       <c r="R44" t="n">
-        <v>6962526</v>
+        <v>6962306</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5045,11 +5060,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5076,10 +5086,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128110836</v>
+        <v>128110978</v>
       </c>
       <c r="B45" t="n">
-        <v>98384</v>
+        <v>98502</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5087,21 +5097,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5111,10 +5121,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533722</v>
+        <v>533708</v>
       </c>
       <c r="R45" t="n">
-        <v>6962426</v>
+        <v>6962645</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5173,32 +5183,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128110767</v>
+        <v>128110836</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5208,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533794</v>
+        <v>533722</v>
       </c>
       <c r="R46" t="n">
-        <v>6962411</v>
+        <v>6962426</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,11 +5254,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5275,32 +5280,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128110824</v>
+        <v>128099282</v>
       </c>
       <c r="B47" t="n">
-        <v>98467</v>
+        <v>80160</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5310,10 +5315,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533712</v>
+        <v>533452</v>
       </c>
       <c r="R47" t="n">
-        <v>6962628</v>
+        <v>6962232</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5346,11 +5351,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5377,32 +5377,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128101106</v>
+        <v>128101702</v>
       </c>
       <c r="B48" t="n">
-        <v>80098</v>
+        <v>91350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229748</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533425</v>
+        <v>533529</v>
       </c>
       <c r="R48" t="n">
-        <v>6962304</v>
+        <v>6962400</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5474,10 +5474,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128101702</v>
+        <v>128107546</v>
       </c>
       <c r="B49" t="n">
-        <v>91349</v>
+        <v>80133</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5485,34 +5485,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533529</v>
+        <v>533648</v>
       </c>
       <c r="R49" t="n">
-        <v>6962400</v>
+        <v>6962374</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128107546</v>
+        <v>128110766</v>
       </c>
       <c r="B50" t="n">
-        <v>80133</v>
+        <v>57672</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5582,34 +5582,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533648</v>
+        <v>533586</v>
       </c>
       <c r="R50" t="n">
-        <v>6962374</v>
+        <v>6962139</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5642,6 +5642,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5668,54 +5673,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128103304</v>
+        <v>128110970</v>
       </c>
       <c r="B51" t="n">
-        <v>91121</v>
+        <v>57672</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533594</v>
+        <v>534050</v>
       </c>
       <c r="R51" t="n">
-        <v>6962541</v>
+        <v>6962743</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5748,6 +5744,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5774,39 +5775,35 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128099088</v>
+        <v>128101106</v>
       </c>
       <c r="B52" t="n">
-        <v>98467</v>
+        <v>80098</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>229748</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
@@ -5816,7 +5813,7 @@
         <v>533425</v>
       </c>
       <c r="R52" t="n">
-        <v>6962182</v>
+        <v>6962304</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5875,45 +5872,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128110812</v>
+        <v>128108922</v>
       </c>
       <c r="B53" t="n">
-        <v>98467</v>
+        <v>105506</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533715</v>
+        <v>533671</v>
       </c>
       <c r="R53" t="n">
-        <v>6962610</v>
+        <v>6962142</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5946,11 +5943,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5977,10 +5969,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128110826</v>
+        <v>128110812</v>
       </c>
       <c r="B54" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6012,10 +6004,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533579</v>
+        <v>533715</v>
       </c>
       <c r="R54" t="n">
-        <v>6962663</v>
+        <v>6962610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6052,7 +6044,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6079,32 +6071,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128110766</v>
+        <v>128110826</v>
       </c>
       <c r="B55" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6114,10 +6106,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533586</v>
+        <v>533579</v>
       </c>
       <c r="R55" t="n">
-        <v>6962139</v>
+        <v>6962663</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6154,7 +6146,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6184,7 +6176,7 @@
         <v>128110804</v>
       </c>
       <c r="B56" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6286,7 +6278,7 @@
         <v>128110990</v>
       </c>
       <c r="B57" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6388,7 +6380,7 @@
         <v>128110814</v>
       </c>
       <c r="B58" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6487,45 +6479,49 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128110970</v>
+        <v>128099088</v>
       </c>
       <c r="B59" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>534050</v>
+        <v>533425</v>
       </c>
       <c r="R59" t="n">
-        <v>6962743</v>
+        <v>6962182</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6558,11 +6554,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6589,10 +6580,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128108922</v>
+        <v>128103304</v>
       </c>
       <c r="B60" t="n">
-        <v>105505</v>
+        <v>91122</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6600,34 +6591,43 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221144</v>
+        <v>3215</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533671</v>
+        <v>533594</v>
       </c>
       <c r="R60" t="n">
-        <v>6962142</v>
+        <v>6962541</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128100636</v>
+        <v>128110971</v>
       </c>
       <c r="B61" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6697,21 +6697,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6721,10 +6721,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533452</v>
+        <v>534036</v>
       </c>
       <c r="R61" t="n">
-        <v>6962350</v>
+        <v>6962734</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6757,6 +6757,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6783,45 +6788,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128099099</v>
+        <v>128108477</v>
       </c>
       <c r="B62" t="n">
-        <v>105505</v>
+        <v>57672</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533416</v>
+        <v>533710</v>
       </c>
       <c r="R62" t="n">
-        <v>6962179</v>
+        <v>6962294</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6854,6 +6864,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6880,10 +6895,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128103587</v>
+        <v>128110827</v>
       </c>
       <c r="B63" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6908,21 +6923,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533650</v>
+        <v>533614</v>
       </c>
       <c r="R63" t="n">
-        <v>6962600</v>
+        <v>6962554</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6955,6 +6966,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6981,45 +6997,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128110971</v>
+        <v>128103587</v>
       </c>
       <c r="B64" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>534036</v>
+        <v>533650</v>
       </c>
       <c r="R64" t="n">
-        <v>6962734</v>
+        <v>6962600</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7052,11 +7072,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7083,10 +7098,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128110827</v>
+        <v>128100184</v>
       </c>
       <c r="B65" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7111,17 +7126,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533614</v>
+        <v>533509</v>
       </c>
       <c r="R65" t="n">
-        <v>6962554</v>
+        <v>6962336</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7154,11 +7173,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7185,10 +7199,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128108477</v>
+        <v>128099984</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7196,39 +7210,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533710</v>
+        <v>533455</v>
       </c>
       <c r="R66" t="n">
-        <v>6962294</v>
+        <v>6962339</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7261,11 +7270,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7292,49 +7296,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128100184</v>
+        <v>128099875</v>
       </c>
       <c r="B67" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533509</v>
+        <v>533445</v>
       </c>
       <c r="R67" t="n">
-        <v>6962336</v>
+        <v>6962324</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7393,32 +7393,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128099984</v>
+        <v>128099099</v>
       </c>
       <c r="B68" t="n">
-        <v>80132</v>
+        <v>105506</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7428,10 +7428,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533455</v>
+        <v>533416</v>
       </c>
       <c r="R68" t="n">
-        <v>6962339</v>
+        <v>6962179</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7490,45 +7490,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128099875</v>
+        <v>128099522</v>
       </c>
       <c r="B69" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533445</v>
+        <v>533349</v>
       </c>
       <c r="R69" t="n">
-        <v>6962324</v>
+        <v>6962197</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7694,54 +7703,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128099522</v>
+        <v>128100636</v>
       </c>
       <c r="B71" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533349</v>
+        <v>533452</v>
       </c>
       <c r="R71" t="n">
-        <v>6962197</v>
+        <v>6962350</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8004,49 +8004,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128101024</v>
+        <v>128110769</v>
       </c>
       <c r="B74" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533375</v>
+        <v>533841</v>
       </c>
       <c r="R74" t="n">
-        <v>6962293</v>
+        <v>6962363</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8079,6 +8075,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack) spår</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8105,7 +8106,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128101911</v>
+        <v>128110775</v>
       </c>
       <c r="B75" t="n">
         <v>57672</v>
@@ -8134,21 +8135,16 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533510</v>
+        <v>533564</v>
       </c>
       <c r="R75" t="n">
-        <v>6962462</v>
+        <v>6962537</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8185,7 +8181,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Färska och äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8319,7 +8315,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128110769</v>
+        <v>128101911</v>
       </c>
       <c r="B77" t="n">
         <v>57672</v>
@@ -8348,16 +8344,21 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533841</v>
+        <v>533510</v>
       </c>
       <c r="R77" t="n">
-        <v>6962363</v>
+        <v>6962462</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8394,7 +8395,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack) spår</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8421,45 +8422,49 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128110775</v>
+        <v>128101024</v>
       </c>
       <c r="B78" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533564</v>
+        <v>533375</v>
       </c>
       <c r="R78" t="n">
-        <v>6962537</v>
+        <v>6962293</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8492,11 +8497,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8526,7 +8526,7 @@
         <v>128110811</v>
       </c>
       <c r="B79" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8625,50 +8625,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128099905</v>
+        <v>128110779</v>
       </c>
       <c r="B80" t="n">
-        <v>57672</v>
+        <v>91122</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533445</v>
+        <v>533678</v>
       </c>
       <c r="R80" t="n">
-        <v>6962324</v>
+        <v>6962542</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8701,11 +8696,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8732,49 +8722,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128101261</v>
+        <v>128102006</v>
       </c>
       <c r="B81" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533424</v>
+        <v>533510</v>
       </c>
       <c r="R81" t="n">
-        <v>6962357</v>
+        <v>6962462</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8833,7 +8819,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128100974</v>
+        <v>128101827</v>
       </c>
       <c r="B82" t="n">
         <v>57672</v>
@@ -8873,10 +8859,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533375</v>
+        <v>533594</v>
       </c>
       <c r="R82" t="n">
-        <v>6962293</v>
+        <v>6962354</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8913,7 +8899,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8940,10 +8926,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128102006</v>
+        <v>128100974</v>
       </c>
       <c r="B83" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8951,34 +8937,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533510</v>
+        <v>533375</v>
       </c>
       <c r="R83" t="n">
-        <v>6962462</v>
+        <v>6962293</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9011,6 +9002,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9037,7 +9033,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128101827</v>
+        <v>128110969</v>
       </c>
       <c r="B84" t="n">
         <v>57672</v>
@@ -9066,21 +9062,16 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533594</v>
+        <v>533825</v>
       </c>
       <c r="R84" t="n">
-        <v>6962354</v>
+        <v>6962690</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9117,7 +9108,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9144,45 +9135,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128110982</v>
+        <v>128099905</v>
       </c>
       <c r="B85" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533681</v>
+        <v>533445</v>
       </c>
       <c r="R85" t="n">
-        <v>6962434</v>
+        <v>6962324</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9219,7 +9215,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>23 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9246,45 +9242,49 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128110969</v>
+        <v>128101261</v>
       </c>
       <c r="B86" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533825</v>
+        <v>533424</v>
       </c>
       <c r="R86" t="n">
-        <v>6962690</v>
+        <v>6962357</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9317,11 +9317,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9348,32 +9343,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128110779</v>
+        <v>128110982</v>
       </c>
       <c r="B87" t="n">
-        <v>91121</v>
+        <v>98468</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9383,10 +9378,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533678</v>
+        <v>533681</v>
       </c>
       <c r="R87" t="n">
-        <v>6962542</v>
+        <v>6962434</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9419,6 +9414,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>23 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9448,7 +9448,7 @@
         <v>128110976</v>
       </c>
       <c r="B88" t="n">
-        <v>98501</v>
+        <v>98502</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>128110810</v>
       </c>
       <c r="B89" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9644,32 +9644,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128110989</v>
+        <v>128110973</v>
       </c>
       <c r="B90" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533912</v>
+        <v>533841</v>
       </c>
       <c r="R90" t="n">
-        <v>6962770</v>
+        <v>6962731</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9719,7 +9719,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9746,10 +9746,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128110806</v>
+        <v>128110989</v>
       </c>
       <c r="B91" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9781,10 +9781,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533638</v>
+        <v>533912</v>
       </c>
       <c r="R91" t="n">
-        <v>6962276</v>
+        <v>6962770</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>4 stycken kan finnas mer I blåbärsriset</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9848,32 +9848,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128110973</v>
+        <v>128110806</v>
       </c>
       <c r="B92" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9883,10 +9883,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>533841</v>
+        <v>533638</v>
       </c>
       <c r="R92" t="n">
-        <v>6962731</v>
+        <v>6962276</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9923,7 +9923,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>4 stycken kan finnas mer I blåbärsriset</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10047,38 +10047,42 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128099555</v>
+        <v>128099401</v>
       </c>
       <c r="B94" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10087,10 +10091,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533471</v>
+        <v>533356</v>
       </c>
       <c r="R94" t="n">
-        <v>6962293</v>
+        <v>6962190</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10123,11 +10127,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10154,10 +10153,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128102067</v>
+        <v>128110816</v>
       </c>
       <c r="B95" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10182,21 +10181,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533510</v>
+        <v>533696</v>
       </c>
       <c r="R95" t="n">
-        <v>6962462</v>
+        <v>6962294</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10229,6 +10224,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10255,50 +10255,49 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128102878</v>
+        <v>128102067</v>
       </c>
       <c r="B96" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533665</v>
+        <v>533510</v>
       </c>
       <c r="R96" t="n">
-        <v>6962515</v>
+        <v>6962462</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10331,11 +10330,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10362,45 +10356,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128110974</v>
+        <v>128099555</v>
       </c>
       <c r="B97" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533937</v>
+        <v>533471</v>
       </c>
       <c r="R97" t="n">
-        <v>6962685</v>
+        <v>6962293</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10433,6 +10432,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10459,10 +10463,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128110834</v>
+        <v>128110974</v>
       </c>
       <c r="B98" t="n">
-        <v>98384</v>
+        <v>80161</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10470,21 +10474,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10494,10 +10498,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>533779</v>
+        <v>533937</v>
       </c>
       <c r="R98" t="n">
-        <v>6962298</v>
+        <v>6962685</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10556,45 +10560,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128110816</v>
+        <v>128102878</v>
       </c>
       <c r="B99" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>533696</v>
+        <v>533665</v>
       </c>
       <c r="R99" t="n">
-        <v>6962294</v>
+        <v>6962515</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10631,7 +10640,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>20 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10765,10 +10774,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128099401</v>
+        <v>128110834</v>
       </c>
       <c r="B101" t="n">
-        <v>92639</v>
+        <v>98385</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10776,43 +10785,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533356</v>
+        <v>533779</v>
       </c>
       <c r="R101" t="n">
-        <v>6962190</v>
+        <v>6962298</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10968,32 +10968,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128110785</v>
+        <v>128110829</v>
       </c>
       <c r="B103" t="n">
-        <v>97344</v>
+        <v>56855</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11003,10 +11003,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>533824</v>
+        <v>533606</v>
       </c>
       <c r="R103" t="n">
-        <v>6962352</v>
+        <v>6962582</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11039,6 +11039,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11065,32 +11070,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128110807</v>
+        <v>128110785</v>
       </c>
       <c r="B104" t="n">
-        <v>98467</v>
+        <v>97345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11100,10 +11105,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>533664</v>
+        <v>533824</v>
       </c>
       <c r="R104" t="n">
-        <v>6962286</v>
+        <v>6962352</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11136,11 +11141,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11170,7 +11170,7 @@
         <v>128110792</v>
       </c>
       <c r="B105" t="n">
-        <v>98501</v>
+        <v>98502</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11269,10 +11269,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128110983</v>
+        <v>128110807</v>
       </c>
       <c r="B106" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11304,10 +11304,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>533665</v>
+        <v>533664</v>
       </c>
       <c r="R106" t="n">
-        <v>6962459</v>
+        <v>6962286</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11344,7 +11344,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>26 ex</t>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11371,32 +11371,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128110829</v>
+        <v>128110983</v>
       </c>
       <c r="B107" t="n">
-        <v>56855</v>
+        <v>98468</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11406,10 +11406,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533606</v>
+        <v>533665</v>
       </c>
       <c r="R107" t="n">
-        <v>6962582</v>
+        <v>6962459</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>1 ex. Sång</t>
+          <t>26 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11473,10 +11473,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128101331</v>
+        <v>128103993</v>
       </c>
       <c r="B108" t="n">
-        <v>80167</v>
+        <v>105506</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11484,34 +11484,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6463</v>
+        <v>221144</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533424</v>
+        <v>533664</v>
       </c>
       <c r="R108" t="n">
-        <v>6962357</v>
+        <v>6962650</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11570,50 +11570,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128100457</v>
+        <v>128108028</v>
       </c>
       <c r="B109" t="n">
-        <v>57672</v>
+        <v>97351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533556</v>
+        <v>533802</v>
       </c>
       <c r="R109" t="n">
-        <v>6962363</v>
+        <v>6962332</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11646,11 +11641,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11677,10 +11667,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128103044</v>
+        <v>128099487</v>
       </c>
       <c r="B110" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11707,19 +11697,19 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533627</v>
+        <v>533474</v>
       </c>
       <c r="R110" t="n">
-        <v>6962544</v>
+        <v>6962267</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11778,45 +11768,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128108395</v>
+        <v>128110838</v>
       </c>
       <c r="B111" t="n">
-        <v>80132</v>
+        <v>98385</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>533735</v>
+        <v>533708</v>
       </c>
       <c r="R111" t="n">
-        <v>6962274</v>
+        <v>6962624</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11849,6 +11839,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11875,10 +11870,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128103993</v>
+        <v>128110793</v>
       </c>
       <c r="B112" t="n">
-        <v>105505</v>
+        <v>98502</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11886,34 +11881,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221144</v>
+        <v>219874</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>533664</v>
+        <v>533693</v>
       </c>
       <c r="R112" t="n">
-        <v>6962650</v>
+        <v>6962647</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11946,6 +11941,11 @@
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11972,49 +11972,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128099487</v>
+        <v>128110783</v>
       </c>
       <c r="B113" t="n">
-        <v>98467</v>
+        <v>91122</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533474</v>
+        <v>533599</v>
       </c>
       <c r="R113" t="n">
-        <v>6962267</v>
+        <v>6962553</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12073,10 +12069,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128108028</v>
+        <v>128101331</v>
       </c>
       <c r="B114" t="n">
-        <v>97350</v>
+        <v>80167</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12084,34 +12080,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533802</v>
+        <v>533424</v>
       </c>
       <c r="R114" t="n">
-        <v>6962332</v>
+        <v>6962357</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12170,10 +12166,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128108378</v>
+        <v>128108395</v>
       </c>
       <c r="B115" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12181,39 +12177,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533750</v>
+        <v>533735</v>
       </c>
       <c r="R115" t="n">
-        <v>6962259</v>
+        <v>6962274</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12246,11 +12237,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12277,45 +12263,50 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128110991</v>
+        <v>128108378</v>
       </c>
       <c r="B116" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533717</v>
+        <v>533750</v>
       </c>
       <c r="R116" t="n">
-        <v>6962645</v>
+        <v>6962259</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12352,7 +12343,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12379,45 +12370,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128110838</v>
+        <v>128100457</v>
       </c>
       <c r="B117" t="n">
-        <v>98384</v>
+        <v>57672</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533708</v>
+        <v>533556</v>
       </c>
       <c r="R117" t="n">
-        <v>6962624</v>
+        <v>6962363</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12454,7 +12450,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>1 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12481,32 +12477,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128110793</v>
+        <v>128110776</v>
       </c>
       <c r="B118" t="n">
-        <v>98501</v>
+        <v>57832</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12516,10 +12512,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533693</v>
+        <v>533719</v>
       </c>
       <c r="R118" t="n">
-        <v>6962647</v>
+        <v>6962615</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12583,32 +12579,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128110776</v>
+        <v>128110794</v>
       </c>
       <c r="B119" t="n">
-        <v>57832</v>
+        <v>98502</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12618,10 +12614,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533719</v>
+        <v>533608</v>
       </c>
       <c r="R119" t="n">
-        <v>6962615</v>
+        <v>6962612</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12658,7 +12654,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12685,32 +12681,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128110783</v>
+        <v>128110991</v>
       </c>
       <c r="B120" t="n">
-        <v>91121</v>
+        <v>98468</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12720,10 +12716,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533599</v>
+        <v>533717</v>
       </c>
       <c r="R120" t="n">
-        <v>6962553</v>
+        <v>6962645</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12756,6 +12752,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12785,7 +12786,7 @@
         <v>128110987</v>
       </c>
       <c r="B121" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12884,45 +12885,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128110794</v>
+        <v>128103044</v>
       </c>
       <c r="B122" t="n">
-        <v>98501</v>
+        <v>98468</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533608</v>
+        <v>533627</v>
       </c>
       <c r="R122" t="n">
-        <v>6962612</v>
+        <v>6962544</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12955,11 +12960,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12989,7 +12989,7 @@
         <v>128110819</v>
       </c>
       <c r="B123" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13088,45 +13088,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128108119</v>
+        <v>128099239</v>
       </c>
       <c r="B124" t="n">
-        <v>98501</v>
+        <v>57672</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>533800</v>
+        <v>533422</v>
       </c>
       <c r="R124" t="n">
-        <v>6962306</v>
+        <v>6962229</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13159,6 +13164,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13185,50 +13195,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128099239</v>
+        <v>128099811</v>
       </c>
       <c r="B125" t="n">
-        <v>57672</v>
+        <v>105506</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>533422</v>
+        <v>533451</v>
       </c>
       <c r="R125" t="n">
-        <v>6962229</v>
+        <v>6962307</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13261,11 +13266,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13292,10 +13292,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128099811</v>
+        <v>128109488</v>
       </c>
       <c r="B126" t="n">
-        <v>105505</v>
+        <v>80161</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13303,21 +13303,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221144</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13327,10 +13327,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>533451</v>
+        <v>533498</v>
       </c>
       <c r="R126" t="n">
-        <v>6962307</v>
+        <v>6962158</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13389,50 +13389,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128100396</v>
+        <v>128109254</v>
       </c>
       <c r="B127" t="n">
-        <v>57832</v>
+        <v>80160</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>103021</v>
+        <v>6461</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>533537</v>
+        <v>533652</v>
       </c>
       <c r="R127" t="n">
-        <v>6962358</v>
+        <v>6962140</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13491,10 +13486,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128109488</v>
+        <v>128110789</v>
       </c>
       <c r="B128" t="n">
-        <v>80161</v>
+        <v>98502</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13502,21 +13497,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>219874</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13526,10 +13521,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>533498</v>
+        <v>533832</v>
       </c>
       <c r="R128" t="n">
-        <v>6962158</v>
+        <v>6962310</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13588,10 +13583,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128109254</v>
+        <v>128108119</v>
       </c>
       <c r="B129" t="n">
-        <v>80160</v>
+        <v>98502</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13599,21 +13594,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6461</v>
+        <v>219874</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13623,10 +13618,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>533652</v>
+        <v>533800</v>
       </c>
       <c r="R129" t="n">
-        <v>6962140</v>
+        <v>6962306</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13685,45 +13680,50 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128110823</v>
+        <v>128100396</v>
       </c>
       <c r="B130" t="n">
-        <v>98467</v>
+        <v>57832</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>533715</v>
+        <v>533537</v>
       </c>
       <c r="R130" t="n">
-        <v>6962631</v>
+        <v>6962358</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13756,11 +13756,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13787,32 +13782,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128110789</v>
+        <v>128110823</v>
       </c>
       <c r="B131" t="n">
-        <v>98501</v>
+        <v>98468</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13822,10 +13817,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>533832</v>
+        <v>533715</v>
       </c>
       <c r="R131" t="n">
-        <v>6962310</v>
+        <v>6962631</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13858,6 +13853,11 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13887,7 +13887,7 @@
         <v>128110825</v>
       </c>
       <c r="B132" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13986,45 +13986,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128100350</v>
+        <v>128103617</v>
       </c>
       <c r="B133" t="n">
-        <v>97344</v>
+        <v>91350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>533545</v>
+        <v>533637</v>
       </c>
       <c r="R133" t="n">
-        <v>6962339</v>
+        <v>6962600</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14083,49 +14083,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128107880</v>
+        <v>128110830</v>
       </c>
       <c r="B134" t="n">
-        <v>98467</v>
+        <v>105506</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>533736</v>
+        <v>533659</v>
       </c>
       <c r="R134" t="n">
-        <v>6962362</v>
+        <v>6962296</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14184,10 +14180,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128110830</v>
+        <v>128100350</v>
       </c>
       <c r="B135" t="n">
-        <v>105505</v>
+        <v>97345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14195,21 +14191,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>221144</v>
+        <v>221945</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14219,10 +14215,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>533659</v>
+        <v>533545</v>
       </c>
       <c r="R135" t="n">
-        <v>6962296</v>
+        <v>6962339</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14284,7 +14280,7 @@
         <v>128110808</v>
       </c>
       <c r="B136" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14383,10 +14379,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128110809</v>
+        <v>128107880</v>
       </c>
       <c r="B137" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14411,17 +14407,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>533748</v>
+        <v>533736</v>
       </c>
       <c r="R137" t="n">
-        <v>6962494</v>
+        <v>6962362</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14454,11 +14454,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14485,10 +14480,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128110984</v>
+        <v>128110809</v>
       </c>
       <c r="B138" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14520,10 +14515,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>533734</v>
+        <v>533748</v>
       </c>
       <c r="R138" t="n">
-        <v>6962473</v>
+        <v>6962494</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14560,7 +14555,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14587,45 +14582,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103617</v>
+        <v>128110984</v>
       </c>
       <c r="B139" t="n">
-        <v>91349</v>
+        <v>98468</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>533637</v>
+        <v>533734</v>
       </c>
       <c r="R139" t="n">
-        <v>6962600</v>
+        <v>6962473</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14658,6 +14653,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14684,38 +14684,37 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128109413</v>
+        <v>128099760</v>
       </c>
       <c r="B140" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P140" t="inlineStr">
@@ -14724,10 +14723,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>533532</v>
+        <v>533451</v>
       </c>
       <c r="R140" t="n">
-        <v>6962150</v>
+        <v>6962307</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14760,11 +14759,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14791,10 +14785,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128109827</v>
+        <v>128102955</v>
       </c>
       <c r="B141" t="n">
-        <v>57672</v>
+        <v>78787</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14802,39 +14796,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>533421</v>
+        <v>533659</v>
       </c>
       <c r="R141" t="n">
-        <v>6962154</v>
+        <v>6962538</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14867,11 +14856,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14901,7 +14885,7 @@
         <v>128110801</v>
       </c>
       <c r="B142" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15003,7 +14987,7 @@
         <v>128110821</v>
       </c>
       <c r="B143" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15105,7 +15089,7 @@
         <v>128110988</v>
       </c>
       <c r="B144" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15204,37 +15188,38 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128099760</v>
+        <v>128102524</v>
       </c>
       <c r="B145" t="n">
-        <v>98467</v>
+        <v>56855</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
@@ -15243,10 +15228,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>533451</v>
+        <v>533640</v>
       </c>
       <c r="R145" t="n">
-        <v>6962307</v>
+        <v>6962482</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15305,10 +15290,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128102955</v>
+        <v>128108442</v>
       </c>
       <c r="B146" t="n">
-        <v>78787</v>
+        <v>57672</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15316,34 +15301,39 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>533659</v>
+        <v>533714</v>
       </c>
       <c r="R146" t="n">
-        <v>6962538</v>
+        <v>6962273</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15376,6 +15366,11 @@
       <c r="AA146" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15402,10 +15397,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128102524</v>
+        <v>128109413</v>
       </c>
       <c r="B147" t="n">
-        <v>56855</v>
+        <v>57672</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15413,16 +15408,16 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -15433,7 +15428,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P147" t="inlineStr">
@@ -15442,10 +15437,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>533640</v>
+        <v>533532</v>
       </c>
       <c r="R147" t="n">
-        <v>6962482</v>
+        <v>6962150</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15478,6 +15473,11 @@
       <c r="AA147" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15504,7 +15504,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128108442</v>
+        <v>128109827</v>
       </c>
       <c r="B148" t="n">
         <v>57672</v>
@@ -15540,14 +15540,14 @@
       </c>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>533714</v>
+        <v>533421</v>
       </c>
       <c r="R148" t="n">
-        <v>6962273</v>
+        <v>6962154</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15611,37 +15611,42 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128101444</v>
+        <v>128099113</v>
       </c>
       <c r="B149" t="n">
-        <v>98467</v>
+        <v>92640</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -15650,10 +15655,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>533424</v>
+        <v>533396</v>
       </c>
       <c r="R149" t="n">
-        <v>6962351</v>
+        <v>6962161</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15686,6 +15691,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15712,32 +15722,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128102121</v>
+        <v>128110831</v>
       </c>
       <c r="B150" t="n">
-        <v>57832</v>
+        <v>58531</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>103021</v>
+        <v>208249</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15747,10 +15757,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>533532</v>
+        <v>533728</v>
       </c>
       <c r="R150" t="n">
-        <v>6962477</v>
+        <v>6962422</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15809,45 +15819,49 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128102104</v>
+        <v>128101444</v>
       </c>
       <c r="B151" t="n">
-        <v>105505</v>
+        <v>98468</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>533615</v>
+        <v>533424</v>
       </c>
       <c r="R151" t="n">
-        <v>6962423</v>
+        <v>6962351</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15906,32 +15920,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128109763</v>
+        <v>128110986</v>
       </c>
       <c r="B152" t="n">
-        <v>80036</v>
+        <v>98468</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15941,10 +15955,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>533449</v>
+        <v>533957</v>
       </c>
       <c r="R152" t="n">
-        <v>6962147</v>
+        <v>6962694</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15977,6 +15991,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>37 ex</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16003,54 +16022,45 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128099113</v>
+        <v>128110796</v>
       </c>
       <c r="B153" t="n">
-        <v>92639</v>
+        <v>80132</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>533396</v>
+        <v>533655</v>
       </c>
       <c r="R153" t="n">
-        <v>6962161</v>
+        <v>6962173</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16083,11 +16093,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16114,32 +16119,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128110768</v>
+        <v>128109763</v>
       </c>
       <c r="B154" t="n">
-        <v>57672</v>
+        <v>80036</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16149,10 +16154,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>533754</v>
+        <v>533449</v>
       </c>
       <c r="R154" t="n">
-        <v>6962450</v>
+        <v>6962147</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16185,11 +16190,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16216,32 +16216,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128110986</v>
+        <v>128110768</v>
       </c>
       <c r="B155" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16251,10 +16251,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>533957</v>
+        <v>533754</v>
       </c>
       <c r="R155" t="n">
-        <v>6962694</v>
+        <v>6962450</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16291,7 +16291,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>37 ex</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16318,10 +16318,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128110796</v>
+        <v>128102121</v>
       </c>
       <c r="B156" t="n">
-        <v>80132</v>
+        <v>57832</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16329,21 +16329,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>533655</v>
+        <v>533532</v>
       </c>
       <c r="R156" t="n">
-        <v>6962173</v>
+        <v>6962477</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16415,10 +16415,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128110831</v>
+        <v>128102104</v>
       </c>
       <c r="B157" t="n">
-        <v>58531</v>
+        <v>105506</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16426,21 +16426,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>208249</v>
+        <v>221144</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16450,10 +16450,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>533728</v>
+        <v>533615</v>
       </c>
       <c r="R157" t="n">
-        <v>6962422</v>
+        <v>6962423</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16512,49 +16512,45 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128109586</v>
+        <v>128110791</v>
       </c>
       <c r="B158" t="n">
-        <v>98467</v>
+        <v>98502</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>533498</v>
+        <v>533658</v>
       </c>
       <c r="R158" t="n">
-        <v>6962158</v>
+        <v>6962570</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16616,7 +16612,7 @@
         <v>128110837</v>
       </c>
       <c r="B159" t="n">
-        <v>98384</v>
+        <v>98385</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16710,32 +16706,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128110795</v>
+        <v>128110777</v>
       </c>
       <c r="B160" t="n">
-        <v>80132</v>
+        <v>91122</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16745,10 +16741,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>533792</v>
+        <v>533841</v>
       </c>
       <c r="R160" t="n">
-        <v>6962400</v>
+        <v>6962306</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16807,32 +16803,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128110805</v>
+        <v>128110795</v>
       </c>
       <c r="B161" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16842,10 +16838,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>533668</v>
+        <v>533792</v>
       </c>
       <c r="R161" t="n">
-        <v>6962160</v>
+        <v>6962400</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16878,11 +16874,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>75 stycken</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17113,32 +17104,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128110777</v>
+        <v>128110774</v>
       </c>
       <c r="B164" t="n">
-        <v>91121</v>
+        <v>57672</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17148,10 +17139,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>533841</v>
+        <v>533585</v>
       </c>
       <c r="R164" t="n">
-        <v>6962306</v>
+        <v>6962612</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17184,6 +17175,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17210,32 +17206,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128110791</v>
+        <v>128110805</v>
       </c>
       <c r="B165" t="n">
-        <v>98501</v>
+        <v>98468</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17245,10 +17241,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>533658</v>
+        <v>533668</v>
       </c>
       <c r="R165" t="n">
-        <v>6962570</v>
+        <v>6962160</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17281,6 +17277,11 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>75 stycken</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17307,45 +17308,49 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128110774</v>
+        <v>128109586</v>
       </c>
       <c r="B166" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P166" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>533585</v>
+        <v>533498</v>
       </c>
       <c r="R166" t="n">
-        <v>6962612</v>
+        <v>6962158</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17378,11 +17383,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Färska ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17409,45 +17409,49 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128101262</v>
+        <v>128101672</v>
       </c>
       <c r="B167" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>533424</v>
+        <v>533534</v>
       </c>
       <c r="R167" t="n">
-        <v>6962357</v>
+        <v>6962408</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17506,10 +17510,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128101672</v>
+        <v>128109121</v>
       </c>
       <c r="B168" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -17536,7 +17540,7 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P168" t="inlineStr">
@@ -17545,10 +17549,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>533534</v>
+        <v>533651</v>
       </c>
       <c r="R168" t="n">
-        <v>6962408</v>
+        <v>6962130</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17607,54 +17611,45 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128102411</v>
+        <v>128110985</v>
       </c>
       <c r="B169" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M169" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>533575</v>
+        <v>533652</v>
       </c>
       <c r="R169" t="n">
-        <v>6962520</v>
+        <v>6962550</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17687,6 +17682,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17713,32 +17713,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128110781</v>
+        <v>128110813</v>
       </c>
       <c r="B170" t="n">
-        <v>91121</v>
+        <v>98468</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17748,10 +17748,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>533700</v>
+        <v>533507</v>
       </c>
       <c r="R170" t="n">
-        <v>6962581</v>
+        <v>6962168</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17784,6 +17784,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17810,10 +17815,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128110782</v>
+        <v>128110781</v>
       </c>
       <c r="B171" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17845,10 +17850,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>533630</v>
+        <v>533700</v>
       </c>
       <c r="R171" t="n">
-        <v>6962701</v>
+        <v>6962581</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17907,32 +17912,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128110985</v>
+        <v>128110782</v>
       </c>
       <c r="B172" t="n">
-        <v>98467</v>
+        <v>91122</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17942,10 +17947,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>533652</v>
+        <v>533630</v>
       </c>
       <c r="R172" t="n">
-        <v>6962550</v>
+        <v>6962701</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17978,11 +17983,6 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18009,7 +18009,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128110797</v>
+        <v>128101262</v>
       </c>
       <c r="B173" t="n">
         <v>80132</v>
@@ -18044,10 +18044,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>533832</v>
+        <v>533424</v>
       </c>
       <c r="R173" t="n">
-        <v>6962351</v>
+        <v>6962357</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18106,32 +18106,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128110813</v>
+        <v>128110797</v>
       </c>
       <c r="B174" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18141,10 +18141,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>533507</v>
+        <v>533832</v>
       </c>
       <c r="R174" t="n">
-        <v>6962168</v>
+        <v>6962351</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18177,11 +18177,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18208,37 +18203,42 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128109121</v>
+        <v>128102411</v>
       </c>
       <c r="B175" t="n">
-        <v>98467</v>
+        <v>57832</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P175" t="inlineStr">
@@ -18247,10 +18247,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>533651</v>
+        <v>533575</v>
       </c>
       <c r="R175" t="n">
-        <v>6962130</v>
+        <v>6962520</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18309,7 +18309,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128101939</v>
+        <v>128108439</v>
       </c>
       <c r="B176" t="n">
         <v>57672</v>
@@ -18345,14 +18345,14 @@
       </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>533638</v>
+        <v>533711</v>
       </c>
       <c r="R176" t="n">
-        <v>6962346</v>
+        <v>6962283</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18416,10 +18416,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128101075</v>
+        <v>128101939</v>
       </c>
       <c r="B177" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18427,34 +18427,39 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>533392</v>
+        <v>533638</v>
       </c>
       <c r="R177" t="n">
-        <v>6962343</v>
+        <v>6962346</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18487,6 +18492,11 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18513,50 +18523,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128100413</v>
+        <v>128110835</v>
       </c>
       <c r="B178" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>533545</v>
+        <v>533748</v>
       </c>
       <c r="R178" t="n">
-        <v>6962372</v>
+        <v>6962431</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18589,11 +18594,6 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18620,49 +18620,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128107826</v>
+        <v>128110799</v>
       </c>
       <c r="B179" t="n">
-        <v>98467</v>
+        <v>80132</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>533723</v>
+        <v>533724</v>
       </c>
       <c r="R179" t="n">
-        <v>6962360</v>
+        <v>6962625</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18721,32 +18717,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128110828</v>
+        <v>128110787</v>
       </c>
       <c r="B180" t="n">
-        <v>98467</v>
+        <v>80160</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18756,10 +18752,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>533365</v>
+        <v>533785</v>
       </c>
       <c r="R180" t="n">
-        <v>6962304</v>
+        <v>6962326</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18792,11 +18788,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18823,7 +18814,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128110799</v>
+        <v>128101075</v>
       </c>
       <c r="B181" t="n">
         <v>80132</v>
@@ -18858,10 +18849,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>533724</v>
+        <v>533392</v>
       </c>
       <c r="R181" t="n">
-        <v>6962625</v>
+        <v>6962343</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18920,45 +18911,50 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128110817</v>
+        <v>128100413</v>
       </c>
       <c r="B182" t="n">
-        <v>98467</v>
+        <v>57672</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>533728</v>
+        <v>533545</v>
       </c>
       <c r="R182" t="n">
-        <v>6962346</v>
+        <v>6962372</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18995,7 +18991,7 @@
       </c>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>40 stycken i blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19022,10 +19018,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128110835</v>
+        <v>128110977</v>
       </c>
       <c r="B183" t="n">
-        <v>98384</v>
+        <v>98502</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19033,21 +19029,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19057,10 +19053,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>533748</v>
+        <v>534040</v>
       </c>
       <c r="R183" t="n">
-        <v>6962431</v>
+        <v>6962718</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19119,32 +19115,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128110787</v>
+        <v>128110828</v>
       </c>
       <c r="B184" t="n">
-        <v>80160</v>
+        <v>98468</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19154,10 +19150,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>533785</v>
+        <v>533365</v>
       </c>
       <c r="R184" t="n">
-        <v>6962326</v>
+        <v>6962304</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19190,6 +19186,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19216,45 +19217,49 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128110977</v>
+        <v>128107826</v>
       </c>
       <c r="B185" t="n">
-        <v>98501</v>
+        <v>98468</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>534040</v>
+        <v>533723</v>
       </c>
       <c r="R185" t="n">
-        <v>6962718</v>
+        <v>6962360</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19313,50 +19318,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128108439</v>
+        <v>128110817</v>
       </c>
       <c r="B186" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>533711</v>
+        <v>533728</v>
       </c>
       <c r="R186" t="n">
-        <v>6962283</v>
+        <v>6962346</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD186" t="b">

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -1311,45 +1311,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128108655</v>
+        <v>128110802</v>
       </c>
       <c r="B8" t="n">
-        <v>92640</v>
+        <v>98468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533673</v>
+        <v>533461</v>
       </c>
       <c r="R8" t="n">
-        <v>6962211</v>
+        <v>6962171</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,6 +1382,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,50 +1413,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128108619</v>
+        <v>128100827</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533675</v>
+        <v>533406</v>
       </c>
       <c r="R9" t="n">
-        <v>6962244</v>
+        <v>6962317</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,11 +1488,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128110972</v>
+        <v>128109460</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1526,21 +1525,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1550,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533997</v>
+        <v>533498</v>
       </c>
       <c r="R10" t="n">
-        <v>6962746</v>
+        <v>6962158</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,11 +1585,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,50 +1611,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128101860</v>
+        <v>128108655</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>92640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533601</v>
+        <v>533673</v>
       </c>
       <c r="R11" t="n">
-        <v>6962344</v>
+        <v>6962211</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,11 +1682,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128109460</v>
+        <v>128108619</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1735,34 +1719,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533498</v>
+        <v>533675</v>
       </c>
       <c r="R12" t="n">
-        <v>6962158</v>
+        <v>6962244</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,6 +1784,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1821,32 +1815,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128110802</v>
+        <v>128110972</v>
       </c>
       <c r="B13" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1856,10 +1850,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533461</v>
+        <v>533997</v>
       </c>
       <c r="R13" t="n">
-        <v>6962171</v>
+        <v>6962746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,7 +1890,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1923,37 +1917,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128100827</v>
+        <v>128101860</v>
       </c>
       <c r="B14" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>13</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1962,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533406</v>
+        <v>533601</v>
       </c>
       <c r="R14" t="n">
-        <v>6962317</v>
+        <v>6962344</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,6 +1993,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2024,50 +2024,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128108700</v>
+        <v>128101567</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>80036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533674</v>
+        <v>533494</v>
       </c>
       <c r="R15" t="n">
-        <v>6962199</v>
+        <v>6962425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2100,11 +2095,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,50 +2121,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128109367</v>
+        <v>128110833</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533550</v>
+        <v>533768</v>
       </c>
       <c r="R16" t="n">
-        <v>6962157</v>
+        <v>6962318</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2207,11 +2192,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2238,7 +2218,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128110818</v>
+        <v>128100131</v>
       </c>
       <c r="B17" t="n">
         <v>98468</v>
@@ -2266,17 +2246,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533766</v>
+        <v>533496</v>
       </c>
       <c r="R17" t="n">
-        <v>6962317</v>
+        <v>6962335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,11 +2293,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>10stycken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2340,45 +2319,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128101567</v>
+        <v>128108700</v>
       </c>
       <c r="B18" t="n">
-        <v>80036</v>
+        <v>57672</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533494</v>
+        <v>533674</v>
       </c>
       <c r="R18" t="n">
-        <v>6962425</v>
+        <v>6962199</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2411,6 +2395,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2437,45 +2426,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128110833</v>
+        <v>128109367</v>
       </c>
       <c r="B19" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533768</v>
+        <v>533550</v>
       </c>
       <c r="R19" t="n">
-        <v>6962318</v>
+        <v>6962157</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2508,6 +2502,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2635,7 +2634,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128100131</v>
+        <v>128110818</v>
       </c>
       <c r="B21" t="n">
         <v>98468</v>
@@ -2663,21 +2662,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533496</v>
+        <v>533766</v>
       </c>
       <c r="R21" t="n">
-        <v>6962335</v>
+        <v>6962317</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,6 +2705,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>10stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2736,45 +2736,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128110771</v>
+        <v>128108592</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>80036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533583</v>
+        <v>533675</v>
       </c>
       <c r="R22" t="n">
-        <v>6962697</v>
+        <v>6962244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,11 +2807,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2838,7 +2833,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128109293</v>
+        <v>128110771</v>
       </c>
       <c r="B23" t="n">
         <v>57672</v>
@@ -2867,21 +2862,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533638</v>
+        <v>533583</v>
       </c>
       <c r="R23" t="n">
-        <v>6962157</v>
+        <v>6962697</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,7 +2908,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2945,49 +2935,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128101601</v>
+        <v>128109293</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533496</v>
+        <v>533638</v>
       </c>
       <c r="R24" t="n">
-        <v>6962407</v>
+        <v>6962157</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,6 +3011,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3046,49 +3042,50 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128108218</v>
+        <v>128099395</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533789</v>
+        <v>533356</v>
       </c>
       <c r="R25" t="n">
-        <v>6962263</v>
+        <v>6962190</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3121,6 +3118,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3147,50 +3149,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128099395</v>
+        <v>128110832</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533356</v>
+        <v>533652</v>
       </c>
       <c r="R26" t="n">
-        <v>6962190</v>
+        <v>6962264</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3223,11 +3220,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3254,45 +3246,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128108592</v>
+        <v>128101601</v>
       </c>
       <c r="B27" t="n">
-        <v>80036</v>
+        <v>98468</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533675</v>
+        <v>533496</v>
       </c>
       <c r="R27" t="n">
-        <v>6962244</v>
+        <v>6962407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,45 +3347,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128110832</v>
+        <v>128108218</v>
       </c>
       <c r="B28" t="n">
-        <v>98385</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533652</v>
+        <v>533789</v>
       </c>
       <c r="R28" t="n">
-        <v>6962264</v>
+        <v>6962263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,50 +3448,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128099402</v>
+        <v>128110780</v>
       </c>
       <c r="B29" t="n">
-        <v>57672</v>
+        <v>91122</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533474</v>
+        <v>533670</v>
       </c>
       <c r="R29" t="n">
-        <v>6962267</v>
+        <v>6962552</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3524,11 +3519,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3555,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128110780</v>
+        <v>128099830</v>
       </c>
       <c r="B30" t="n">
-        <v>91122</v>
+        <v>92640</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3566,34 +3556,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533670</v>
+        <v>533353</v>
       </c>
       <c r="R30" t="n">
-        <v>6962552</v>
+        <v>6962231</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3626,6 +3625,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3652,45 +3656,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128110981</v>
+        <v>128099402</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533689</v>
+        <v>533474</v>
       </c>
       <c r="R31" t="n">
-        <v>6962405</v>
+        <v>6962267</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3727,7 +3736,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3754,7 +3763,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128109875</v>
+        <v>128110803</v>
       </c>
       <c r="B32" t="n">
         <v>98468</v>
@@ -3782,21 +3791,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533436</v>
+        <v>533524</v>
       </c>
       <c r="R32" t="n">
-        <v>6962158</v>
+        <v>6962153</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3829,6 +3834,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3855,7 +3865,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128102143</v>
+        <v>128110981</v>
       </c>
       <c r="B33" t="n">
         <v>98468</v>
@@ -3883,21 +3893,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533615</v>
+        <v>533689</v>
       </c>
       <c r="R33" t="n">
-        <v>6962423</v>
+        <v>6962405</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3930,6 +3936,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3956,7 +3967,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128100230</v>
+        <v>128109875</v>
       </c>
       <c r="B34" t="n">
         <v>98468</v>
@@ -3986,7 +3997,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3995,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533506</v>
+        <v>533436</v>
       </c>
       <c r="R34" t="n">
-        <v>6962358</v>
+        <v>6962158</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4057,42 +4068,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128099830</v>
+        <v>128102143</v>
       </c>
       <c r="B35" t="n">
-        <v>92640</v>
+        <v>98468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4101,10 +4107,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533353</v>
+        <v>533615</v>
       </c>
       <c r="R35" t="n">
-        <v>6962231</v>
+        <v>6962423</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4137,11 +4143,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4270,7 +4271,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128110803</v>
+        <v>128100230</v>
       </c>
       <c r="B37" t="n">
         <v>98468</v>
@@ -4298,17 +4299,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533524</v>
+        <v>533506</v>
       </c>
       <c r="R37" t="n">
-        <v>6962153</v>
+        <v>6962358</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4341,11 +4346,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4372,45 +4372,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128110968</v>
+        <v>128108150</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533634</v>
+        <v>533800</v>
       </c>
       <c r="R38" t="n">
-        <v>6962526</v>
+        <v>6962306</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4443,11 +4443,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4474,50 +4469,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128102724</v>
+        <v>128110978</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>98502</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533659</v>
+        <v>533708</v>
       </c>
       <c r="R39" t="n">
-        <v>6962512</v>
+        <v>6962645</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4550,11 +4540,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4581,50 +4566,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128101831</v>
+        <v>128110836</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533513</v>
+        <v>533722</v>
       </c>
       <c r="R40" t="n">
-        <v>6962442</v>
+        <v>6962426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4657,11 +4637,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4688,32 +4663,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128110767</v>
+        <v>128110788</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>98502</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4723,10 +4698,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533794</v>
+        <v>533590</v>
       </c>
       <c r="R41" t="n">
-        <v>6962411</v>
+        <v>6962592</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4759,11 +4734,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4790,32 +4760,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128110788</v>
+        <v>128110968</v>
       </c>
       <c r="B42" t="n">
-        <v>98502</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4825,10 +4795,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533590</v>
+        <v>533634</v>
       </c>
       <c r="R42" t="n">
-        <v>6962592</v>
+        <v>6962526</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4861,6 +4831,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4887,32 +4862,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128110824</v>
+        <v>128110767</v>
       </c>
       <c r="B43" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533712</v>
+        <v>533794</v>
       </c>
       <c r="R43" t="n">
-        <v>6962628</v>
+        <v>6962411</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4962,7 +4937,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>20 stycken</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4989,45 +4964,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128108150</v>
+        <v>128110824</v>
       </c>
       <c r="B44" t="n">
-        <v>80161</v>
+        <v>98468</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533800</v>
+        <v>533712</v>
       </c>
       <c r="R44" t="n">
-        <v>6962306</v>
+        <v>6962628</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5060,6 +5035,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5086,45 +5066,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128110978</v>
+        <v>128102724</v>
       </c>
       <c r="B45" t="n">
-        <v>98502</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533708</v>
+        <v>533659</v>
       </c>
       <c r="R45" t="n">
-        <v>6962645</v>
+        <v>6962512</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5157,6 +5142,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5183,45 +5173,50 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128110836</v>
+        <v>128101831</v>
       </c>
       <c r="B46" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533722</v>
+        <v>533513</v>
       </c>
       <c r="R46" t="n">
-        <v>6962426</v>
+        <v>6962442</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5254,6 +5249,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5377,10 +5377,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128101702</v>
+        <v>128110970</v>
       </c>
       <c r="B48" t="n">
-        <v>91350</v>
+        <v>57672</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5388,21 +5388,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533529</v>
+        <v>534050</v>
       </c>
       <c r="R48" t="n">
-        <v>6962400</v>
+        <v>6962743</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5448,6 +5448,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5474,10 +5479,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128107546</v>
+        <v>128110766</v>
       </c>
       <c r="B49" t="n">
-        <v>80133</v>
+        <v>57672</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5485,34 +5490,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533648</v>
+        <v>533586</v>
       </c>
       <c r="R49" t="n">
-        <v>6962374</v>
+        <v>6962139</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5545,6 +5550,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5571,45 +5581,54 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128110766</v>
+        <v>128103304</v>
       </c>
       <c r="B50" t="n">
-        <v>57672</v>
+        <v>91122</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533586</v>
+        <v>533594</v>
       </c>
       <c r="R50" t="n">
-        <v>6962139</v>
+        <v>6962541</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5642,11 +5661,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5673,10 +5687,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128110970</v>
+        <v>128101702</v>
       </c>
       <c r="B51" t="n">
-        <v>57672</v>
+        <v>91350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5684,21 +5698,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5708,10 +5722,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>534050</v>
+        <v>533529</v>
       </c>
       <c r="R51" t="n">
-        <v>6962743</v>
+        <v>6962400</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5744,11 +5758,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5775,45 +5784,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128101106</v>
+        <v>128107546</v>
       </c>
       <c r="B52" t="n">
-        <v>80098</v>
+        <v>80133</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229748</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533425</v>
+        <v>533648</v>
       </c>
       <c r="R52" t="n">
-        <v>6962304</v>
+        <v>6962374</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5872,45 +5881,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128108922</v>
+        <v>128110812</v>
       </c>
       <c r="B53" t="n">
-        <v>105506</v>
+        <v>98468</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533671</v>
+        <v>533715</v>
       </c>
       <c r="R53" t="n">
-        <v>6962142</v>
+        <v>6962610</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5943,6 +5952,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5969,7 +5983,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128110812</v>
+        <v>128110826</v>
       </c>
       <c r="B54" t="n">
         <v>98468</v>
@@ -6004,10 +6018,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533715</v>
+        <v>533579</v>
       </c>
       <c r="R54" t="n">
-        <v>6962610</v>
+        <v>6962663</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6044,7 +6058,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>60 stycken</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6071,45 +6085,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128110826</v>
+        <v>128108922</v>
       </c>
       <c r="B55" t="n">
-        <v>98468</v>
+        <v>105506</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533579</v>
+        <v>533671</v>
       </c>
       <c r="R55" t="n">
-        <v>6962663</v>
+        <v>6962142</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6142,11 +6156,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6173,7 +6182,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128110804</v>
+        <v>128110814</v>
       </c>
       <c r="B56" t="n">
         <v>98468</v>
@@ -6208,10 +6217,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533532</v>
+        <v>533650</v>
       </c>
       <c r="R56" t="n">
-        <v>6962156</v>
+        <v>6962134</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6248,7 +6257,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
+          <t>50 stycken ( några har blommat).</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6275,7 +6284,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128110990</v>
+        <v>128110804</v>
       </c>
       <c r="B57" t="n">
         <v>98468</v>
@@ -6310,10 +6319,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533873</v>
+        <v>533532</v>
       </c>
       <c r="R57" t="n">
-        <v>6962782</v>
+        <v>6962156</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6350,7 +6359,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6377,7 +6386,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128110814</v>
+        <v>128110990</v>
       </c>
       <c r="B58" t="n">
         <v>98468</v>
@@ -6412,10 +6421,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533650</v>
+        <v>533873</v>
       </c>
       <c r="R58" t="n">
-        <v>6962134</v>
+        <v>6962782</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6452,7 +6461,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>50 stycken ( några har blommat).</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6479,39 +6488,35 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128099088</v>
+        <v>128101106</v>
       </c>
       <c r="B59" t="n">
-        <v>98468</v>
+        <v>80098</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>229748</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
@@ -6521,7 +6526,7 @@
         <v>533425</v>
       </c>
       <c r="R59" t="n">
-        <v>6962182</v>
+        <v>6962304</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6580,42 +6585,37 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128103304</v>
+        <v>128099088</v>
       </c>
       <c r="B60" t="n">
-        <v>91122</v>
+        <v>98468</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6624,10 +6624,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533594</v>
+        <v>533425</v>
       </c>
       <c r="R60" t="n">
-        <v>6962541</v>
+        <v>6962182</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128110971</v>
+        <v>128100636</v>
       </c>
       <c r="B61" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6697,21 +6697,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6721,10 +6721,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>534036</v>
+        <v>533452</v>
       </c>
       <c r="R61" t="n">
-        <v>6962734</v>
+        <v>6962350</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6757,11 +6757,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6788,10 +6783,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128108477</v>
+        <v>128099984</v>
       </c>
       <c r="B62" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6799,39 +6794,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533710</v>
+        <v>533455</v>
       </c>
       <c r="R62" t="n">
-        <v>6962294</v>
+        <v>6962339</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6864,11 +6854,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6895,32 +6880,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128110827</v>
+        <v>128099875</v>
       </c>
       <c r="B63" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6930,10 +6915,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533614</v>
+        <v>533445</v>
       </c>
       <c r="R63" t="n">
-        <v>6962554</v>
+        <v>6962324</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6966,11 +6951,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6997,49 +6977,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128103587</v>
+        <v>128110971</v>
       </c>
       <c r="B64" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533650</v>
+        <v>534036</v>
       </c>
       <c r="R64" t="n">
-        <v>6962600</v>
+        <v>6962734</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7072,6 +7048,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7098,49 +7079,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128100184</v>
+        <v>128108477</v>
       </c>
       <c r="B65" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533509</v>
+        <v>533710</v>
       </c>
       <c r="R65" t="n">
-        <v>6962336</v>
+        <v>6962294</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7173,6 +7155,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7199,10 +7186,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128099984</v>
+        <v>128099885</v>
       </c>
       <c r="B66" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7210,34 +7197,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533455</v>
+        <v>533361</v>
       </c>
       <c r="R66" t="n">
-        <v>6962339</v>
+        <v>6962247</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7270,6 +7262,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7296,45 +7293,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128099875</v>
+        <v>128100184</v>
       </c>
       <c r="B67" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533445</v>
+        <v>533509</v>
       </c>
       <c r="R67" t="n">
-        <v>6962324</v>
+        <v>6962336</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7393,45 +7394,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128099099</v>
+        <v>128103587</v>
       </c>
       <c r="B68" t="n">
-        <v>105506</v>
+        <v>98468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533416</v>
+        <v>533650</v>
       </c>
       <c r="R68" t="n">
-        <v>6962179</v>
+        <v>6962600</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7490,7 +7495,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128099522</v>
+        <v>128110827</v>
       </c>
       <c r="B69" t="n">
         <v>98468</v>
@@ -7518,26 +7523,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533349</v>
+        <v>533614</v>
       </c>
       <c r="R69" t="n">
-        <v>6962197</v>
+        <v>6962554</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7570,6 +7566,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7596,38 +7597,42 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128099885</v>
+        <v>128099522</v>
       </c>
       <c r="B70" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -7636,10 +7641,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533361</v>
+        <v>533349</v>
       </c>
       <c r="R70" t="n">
-        <v>6962247</v>
+        <v>6962197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7672,11 +7677,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7703,32 +7703,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128100636</v>
+        <v>128099099</v>
       </c>
       <c r="B71" t="n">
-        <v>80132</v>
+        <v>105506</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533452</v>
+        <v>533416</v>
       </c>
       <c r="R71" t="n">
-        <v>6962350</v>
+        <v>6962179</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7800,45 +7800,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128099857</v>
+        <v>128108355</v>
       </c>
       <c r="B72" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533445</v>
+        <v>533768</v>
       </c>
       <c r="R72" t="n">
-        <v>6962324</v>
+        <v>6962269</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7871,6 +7876,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7897,50 +7907,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128099712</v>
+        <v>128099857</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533451</v>
+        <v>533445</v>
       </c>
       <c r="R73" t="n">
-        <v>6962307</v>
+        <v>6962324</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7973,11 +7978,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8004,7 +8004,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128110769</v>
+        <v>128110775</v>
       </c>
       <c r="B74" t="n">
         <v>57672</v>
@@ -8039,10 +8039,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533841</v>
+        <v>533564</v>
       </c>
       <c r="R74" t="n">
-        <v>6962363</v>
+        <v>6962537</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack) spår</t>
+          <t>Färska och äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8106,7 +8106,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128110775</v>
+        <v>128101911</v>
       </c>
       <c r="B75" t="n">
         <v>57672</v>
@@ -8135,16 +8135,21 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533564</v>
+        <v>533510</v>
       </c>
       <c r="R75" t="n">
-        <v>6962537</v>
+        <v>6962462</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8181,7 +8186,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på Tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8208,7 +8213,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128108355</v>
+        <v>128110769</v>
       </c>
       <c r="B76" t="n">
         <v>57672</v>
@@ -8237,21 +8242,16 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533768</v>
+        <v>533841</v>
       </c>
       <c r="R76" t="n">
-        <v>6962269</v>
+        <v>6962363</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack) spår</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8315,7 +8315,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128101911</v>
+        <v>128099712</v>
       </c>
       <c r="B77" t="n">
         <v>57672</v>
@@ -8346,7 +8346,7 @@
       <c r="I77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8355,10 +8355,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533510</v>
+        <v>533451</v>
       </c>
       <c r="R77" t="n">
-        <v>6962462</v>
+        <v>6962307</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8395,7 +8395,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8819,7 +8819,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128101827</v>
+        <v>128110969</v>
       </c>
       <c r="B82" t="n">
         <v>57672</v>
@@ -8848,21 +8848,16 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533594</v>
+        <v>533825</v>
       </c>
       <c r="R82" t="n">
-        <v>6962354</v>
+        <v>6962690</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8899,7 +8894,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8926,7 +8921,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128100974</v>
+        <v>128101827</v>
       </c>
       <c r="B83" t="n">
         <v>57672</v>
@@ -8966,10 +8961,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533375</v>
+        <v>533594</v>
       </c>
       <c r="R83" t="n">
-        <v>6962293</v>
+        <v>6962354</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9006,7 +9001,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9033,7 +9028,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128110969</v>
+        <v>128100974</v>
       </c>
       <c r="B84" t="n">
         <v>57672</v>
@@ -9062,16 +9057,21 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533825</v>
+        <v>533375</v>
       </c>
       <c r="R84" t="n">
-        <v>6962690</v>
+        <v>6962293</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9108,7 +9108,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9135,38 +9135,37 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128099905</v>
+        <v>128101261</v>
       </c>
       <c r="B85" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9175,10 +9174,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533445</v>
+        <v>533424</v>
       </c>
       <c r="R85" t="n">
-        <v>6962324</v>
+        <v>6962357</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9211,11 +9210,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9242,49 +9236,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128101261</v>
+        <v>128110976</v>
       </c>
       <c r="B86" t="n">
-        <v>98468</v>
+        <v>98502</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533424</v>
+        <v>533868</v>
       </c>
       <c r="R86" t="n">
-        <v>6962357</v>
+        <v>6962692</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9317,6 +9307,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9343,45 +9338,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128110982</v>
+        <v>128099905</v>
       </c>
       <c r="B87" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533681</v>
+        <v>533445</v>
       </c>
       <c r="R87" t="n">
-        <v>6962434</v>
+        <v>6962324</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9418,7 +9418,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>23 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9445,32 +9445,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128110976</v>
+        <v>128110810</v>
       </c>
       <c r="B88" t="n">
-        <v>98502</v>
+        <v>98468</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533868</v>
+        <v>533645</v>
       </c>
       <c r="R88" t="n">
-        <v>6962692</v>
+        <v>6962593</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9516,11 +9516,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9547,7 +9542,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128110810</v>
+        <v>128110982</v>
       </c>
       <c r="B89" t="n">
         <v>98468</v>
@@ -9582,10 +9577,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533645</v>
+        <v>533681</v>
       </c>
       <c r="R89" t="n">
-        <v>6962593</v>
+        <v>6962434</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9618,6 +9613,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>23 ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9644,32 +9644,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>128110973</v>
+        <v>128100745</v>
       </c>
       <c r="B90" t="n">
-        <v>57672</v>
+        <v>80036</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9679,10 +9679,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>533841</v>
+        <v>533422</v>
       </c>
       <c r="R90" t="n">
-        <v>6962731</v>
+        <v>6962322</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9715,11 +9715,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9746,32 +9741,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>128110989</v>
+        <v>128110973</v>
       </c>
       <c r="B91" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9781,10 +9776,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>533912</v>
+        <v>533841</v>
       </c>
       <c r="R91" t="n">
-        <v>6962770</v>
+        <v>6962731</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9821,7 +9816,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9950,32 +9945,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128100745</v>
+        <v>128110989</v>
       </c>
       <c r="B93" t="n">
-        <v>80036</v>
+        <v>98468</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9985,10 +9980,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>533422</v>
+        <v>533912</v>
       </c>
       <c r="R93" t="n">
-        <v>6962322</v>
+        <v>6962770</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10021,6 +10016,11 @@
       <c r="AA93" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10153,32 +10153,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128110816</v>
+        <v>128110974</v>
       </c>
       <c r="B95" t="n">
-        <v>98468</v>
+        <v>80161</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10188,10 +10188,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533696</v>
+        <v>533937</v>
       </c>
       <c r="R95" t="n">
-        <v>6962294</v>
+        <v>6962685</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10224,11 +10224,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10255,7 +10250,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128102067</v>
+        <v>128110816</v>
       </c>
       <c r="B96" t="n">
         <v>98468</v>
@@ -10283,21 +10278,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533510</v>
+        <v>533696</v>
       </c>
       <c r="R96" t="n">
-        <v>6962462</v>
+        <v>6962294</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10330,6 +10321,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10356,38 +10352,37 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128099555</v>
+        <v>128102067</v>
       </c>
       <c r="B97" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10396,10 +10391,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533471</v>
+        <v>533510</v>
       </c>
       <c r="R97" t="n">
-        <v>6962293</v>
+        <v>6962462</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10432,11 +10427,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10463,45 +10453,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128110974</v>
+        <v>128099555</v>
       </c>
       <c r="B98" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>533937</v>
+        <v>533471</v>
       </c>
       <c r="R98" t="n">
-        <v>6962685</v>
+        <v>6962293</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10534,6 +10529,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10560,50 +10560,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128102878</v>
+        <v>128110834</v>
       </c>
       <c r="B99" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>533665</v>
+        <v>533779</v>
       </c>
       <c r="R99" t="n">
-        <v>6962515</v>
+        <v>6962298</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10636,11 +10631,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10667,7 +10657,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128100043</v>
+        <v>128102878</v>
       </c>
       <c r="B100" t="n">
         <v>57672</v>
@@ -10703,14 +10693,14 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>533496</v>
+        <v>533665</v>
       </c>
       <c r="R100" t="n">
-        <v>6962335</v>
+        <v>6962515</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10774,45 +10764,50 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128110834</v>
+        <v>128100043</v>
       </c>
       <c r="B101" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533779</v>
+        <v>533496</v>
       </c>
       <c r="R101" t="n">
-        <v>6962298</v>
+        <v>6962335</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10845,6 +10840,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10871,32 +10871,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128101073</v>
+        <v>128110807</v>
       </c>
       <c r="B102" t="n">
-        <v>80168</v>
+        <v>98468</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10906,10 +10906,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>533385</v>
+        <v>533664</v>
       </c>
       <c r="R102" t="n">
-        <v>6962288</v>
+        <v>6962286</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10942,6 +10942,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10968,32 +10973,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128110829</v>
+        <v>128101073</v>
       </c>
       <c r="B103" t="n">
-        <v>56855</v>
+        <v>80168</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11003,10 +11008,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>533606</v>
+        <v>533385</v>
       </c>
       <c r="R103" t="n">
-        <v>6962582</v>
+        <v>6962288</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11039,11 +11044,6 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11070,32 +11070,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128110785</v>
+        <v>128110829</v>
       </c>
       <c r="B104" t="n">
-        <v>97345</v>
+        <v>56855</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11105,10 +11105,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>533824</v>
+        <v>533606</v>
       </c>
       <c r="R104" t="n">
-        <v>6962352</v>
+        <v>6962582</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11141,6 +11141,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11269,7 +11274,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128110807</v>
+        <v>128110983</v>
       </c>
       <c r="B106" t="n">
         <v>98468</v>
@@ -11304,10 +11309,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>533664</v>
+        <v>533665</v>
       </c>
       <c r="R106" t="n">
-        <v>6962286</v>
+        <v>6962459</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11344,7 +11349,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>23 stycken</t>
+          <t>26 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11371,32 +11376,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128110983</v>
+        <v>128110785</v>
       </c>
       <c r="B107" t="n">
-        <v>98468</v>
+        <v>97345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11406,10 +11411,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533665</v>
+        <v>533824</v>
       </c>
       <c r="R107" t="n">
-        <v>6962459</v>
+        <v>6962352</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11442,11 +11447,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>26 ex</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11473,45 +11473,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128103993</v>
+        <v>128108378</v>
       </c>
       <c r="B108" t="n">
-        <v>105506</v>
+        <v>57672</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533664</v>
+        <v>533750</v>
       </c>
       <c r="R108" t="n">
-        <v>6962650</v>
+        <v>6962259</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11544,6 +11549,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11570,45 +11580,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128108028</v>
+        <v>128110819</v>
       </c>
       <c r="B109" t="n">
-        <v>97351</v>
+        <v>98468</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533802</v>
+        <v>533834</v>
       </c>
       <c r="R109" t="n">
-        <v>6962332</v>
+        <v>6962298</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11641,6 +11651,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11667,49 +11682,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128099487</v>
+        <v>128110794</v>
       </c>
       <c r="B110" t="n">
-        <v>98468</v>
+        <v>98502</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533474</v>
+        <v>533608</v>
       </c>
       <c r="R110" t="n">
-        <v>6962267</v>
+        <v>6962612</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11742,6 +11753,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11972,10 +11988,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128110783</v>
+        <v>128108028</v>
       </c>
       <c r="B113" t="n">
-        <v>91122</v>
+        <v>97351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11983,34 +11999,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>3215</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533599</v>
+        <v>533802</v>
       </c>
       <c r="R113" t="n">
-        <v>6962553</v>
+        <v>6962332</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12069,45 +12085,49 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128101331</v>
+        <v>128099487</v>
       </c>
       <c r="B114" t="n">
-        <v>80167</v>
+        <v>98468</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533424</v>
+        <v>533474</v>
       </c>
       <c r="R114" t="n">
-        <v>6962357</v>
+        <v>6962267</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12166,45 +12186,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128108395</v>
+        <v>128110783</v>
       </c>
       <c r="B115" t="n">
-        <v>80132</v>
+        <v>91122</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533735</v>
+        <v>533599</v>
       </c>
       <c r="R115" t="n">
-        <v>6962274</v>
+        <v>6962553</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12263,50 +12283,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128108378</v>
+        <v>128101331</v>
       </c>
       <c r="B116" t="n">
-        <v>57672</v>
+        <v>80167</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533750</v>
+        <v>533424</v>
       </c>
       <c r="R116" t="n">
-        <v>6962259</v>
+        <v>6962357</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12339,11 +12354,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12370,10 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128100457</v>
+        <v>128108395</v>
       </c>
       <c r="B117" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12381,39 +12391,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533556</v>
+        <v>533735</v>
       </c>
       <c r="R117" t="n">
-        <v>6962363</v>
+        <v>6962274</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12446,11 +12451,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12579,32 +12579,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128110794</v>
+        <v>128110991</v>
       </c>
       <c r="B119" t="n">
-        <v>98502</v>
+        <v>98468</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12614,10 +12614,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533608</v>
+        <v>533717</v>
       </c>
       <c r="R119" t="n">
-        <v>6962612</v>
+        <v>6962645</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12654,7 +12654,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12681,7 +12681,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128110991</v>
+        <v>128110987</v>
       </c>
       <c r="B120" t="n">
         <v>98468</v>
@@ -12716,10 +12716,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533717</v>
+        <v>533999</v>
       </c>
       <c r="R120" t="n">
-        <v>6962645</v>
+        <v>6962664</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12783,45 +12783,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128110987</v>
+        <v>128100457</v>
       </c>
       <c r="B121" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533999</v>
+        <v>533556</v>
       </c>
       <c r="R121" t="n">
-        <v>6962664</v>
+        <v>6962363</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12858,7 +12863,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12885,49 +12890,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103044</v>
+        <v>128103993</v>
       </c>
       <c r="B122" t="n">
-        <v>98468</v>
+        <v>105506</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533627</v>
+        <v>533664</v>
       </c>
       <c r="R122" t="n">
-        <v>6962544</v>
+        <v>6962650</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12986,7 +12987,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128110819</v>
+        <v>128103044</v>
       </c>
       <c r="B123" t="n">
         <v>98468</v>
@@ -13014,17 +13015,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr"/>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>533834</v>
+        <v>533627</v>
       </c>
       <c r="R123" t="n">
-        <v>6962298</v>
+        <v>6962544</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13057,11 +13062,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13195,45 +13195,50 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128099811</v>
+        <v>128100396</v>
       </c>
       <c r="B125" t="n">
-        <v>105506</v>
+        <v>57832</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>533451</v>
+        <v>533537</v>
       </c>
       <c r="R125" t="n">
-        <v>6962307</v>
+        <v>6962358</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13292,32 +13297,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128109488</v>
+        <v>128110825</v>
       </c>
       <c r="B126" t="n">
-        <v>80161</v>
+        <v>98468</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13327,10 +13332,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>533498</v>
+        <v>533583</v>
       </c>
       <c r="R126" t="n">
-        <v>6962158</v>
+        <v>6962689</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13363,6 +13368,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>84stycken</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13389,10 +13399,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128109254</v>
+        <v>128099811</v>
       </c>
       <c r="B127" t="n">
-        <v>80160</v>
+        <v>105506</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13400,34 +13410,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6461</v>
+        <v>221144</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>533652</v>
+        <v>533451</v>
       </c>
       <c r="R127" t="n">
-        <v>6962140</v>
+        <v>6962307</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13486,10 +13496,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128110789</v>
+        <v>128109488</v>
       </c>
       <c r="B128" t="n">
-        <v>98502</v>
+        <v>80161</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13497,21 +13507,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13521,10 +13531,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>533832</v>
+        <v>533498</v>
       </c>
       <c r="R128" t="n">
-        <v>6962310</v>
+        <v>6962158</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13583,10 +13593,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128108119</v>
+        <v>128109254</v>
       </c>
       <c r="B129" t="n">
-        <v>98502</v>
+        <v>80160</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13594,21 +13604,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>219874</v>
+        <v>6461</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13618,10 +13628,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>533800</v>
+        <v>533652</v>
       </c>
       <c r="R129" t="n">
-        <v>6962306</v>
+        <v>6962140</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13680,50 +13690,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128100396</v>
+        <v>128110823</v>
       </c>
       <c r="B130" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>533537</v>
+        <v>533715</v>
       </c>
       <c r="R130" t="n">
-        <v>6962358</v>
+        <v>6962631</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13756,6 +13761,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13782,32 +13792,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128110823</v>
+        <v>128110789</v>
       </c>
       <c r="B131" t="n">
-        <v>98468</v>
+        <v>98502</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13817,10 +13827,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>533715</v>
+        <v>533832</v>
       </c>
       <c r="R131" t="n">
-        <v>6962631</v>
+        <v>6962310</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13853,11 +13863,6 @@
       <c r="AA131" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -13884,45 +13889,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128110825</v>
+        <v>128108119</v>
       </c>
       <c r="B132" t="n">
-        <v>98468</v>
+        <v>98502</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>533583</v>
+        <v>533800</v>
       </c>
       <c r="R132" t="n">
-        <v>6962689</v>
+        <v>6962306</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13955,11 +13960,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>84stycken</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14083,32 +14083,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128110830</v>
+        <v>128110808</v>
       </c>
       <c r="B134" t="n">
-        <v>105506</v>
+        <v>98468</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14118,10 +14118,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>533659</v>
+        <v>533745</v>
       </c>
       <c r="R134" t="n">
-        <v>6962296</v>
+        <v>6962429</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14154,6 +14154,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14180,45 +14185,49 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128100350</v>
+        <v>128107880</v>
       </c>
       <c r="B135" t="n">
-        <v>97345</v>
+        <v>98468</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>533545</v>
+        <v>533736</v>
       </c>
       <c r="R135" t="n">
-        <v>6962339</v>
+        <v>6962362</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14277,7 +14286,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128110808</v>
+        <v>128110809</v>
       </c>
       <c r="B136" t="n">
         <v>98468</v>
@@ -14312,10 +14321,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>533745</v>
+        <v>533748</v>
       </c>
       <c r="R136" t="n">
-        <v>6962429</v>
+        <v>6962494</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14352,7 +14361,7 @@
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>22 stycken</t>
+          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14379,7 +14388,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128107880</v>
+        <v>128110984</v>
       </c>
       <c r="B137" t="n">
         <v>98468</v>
@@ -14407,21 +14416,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>533736</v>
+        <v>533734</v>
       </c>
       <c r="R137" t="n">
-        <v>6962362</v>
+        <v>6962473</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14454,6 +14459,11 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14480,32 +14490,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128110809</v>
+        <v>128100350</v>
       </c>
       <c r="B138" t="n">
-        <v>98468</v>
+        <v>97345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14515,10 +14525,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>533748</v>
+        <v>533545</v>
       </c>
       <c r="R138" t="n">
-        <v>6962494</v>
+        <v>6962339</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14551,11 +14561,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14582,32 +14587,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128110984</v>
+        <v>128110830</v>
       </c>
       <c r="B139" t="n">
-        <v>98468</v>
+        <v>105506</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14617,10 +14622,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>533734</v>
+        <v>533659</v>
       </c>
       <c r="R139" t="n">
-        <v>6962473</v>
+        <v>6962296</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14653,11 +14658,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14684,49 +14684,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128099760</v>
+        <v>128102955</v>
       </c>
       <c r="B140" t="n">
-        <v>98468</v>
+        <v>78787</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>533451</v>
+        <v>533659</v>
       </c>
       <c r="R140" t="n">
-        <v>6962307</v>
+        <v>6962538</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14785,10 +14781,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128102955</v>
+        <v>128108442</v>
       </c>
       <c r="B141" t="n">
-        <v>78787</v>
+        <v>57672</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14796,34 +14792,39 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>533659</v>
+        <v>533714</v>
       </c>
       <c r="R141" t="n">
-        <v>6962538</v>
+        <v>6962273</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14856,6 +14857,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14882,45 +14888,50 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128110801</v>
+        <v>128109413</v>
       </c>
       <c r="B142" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>533442</v>
+        <v>533532</v>
       </c>
       <c r="R142" t="n">
-        <v>6962166</v>
+        <v>6962150</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14957,7 +14968,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>4 stycken  ( finns möjligtvis fler I blåbärsriset)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14984,45 +14995,50 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128110821</v>
+        <v>128109827</v>
       </c>
       <c r="B143" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>533705</v>
+        <v>533421</v>
       </c>
       <c r="R143" t="n">
-        <v>6962430</v>
+        <v>6962154</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15059,7 +15075,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>7 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15086,45 +15102,50 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128110988</v>
+        <v>128102524</v>
       </c>
       <c r="B144" t="n">
-        <v>98468</v>
+        <v>56855</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>533959</v>
+        <v>533640</v>
       </c>
       <c r="R144" t="n">
-        <v>6962738</v>
+        <v>6962482</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15157,11 +15178,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15188,50 +15204,45 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128102524</v>
+        <v>128110821</v>
       </c>
       <c r="B145" t="n">
-        <v>56855</v>
+        <v>98468</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>533640</v>
+        <v>533705</v>
       </c>
       <c r="R145" t="n">
-        <v>6962482</v>
+        <v>6962430</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15264,6 +15275,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>7 stycken</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15290,50 +15306,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128108442</v>
+        <v>128110801</v>
       </c>
       <c r="B146" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>533714</v>
+        <v>533442</v>
       </c>
       <c r="R146" t="n">
-        <v>6962273</v>
+        <v>6962166</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15370,7 +15381,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>4 stycken  ( finns möjligtvis fler I blåbärsriset)</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15397,50 +15408,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128109413</v>
+        <v>128110988</v>
       </c>
       <c r="B147" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>533532</v>
+        <v>533959</v>
       </c>
       <c r="R147" t="n">
-        <v>6962150</v>
+        <v>6962738</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15477,7 +15483,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15504,38 +15510,37 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128109827</v>
+        <v>128099760</v>
       </c>
       <c r="B148" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P148" t="inlineStr">
@@ -15544,10 +15549,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>533421</v>
+        <v>533451</v>
       </c>
       <c r="R148" t="n">
-        <v>6962154</v>
+        <v>6962307</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15580,11 +15585,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15611,54 +15611,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128099113</v>
+        <v>128110796</v>
       </c>
       <c r="B149" t="n">
-        <v>92640</v>
+        <v>80132</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>533396</v>
+        <v>533655</v>
       </c>
       <c r="R149" t="n">
-        <v>6962161</v>
+        <v>6962173</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15691,11 +15682,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15722,10 +15708,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128110831</v>
+        <v>128109763</v>
       </c>
       <c r="B150" t="n">
-        <v>58531</v>
+        <v>80036</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15733,21 +15719,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>208249</v>
+        <v>6456</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15757,10 +15743,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>533728</v>
+        <v>533449</v>
       </c>
       <c r="R150" t="n">
-        <v>6962422</v>
+        <v>6962147</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15819,37 +15805,42 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128101444</v>
+        <v>128099113</v>
       </c>
       <c r="B151" t="n">
-        <v>98468</v>
+        <v>92640</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -15858,10 +15849,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>533424</v>
+        <v>533396</v>
       </c>
       <c r="R151" t="n">
-        <v>6962351</v>
+        <v>6962161</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15894,6 +15885,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15920,32 +15916,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128110986</v>
+        <v>128102121</v>
       </c>
       <c r="B152" t="n">
-        <v>98468</v>
+        <v>57832</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15955,10 +15951,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>533957</v>
+        <v>533532</v>
       </c>
       <c r="R152" t="n">
-        <v>6962694</v>
+        <v>6962477</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15991,11 +15987,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>37 ex</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16022,32 +16013,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128110796</v>
+        <v>128110831</v>
       </c>
       <c r="B153" t="n">
-        <v>80132</v>
+        <v>58531</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>208249</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16057,10 +16048,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>533655</v>
+        <v>533728</v>
       </c>
       <c r="R153" t="n">
-        <v>6962173</v>
+        <v>6962422</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16119,45 +16110,49 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128109763</v>
+        <v>128101444</v>
       </c>
       <c r="B154" t="n">
-        <v>80036</v>
+        <v>98468</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>533449</v>
+        <v>533424</v>
       </c>
       <c r="R154" t="n">
-        <v>6962147</v>
+        <v>6962351</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16216,32 +16211,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128110768</v>
+        <v>128110986</v>
       </c>
       <c r="B155" t="n">
-        <v>57672</v>
+        <v>98468</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16251,10 +16246,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>533754</v>
+        <v>533957</v>
       </c>
       <c r="R155" t="n">
-        <v>6962450</v>
+        <v>6962694</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16291,7 +16286,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
+          <t>37 ex</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16318,32 +16313,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128102121</v>
+        <v>128102104</v>
       </c>
       <c r="B156" t="n">
-        <v>57832</v>
+        <v>105506</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16353,10 +16348,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>533532</v>
+        <v>533615</v>
       </c>
       <c r="R156" t="n">
-        <v>6962477</v>
+        <v>6962423</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16415,32 +16410,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128102104</v>
+        <v>128110768</v>
       </c>
       <c r="B157" t="n">
-        <v>105506</v>
+        <v>57672</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16450,10 +16445,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>533615</v>
+        <v>533754</v>
       </c>
       <c r="R157" t="n">
-        <v>6962423</v>
+        <v>6962450</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16486,6 +16481,11 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16512,10 +16512,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128110791</v>
+        <v>128110777</v>
       </c>
       <c r="B158" t="n">
-        <v>98502</v>
+        <v>91122</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16523,21 +16523,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16547,10 +16547,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>533658</v>
+        <v>533841</v>
       </c>
       <c r="R158" t="n">
-        <v>6962570</v>
+        <v>6962306</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16609,32 +16609,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128110837</v>
+        <v>128110795</v>
       </c>
       <c r="B159" t="n">
-        <v>98385</v>
+        <v>80132</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16644,10 +16644,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>533617</v>
+        <v>533792</v>
       </c>
       <c r="R159" t="n">
-        <v>6962560</v>
+        <v>6962400</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16706,32 +16706,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128110777</v>
+        <v>128110805</v>
       </c>
       <c r="B160" t="n">
-        <v>91122</v>
+        <v>98468</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16741,10 +16741,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>533841</v>
+        <v>533668</v>
       </c>
       <c r="R160" t="n">
-        <v>6962306</v>
+        <v>6962160</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16777,6 +16777,11 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>75 stycken</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16803,45 +16808,49 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128110795</v>
+        <v>128109586</v>
       </c>
       <c r="B161" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P161" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>533792</v>
+        <v>533498</v>
       </c>
       <c r="R161" t="n">
-        <v>6962400</v>
+        <v>6962158</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16900,32 +16909,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128110967</v>
+        <v>128110791</v>
       </c>
       <c r="B162" t="n">
-        <v>57672</v>
+        <v>98502</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16935,10 +16944,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>533691</v>
+        <v>533658</v>
       </c>
       <c r="R162" t="n">
-        <v>6962407</v>
+        <v>6962570</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16971,11 +16980,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17002,32 +17006,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128110773</v>
+        <v>128110837</v>
       </c>
       <c r="B163" t="n">
-        <v>57672</v>
+        <v>98385</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17037,10 +17041,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>533604</v>
+        <v>533617</v>
       </c>
       <c r="R163" t="n">
-        <v>6962650</v>
+        <v>6962560</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17073,11 +17077,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17104,7 +17103,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128110774</v>
+        <v>128110967</v>
       </c>
       <c r="B164" t="n">
         <v>57672</v>
@@ -17139,10 +17138,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>533585</v>
+        <v>533691</v>
       </c>
       <c r="R164" t="n">
-        <v>6962612</v>
+        <v>6962407</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17179,7 +17178,7 @@
       </c>
       <c r="AC164" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett på Tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17206,32 +17205,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128110805</v>
+        <v>128110773</v>
       </c>
       <c r="B165" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17241,10 +17240,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>533668</v>
+        <v>533604</v>
       </c>
       <c r="R165" t="n">
-        <v>6962160</v>
+        <v>6962650</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17281,7 +17280,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>75 stycken</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17308,49 +17307,45 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128109586</v>
+        <v>128110774</v>
       </c>
       <c r="B166" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>533498</v>
+        <v>533585</v>
       </c>
       <c r="R166" t="n">
-        <v>6962158</v>
+        <v>6962612</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17383,6 +17378,11 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17409,49 +17409,45 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128101672</v>
+        <v>128101262</v>
       </c>
       <c r="B167" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>533534</v>
+        <v>533424</v>
       </c>
       <c r="R167" t="n">
-        <v>6962408</v>
+        <v>6962357</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17510,49 +17506,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128109121</v>
+        <v>128110797</v>
       </c>
       <c r="B168" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>533651</v>
+        <v>533832</v>
       </c>
       <c r="R168" t="n">
-        <v>6962130</v>
+        <v>6962351</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17611,7 +17603,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128110985</v>
+        <v>128110813</v>
       </c>
       <c r="B169" t="n">
         <v>98468</v>
@@ -17646,10 +17638,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>533652</v>
+        <v>533507</v>
       </c>
       <c r="R169" t="n">
-        <v>6962550</v>
+        <v>6962168</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17686,7 +17678,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17713,32 +17705,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128110813</v>
+        <v>128110782</v>
       </c>
       <c r="B170" t="n">
-        <v>98468</v>
+        <v>91122</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17748,10 +17740,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>533507</v>
+        <v>533630</v>
       </c>
       <c r="R170" t="n">
-        <v>6962168</v>
+        <v>6962701</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17784,11 +17776,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17912,45 +17899,54 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128110782</v>
+        <v>128102411</v>
       </c>
       <c r="B172" t="n">
-        <v>91122</v>
+        <v>57832</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>533630</v>
+        <v>533575</v>
       </c>
       <c r="R172" t="n">
-        <v>6962701</v>
+        <v>6962520</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18009,45 +18005,49 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128101262</v>
+        <v>128101672</v>
       </c>
       <c r="B173" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>533424</v>
+        <v>533534</v>
       </c>
       <c r="R173" t="n">
-        <v>6962357</v>
+        <v>6962408</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18106,45 +18106,49 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128110797</v>
+        <v>128109121</v>
       </c>
       <c r="B174" t="n">
-        <v>80132</v>
+        <v>98468</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I174" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>533832</v>
+        <v>533651</v>
       </c>
       <c r="R174" t="n">
-        <v>6962351</v>
+        <v>6962130</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18203,54 +18207,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128102411</v>
+        <v>128110985</v>
       </c>
       <c r="B175" t="n">
-        <v>57832</v>
+        <v>98468</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>533575</v>
+        <v>533652</v>
       </c>
       <c r="R175" t="n">
-        <v>6962520</v>
+        <v>6962550</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18283,6 +18278,11 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18309,50 +18309,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128108439</v>
+        <v>128110977</v>
       </c>
       <c r="B176" t="n">
-        <v>57672</v>
+        <v>98502</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>533711</v>
+        <v>534040</v>
       </c>
       <c r="R176" t="n">
-        <v>6962283</v>
+        <v>6962718</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18385,11 +18380,6 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18416,10 +18406,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128101939</v>
+        <v>128110799</v>
       </c>
       <c r="B177" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18427,39 +18417,34 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>533638</v>
+        <v>533724</v>
       </c>
       <c r="R177" t="n">
-        <v>6962346</v>
+        <v>6962625</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18492,11 +18477,6 @@
       <c r="AA177" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -18523,10 +18503,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128110835</v>
+        <v>128110787</v>
       </c>
       <c r="B178" t="n">
-        <v>98385</v>
+        <v>80160</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18534,21 +18514,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>219790</v>
+        <v>6461</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18558,10 +18538,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>533748</v>
+        <v>533785</v>
       </c>
       <c r="R178" t="n">
-        <v>6962431</v>
+        <v>6962326</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18620,7 +18600,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128110799</v>
+        <v>128101075</v>
       </c>
       <c r="B179" t="n">
         <v>80132</v>
@@ -18655,10 +18635,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>533724</v>
+        <v>533392</v>
       </c>
       <c r="R179" t="n">
-        <v>6962625</v>
+        <v>6962343</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18717,45 +18697,50 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128110787</v>
+        <v>128108439</v>
       </c>
       <c r="B180" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>533785</v>
+        <v>533711</v>
       </c>
       <c r="R180" t="n">
-        <v>6962326</v>
+        <v>6962283</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18788,6 +18773,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18814,10 +18804,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128101075</v>
+        <v>128100413</v>
       </c>
       <c r="B181" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -18825,34 +18815,39 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>533392</v>
+        <v>533545</v>
       </c>
       <c r="R181" t="n">
-        <v>6962343</v>
+        <v>6962372</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18885,6 +18880,11 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18911,7 +18911,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128100413</v>
+        <v>128101939</v>
       </c>
       <c r="B182" t="n">
         <v>57672</v>
@@ -18951,10 +18951,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>533545</v>
+        <v>533638</v>
       </c>
       <c r="R182" t="n">
-        <v>6962372</v>
+        <v>6962346</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19018,32 +19018,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128110977</v>
+        <v>128110828</v>
       </c>
       <c r="B183" t="n">
-        <v>98502</v>
+        <v>98468</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19053,10 +19053,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>534040</v>
+        <v>533365</v>
       </c>
       <c r="R183" t="n">
-        <v>6962718</v>
+        <v>6962304</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19089,6 +19089,11 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19115,7 +19120,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128110828</v>
+        <v>128107826</v>
       </c>
       <c r="B184" t="n">
         <v>98468</v>
@@ -19143,17 +19148,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>533365</v>
+        <v>533723</v>
       </c>
       <c r="R184" t="n">
-        <v>6962304</v>
+        <v>6962360</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19186,11 +19195,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19217,7 +19221,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128107826</v>
+        <v>128110817</v>
       </c>
       <c r="B185" t="n">
         <v>98468</v>
@@ -19245,21 +19249,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>533723</v>
+        <v>533728</v>
       </c>
       <c r="R185" t="n">
-        <v>6962360</v>
+        <v>6962346</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19292,6 +19292,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19318,32 +19323,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128110817</v>
+        <v>128110835</v>
       </c>
       <c r="B186" t="n">
-        <v>98468</v>
+        <v>98385</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19353,10 +19358,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>533728</v>
+        <v>533748</v>
       </c>
       <c r="R186" t="n">
-        <v>6962346</v>
+        <v>6962431</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19389,11 +19394,6 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD186" t="b">

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -1311,45 +1311,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128110802</v>
+        <v>128108619</v>
       </c>
       <c r="B8" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533461</v>
+        <v>533675</v>
       </c>
       <c r="R8" t="n">
-        <v>6962171</v>
+        <v>6962244</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,7 +1391,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,49 +1418,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128100827</v>
+        <v>128110972</v>
       </c>
       <c r="B9" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533406</v>
+        <v>533997</v>
       </c>
       <c r="R9" t="n">
-        <v>6962317</v>
+        <v>6962746</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1488,6 +1489,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,10 +1520,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128109460</v>
+        <v>128101860</v>
       </c>
       <c r="B10" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,34 +1531,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533498</v>
+        <v>533601</v>
       </c>
       <c r="R10" t="n">
-        <v>6962158</v>
+        <v>6962344</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,6 +1596,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,45 +1627,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128108655</v>
+        <v>128109460</v>
       </c>
       <c r="B11" t="n">
-        <v>92640</v>
+        <v>80132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533673</v>
+        <v>533498</v>
       </c>
       <c r="R11" t="n">
-        <v>6962211</v>
+        <v>6962158</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,50 +1724,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128108619</v>
+        <v>128108655</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>92641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533675</v>
+        <v>533673</v>
       </c>
       <c r="R12" t="n">
-        <v>6962244</v>
+        <v>6962211</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1784,11 +1795,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1815,32 +1821,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128110972</v>
+        <v>128110802</v>
       </c>
       <c r="B13" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1850,10 +1856,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533997</v>
+        <v>533461</v>
       </c>
       <c r="R13" t="n">
-        <v>6962746</v>
+        <v>6962171</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1890,7 +1896,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1917,38 +1923,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128101860</v>
+        <v>128100827</v>
       </c>
       <c r="B14" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1957,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533601</v>
+        <v>533406</v>
       </c>
       <c r="R14" t="n">
-        <v>6962344</v>
+        <v>6962317</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1993,11 +1998,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2024,45 +2024,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128101567</v>
+        <v>128108700</v>
       </c>
       <c r="B15" t="n">
-        <v>80036</v>
+        <v>57672</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533494</v>
+        <v>533674</v>
       </c>
       <c r="R15" t="n">
-        <v>6962425</v>
+        <v>6962199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2095,6 +2100,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2121,45 +2131,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128110833</v>
+        <v>128109367</v>
       </c>
       <c r="B16" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533768</v>
+        <v>533550</v>
       </c>
       <c r="R16" t="n">
-        <v>6962318</v>
+        <v>6962157</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2192,6 +2207,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2218,49 +2238,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128100131</v>
+        <v>128110833</v>
       </c>
       <c r="B17" t="n">
-        <v>98468</v>
+        <v>98386</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533496</v>
+        <v>533768</v>
       </c>
       <c r="R17" t="n">
-        <v>6962335</v>
+        <v>6962318</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2319,50 +2335,49 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128108700</v>
+        <v>128100321</v>
       </c>
       <c r="B18" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533674</v>
+        <v>533537</v>
       </c>
       <c r="R18" t="n">
-        <v>6962199</v>
+        <v>6962358</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2395,11 +2410,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2426,38 +2436,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128109367</v>
+        <v>128100131</v>
       </c>
       <c r="B19" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2466,10 +2475,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533550</v>
+        <v>533496</v>
       </c>
       <c r="R19" t="n">
-        <v>6962157</v>
+        <v>6962335</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2502,11 +2511,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2533,10 +2537,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128100321</v>
+        <v>128110818</v>
       </c>
       <c r="B20" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2561,21 +2565,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533537</v>
+        <v>533766</v>
       </c>
       <c r="R20" t="n">
-        <v>6962358</v>
+        <v>6962317</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2608,6 +2608,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>10stycken</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2634,32 +2639,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128110818</v>
+        <v>128101567</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>80036</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2669,10 +2674,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533766</v>
+        <v>533494</v>
       </c>
       <c r="R21" t="n">
-        <v>6962317</v>
+        <v>6962425</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,11 +2710,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>10stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3042,50 +3042,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128099395</v>
+        <v>128110832</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>98386</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533356</v>
+        <v>533652</v>
       </c>
       <c r="R25" t="n">
-        <v>6962190</v>
+        <v>6962264</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,11 +3113,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3149,45 +3139,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128110832</v>
+        <v>128101601</v>
       </c>
       <c r="B26" t="n">
-        <v>98385</v>
+        <v>98469</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533652</v>
+        <v>533496</v>
       </c>
       <c r="R26" t="n">
-        <v>6962264</v>
+        <v>6962407</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3246,10 +3240,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128101601</v>
+        <v>128108218</v>
       </c>
       <c r="B27" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3276,19 +3270,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533496</v>
+        <v>533789</v>
       </c>
       <c r="R27" t="n">
-        <v>6962407</v>
+        <v>6962263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3347,49 +3341,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128108218</v>
+        <v>128099395</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533789</v>
+        <v>533356</v>
       </c>
       <c r="R28" t="n">
-        <v>6962263</v>
+        <v>6962190</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,6 +3417,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128110780</v>
+        <v>128099830</v>
       </c>
       <c r="B29" t="n">
-        <v>91122</v>
+        <v>92641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,34 +3459,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533670</v>
+        <v>533353</v>
       </c>
       <c r="R29" t="n">
-        <v>6962552</v>
+        <v>6962231</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3519,6 +3528,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3545,42 +3559,38 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128099830</v>
+        <v>128099402</v>
       </c>
       <c r="B30" t="n">
-        <v>92640</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3589,10 +3599,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533353</v>
+        <v>533474</v>
       </c>
       <c r="R30" t="n">
-        <v>6962231</v>
+        <v>6962267</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3629,7 +3639,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Äldre exemplar</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3656,50 +3666,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128099402</v>
+        <v>128110780</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>91123</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533474</v>
+        <v>533670</v>
       </c>
       <c r="R31" t="n">
-        <v>6962267</v>
+        <v>6962552</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3732,11 +3737,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3763,32 +3763,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128110803</v>
+        <v>128110790</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>98503</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533524</v>
+        <v>533822</v>
       </c>
       <c r="R32" t="n">
-        <v>6962153</v>
+        <v>6962344</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128110981</v>
+        <v>128110803</v>
       </c>
       <c r="B33" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533689</v>
+        <v>533524</v>
       </c>
       <c r="R33" t="n">
-        <v>6962405</v>
+        <v>6962153</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3967,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128109875</v>
+        <v>128110981</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3995,21 +3995,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533436</v>
+        <v>533689</v>
       </c>
       <c r="R34" t="n">
-        <v>6962158</v>
+        <v>6962405</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4042,6 +4038,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4068,10 +4069,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128102143</v>
+        <v>128109875</v>
       </c>
       <c r="B35" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4098,7 +4099,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4107,10 +4108,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533615</v>
+        <v>533436</v>
       </c>
       <c r="R35" t="n">
-        <v>6962423</v>
+        <v>6962158</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4169,45 +4170,49 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128110790</v>
+        <v>128102143</v>
       </c>
       <c r="B36" t="n">
-        <v>98502</v>
+        <v>98469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533822</v>
+        <v>533615</v>
       </c>
       <c r="R36" t="n">
-        <v>6962344</v>
+        <v>6962423</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4240,11 +4245,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4274,7 +4274,7 @@
         <v>128100230</v>
       </c>
       <c r="B37" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128108150</v>
+        <v>128099282</v>
       </c>
       <c r="B38" t="n">
-        <v>80161</v>
+        <v>80160</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4383,34 +4383,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533800</v>
+        <v>533452</v>
       </c>
       <c r="R38" t="n">
-        <v>6962306</v>
+        <v>6962232</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128110978</v>
+        <v>128108150</v>
       </c>
       <c r="B39" t="n">
-        <v>98502</v>
+        <v>80161</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4480,34 +4480,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533708</v>
+        <v>533800</v>
       </c>
       <c r="R39" t="n">
-        <v>6962645</v>
+        <v>6962306</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,32 +4566,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128110836</v>
+        <v>128110968</v>
       </c>
       <c r="B40" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4601,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533722</v>
+        <v>533634</v>
       </c>
       <c r="R40" t="n">
-        <v>6962426</v>
+        <v>6962526</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4637,6 +4637,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4663,45 +4668,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128110788</v>
+        <v>128102724</v>
       </c>
       <c r="B41" t="n">
-        <v>98502</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533590</v>
+        <v>533659</v>
       </c>
       <c r="R41" t="n">
-        <v>6962592</v>
+        <v>6962512</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4734,6 +4744,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4760,7 +4775,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128110968</v>
+        <v>128101831</v>
       </c>
       <c r="B42" t="n">
         <v>57672</v>
@@ -4789,16 +4804,21 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533634</v>
+        <v>533513</v>
       </c>
       <c r="R42" t="n">
-        <v>6962526</v>
+        <v>6962442</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4835,7 +4855,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>En födosökande individ</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4964,32 +4984,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128110824</v>
+        <v>128110978</v>
       </c>
       <c r="B44" t="n">
-        <v>98468</v>
+        <v>98503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +5019,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533712</v>
+        <v>533708</v>
       </c>
       <c r="R44" t="n">
-        <v>6962628</v>
+        <v>6962645</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5035,11 +5055,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5066,50 +5081,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128102724</v>
+        <v>128110788</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>98503</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533659</v>
+        <v>533590</v>
       </c>
       <c r="R45" t="n">
-        <v>6962512</v>
+        <v>6962592</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5142,11 +5152,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5173,50 +5178,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128101831</v>
+        <v>128110836</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>98386</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533513</v>
+        <v>533722</v>
       </c>
       <c r="R46" t="n">
-        <v>6962442</v>
+        <v>6962426</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,11 +5249,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5280,32 +5275,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128099282</v>
+        <v>128110824</v>
       </c>
       <c r="B47" t="n">
-        <v>80160</v>
+        <v>98469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5315,10 +5310,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533452</v>
+        <v>533712</v>
       </c>
       <c r="R47" t="n">
-        <v>6962232</v>
+        <v>6962628</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,6 +5346,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5377,45 +5377,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128110970</v>
+        <v>128099088</v>
       </c>
       <c r="B48" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>534050</v>
+        <v>533425</v>
       </c>
       <c r="R48" t="n">
-        <v>6962743</v>
+        <v>6962182</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5448,11 +5452,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5479,10 +5478,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128110766</v>
+        <v>128107546</v>
       </c>
       <c r="B49" t="n">
-        <v>57672</v>
+        <v>80133</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5490,34 +5489,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533586</v>
+        <v>533648</v>
       </c>
       <c r="R49" t="n">
-        <v>6962139</v>
+        <v>6962374</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5550,11 +5549,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5584,7 +5578,7 @@
         <v>128103304</v>
       </c>
       <c r="B50" t="n">
-        <v>91122</v>
+        <v>91123</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5690,7 +5684,7 @@
         <v>128101702</v>
       </c>
       <c r="B51" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5784,10 +5778,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128107546</v>
+        <v>128110766</v>
       </c>
       <c r="B52" t="n">
-        <v>80133</v>
+        <v>57672</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5795,34 +5789,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533648</v>
+        <v>533586</v>
       </c>
       <c r="R52" t="n">
-        <v>6962374</v>
+        <v>6962139</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5855,6 +5849,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5881,32 +5880,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128110812</v>
+        <v>128110970</v>
       </c>
       <c r="B53" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5916,10 +5915,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533715</v>
+        <v>534050</v>
       </c>
       <c r="R53" t="n">
-        <v>6962610</v>
+        <v>6962743</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5956,7 +5955,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>60 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5983,10 +5982,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128110826</v>
+        <v>128110812</v>
       </c>
       <c r="B54" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6018,10 +6017,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533579</v>
+        <v>533715</v>
       </c>
       <c r="R54" t="n">
-        <v>6962663</v>
+        <v>6962610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6058,7 +6057,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6085,45 +6084,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128108922</v>
+        <v>128110826</v>
       </c>
       <c r="B55" t="n">
-        <v>105506</v>
+        <v>98469</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533671</v>
+        <v>533579</v>
       </c>
       <c r="R55" t="n">
-        <v>6962142</v>
+        <v>6962663</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6156,6 +6155,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6182,45 +6186,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128110814</v>
+        <v>128108922</v>
       </c>
       <c r="B56" t="n">
-        <v>98468</v>
+        <v>105507</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533650</v>
+        <v>533671</v>
       </c>
       <c r="R56" t="n">
-        <v>6962134</v>
+        <v>6962142</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6253,11 +6257,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>50 stycken ( några har blommat).</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6287,7 +6286,7 @@
         <v>128110804</v>
       </c>
       <c r="B57" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6389,7 +6388,7 @@
         <v>128110990</v>
       </c>
       <c r="B58" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6488,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128101106</v>
+        <v>128110814</v>
       </c>
       <c r="B59" t="n">
-        <v>80098</v>
+        <v>98469</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6523,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533425</v>
+        <v>533650</v>
       </c>
       <c r="R59" t="n">
-        <v>6962304</v>
+        <v>6962134</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6559,6 +6558,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>50 stycken ( några har blommat).</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6585,39 +6589,35 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128099088</v>
+        <v>128101106</v>
       </c>
       <c r="B60" t="n">
-        <v>98468</v>
+        <v>80098</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>229748</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
@@ -6627,7 +6627,7 @@
         <v>533425</v>
       </c>
       <c r="R60" t="n">
-        <v>6962182</v>
+        <v>6962304</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6686,7 +6686,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128100636</v>
+        <v>128099984</v>
       </c>
       <c r="B61" t="n">
         <v>80132</v>
@@ -6721,10 +6721,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533452</v>
+        <v>533455</v>
       </c>
       <c r="R61" t="n">
-        <v>6962350</v>
+        <v>6962339</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6783,7 +6783,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128099984</v>
+        <v>128099875</v>
       </c>
       <c r="B62" t="n">
         <v>80132</v>
@@ -6818,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533455</v>
+        <v>533445</v>
       </c>
       <c r="R62" t="n">
-        <v>6962339</v>
+        <v>6962324</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6880,10 +6880,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128099875</v>
+        <v>128099885</v>
       </c>
       <c r="B63" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6891,34 +6891,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533445</v>
+        <v>533361</v>
       </c>
       <c r="R63" t="n">
-        <v>6962324</v>
+        <v>6962247</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6951,6 +6956,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6977,32 +6987,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128110971</v>
+        <v>128099099</v>
       </c>
       <c r="B64" t="n">
-        <v>57672</v>
+        <v>105507</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7012,10 +7022,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>534036</v>
+        <v>533416</v>
       </c>
       <c r="R64" t="n">
-        <v>6962734</v>
+        <v>6962179</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7048,11 +7058,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7079,50 +7084,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128108477</v>
+        <v>128099522</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533710</v>
+        <v>533349</v>
       </c>
       <c r="R65" t="n">
-        <v>6962294</v>
+        <v>6962197</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7155,11 +7164,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7186,7 +7190,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128099885</v>
+        <v>128110971</v>
       </c>
       <c r="B66" t="n">
         <v>57672</v>
@@ -7215,21 +7219,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533361</v>
+        <v>534036</v>
       </c>
       <c r="R66" t="n">
-        <v>6962247</v>
+        <v>6962734</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7266,7 +7265,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7293,49 +7292,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128100184</v>
+        <v>128108477</v>
       </c>
       <c r="B67" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533509</v>
+        <v>533710</v>
       </c>
       <c r="R67" t="n">
-        <v>6962336</v>
+        <v>6962294</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,6 +7368,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7394,10 +7399,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128103587</v>
+        <v>128110827</v>
       </c>
       <c r="B68" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7422,21 +7427,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533650</v>
+        <v>533614</v>
       </c>
       <c r="R68" t="n">
-        <v>6962600</v>
+        <v>6962554</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7469,6 +7470,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7495,10 +7501,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128110827</v>
+        <v>128100184</v>
       </c>
       <c r="B69" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7523,17 +7529,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533614</v>
+        <v>533509</v>
       </c>
       <c r="R69" t="n">
-        <v>6962554</v>
+        <v>6962336</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7566,11 +7576,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7597,10 +7602,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128099522</v>
+        <v>128103587</v>
       </c>
       <c r="B70" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7627,24 +7632,19 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>120</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533349</v>
+        <v>533650</v>
       </c>
       <c r="R70" t="n">
-        <v>6962197</v>
+        <v>6962600</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7703,32 +7703,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128099099</v>
+        <v>128100636</v>
       </c>
       <c r="B71" t="n">
-        <v>105506</v>
+        <v>80132</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533416</v>
+        <v>533452</v>
       </c>
       <c r="R71" t="n">
-        <v>6962179</v>
+        <v>6962350</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7800,50 +7800,49 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128108355</v>
+        <v>128101024</v>
       </c>
       <c r="B72" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533768</v>
+        <v>533375</v>
       </c>
       <c r="R72" t="n">
-        <v>6962269</v>
+        <v>6962293</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7876,11 +7875,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8004,7 +7998,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128110775</v>
+        <v>128099712</v>
       </c>
       <c r="B74" t="n">
         <v>57672</v>
@@ -8033,16 +8027,21 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533564</v>
+        <v>533451</v>
       </c>
       <c r="R74" t="n">
-        <v>6962537</v>
+        <v>6962307</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8079,7 +8078,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8106,7 +8105,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128101911</v>
+        <v>128110769</v>
       </c>
       <c r="B75" t="n">
         <v>57672</v>
@@ -8135,21 +8134,16 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533510</v>
+        <v>533841</v>
       </c>
       <c r="R75" t="n">
-        <v>6962462</v>
+        <v>6962363</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8186,7 +8180,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack) spår</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8213,7 +8207,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128110769</v>
+        <v>128110775</v>
       </c>
       <c r="B76" t="n">
         <v>57672</v>
@@ -8248,10 +8242,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533841</v>
+        <v>533564</v>
       </c>
       <c r="R76" t="n">
-        <v>6962363</v>
+        <v>6962537</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8288,7 +8282,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack) spår</t>
+          <t>Färska och äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8315,7 +8309,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128099712</v>
+        <v>128108355</v>
       </c>
       <c r="B77" t="n">
         <v>57672</v>
@@ -8351,14 +8345,14 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533451</v>
+        <v>533768</v>
       </c>
       <c r="R77" t="n">
-        <v>6962307</v>
+        <v>6962269</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8422,37 +8416,38 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128101024</v>
+        <v>128101911</v>
       </c>
       <c r="B78" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8461,10 +8456,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533375</v>
+        <v>533510</v>
       </c>
       <c r="R78" t="n">
-        <v>6962293</v>
+        <v>6962462</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8497,6 +8492,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8526,7 +8526,7 @@
         <v>128110811</v>
       </c>
       <c r="B79" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>128110779</v>
       </c>
       <c r="B80" t="n">
-        <v>91122</v>
+        <v>91123</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128102006</v>
+        <v>128099905</v>
       </c>
       <c r="B81" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8733,34 +8733,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533510</v>
+        <v>533445</v>
       </c>
       <c r="R81" t="n">
-        <v>6962462</v>
+        <v>6962324</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8793,6 +8798,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8819,10 +8829,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128110969</v>
+        <v>128102006</v>
       </c>
       <c r="B82" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8830,21 +8840,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8854,10 +8864,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533825</v>
+        <v>533510</v>
       </c>
       <c r="R82" t="n">
-        <v>6962690</v>
+        <v>6962462</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8890,11 +8900,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9135,49 +9140,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128101261</v>
+        <v>128110969</v>
       </c>
       <c r="B85" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533424</v>
+        <v>533825</v>
       </c>
       <c r="R85" t="n">
-        <v>6962357</v>
+        <v>6962690</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9210,6 +9211,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9239,7 +9245,7 @@
         <v>128110976</v>
       </c>
       <c r="B86" t="n">
-        <v>98502</v>
+        <v>98503</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9338,38 +9344,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128099905</v>
+        <v>128101261</v>
       </c>
       <c r="B87" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9378,10 +9383,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533445</v>
+        <v>533424</v>
       </c>
       <c r="R87" t="n">
-        <v>6962324</v>
+        <v>6962357</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9414,11 +9419,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9445,10 +9445,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128110810</v>
+        <v>128110982</v>
       </c>
       <c r="B88" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533645</v>
+        <v>533681</v>
       </c>
       <c r="R88" t="n">
-        <v>6962593</v>
+        <v>6962434</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9516,6 +9516,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>23 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9542,10 +9547,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128110982</v>
+        <v>128110810</v>
       </c>
       <c r="B89" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9577,10 +9582,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533681</v>
+        <v>533645</v>
       </c>
       <c r="R89" t="n">
-        <v>6962434</v>
+        <v>6962593</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9613,11 +9618,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>23 ex</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9843,10 +9843,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>128110806</v>
+        <v>128110989</v>
       </c>
       <c r="B92" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9878,10 +9878,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>533638</v>
+        <v>533912</v>
       </c>
       <c r="R92" t="n">
-        <v>6962276</v>
+        <v>6962770</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9918,7 +9918,7 @@
       </c>
       <c r="AC92" t="inlineStr">
         <is>
-          <t>4 stycken kan finnas mer I blåbärsriset</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9945,10 +9945,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128110989</v>
+        <v>128110806</v>
       </c>
       <c r="B93" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9980,10 +9980,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>533912</v>
+        <v>533638</v>
       </c>
       <c r="R93" t="n">
-        <v>6962770</v>
+        <v>6962276</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10020,7 +10020,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>4 stycken kan finnas mer I blåbärsriset</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10047,10 +10047,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128099401</v>
+        <v>128110974</v>
       </c>
       <c r="B94" t="n">
-        <v>92640</v>
+        <v>80161</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10058,43 +10058,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533356</v>
+        <v>533937</v>
       </c>
       <c r="R94" t="n">
-        <v>6962190</v>
+        <v>6962685</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10153,45 +10144,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128110974</v>
+        <v>128102878</v>
       </c>
       <c r="B95" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533937</v>
+        <v>533665</v>
       </c>
       <c r="R95" t="n">
-        <v>6962685</v>
+        <v>6962515</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10224,6 +10220,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10250,45 +10251,50 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128110816</v>
+        <v>128100043</v>
       </c>
       <c r="B96" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533696</v>
+        <v>533496</v>
       </c>
       <c r="R96" t="n">
-        <v>6962294</v>
+        <v>6962335</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10325,7 +10331,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>20 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10352,49 +10358,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128102067</v>
+        <v>128110834</v>
       </c>
       <c r="B97" t="n">
-        <v>98468</v>
+        <v>98386</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533510</v>
+        <v>533779</v>
       </c>
       <c r="R97" t="n">
-        <v>6962462</v>
+        <v>6962298</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10453,38 +10455,42 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128099555</v>
+        <v>128099401</v>
       </c>
       <c r="B98" t="n">
-        <v>57672</v>
+        <v>92641</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -10493,10 +10499,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>533471</v>
+        <v>533356</v>
       </c>
       <c r="R98" t="n">
-        <v>6962293</v>
+        <v>6962190</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10529,11 +10535,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10560,45 +10561,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128110834</v>
+        <v>128099555</v>
       </c>
       <c r="B99" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>533779</v>
+        <v>533471</v>
       </c>
       <c r="R99" t="n">
-        <v>6962298</v>
+        <v>6962293</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10631,6 +10637,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10657,50 +10668,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128102878</v>
+        <v>128110816</v>
       </c>
       <c r="B100" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>533665</v>
+        <v>533696</v>
       </c>
       <c r="R100" t="n">
-        <v>6962515</v>
+        <v>6962294</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10737,7 +10743,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10764,38 +10770,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128100043</v>
+        <v>128102067</v>
       </c>
       <c r="B101" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -10804,10 +10809,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533496</v>
+        <v>533510</v>
       </c>
       <c r="R101" t="n">
-        <v>6962335</v>
+        <v>6962462</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10840,11 +10845,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10871,32 +10871,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128110807</v>
+        <v>128110829</v>
       </c>
       <c r="B102" t="n">
-        <v>98468</v>
+        <v>56855</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10906,10 +10906,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>533664</v>
+        <v>533606</v>
       </c>
       <c r="R102" t="n">
-        <v>6962286</v>
+        <v>6962582</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>23 stycken</t>
+          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10973,10 +10973,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128101073</v>
+        <v>128110792</v>
       </c>
       <c r="B103" t="n">
-        <v>80168</v>
+        <v>98503</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10984,21 +10984,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6464</v>
+        <v>219874</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11008,10 +11008,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>533385</v>
+        <v>533719</v>
       </c>
       <c r="R103" t="n">
-        <v>6962288</v>
+        <v>6962615</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11044,6 +11044,11 @@
       <c r="AA103" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11070,32 +11075,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128110829</v>
+        <v>128110785</v>
       </c>
       <c r="B104" t="n">
-        <v>56855</v>
+        <v>97346</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11105,10 +11110,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>533606</v>
+        <v>533824</v>
       </c>
       <c r="R104" t="n">
-        <v>6962582</v>
+        <v>6962352</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11141,11 +11146,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11172,32 +11172,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128110792</v>
+        <v>128110807</v>
       </c>
       <c r="B105" t="n">
-        <v>98502</v>
+        <v>98469</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11207,10 +11207,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>533719</v>
+        <v>533664</v>
       </c>
       <c r="R105" t="n">
-        <v>6962615</v>
+        <v>6962286</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11277,7 +11277,7 @@
         <v>128110983</v>
       </c>
       <c r="B106" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11376,10 +11376,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128110785</v>
+        <v>128101073</v>
       </c>
       <c r="B107" t="n">
-        <v>97345</v>
+        <v>80168</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11387,21 +11387,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11411,10 +11411,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533824</v>
+        <v>533385</v>
       </c>
       <c r="R107" t="n">
-        <v>6962352</v>
+        <v>6962288</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11473,50 +11473,49 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128108378</v>
+        <v>128099487</v>
       </c>
       <c r="B108" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533750</v>
+        <v>533474</v>
       </c>
       <c r="R108" t="n">
-        <v>6962259</v>
+        <v>6962267</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11549,11 +11548,6 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11580,32 +11574,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128110819</v>
+        <v>128101331</v>
       </c>
       <c r="B109" t="n">
-        <v>98468</v>
+        <v>80167</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11615,10 +11609,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533834</v>
+        <v>533424</v>
       </c>
       <c r="R109" t="n">
-        <v>6962298</v>
+        <v>6962357</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11651,11 +11645,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11682,45 +11671,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128110794</v>
+        <v>128108395</v>
       </c>
       <c r="B110" t="n">
-        <v>98502</v>
+        <v>80132</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533608</v>
+        <v>533735</v>
       </c>
       <c r="R110" t="n">
-        <v>6962612</v>
+        <v>6962274</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11753,11 +11742,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11784,10 +11768,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128110838</v>
+        <v>128110783</v>
       </c>
       <c r="B111" t="n">
-        <v>98385</v>
+        <v>91123</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11795,21 +11779,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>219790</v>
+        <v>3215</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11819,10 +11803,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>533708</v>
+        <v>533599</v>
       </c>
       <c r="R111" t="n">
-        <v>6962624</v>
+        <v>6962553</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11855,11 +11839,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11886,45 +11865,50 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128110793</v>
+        <v>128108378</v>
       </c>
       <c r="B112" t="n">
-        <v>98502</v>
+        <v>57672</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>533693</v>
+        <v>533750</v>
       </c>
       <c r="R112" t="n">
-        <v>6962647</v>
+        <v>6962259</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11961,7 +11945,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11988,45 +11972,50 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128108028</v>
+        <v>128100457</v>
       </c>
       <c r="B113" t="n">
-        <v>97351</v>
+        <v>57672</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533802</v>
+        <v>533556</v>
       </c>
       <c r="R113" t="n">
-        <v>6962332</v>
+        <v>6962363</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12059,6 +12048,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12085,49 +12079,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128099487</v>
+        <v>128110776</v>
       </c>
       <c r="B114" t="n">
-        <v>98468</v>
+        <v>57832</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533474</v>
+        <v>533719</v>
       </c>
       <c r="R114" t="n">
-        <v>6962267</v>
+        <v>6962615</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12160,6 +12150,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12186,10 +12181,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128110783</v>
+        <v>128110838</v>
       </c>
       <c r="B115" t="n">
-        <v>91122</v>
+        <v>98386</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12197,21 +12192,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>3215</v>
+        <v>219790</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12221,10 +12216,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533599</v>
+        <v>533708</v>
       </c>
       <c r="R115" t="n">
-        <v>6962553</v>
+        <v>6962624</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12257,6 +12252,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12283,10 +12283,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128101331</v>
+        <v>128110793</v>
       </c>
       <c r="B116" t="n">
-        <v>80167</v>
+        <v>98503</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12294,21 +12294,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6463</v>
+        <v>219874</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12318,10 +12318,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533424</v>
+        <v>533693</v>
       </c>
       <c r="R116" t="n">
-        <v>6962357</v>
+        <v>6962647</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12354,6 +12354,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12380,45 +12385,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128108395</v>
+        <v>128110794</v>
       </c>
       <c r="B117" t="n">
-        <v>80132</v>
+        <v>98503</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533735</v>
+        <v>533608</v>
       </c>
       <c r="R117" t="n">
-        <v>6962274</v>
+        <v>6962612</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12451,6 +12456,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12477,45 +12487,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128110776</v>
+        <v>128108028</v>
       </c>
       <c r="B118" t="n">
-        <v>57832</v>
+        <v>97352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>221941</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533719</v>
+        <v>533802</v>
       </c>
       <c r="R118" t="n">
-        <v>6962615</v>
+        <v>6962332</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12548,11 +12558,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12582,7 +12587,7 @@
         <v>128110991</v>
       </c>
       <c r="B119" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12681,45 +12686,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128110987</v>
+        <v>128103993</v>
       </c>
       <c r="B120" t="n">
-        <v>98468</v>
+        <v>105507</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533999</v>
+        <v>533664</v>
       </c>
       <c r="R120" t="n">
-        <v>6962664</v>
+        <v>6962650</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12752,11 +12757,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>85 ex</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12783,50 +12783,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128100457</v>
+        <v>128110987</v>
       </c>
       <c r="B121" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533556</v>
+        <v>533999</v>
       </c>
       <c r="R121" t="n">
-        <v>6962363</v>
+        <v>6962664</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12863,7 +12858,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12890,45 +12885,49 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103993</v>
+        <v>128103044</v>
       </c>
       <c r="B122" t="n">
-        <v>105506</v>
+        <v>98469</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533664</v>
+        <v>533627</v>
       </c>
       <c r="R122" t="n">
-        <v>6962650</v>
+        <v>6962544</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12987,10 +12986,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128103044</v>
+        <v>128110819</v>
       </c>
       <c r="B123" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13015,21 +13014,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>533627</v>
+        <v>533834</v>
       </c>
       <c r="R123" t="n">
-        <v>6962544</v>
+        <v>6962298</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13062,6 +13057,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13088,50 +13088,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128099239</v>
+        <v>128099811</v>
       </c>
       <c r="B124" t="n">
-        <v>57672</v>
+        <v>105507</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>533422</v>
+        <v>533451</v>
       </c>
       <c r="R124" t="n">
-        <v>6962229</v>
+        <v>6962307</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13164,11 +13159,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13195,50 +13185,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128100396</v>
+        <v>128109488</v>
       </c>
       <c r="B125" t="n">
-        <v>57832</v>
+        <v>80161</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>533537</v>
+        <v>533498</v>
       </c>
       <c r="R125" t="n">
-        <v>6962358</v>
+        <v>6962158</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13297,45 +13282,45 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128110825</v>
+        <v>128109254</v>
       </c>
       <c r="B126" t="n">
-        <v>98468</v>
+        <v>80160</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>533583</v>
+        <v>533652</v>
       </c>
       <c r="R126" t="n">
-        <v>6962689</v>
+        <v>6962140</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13368,11 +13353,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>84stycken</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13399,32 +13379,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128099811</v>
+        <v>128110825</v>
       </c>
       <c r="B127" t="n">
-        <v>105506</v>
+        <v>98469</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13434,10 +13414,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>533451</v>
+        <v>533583</v>
       </c>
       <c r="R127" t="n">
-        <v>6962307</v>
+        <v>6962689</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13470,6 +13450,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>84stycken</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13496,45 +13481,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128109488</v>
+        <v>128099239</v>
       </c>
       <c r="B128" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>533498</v>
+        <v>533422</v>
       </c>
       <c r="R128" t="n">
-        <v>6962158</v>
+        <v>6962229</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13567,6 +13557,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13593,45 +13588,50 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128109254</v>
+        <v>128100396</v>
       </c>
       <c r="B129" t="n">
-        <v>80160</v>
+        <v>57832</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>533652</v>
+        <v>533537</v>
       </c>
       <c r="R129" t="n">
-        <v>6962140</v>
+        <v>6962358</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13690,32 +13690,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128110823</v>
+        <v>128110789</v>
       </c>
       <c r="B130" t="n">
-        <v>98468</v>
+        <v>98503</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>533715</v>
+        <v>533832</v>
       </c>
       <c r="R130" t="n">
-        <v>6962631</v>
+        <v>6962310</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13761,11 +13761,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13792,10 +13787,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128110789</v>
+        <v>128108119</v>
       </c>
       <c r="B131" t="n">
-        <v>98502</v>
+        <v>98503</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13823,14 +13818,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>533832</v>
+        <v>533800</v>
       </c>
       <c r="R131" t="n">
-        <v>6962310</v>
+        <v>6962306</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13889,45 +13884,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128108119</v>
+        <v>128110823</v>
       </c>
       <c r="B132" t="n">
-        <v>98502</v>
+        <v>98469</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>533800</v>
+        <v>533715</v>
       </c>
       <c r="R132" t="n">
-        <v>6962306</v>
+        <v>6962631</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13960,6 +13955,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13986,45 +13986,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103617</v>
+        <v>128100350</v>
       </c>
       <c r="B133" t="n">
-        <v>91350</v>
+        <v>97346</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>533637</v>
+        <v>533545</v>
       </c>
       <c r="R133" t="n">
-        <v>6962600</v>
+        <v>6962339</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14083,32 +14083,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128110808</v>
+        <v>128110830</v>
       </c>
       <c r="B134" t="n">
-        <v>98468</v>
+        <v>105507</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14118,10 +14118,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>533745</v>
+        <v>533659</v>
       </c>
       <c r="R134" t="n">
-        <v>6962429</v>
+        <v>6962296</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14154,11 +14154,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14185,10 +14180,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128107880</v>
+        <v>128110808</v>
       </c>
       <c r="B135" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14213,21 +14208,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>533736</v>
+        <v>533745</v>
       </c>
       <c r="R135" t="n">
-        <v>6962362</v>
+        <v>6962429</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14260,6 +14251,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14286,10 +14282,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128110809</v>
+        <v>128107880</v>
       </c>
       <c r="B136" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14314,17 +14310,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>533748</v>
+        <v>533736</v>
       </c>
       <c r="R136" t="n">
-        <v>6962494</v>
+        <v>6962362</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14357,11 +14357,6 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14388,10 +14383,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128110984</v>
+        <v>128110809</v>
       </c>
       <c r="B137" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14423,10 +14418,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>533734</v>
+        <v>533748</v>
       </c>
       <c r="R137" t="n">
-        <v>6962473</v>
+        <v>6962494</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14463,7 +14458,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14490,32 +14485,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128100350</v>
+        <v>128110984</v>
       </c>
       <c r="B138" t="n">
-        <v>97345</v>
+        <v>98469</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14525,10 +14520,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>533545</v>
+        <v>533734</v>
       </c>
       <c r="R138" t="n">
-        <v>6962339</v>
+        <v>6962473</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14561,6 +14556,11 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14587,45 +14587,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128110830</v>
+        <v>128103617</v>
       </c>
       <c r="B139" t="n">
-        <v>105506</v>
+        <v>91351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>533659</v>
+        <v>533637</v>
       </c>
       <c r="R139" t="n">
-        <v>6962296</v>
+        <v>6962600</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14684,45 +14684,49 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128102955</v>
+        <v>128099760</v>
       </c>
       <c r="B140" t="n">
-        <v>78787</v>
+        <v>98469</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>533659</v>
+        <v>533451</v>
       </c>
       <c r="R140" t="n">
-        <v>6962538</v>
+        <v>6962307</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14781,10 +14785,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128108442</v>
+        <v>128102955</v>
       </c>
       <c r="B141" t="n">
-        <v>57672</v>
+        <v>78787</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14792,39 +14796,34 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P141" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>533714</v>
+        <v>533659</v>
       </c>
       <c r="R141" t="n">
-        <v>6962273</v>
+        <v>6962538</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14857,11 +14856,6 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14888,10 +14882,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128109413</v>
+        <v>128102524</v>
       </c>
       <c r="B142" t="n">
-        <v>57672</v>
+        <v>56855</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14899,16 +14893,16 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -14919,7 +14913,7 @@
       <c r="I142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P142" t="inlineStr">
@@ -14928,10 +14922,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>533532</v>
+        <v>533640</v>
       </c>
       <c r="R142" t="n">
-        <v>6962150</v>
+        <v>6962482</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14964,11 +14958,6 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14995,7 +14984,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128109827</v>
+        <v>128108442</v>
       </c>
       <c r="B143" t="n">
         <v>57672</v>
@@ -15031,14 +15020,14 @@
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>533421</v>
+        <v>533714</v>
       </c>
       <c r="R143" t="n">
-        <v>6962154</v>
+        <v>6962273</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15102,10 +15091,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128102524</v>
+        <v>128109413</v>
       </c>
       <c r="B144" t="n">
-        <v>56855</v>
+        <v>57672</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15113,16 +15102,16 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -15133,7 +15122,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -15142,10 +15131,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>533640</v>
+        <v>533532</v>
       </c>
       <c r="R144" t="n">
-        <v>6962482</v>
+        <v>6962150</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15178,6 +15167,11 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15204,45 +15198,50 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128110821</v>
+        <v>128109827</v>
       </c>
       <c r="B145" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>533705</v>
+        <v>533421</v>
       </c>
       <c r="R145" t="n">
-        <v>6962430</v>
+        <v>6962154</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15279,7 +15278,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>7 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15309,7 +15308,7 @@
         <v>128110801</v>
       </c>
       <c r="B146" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15408,10 +15407,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128110988</v>
+        <v>128110821</v>
       </c>
       <c r="B147" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15443,10 +15442,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>533959</v>
+        <v>533705</v>
       </c>
       <c r="R147" t="n">
-        <v>6962738</v>
+        <v>6962430</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15483,7 +15482,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>7 stycken</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15510,10 +15509,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128099760</v>
+        <v>128110988</v>
       </c>
       <c r="B148" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -15538,21 +15537,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>533451</v>
+        <v>533959</v>
       </c>
       <c r="R148" t="n">
-        <v>6962307</v>
+        <v>6962738</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15585,6 +15580,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15611,45 +15611,54 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128110796</v>
+        <v>128099113</v>
       </c>
       <c r="B149" t="n">
-        <v>80132</v>
+        <v>92641</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>533655</v>
+        <v>533396</v>
       </c>
       <c r="R149" t="n">
-        <v>6962173</v>
+        <v>6962161</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15682,6 +15691,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15708,32 +15722,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128109763</v>
+        <v>128102121</v>
       </c>
       <c r="B150" t="n">
-        <v>80036</v>
+        <v>57832</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15743,10 +15757,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>533449</v>
+        <v>533532</v>
       </c>
       <c r="R150" t="n">
-        <v>6962147</v>
+        <v>6962477</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15805,42 +15819,37 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128099113</v>
+        <v>128101444</v>
       </c>
       <c r="B151" t="n">
-        <v>92640</v>
+        <v>98469</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -15849,10 +15858,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>533396</v>
+        <v>533424</v>
       </c>
       <c r="R151" t="n">
-        <v>6962161</v>
+        <v>6962351</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15885,11 +15894,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15916,32 +15920,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128102121</v>
+        <v>128110986</v>
       </c>
       <c r="B152" t="n">
-        <v>57832</v>
+        <v>98469</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15951,10 +15955,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>533532</v>
+        <v>533957</v>
       </c>
       <c r="R152" t="n">
-        <v>6962477</v>
+        <v>6962694</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15987,6 +15991,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>37 ex</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16013,10 +16022,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128110831</v>
+        <v>128102104</v>
       </c>
       <c r="B153" t="n">
-        <v>58531</v>
+        <v>105507</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16024,21 +16033,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>208249</v>
+        <v>221144</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16048,10 +16057,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>533728</v>
+        <v>533615</v>
       </c>
       <c r="R153" t="n">
-        <v>6962422</v>
+        <v>6962423</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16110,49 +16119,45 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128101444</v>
+        <v>128110796</v>
       </c>
       <c r="B154" t="n">
-        <v>98468</v>
+        <v>80132</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>533424</v>
+        <v>533655</v>
       </c>
       <c r="R154" t="n">
-        <v>6962351</v>
+        <v>6962173</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16211,32 +16216,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128110986</v>
+        <v>128109763</v>
       </c>
       <c r="B155" t="n">
-        <v>98468</v>
+        <v>80036</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16246,10 +16251,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>533957</v>
+        <v>533449</v>
       </c>
       <c r="R155" t="n">
-        <v>6962694</v>
+        <v>6962147</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16282,11 +16287,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>37 ex</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16313,32 +16313,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128102104</v>
+        <v>128110768</v>
       </c>
       <c r="B156" t="n">
-        <v>105506</v>
+        <v>57672</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16348,10 +16348,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>533615</v>
+        <v>533754</v>
       </c>
       <c r="R156" t="n">
-        <v>6962423</v>
+        <v>6962450</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16384,6 +16384,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16410,32 +16415,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128110768</v>
+        <v>128110831</v>
       </c>
       <c r="B157" t="n">
-        <v>57672</v>
+        <v>58531</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>208249</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16445,10 +16450,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>533754</v>
+        <v>533728</v>
       </c>
       <c r="R157" t="n">
-        <v>6962450</v>
+        <v>6962422</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16481,11 +16486,6 @@
       <c r="AA157" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16512,32 +16512,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128110777</v>
+        <v>128110967</v>
       </c>
       <c r="B158" t="n">
-        <v>91122</v>
+        <v>57672</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16547,10 +16547,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>533841</v>
+        <v>533691</v>
       </c>
       <c r="R158" t="n">
-        <v>6962306</v>
+        <v>6962407</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16583,6 +16583,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16609,10 +16614,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128110795</v>
+        <v>128110773</v>
       </c>
       <c r="B159" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16620,21 +16625,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16644,10 +16649,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>533792</v>
+        <v>533604</v>
       </c>
       <c r="R159" t="n">
-        <v>6962400</v>
+        <v>6962650</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16680,6 +16685,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16706,32 +16716,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128110805</v>
+        <v>128110774</v>
       </c>
       <c r="B160" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16741,10 +16751,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>533668</v>
+        <v>533585</v>
       </c>
       <c r="R160" t="n">
-        <v>6962160</v>
+        <v>6962612</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16781,7 +16791,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>75 stycken</t>
+          <t>Färska ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16808,49 +16818,45 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128109586</v>
+        <v>128110837</v>
       </c>
       <c r="B161" t="n">
-        <v>98468</v>
+        <v>98386</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>533498</v>
+        <v>533617</v>
       </c>
       <c r="R161" t="n">
-        <v>6962158</v>
+        <v>6962560</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16912,7 +16918,7 @@
         <v>128110791</v>
       </c>
       <c r="B162" t="n">
-        <v>98502</v>
+        <v>98503</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -17006,32 +17012,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128110837</v>
+        <v>128110805</v>
       </c>
       <c r="B163" t="n">
-        <v>98385</v>
+        <v>98469</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17041,10 +17047,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>533617</v>
+        <v>533668</v>
       </c>
       <c r="R163" t="n">
-        <v>6962560</v>
+        <v>6962160</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17077,6 +17083,11 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>75 stycken</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17103,45 +17114,49 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128110967</v>
+        <v>128109586</v>
       </c>
       <c r="B164" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>533691</v>
+        <v>533498</v>
       </c>
       <c r="R164" t="n">
-        <v>6962407</v>
+        <v>6962158</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17174,11 +17189,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17205,10 +17215,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128110773</v>
+        <v>128110795</v>
       </c>
       <c r="B165" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -17216,21 +17226,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17240,10 +17250,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>533604</v>
+        <v>533792</v>
       </c>
       <c r="R165" t="n">
-        <v>6962650</v>
+        <v>6962400</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17276,11 +17286,6 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17307,32 +17312,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128110774</v>
+        <v>128110777</v>
       </c>
       <c r="B166" t="n">
-        <v>57672</v>
+        <v>91123</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17342,10 +17347,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>533585</v>
+        <v>533841</v>
       </c>
       <c r="R166" t="n">
-        <v>6962612</v>
+        <v>6962306</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17378,11 +17383,6 @@
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>Färska ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -17603,32 +17603,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128110813</v>
+        <v>128110781</v>
       </c>
       <c r="B169" t="n">
-        <v>98468</v>
+        <v>91123</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17638,10 +17638,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>533507</v>
+        <v>533700</v>
       </c>
       <c r="R169" t="n">
-        <v>6962168</v>
+        <v>6962581</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17674,11 +17674,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17708,7 +17703,7 @@
         <v>128110782</v>
       </c>
       <c r="B170" t="n">
-        <v>91122</v>
+        <v>91123</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17802,45 +17797,54 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128110781</v>
+        <v>128102411</v>
       </c>
       <c r="B171" t="n">
-        <v>91122</v>
+        <v>57832</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>3215</v>
+        <v>103021</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>533700</v>
+        <v>533575</v>
       </c>
       <c r="R171" t="n">
-        <v>6962581</v>
+        <v>6962520</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17899,42 +17903,37 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128102411</v>
+        <v>128101672</v>
       </c>
       <c r="B172" t="n">
-        <v>57832</v>
+        <v>98469</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P172" t="inlineStr">
@@ -17943,10 +17942,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>533575</v>
+        <v>533534</v>
       </c>
       <c r="R172" t="n">
-        <v>6962520</v>
+        <v>6962408</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18005,10 +18004,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128101672</v>
+        <v>128109121</v>
       </c>
       <c r="B173" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18035,7 +18034,7 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P173" t="inlineStr">
@@ -18044,10 +18043,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>533534</v>
+        <v>533651</v>
       </c>
       <c r="R173" t="n">
-        <v>6962408</v>
+        <v>6962130</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18106,10 +18105,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128109121</v>
+        <v>128110985</v>
       </c>
       <c r="B174" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18134,21 +18133,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+      <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>533651</v>
+        <v>533652</v>
       </c>
       <c r="R174" t="n">
-        <v>6962130</v>
+        <v>6962550</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18181,6 +18176,11 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18207,10 +18207,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128110985</v>
+        <v>128110813</v>
       </c>
       <c r="B175" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18242,10 +18242,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>533652</v>
+        <v>533507</v>
       </c>
       <c r="R175" t="n">
-        <v>6962550</v>
+        <v>6962168</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18282,7 +18282,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>80 ex</t>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18309,32 +18309,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128110977</v>
+        <v>128110799</v>
       </c>
       <c r="B176" t="n">
-        <v>98502</v>
+        <v>80132</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18344,10 +18344,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>534040</v>
+        <v>533724</v>
       </c>
       <c r="R176" t="n">
-        <v>6962718</v>
+        <v>6962625</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18406,32 +18406,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128110799</v>
+        <v>128110787</v>
       </c>
       <c r="B177" t="n">
-        <v>80132</v>
+        <v>80160</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18441,10 +18441,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>533724</v>
+        <v>533785</v>
       </c>
       <c r="R177" t="n">
-        <v>6962625</v>
+        <v>6962326</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18503,32 +18503,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128110787</v>
+        <v>128101075</v>
       </c>
       <c r="B178" t="n">
-        <v>80160</v>
+        <v>80132</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18538,10 +18538,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>533785</v>
+        <v>533392</v>
       </c>
       <c r="R178" t="n">
-        <v>6962326</v>
+        <v>6962343</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18600,32 +18600,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128101075</v>
+        <v>128110835</v>
       </c>
       <c r="B179" t="n">
-        <v>80132</v>
+        <v>98386</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>533392</v>
+        <v>533748</v>
       </c>
       <c r="R179" t="n">
-        <v>6962343</v>
+        <v>6962431</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18697,50 +18697,45 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128108439</v>
+        <v>128110977</v>
       </c>
       <c r="B180" t="n">
-        <v>57672</v>
+        <v>98503</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>533711</v>
+        <v>534040</v>
       </c>
       <c r="R180" t="n">
-        <v>6962283</v>
+        <v>6962718</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18773,11 +18768,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18804,50 +18794,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128100413</v>
+        <v>128110828</v>
       </c>
       <c r="B181" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>533545</v>
+        <v>533365</v>
       </c>
       <c r="R181" t="n">
-        <v>6962372</v>
+        <v>6962304</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18884,7 +18869,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18911,50 +18896,49 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128101939</v>
+        <v>128107826</v>
       </c>
       <c r="B182" t="n">
-        <v>57672</v>
+        <v>98469</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>533638</v>
+        <v>533723</v>
       </c>
       <c r="R182" t="n">
-        <v>6962346</v>
+        <v>6962360</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18987,11 +18971,6 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19018,10 +18997,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128110828</v>
+        <v>128110817</v>
       </c>
       <c r="B183" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19053,10 +19032,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>533365</v>
+        <v>533728</v>
       </c>
       <c r="R183" t="n">
-        <v>6962304</v>
+        <v>6962346</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19093,7 +19072,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19120,37 +19099,38 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128107826</v>
+        <v>128108439</v>
       </c>
       <c r="B184" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P184" t="inlineStr">
@@ -19159,10 +19139,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>533723</v>
+        <v>533711</v>
       </c>
       <c r="R184" t="n">
-        <v>6962360</v>
+        <v>6962283</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19195,6 +19175,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19221,42 +19206,47 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128110817</v>
+        <v>128101939</v>
       </c>
       <c r="B185" t="n">
-        <v>98468</v>
+        <v>57672</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>533728</v>
+        <v>533638</v>
       </c>
       <c r="R185" t="n">
         <v>6962346</v>
@@ -19296,7 +19286,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>40 stycken i blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19323,45 +19313,50 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128110835</v>
+        <v>128100413</v>
       </c>
       <c r="B186" t="n">
-        <v>98385</v>
+        <v>57672</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>533748</v>
+        <v>533545</v>
       </c>
       <c r="R186" t="n">
-        <v>6962431</v>
+        <v>6962372</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19394,6 +19389,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD186" t="b">

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY186"/>
+  <dimension ref="A1:AY189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1311,50 +1311,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128108619</v>
+        <v>128108655</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533675</v>
+        <v>533673</v>
       </c>
       <c r="R8" t="n">
-        <v>6962244</v>
+        <v>6962211</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,11 +1382,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,7 +1408,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128110972</v>
+        <v>128108619</v>
       </c>
       <c r="B9" t="n">
         <v>57672</v>
@@ -1447,16 +1437,21 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533997</v>
+        <v>533675</v>
       </c>
       <c r="R9" t="n">
-        <v>6962746</v>
+        <v>6962244</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,7 +1488,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1520,7 +1515,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128101860</v>
+        <v>128110972</v>
       </c>
       <c r="B10" t="n">
         <v>57672</v>
@@ -1549,21 +1544,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533601</v>
+        <v>533997</v>
       </c>
       <c r="R10" t="n">
-        <v>6962344</v>
+        <v>6962746</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1600,7 +1590,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1627,10 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128109460</v>
+        <v>128101860</v>
       </c>
       <c r="B11" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1638,34 +1628,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533498</v>
+        <v>533601</v>
       </c>
       <c r="R11" t="n">
-        <v>6962158</v>
+        <v>6962344</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,6 +1693,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,45 +1724,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128108655</v>
+        <v>128109460</v>
       </c>
       <c r="B12" t="n">
-        <v>92641</v>
+        <v>80132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533673</v>
+        <v>533498</v>
       </c>
       <c r="R12" t="n">
-        <v>6962211</v>
+        <v>6962158</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1824,7 +1824,7 @@
         <v>128110802</v>
       </c>
       <c r="B13" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>128100827</v>
       </c>
       <c r="B14" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,50 +2024,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128108700</v>
+        <v>128101567</v>
       </c>
       <c r="B15" t="n">
-        <v>57672</v>
+        <v>80036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533674</v>
+        <v>533494</v>
       </c>
       <c r="R15" t="n">
-        <v>6962199</v>
+        <v>6962425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2100,11 +2095,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,7 +2121,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128109367</v>
+        <v>128108700</v>
       </c>
       <c r="B16" t="n">
         <v>57672</v>
@@ -2167,14 +2157,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533550</v>
+        <v>533674</v>
       </c>
       <c r="R16" t="n">
-        <v>6962157</v>
+        <v>6962199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2238,45 +2228,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128110833</v>
+        <v>128109367</v>
       </c>
       <c r="B17" t="n">
-        <v>98386</v>
+        <v>57672</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533768</v>
+        <v>533550</v>
       </c>
       <c r="R17" t="n">
-        <v>6962318</v>
+        <v>6962157</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2309,6 +2304,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,49 +2335,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128100321</v>
+        <v>128110833</v>
       </c>
       <c r="B18" t="n">
-        <v>98469</v>
+        <v>98387</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533537</v>
+        <v>533768</v>
       </c>
       <c r="R18" t="n">
-        <v>6962358</v>
+        <v>6962318</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2436,10 +2432,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128100131</v>
+        <v>128100321</v>
       </c>
       <c r="B19" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2466,7 +2462,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2475,10 +2471,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533496</v>
+        <v>533537</v>
       </c>
       <c r="R19" t="n">
-        <v>6962335</v>
+        <v>6962358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,10 +2533,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128110818</v>
+        <v>128100131</v>
       </c>
       <c r="B20" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2565,17 +2561,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533766</v>
+        <v>533496</v>
       </c>
       <c r="R20" t="n">
-        <v>6962317</v>
+        <v>6962335</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2608,11 +2608,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>10stycken</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2639,32 +2634,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128101567</v>
+        <v>128110818</v>
       </c>
       <c r="B21" t="n">
-        <v>80036</v>
+        <v>98470</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2674,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533494</v>
+        <v>533766</v>
       </c>
       <c r="R21" t="n">
-        <v>6962425</v>
+        <v>6962317</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,6 +2705,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>10stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2833,32 +2833,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128110771</v>
+        <v>128110832</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2868,10 +2868,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533583</v>
+        <v>533652</v>
       </c>
       <c r="R23" t="n">
-        <v>6962697</v>
+        <v>6962264</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2904,11 +2904,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2935,7 +2930,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128109293</v>
+        <v>128099395</v>
       </c>
       <c r="B24" t="n">
         <v>57672</v>
@@ -2971,14 +2966,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533638</v>
+        <v>533356</v>
       </c>
       <c r="R24" t="n">
-        <v>6962157</v>
+        <v>6962190</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3015,7 +3010,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3042,32 +3037,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128110832</v>
+        <v>128110771</v>
       </c>
       <c r="B25" t="n">
-        <v>98386</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3077,10 +3072,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533652</v>
+        <v>533583</v>
       </c>
       <c r="R25" t="n">
-        <v>6962264</v>
+        <v>6962697</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3113,6 +3108,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3139,49 +3139,50 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128101601</v>
+        <v>128109293</v>
       </c>
       <c r="B26" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533496</v>
+        <v>533638</v>
       </c>
       <c r="R26" t="n">
-        <v>6962407</v>
+        <v>6962157</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,6 +3215,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3240,10 +3246,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128108218</v>
+        <v>128101601</v>
       </c>
       <c r="B27" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3270,19 +3276,19 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533789</v>
+        <v>533496</v>
       </c>
       <c r="R27" t="n">
-        <v>6962263</v>
+        <v>6962407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3341,50 +3347,49 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128099395</v>
+        <v>128108218</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533356</v>
+        <v>533789</v>
       </c>
       <c r="R28" t="n">
-        <v>6962190</v>
+        <v>6962263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3417,11 +3422,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3451,7 +3451,7 @@
         <v>128099830</v>
       </c>
       <c r="B29" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3669,7 +3669,7 @@
         <v>128110780</v>
       </c>
       <c r="B31" t="n">
-        <v>91123</v>
+        <v>91124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3763,32 +3763,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128110790</v>
+        <v>128110803</v>
       </c>
       <c r="B32" t="n">
-        <v>98503</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533822</v>
+        <v>533524</v>
       </c>
       <c r="R32" t="n">
-        <v>6962344</v>
+        <v>6962153</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,10 +3865,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128110803</v>
+        <v>128110981</v>
       </c>
       <c r="B33" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533524</v>
+        <v>533689</v>
       </c>
       <c r="R33" t="n">
-        <v>6962153</v>
+        <v>6962405</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3967,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128110981</v>
+        <v>128109875</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3995,17 +3995,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533689</v>
+        <v>533436</v>
       </c>
       <c r="R34" t="n">
-        <v>6962405</v>
+        <v>6962158</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,11 +4042,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4069,10 +4068,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128109875</v>
+        <v>128102143</v>
       </c>
       <c r="B35" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4099,7 +4098,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4108,10 +4107,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533436</v>
+        <v>533615</v>
       </c>
       <c r="R35" t="n">
-        <v>6962158</v>
+        <v>6962423</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4170,10 +4169,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128102143</v>
+        <v>128100230</v>
       </c>
       <c r="B36" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4200,7 +4199,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4209,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533615</v>
+        <v>533506</v>
       </c>
       <c r="R36" t="n">
-        <v>6962423</v>
+        <v>6962358</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4271,49 +4270,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128100230</v>
+        <v>128110790</v>
       </c>
       <c r="B37" t="n">
-        <v>98469</v>
+        <v>98504</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533506</v>
+        <v>533822</v>
       </c>
       <c r="R37" t="n">
-        <v>6962358</v>
+        <v>6962344</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4346,6 +4341,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128099282</v>
+        <v>128108150</v>
       </c>
       <c r="B38" t="n">
-        <v>80160</v>
+        <v>80161</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4383,34 +4383,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533452</v>
+        <v>533800</v>
       </c>
       <c r="R38" t="n">
-        <v>6962232</v>
+        <v>6962306</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,45 +4469,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128108150</v>
+        <v>128110968</v>
       </c>
       <c r="B39" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533800</v>
+        <v>533634</v>
       </c>
       <c r="R39" t="n">
-        <v>6962306</v>
+        <v>6962526</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4540,6 +4540,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4566,7 +4571,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128110968</v>
+        <v>128102724</v>
       </c>
       <c r="B40" t="n">
         <v>57672</v>
@@ -4595,16 +4600,21 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533634</v>
+        <v>533659</v>
       </c>
       <c r="R40" t="n">
-        <v>6962526</v>
+        <v>6962512</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4641,7 +4651,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>En födosökande individ</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4668,7 +4678,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128102724</v>
+        <v>128101831</v>
       </c>
       <c r="B41" t="n">
         <v>57672</v>
@@ -4699,7 +4709,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4708,10 +4718,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533659</v>
+        <v>533513</v>
       </c>
       <c r="R41" t="n">
-        <v>6962512</v>
+        <v>6962442</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4748,7 +4758,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4775,7 +4785,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128101831</v>
+        <v>128110767</v>
       </c>
       <c r="B42" t="n">
         <v>57672</v>
@@ -4804,21 +4814,16 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533513</v>
+        <v>533794</v>
       </c>
       <c r="R42" t="n">
-        <v>6962442</v>
+        <v>6962411</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4855,7 +4860,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4882,32 +4887,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128110767</v>
+        <v>128110824</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4917,10 +4922,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533794</v>
+        <v>533712</v>
       </c>
       <c r="R43" t="n">
-        <v>6962411</v>
+        <v>6962628</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4957,7 +4962,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4987,7 +4992,7 @@
         <v>128110978</v>
       </c>
       <c r="B44" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5084,7 +5089,7 @@
         <v>128110788</v>
       </c>
       <c r="B45" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5181,7 +5186,7 @@
         <v>128110836</v>
       </c>
       <c r="B46" t="n">
-        <v>98386</v>
+        <v>98387</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5275,32 +5280,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128110824</v>
+        <v>128099282</v>
       </c>
       <c r="B47" t="n">
-        <v>98469</v>
+        <v>80160</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5310,10 +5315,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533712</v>
+        <v>533452</v>
       </c>
       <c r="R47" t="n">
-        <v>6962628</v>
+        <v>6962232</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5346,11 +5351,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5377,37 +5377,42 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128099088</v>
+        <v>128103304</v>
       </c>
       <c r="B48" t="n">
-        <v>98469</v>
+        <v>91124</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5416,10 +5421,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533425</v>
+        <v>533594</v>
       </c>
       <c r="R48" t="n">
-        <v>6962182</v>
+        <v>6962541</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5478,45 +5483,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128107546</v>
+        <v>128101106</v>
       </c>
       <c r="B49" t="n">
-        <v>80133</v>
+        <v>80098</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2081</v>
+        <v>229748</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533648</v>
+        <v>533425</v>
       </c>
       <c r="R49" t="n">
-        <v>6962374</v>
+        <v>6962304</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5575,42 +5580,37 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128103304</v>
+        <v>128099088</v>
       </c>
       <c r="B50" t="n">
-        <v>91123</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -5619,10 +5619,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533594</v>
+        <v>533425</v>
       </c>
       <c r="R50" t="n">
-        <v>6962541</v>
+        <v>6962182</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5684,7 +5684,7 @@
         <v>128101702</v>
       </c>
       <c r="B51" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5778,10 +5778,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128110766</v>
+        <v>128107546</v>
       </c>
       <c r="B52" t="n">
-        <v>57672</v>
+        <v>80133</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5789,34 +5789,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533586</v>
+        <v>533648</v>
       </c>
       <c r="R52" t="n">
-        <v>6962139</v>
+        <v>6962374</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5849,11 +5849,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5880,7 +5875,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128110970</v>
+        <v>128110766</v>
       </c>
       <c r="B53" t="n">
         <v>57672</v>
@@ -5915,10 +5910,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>534050</v>
+        <v>533586</v>
       </c>
       <c r="R53" t="n">
-        <v>6962743</v>
+        <v>6962139</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5955,7 +5950,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5982,32 +5977,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128110812</v>
+        <v>128110970</v>
       </c>
       <c r="B54" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6017,10 +6012,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533715</v>
+        <v>534050</v>
       </c>
       <c r="R54" t="n">
-        <v>6962610</v>
+        <v>6962743</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6057,7 +6052,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>60 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6084,10 +6079,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128110826</v>
+        <v>128110812</v>
       </c>
       <c r="B55" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6119,10 +6114,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533579</v>
+        <v>533715</v>
       </c>
       <c r="R55" t="n">
-        <v>6962663</v>
+        <v>6962610</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6159,7 +6154,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6186,45 +6181,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128108922</v>
+        <v>128110826</v>
       </c>
       <c r="B56" t="n">
-        <v>105507</v>
+        <v>98470</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533671</v>
+        <v>533579</v>
       </c>
       <c r="R56" t="n">
-        <v>6962142</v>
+        <v>6962663</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6257,6 +6252,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6283,45 +6283,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128110804</v>
+        <v>128108922</v>
       </c>
       <c r="B57" t="n">
-        <v>98469</v>
+        <v>105508</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533532</v>
+        <v>533671</v>
       </c>
       <c r="R57" t="n">
-        <v>6962156</v>
+        <v>6962142</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6354,11 +6354,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6385,10 +6380,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128110990</v>
+        <v>128110804</v>
       </c>
       <c r="B58" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6420,10 +6415,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533873</v>
+        <v>533532</v>
       </c>
       <c r="R58" t="n">
-        <v>6962782</v>
+        <v>6962156</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6460,7 +6455,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6487,10 +6482,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128110814</v>
+        <v>128110990</v>
       </c>
       <c r="B59" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6522,10 +6517,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533650</v>
+        <v>533873</v>
       </c>
       <c r="R59" t="n">
-        <v>6962134</v>
+        <v>6962782</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6562,7 +6557,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>50 stycken ( några har blommat).</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6589,32 +6584,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128101106</v>
+        <v>128110814</v>
       </c>
       <c r="B60" t="n">
-        <v>80098</v>
+        <v>98470</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6624,10 +6619,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533425</v>
+        <v>533650</v>
       </c>
       <c r="R60" t="n">
-        <v>6962304</v>
+        <v>6962134</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6660,6 +6655,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>50 stycken ( några har blommat).</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6783,45 +6783,54 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128099875</v>
+        <v>128099522</v>
       </c>
       <c r="B62" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533445</v>
+        <v>533349</v>
       </c>
       <c r="R62" t="n">
-        <v>6962324</v>
+        <v>6962197</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6880,50 +6889,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128099885</v>
+        <v>128099099</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>105508</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533361</v>
+        <v>533416</v>
       </c>
       <c r="R63" t="n">
-        <v>6962247</v>
+        <v>6962179</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6956,11 +6960,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6987,32 +6986,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128099099</v>
+        <v>128100636</v>
       </c>
       <c r="B64" t="n">
-        <v>105507</v>
+        <v>80132</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7022,10 +7021,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533416</v>
+        <v>533452</v>
       </c>
       <c r="R64" t="n">
-        <v>6962179</v>
+        <v>6962350</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7084,10 +7083,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128099522</v>
+        <v>128110827</v>
       </c>
       <c r="B65" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7112,26 +7111,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533349</v>
+        <v>533614</v>
       </c>
       <c r="R65" t="n">
-        <v>6962197</v>
+        <v>6962554</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7164,6 +7154,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7190,45 +7185,49 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128110971</v>
+        <v>128100184</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>534036</v>
+        <v>533509</v>
       </c>
       <c r="R66" t="n">
-        <v>6962734</v>
+        <v>6962336</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7261,11 +7260,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7292,38 +7286,37 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128108477</v>
+        <v>128103587</v>
       </c>
       <c r="B67" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>120</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7332,10 +7325,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533710</v>
+        <v>533650</v>
       </c>
       <c r="R67" t="n">
-        <v>6962294</v>
+        <v>6962600</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7368,11 +7361,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7399,32 +7387,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128110827</v>
+        <v>128110971</v>
       </c>
       <c r="B68" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7434,10 +7422,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533614</v>
+        <v>534036</v>
       </c>
       <c r="R68" t="n">
-        <v>6962554</v>
+        <v>6962734</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7474,7 +7462,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7501,49 +7489,50 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128100184</v>
+        <v>128108477</v>
       </c>
       <c r="B69" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533509</v>
+        <v>533710</v>
       </c>
       <c r="R69" t="n">
-        <v>6962336</v>
+        <v>6962294</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7576,6 +7565,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7602,49 +7596,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128103587</v>
+        <v>128099875</v>
       </c>
       <c r="B70" t="n">
-        <v>98469</v>
+        <v>80132</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533650</v>
+        <v>533445</v>
       </c>
       <c r="R70" t="n">
-        <v>6962600</v>
+        <v>6962324</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7703,10 +7693,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128100636</v>
+        <v>128099885</v>
       </c>
       <c r="B71" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7714,34 +7704,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533452</v>
+        <v>533361</v>
       </c>
       <c r="R71" t="n">
-        <v>6962350</v>
+        <v>6962247</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7774,6 +7769,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7800,37 +7800,38 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128101024</v>
+        <v>128099712</v>
       </c>
       <c r="B72" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -7839,10 +7840,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533375</v>
+        <v>533451</v>
       </c>
       <c r="R72" t="n">
-        <v>6962293</v>
+        <v>6962307</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7875,6 +7876,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7901,32 +7907,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128099857</v>
+        <v>128110769</v>
       </c>
       <c r="B73" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7936,10 +7942,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533445</v>
+        <v>533841</v>
       </c>
       <c r="R73" t="n">
-        <v>6962324</v>
+        <v>6962363</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7972,6 +7978,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack) spår</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7998,7 +8009,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128099712</v>
+        <v>128110775</v>
       </c>
       <c r="B74" t="n">
         <v>57672</v>
@@ -8027,21 +8038,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533451</v>
+        <v>533564</v>
       </c>
       <c r="R74" t="n">
-        <v>6962307</v>
+        <v>6962537</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8078,7 +8084,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska och äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8105,7 +8111,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128110769</v>
+        <v>128108355</v>
       </c>
       <c r="B75" t="n">
         <v>57672</v>
@@ -8134,16 +8140,21 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533841</v>
+        <v>533768</v>
       </c>
       <c r="R75" t="n">
-        <v>6962363</v>
+        <v>6962269</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8180,7 +8191,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack) spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8207,7 +8218,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128110775</v>
+        <v>128101911</v>
       </c>
       <c r="B76" t="n">
         <v>57672</v>
@@ -8236,16 +8247,21 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533564</v>
+        <v>533510</v>
       </c>
       <c r="R76" t="n">
-        <v>6962537</v>
+        <v>6962462</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8282,7 +8298,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på Tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8309,50 +8325,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128108355</v>
+        <v>128101024</v>
       </c>
       <c r="B77" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533768</v>
+        <v>533375</v>
       </c>
       <c r="R77" t="n">
-        <v>6962269</v>
+        <v>6962293</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8385,11 +8400,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8416,50 +8426,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128101911</v>
+        <v>128110811</v>
       </c>
       <c r="B78" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533510</v>
+        <v>533706</v>
       </c>
       <c r="R78" t="n">
-        <v>6962462</v>
+        <v>6962596</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8496,7 +8501,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>24 stycken</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8523,32 +8528,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128110811</v>
+        <v>128099857</v>
       </c>
       <c r="B79" t="n">
-        <v>98469</v>
+        <v>80161</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8558,10 +8563,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533706</v>
+        <v>533445</v>
       </c>
       <c r="R79" t="n">
-        <v>6962596</v>
+        <v>6962324</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8594,11 +8599,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>24 stycken</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8628,7 +8628,7 @@
         <v>128110779</v>
       </c>
       <c r="B80" t="n">
-        <v>91123</v>
+        <v>91124</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8722,10 +8722,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128099905</v>
+        <v>128102006</v>
       </c>
       <c r="B81" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8733,39 +8733,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533445</v>
+        <v>533510</v>
       </c>
       <c r="R81" t="n">
-        <v>6962324</v>
+        <v>6962462</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8798,11 +8793,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8829,10 +8819,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128102006</v>
+        <v>128099905</v>
       </c>
       <c r="B82" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8840,34 +8830,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533510</v>
+        <v>533445</v>
       </c>
       <c r="R82" t="n">
-        <v>6962462</v>
+        <v>6962324</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8900,6 +8895,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9242,45 +9242,49 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128110976</v>
+        <v>128101261</v>
       </c>
       <c r="B86" t="n">
-        <v>98503</v>
+        <v>98470</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533868</v>
+        <v>533424</v>
       </c>
       <c r="R86" t="n">
-        <v>6962692</v>
+        <v>6962357</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9313,11 +9317,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9344,10 +9343,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128101261</v>
+        <v>128110982</v>
       </c>
       <c r="B87" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9372,21 +9371,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533424</v>
+        <v>533681</v>
       </c>
       <c r="R87" t="n">
-        <v>6962357</v>
+        <v>6962434</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9419,6 +9414,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>23 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9445,10 +9445,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128110982</v>
+        <v>128110810</v>
       </c>
       <c r="B88" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9480,10 +9480,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533681</v>
+        <v>533645</v>
       </c>
       <c r="R88" t="n">
-        <v>6962434</v>
+        <v>6962593</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9516,11 +9516,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>23 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9547,32 +9542,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128110810</v>
+        <v>128110976</v>
       </c>
       <c r="B89" t="n">
-        <v>98469</v>
+        <v>98504</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9582,10 +9577,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533645</v>
+        <v>533868</v>
       </c>
       <c r="R89" t="n">
-        <v>6962593</v>
+        <v>6962692</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9618,6 +9613,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9846,7 +9846,7 @@
         <v>128110989</v>
       </c>
       <c r="B92" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>128110806</v>
       </c>
       <c r="B93" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10047,10 +10047,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128110974</v>
+        <v>128099401</v>
       </c>
       <c r="B94" t="n">
-        <v>80161</v>
+        <v>92642</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10058,34 +10058,43 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533937</v>
+        <v>533356</v>
       </c>
       <c r="R94" t="n">
-        <v>6962685</v>
+        <v>6962190</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10144,50 +10153,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128102878</v>
+        <v>128110974</v>
       </c>
       <c r="B95" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533665</v>
+        <v>533937</v>
       </c>
       <c r="R95" t="n">
-        <v>6962515</v>
+        <v>6962685</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10220,11 +10224,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10251,50 +10250,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128100043</v>
+        <v>128110816</v>
       </c>
       <c r="B96" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533496</v>
+        <v>533696</v>
       </c>
       <c r="R96" t="n">
-        <v>6962335</v>
+        <v>6962294</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10331,7 +10325,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10358,45 +10352,49 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128110834</v>
+        <v>128102067</v>
       </c>
       <c r="B97" t="n">
-        <v>98386</v>
+        <v>98470</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533779</v>
+        <v>533510</v>
       </c>
       <c r="R97" t="n">
-        <v>6962298</v>
+        <v>6962462</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10455,10 +10453,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128099401</v>
+        <v>128110834</v>
       </c>
       <c r="B98" t="n">
-        <v>92641</v>
+        <v>98387</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10466,43 +10464,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>533356</v>
+        <v>533779</v>
       </c>
       <c r="R98" t="n">
-        <v>6962190</v>
+        <v>6962298</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10668,45 +10657,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128110816</v>
+        <v>128102878</v>
       </c>
       <c r="B100" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>533696</v>
+        <v>533665</v>
       </c>
       <c r="R100" t="n">
-        <v>6962294</v>
+        <v>6962515</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10743,7 +10737,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>20 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10770,37 +10764,38 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128102067</v>
+        <v>128100043</v>
       </c>
       <c r="B101" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -10809,10 +10804,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533510</v>
+        <v>533496</v>
       </c>
       <c r="R101" t="n">
-        <v>6962462</v>
+        <v>6962335</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10845,6 +10840,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10871,32 +10871,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128110829</v>
+        <v>128101073</v>
       </c>
       <c r="B102" t="n">
-        <v>56855</v>
+        <v>80168</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10906,10 +10906,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>533606</v>
+        <v>533385</v>
       </c>
       <c r="R102" t="n">
-        <v>6962582</v>
+        <v>6962288</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10942,11 +10942,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10973,32 +10968,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128110792</v>
+        <v>128110829</v>
       </c>
       <c r="B103" t="n">
-        <v>98503</v>
+        <v>56855</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>219874</v>
+        <v>102612</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11008,10 +11003,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>533719</v>
+        <v>533606</v>
       </c>
       <c r="R103" t="n">
-        <v>6962615</v>
+        <v>6962582</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11048,7 +11043,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11078,7 +11073,7 @@
         <v>128110785</v>
       </c>
       <c r="B104" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11175,7 +11170,7 @@
         <v>128110807</v>
       </c>
       <c r="B105" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11277,7 +11272,7 @@
         <v>128110983</v>
       </c>
       <c r="B106" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11376,10 +11371,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128101073</v>
+        <v>128110792</v>
       </c>
       <c r="B107" t="n">
-        <v>80168</v>
+        <v>98504</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11387,21 +11382,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>219874</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11411,10 +11406,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533385</v>
+        <v>533719</v>
       </c>
       <c r="R107" t="n">
-        <v>6962288</v>
+        <v>6962615</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11447,6 +11442,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11476,7 +11476,7 @@
         <v>128099487</v>
       </c>
       <c r="B108" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11574,10 +11574,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128101331</v>
+        <v>128110783</v>
       </c>
       <c r="B109" t="n">
-        <v>80167</v>
+        <v>91124</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11585,21 +11585,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6463</v>
+        <v>3215</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533424</v>
+        <v>533599</v>
       </c>
       <c r="R109" t="n">
-        <v>6962357</v>
+        <v>6962553</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11671,10 +11671,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128108395</v>
+        <v>128108378</v>
       </c>
       <c r="B110" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11682,34 +11682,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533735</v>
+        <v>533750</v>
       </c>
       <c r="R110" t="n">
-        <v>6962274</v>
+        <v>6962259</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11742,6 +11747,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11768,45 +11778,50 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128110783</v>
+        <v>128100457</v>
       </c>
       <c r="B111" t="n">
-        <v>91123</v>
+        <v>57672</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>533599</v>
+        <v>533556</v>
       </c>
       <c r="R111" t="n">
-        <v>6962553</v>
+        <v>6962363</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11839,6 +11854,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11865,50 +11885,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128108378</v>
+        <v>128110991</v>
       </c>
       <c r="B112" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>533750</v>
+        <v>533717</v>
       </c>
       <c r="R112" t="n">
-        <v>6962259</v>
+        <v>6962645</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11945,7 +11960,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11972,50 +11987,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128100457</v>
+        <v>128103993</v>
       </c>
       <c r="B113" t="n">
-        <v>57672</v>
+        <v>105508</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533556</v>
+        <v>533664</v>
       </c>
       <c r="R113" t="n">
-        <v>6962363</v>
+        <v>6962650</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12048,11 +12058,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12079,32 +12084,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128110776</v>
+        <v>128110987</v>
       </c>
       <c r="B114" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12114,10 +12119,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533719</v>
+        <v>533999</v>
       </c>
       <c r="R114" t="n">
-        <v>6962615</v>
+        <v>6962664</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12154,7 +12159,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12181,45 +12186,49 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128110838</v>
+        <v>128103044</v>
       </c>
       <c r="B115" t="n">
-        <v>98386</v>
+        <v>98470</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533708</v>
+        <v>533627</v>
       </c>
       <c r="R115" t="n">
-        <v>6962624</v>
+        <v>6962544</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12252,11 +12261,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12283,32 +12287,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128110793</v>
+        <v>128110819</v>
       </c>
       <c r="B116" t="n">
-        <v>98503</v>
+        <v>98470</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12318,10 +12322,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533693</v>
+        <v>533834</v>
       </c>
       <c r="R116" t="n">
-        <v>6962647</v>
+        <v>6962298</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12358,7 +12362,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12385,10 +12389,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128110794</v>
+        <v>128108028</v>
       </c>
       <c r="B117" t="n">
-        <v>98503</v>
+        <v>97353</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12396,34 +12400,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219874</v>
+        <v>221941</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533608</v>
+        <v>533802</v>
       </c>
       <c r="R117" t="n">
-        <v>6962612</v>
+        <v>6962332</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12456,11 +12460,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12487,10 +12486,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128108028</v>
+        <v>128101331</v>
       </c>
       <c r="B118" t="n">
-        <v>97352</v>
+        <v>80167</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12498,34 +12497,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>221941</v>
+        <v>6463</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533802</v>
+        <v>533424</v>
       </c>
       <c r="R118" t="n">
-        <v>6962332</v>
+        <v>6962357</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12584,45 +12583,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128110991</v>
+        <v>128108395</v>
       </c>
       <c r="B119" t="n">
-        <v>98469</v>
+        <v>80132</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533717</v>
+        <v>533735</v>
       </c>
       <c r="R119" t="n">
-        <v>6962645</v>
+        <v>6962274</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12655,11 +12654,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12686,45 +12680,45 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103993</v>
+        <v>128110776</v>
       </c>
       <c r="B120" t="n">
-        <v>105507</v>
+        <v>57832</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533664</v>
+        <v>533719</v>
       </c>
       <c r="R120" t="n">
-        <v>6962650</v>
+        <v>6962615</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12757,6 +12751,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12783,32 +12782,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128110987</v>
+        <v>128110838</v>
       </c>
       <c r="B121" t="n">
-        <v>98469</v>
+        <v>98387</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12818,10 +12817,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533999</v>
+        <v>533708</v>
       </c>
       <c r="R121" t="n">
-        <v>6962664</v>
+        <v>6962624</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12858,7 +12857,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12885,49 +12884,45 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128103044</v>
+        <v>128110793</v>
       </c>
       <c r="B122" t="n">
-        <v>98469</v>
+        <v>98504</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533627</v>
+        <v>533693</v>
       </c>
       <c r="R122" t="n">
-        <v>6962544</v>
+        <v>6962647</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12960,6 +12955,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12986,32 +12986,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128110819</v>
+        <v>128110794</v>
       </c>
       <c r="B123" t="n">
-        <v>98469</v>
+        <v>98504</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13021,10 +13021,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>533834</v>
+        <v>533608</v>
       </c>
       <c r="R123" t="n">
-        <v>6962298</v>
+        <v>6962612</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13061,7 +13061,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>10 stycken kan finnas fler runt omkring</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13088,45 +13088,50 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128099811</v>
+        <v>128099239</v>
       </c>
       <c r="B124" t="n">
-        <v>105507</v>
+        <v>57672</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>533451</v>
+        <v>533422</v>
       </c>
       <c r="R124" t="n">
-        <v>6962307</v>
+        <v>6962229</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13159,6 +13164,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13185,10 +13195,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128109488</v>
+        <v>128099811</v>
       </c>
       <c r="B125" t="n">
-        <v>80161</v>
+        <v>105508</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13196,21 +13206,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>221144</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13220,10 +13230,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>533498</v>
+        <v>533451</v>
       </c>
       <c r="R125" t="n">
-        <v>6962158</v>
+        <v>6962307</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13282,10 +13292,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128109254</v>
+        <v>128109488</v>
       </c>
       <c r="B126" t="n">
-        <v>80160</v>
+        <v>80161</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13293,34 +13303,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>533652</v>
+        <v>533498</v>
       </c>
       <c r="R126" t="n">
-        <v>6962140</v>
+        <v>6962158</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13379,45 +13389,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128110825</v>
+        <v>128109254</v>
       </c>
       <c r="B127" t="n">
-        <v>98469</v>
+        <v>80160</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>533583</v>
+        <v>533652</v>
       </c>
       <c r="R127" t="n">
-        <v>6962689</v>
+        <v>6962140</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13450,11 +13460,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>84stycken</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13481,10 +13486,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128099239</v>
+        <v>128100396</v>
       </c>
       <c r="B128" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13492,27 +13497,27 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -13521,10 +13526,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>533422</v>
+        <v>533537</v>
       </c>
       <c r="R128" t="n">
-        <v>6962229</v>
+        <v>6962358</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13557,11 +13562,6 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13588,50 +13588,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128100396</v>
+        <v>128110823</v>
       </c>
       <c r="B129" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>533537</v>
+        <v>533715</v>
       </c>
       <c r="R129" t="n">
-        <v>6962358</v>
+        <v>6962631</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13664,6 +13659,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13690,32 +13690,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128110789</v>
+        <v>128110825</v>
       </c>
       <c r="B130" t="n">
-        <v>98503</v>
+        <v>98470</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>533832</v>
+        <v>533583</v>
       </c>
       <c r="R130" t="n">
-        <v>6962310</v>
+        <v>6962689</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13761,6 +13761,11 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>84stycken</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13787,10 +13792,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128108119</v>
+        <v>128110789</v>
       </c>
       <c r="B131" t="n">
-        <v>98503</v>
+        <v>98504</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13818,14 +13823,14 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>533800</v>
+        <v>533832</v>
       </c>
       <c r="R131" t="n">
-        <v>6962306</v>
+        <v>6962310</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13884,45 +13889,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128110823</v>
+        <v>128108119</v>
       </c>
       <c r="B132" t="n">
-        <v>98469</v>
+        <v>98504</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>533715</v>
+        <v>533800</v>
       </c>
       <c r="R132" t="n">
-        <v>6962631</v>
+        <v>6962306</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13955,11 +13960,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13986,45 +13986,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128100350</v>
+        <v>128103617</v>
       </c>
       <c r="B133" t="n">
-        <v>97346</v>
+        <v>91352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>533545</v>
+        <v>533637</v>
       </c>
       <c r="R133" t="n">
-        <v>6962339</v>
+        <v>6962600</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14086,7 +14086,7 @@
         <v>128110830</v>
       </c>
       <c r="B134" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>128110808</v>
       </c>
       <c r="B135" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14285,7 +14285,7 @@
         <v>128107880</v>
       </c>
       <c r="B136" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>128110809</v>
       </c>
       <c r="B137" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14488,7 +14488,7 @@
         <v>128110984</v>
       </c>
       <c r="B138" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14587,45 +14587,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103617</v>
+        <v>128100350</v>
       </c>
       <c r="B139" t="n">
-        <v>91351</v>
+        <v>97347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>533637</v>
+        <v>533545</v>
       </c>
       <c r="R139" t="n">
-        <v>6962600</v>
+        <v>6962339</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14684,10 +14684,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128099760</v>
+        <v>128110801</v>
       </c>
       <c r="B140" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14712,21 +14712,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>533451</v>
+        <v>533442</v>
       </c>
       <c r="R140" t="n">
-        <v>6962307</v>
+        <v>6962166</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14759,6 +14755,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>4 stycken  ( finns möjligtvis fler I blåbärsriset)</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14785,45 +14786,45 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128102955</v>
+        <v>128110821</v>
       </c>
       <c r="B141" t="n">
-        <v>78787</v>
+        <v>98470</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>533659</v>
+        <v>533705</v>
       </c>
       <c r="R141" t="n">
-        <v>6962538</v>
+        <v>6962430</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14856,6 +14857,11 @@
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>7 stycken</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14882,50 +14888,45 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128102524</v>
+        <v>128110988</v>
       </c>
       <c r="B142" t="n">
-        <v>56855</v>
+        <v>98470</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>533640</v>
+        <v>533959</v>
       </c>
       <c r="R142" t="n">
-        <v>6962482</v>
+        <v>6962738</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14958,6 +14959,11 @@
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14984,50 +14990,49 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128108442</v>
+        <v>128099760</v>
       </c>
       <c r="B143" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>533714</v>
+        <v>533451</v>
       </c>
       <c r="R143" t="n">
-        <v>6962273</v>
+        <v>6962307</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15060,11 +15065,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15091,10 +15091,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128109413</v>
+        <v>128102955</v>
       </c>
       <c r="B144" t="n">
-        <v>57672</v>
+        <v>78787</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15102,39 +15102,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>533532</v>
+        <v>533659</v>
       </c>
       <c r="R144" t="n">
-        <v>6962150</v>
+        <v>6962538</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15167,11 +15162,6 @@
       <c r="AA144" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15198,7 +15188,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128109827</v>
+        <v>128108442</v>
       </c>
       <c r="B145" t="n">
         <v>57672</v>
@@ -15234,14 +15224,14 @@
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>533421</v>
+        <v>533714</v>
       </c>
       <c r="R145" t="n">
-        <v>6962154</v>
+        <v>6962273</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15305,45 +15295,50 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128110801</v>
+        <v>128109413</v>
       </c>
       <c r="B146" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>533442</v>
+        <v>533532</v>
       </c>
       <c r="R146" t="n">
-        <v>6962166</v>
+        <v>6962150</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15380,7 +15375,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>4 stycken  ( finns möjligtvis fler I blåbärsriset)</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15407,45 +15402,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128110821</v>
+        <v>128109827</v>
       </c>
       <c r="B147" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>533705</v>
+        <v>533421</v>
       </c>
       <c r="R147" t="n">
-        <v>6962430</v>
+        <v>6962154</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>7 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15509,45 +15509,50 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128110988</v>
+        <v>128102524</v>
       </c>
       <c r="B148" t="n">
-        <v>98469</v>
+        <v>56855</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>533959</v>
+        <v>533640</v>
       </c>
       <c r="R148" t="n">
-        <v>6962738</v>
+        <v>6962482</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15580,11 +15585,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15611,54 +15611,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128099113</v>
+        <v>128102121</v>
       </c>
       <c r="B149" t="n">
-        <v>92641</v>
+        <v>57832</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>533396</v>
+        <v>533532</v>
       </c>
       <c r="R149" t="n">
-        <v>6962161</v>
+        <v>6962477</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15691,11 +15682,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15722,32 +15708,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128102121</v>
+        <v>128110831</v>
       </c>
       <c r="B150" t="n">
-        <v>57832</v>
+        <v>58531</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>103021</v>
+        <v>208249</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15757,10 +15743,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>533532</v>
+        <v>533728</v>
       </c>
       <c r="R150" t="n">
-        <v>6962477</v>
+        <v>6962422</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15822,7 +15808,7 @@
         <v>128101444</v>
       </c>
       <c r="B151" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15923,7 +15909,7 @@
         <v>128110986</v>
       </c>
       <c r="B152" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16025,7 +16011,7 @@
         <v>128102104</v>
       </c>
       <c r="B153" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16119,10 +16105,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128110796</v>
+        <v>128110768</v>
       </c>
       <c r="B154" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16130,21 +16116,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16154,10 +16140,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>533655</v>
+        <v>533754</v>
       </c>
       <c r="R154" t="n">
-        <v>6962173</v>
+        <v>6962450</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16190,6 +16176,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16216,10 +16207,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128109763</v>
+        <v>128099113</v>
       </c>
       <c r="B155" t="n">
-        <v>80036</v>
+        <v>92642</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16227,34 +16218,43 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>533449</v>
+        <v>533396</v>
       </c>
       <c r="R155" t="n">
-        <v>6962147</v>
+        <v>6962161</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16287,6 +16287,11 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16313,10 +16318,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128110768</v>
+        <v>128110796</v>
       </c>
       <c r="B156" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -16324,21 +16329,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16348,10 +16353,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>533754</v>
+        <v>533655</v>
       </c>
       <c r="R156" t="n">
-        <v>6962450</v>
+        <v>6962173</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16384,11 +16389,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16415,10 +16415,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128110831</v>
+        <v>128109763</v>
       </c>
       <c r="B157" t="n">
-        <v>58531</v>
+        <v>80036</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16426,21 +16426,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>208249</v>
+        <v>6456</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16450,10 +16450,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>533728</v>
+        <v>533449</v>
       </c>
       <c r="R157" t="n">
-        <v>6962422</v>
+        <v>6962147</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16512,32 +16512,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128110967</v>
+        <v>128110777</v>
       </c>
       <c r="B158" t="n">
-        <v>57672</v>
+        <v>91124</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16547,10 +16547,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>533691</v>
+        <v>533841</v>
       </c>
       <c r="R158" t="n">
-        <v>6962407</v>
+        <v>6962306</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16583,11 +16583,6 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16614,10 +16609,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128110773</v>
+        <v>128110795</v>
       </c>
       <c r="B159" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16625,21 +16620,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16649,10 +16644,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>533604</v>
+        <v>533792</v>
       </c>
       <c r="R159" t="n">
-        <v>6962650</v>
+        <v>6962400</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16685,11 +16680,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16716,7 +16706,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128110774</v>
+        <v>128110967</v>
       </c>
       <c r="B160" t="n">
         <v>57672</v>
@@ -16751,10 +16741,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>533585</v>
+        <v>533691</v>
       </c>
       <c r="R160" t="n">
-        <v>6962612</v>
+        <v>6962407</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16791,7 +16781,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett på Tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16818,32 +16808,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128110837</v>
+        <v>128110773</v>
       </c>
       <c r="B161" t="n">
-        <v>98386</v>
+        <v>57672</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16853,10 +16843,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>533617</v>
+        <v>533604</v>
       </c>
       <c r="R161" t="n">
-        <v>6962560</v>
+        <v>6962650</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16889,6 +16879,11 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16915,32 +16910,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128110791</v>
+        <v>128110774</v>
       </c>
       <c r="B162" t="n">
-        <v>98503</v>
+        <v>57672</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16950,10 +16945,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>533658</v>
+        <v>533585</v>
       </c>
       <c r="R162" t="n">
-        <v>6962570</v>
+        <v>6962612</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16986,6 +16981,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17015,7 +17015,7 @@
         <v>128110805</v>
       </c>
       <c r="B163" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>128109586</v>
       </c>
       <c r="B164" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17215,32 +17215,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128110795</v>
+        <v>128110837</v>
       </c>
       <c r="B165" t="n">
-        <v>80132</v>
+        <v>98387</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17250,10 +17250,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>533792</v>
+        <v>533617</v>
       </c>
       <c r="R165" t="n">
-        <v>6962400</v>
+        <v>6962560</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17312,10 +17312,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128110777</v>
+        <v>128110791</v>
       </c>
       <c r="B166" t="n">
-        <v>91123</v>
+        <v>98504</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17323,21 +17323,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17347,10 +17347,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>533841</v>
+        <v>533658</v>
       </c>
       <c r="R166" t="n">
-        <v>6962306</v>
+        <v>6962570</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17409,32 +17409,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128101262</v>
+        <v>128110782</v>
       </c>
       <c r="B167" t="n">
-        <v>80132</v>
+        <v>91124</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17444,10 +17444,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>533424</v>
+        <v>533630</v>
       </c>
       <c r="R167" t="n">
-        <v>6962357</v>
+        <v>6962701</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17506,32 +17506,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128110797</v>
+        <v>128110781</v>
       </c>
       <c r="B168" t="n">
-        <v>80132</v>
+        <v>91124</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17541,10 +17541,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>533832</v>
+        <v>533700</v>
       </c>
       <c r="R168" t="n">
-        <v>6962351</v>
+        <v>6962581</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17603,32 +17603,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128110781</v>
+        <v>128101262</v>
       </c>
       <c r="B169" t="n">
-        <v>91123</v>
+        <v>80132</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>3215</v>
+        <v>6458</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17638,10 +17638,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>533700</v>
+        <v>533424</v>
       </c>
       <c r="R169" t="n">
-        <v>6962581</v>
+        <v>6962357</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17700,32 +17700,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128110782</v>
+        <v>128110797</v>
       </c>
       <c r="B170" t="n">
-        <v>91123</v>
+        <v>80132</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3215</v>
+        <v>6458</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17735,10 +17735,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>533630</v>
+        <v>533832</v>
       </c>
       <c r="R170" t="n">
-        <v>6962701</v>
+        <v>6962351</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17906,7 +17906,7 @@
         <v>128101672</v>
       </c>
       <c r="B172" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -18007,7 +18007,7 @@
         <v>128109121</v>
       </c>
       <c r="B173" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>128110985</v>
       </c>
       <c r="B174" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>128110813</v>
       </c>
       <c r="B175" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18600,45 +18600,50 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128110835</v>
+        <v>128108439</v>
       </c>
       <c r="B179" t="n">
-        <v>98386</v>
+        <v>57672</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>533748</v>
+        <v>533711</v>
       </c>
       <c r="R179" t="n">
-        <v>6962431</v>
+        <v>6962283</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18671,6 +18676,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18697,45 +18707,50 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128110977</v>
+        <v>128101939</v>
       </c>
       <c r="B180" t="n">
-        <v>98503</v>
+        <v>57672</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>534040</v>
+        <v>533638</v>
       </c>
       <c r="R180" t="n">
-        <v>6962718</v>
+        <v>6962346</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18768,6 +18783,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18794,45 +18814,50 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128110828</v>
+        <v>128100413</v>
       </c>
       <c r="B181" t="n">
-        <v>98469</v>
+        <v>57672</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>533365</v>
+        <v>533545</v>
       </c>
       <c r="R181" t="n">
-        <v>6962304</v>
+        <v>6962372</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18869,7 +18894,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18896,10 +18921,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128107826</v>
+        <v>128110828</v>
       </c>
       <c r="B182" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -18924,21 +18949,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>533723</v>
+        <v>533365</v>
       </c>
       <c r="R182" t="n">
-        <v>6962360</v>
+        <v>6962304</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18971,6 +18992,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -18997,10 +19023,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128110817</v>
+        <v>128107826</v>
       </c>
       <c r="B183" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19025,17 +19051,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>533728</v>
+        <v>533723</v>
       </c>
       <c r="R183" t="n">
-        <v>6962346</v>
+        <v>6962360</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19068,11 +19098,6 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19099,50 +19124,45 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128108439</v>
+        <v>128110817</v>
       </c>
       <c r="B184" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>533711</v>
+        <v>533728</v>
       </c>
       <c r="R184" t="n">
-        <v>6962283</v>
+        <v>6962346</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19179,7 +19199,7 @@
       </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19206,50 +19226,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128101939</v>
+        <v>128110835</v>
       </c>
       <c r="B185" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>533638</v>
+        <v>533748</v>
       </c>
       <c r="R185" t="n">
-        <v>6962346</v>
+        <v>6962431</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19282,11 +19297,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19313,50 +19323,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128100413</v>
+        <v>128110977</v>
       </c>
       <c r="B186" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>533545</v>
+        <v>534040</v>
       </c>
       <c r="R186" t="n">
-        <v>6962372</v>
+        <v>6962718</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19391,11 +19396,6 @@
           <t>2025-08-31</t>
         </is>
       </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
-        </is>
-      </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
@@ -19417,6 +19417,307 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>128269237</v>
+      </c>
+      <c r="B187" t="n">
+        <v>98470</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>533460</v>
+      </c>
+      <c r="R187" t="n">
+        <v>6962201</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>20 ex</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>128269235</v>
+      </c>
+      <c r="B188" t="n">
+        <v>57672</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>533571</v>
+      </c>
+      <c r="R188" t="n">
+        <v>6962220</v>
+      </c>
+      <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>128269236</v>
+      </c>
+      <c r="B189" t="n">
+        <v>80133</v>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Mörttjärnbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>533748</v>
+      </c>
+      <c r="R189" t="n">
+        <v>6962295</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Nyhem</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -1408,10 +1408,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128108619</v>
+        <v>128109460</v>
       </c>
       <c r="B9" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1419,39 +1419,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533675</v>
+        <v>533498</v>
       </c>
       <c r="R9" t="n">
-        <v>6962244</v>
+        <v>6962158</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1484,11 +1479,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1515,7 +1505,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128110972</v>
+        <v>128108619</v>
       </c>
       <c r="B10" t="n">
         <v>57672</v>
@@ -1544,16 +1534,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533997</v>
+        <v>533675</v>
       </c>
       <c r="R10" t="n">
-        <v>6962746</v>
+        <v>6962244</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1590,7 +1585,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1617,7 +1612,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128101860</v>
+        <v>128110972</v>
       </c>
       <c r="B11" t="n">
         <v>57672</v>
@@ -1646,21 +1641,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533601</v>
+        <v>533997</v>
       </c>
       <c r="R11" t="n">
-        <v>6962344</v>
+        <v>6962746</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1697,7 +1687,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,10 +1714,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128109460</v>
+        <v>128101860</v>
       </c>
       <c r="B12" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1735,34 +1725,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533498</v>
+        <v>533601</v>
       </c>
       <c r="R12" t="n">
-        <v>6962158</v>
+        <v>6962344</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1795,6 +1790,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128101567</v>
+        <v>128110833</v>
       </c>
       <c r="B15" t="n">
-        <v>80036</v>
+        <v>98387</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533494</v>
+        <v>533768</v>
       </c>
       <c r="R15" t="n">
-        <v>6962425</v>
+        <v>6962318</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,50 +2121,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128108700</v>
+        <v>128100321</v>
       </c>
       <c r="B16" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533674</v>
+        <v>533537</v>
       </c>
       <c r="R16" t="n">
-        <v>6962199</v>
+        <v>6962358</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2197,11 +2196,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2228,38 +2222,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128109367</v>
+        <v>128100131</v>
       </c>
       <c r="B17" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2268,10 +2261,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533550</v>
+        <v>533496</v>
       </c>
       <c r="R17" t="n">
-        <v>6962157</v>
+        <v>6962335</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2304,11 +2297,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,32 +2323,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128110833</v>
+        <v>128110818</v>
       </c>
       <c r="B18" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2370,10 +2358,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533768</v>
+        <v>533766</v>
       </c>
       <c r="R18" t="n">
-        <v>6962318</v>
+        <v>6962317</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,6 +2394,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>10stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2432,49 +2425,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128100321</v>
+        <v>128101567</v>
       </c>
       <c r="B19" t="n">
-        <v>98470</v>
+        <v>80036</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533537</v>
+        <v>533494</v>
       </c>
       <c r="R19" t="n">
-        <v>6962358</v>
+        <v>6962425</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2533,49 +2522,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128100131</v>
+        <v>128108700</v>
       </c>
       <c r="B20" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533496</v>
+        <v>533674</v>
       </c>
       <c r="R20" t="n">
-        <v>6962335</v>
+        <v>6962199</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2608,6 +2598,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2634,45 +2629,50 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128110818</v>
+        <v>128109367</v>
       </c>
       <c r="B21" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533766</v>
+        <v>533550</v>
       </c>
       <c r="R21" t="n">
-        <v>6962317</v>
+        <v>6962157</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>10stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2736,45 +2736,50 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128108592</v>
+        <v>128099395</v>
       </c>
       <c r="B22" t="n">
-        <v>80036</v>
+        <v>57672</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533675</v>
+        <v>533356</v>
       </c>
       <c r="R22" t="n">
-        <v>6962244</v>
+        <v>6962190</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2807,6 +2812,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2930,38 +2940,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128099395</v>
+        <v>128101601</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2970,10 +2979,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533356</v>
+        <v>533496</v>
       </c>
       <c r="R24" t="n">
-        <v>6962190</v>
+        <v>6962407</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3006,11 +3015,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3037,45 +3041,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128110771</v>
+        <v>128108218</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533583</v>
+        <v>533789</v>
       </c>
       <c r="R25" t="n">
-        <v>6962697</v>
+        <v>6962263</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3108,11 +3116,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3139,50 +3142,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128109293</v>
+        <v>128108592</v>
       </c>
       <c r="B26" t="n">
-        <v>57672</v>
+        <v>80036</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533638</v>
+        <v>533675</v>
       </c>
       <c r="R26" t="n">
-        <v>6962157</v>
+        <v>6962244</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3215,11 +3213,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3246,49 +3239,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128101601</v>
+        <v>128110771</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533496</v>
+        <v>533583</v>
       </c>
       <c r="R27" t="n">
-        <v>6962407</v>
+        <v>6962697</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,6 +3310,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3347,37 +3341,38 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128108218</v>
+        <v>128109293</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3386,10 +3381,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533789</v>
+        <v>533638</v>
       </c>
       <c r="R28" t="n">
-        <v>6962263</v>
+        <v>6962157</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,6 +3417,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,50 +3559,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128099402</v>
+        <v>128110780</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>91124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533474</v>
+        <v>533670</v>
       </c>
       <c r="R30" t="n">
-        <v>6962267</v>
+        <v>6962552</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3635,11 +3630,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3666,45 +3656,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128110780</v>
+        <v>128099402</v>
       </c>
       <c r="B31" t="n">
-        <v>91124</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533670</v>
+        <v>533474</v>
       </c>
       <c r="R31" t="n">
-        <v>6962552</v>
+        <v>6962267</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3737,6 +3732,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3763,32 +3763,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128110803</v>
+        <v>128110790</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533524</v>
+        <v>533822</v>
       </c>
       <c r="R32" t="n">
-        <v>6962153</v>
+        <v>6962344</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,7 +3865,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128110981</v>
+        <v>128110803</v>
       </c>
       <c r="B33" t="n">
         <v>98470</v>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533689</v>
+        <v>533524</v>
       </c>
       <c r="R33" t="n">
-        <v>6962405</v>
+        <v>6962153</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128109875</v>
+        <v>128110981</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -3995,21 +3995,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533436</v>
+        <v>533689</v>
       </c>
       <c r="R34" t="n">
-        <v>6962158</v>
+        <v>6962405</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4042,6 +4038,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4068,7 +4069,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128102143</v>
+        <v>128109875</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4098,7 +4099,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4107,10 +4108,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533615</v>
+        <v>533436</v>
       </c>
       <c r="R35" t="n">
-        <v>6962423</v>
+        <v>6962158</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4169,7 +4170,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128100230</v>
+        <v>128102143</v>
       </c>
       <c r="B36" t="n">
         <v>98470</v>
@@ -4199,7 +4200,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4208,10 +4209,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533506</v>
+        <v>533615</v>
       </c>
       <c r="R36" t="n">
-        <v>6962358</v>
+        <v>6962423</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,45 +4271,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128110790</v>
+        <v>128100230</v>
       </c>
       <c r="B37" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533822</v>
+        <v>533506</v>
       </c>
       <c r="R37" t="n">
-        <v>6962344</v>
+        <v>6962358</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4341,11 +4346,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4372,10 +4372,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128108150</v>
+        <v>128099282</v>
       </c>
       <c r="B38" t="n">
-        <v>80161</v>
+        <v>80160</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4383,34 +4383,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533800</v>
+        <v>533452</v>
       </c>
       <c r="R38" t="n">
-        <v>6962306</v>
+        <v>6962232</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4469,32 +4469,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128110968</v>
+        <v>128110978</v>
       </c>
       <c r="B39" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4504,10 +4504,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533634</v>
+        <v>533708</v>
       </c>
       <c r="R39" t="n">
-        <v>6962526</v>
+        <v>6962645</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4540,11 +4540,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4571,50 +4566,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128102724</v>
+        <v>128110788</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533659</v>
+        <v>533590</v>
       </c>
       <c r="R40" t="n">
-        <v>6962512</v>
+        <v>6962592</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4647,11 +4637,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4678,50 +4663,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128101831</v>
+        <v>128110836</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533513</v>
+        <v>533722</v>
       </c>
       <c r="R41" t="n">
-        <v>6962442</v>
+        <v>6962426</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4754,11 +4734,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4785,45 +4760,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128110767</v>
+        <v>128108150</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533794</v>
+        <v>533800</v>
       </c>
       <c r="R42" t="n">
-        <v>6962411</v>
+        <v>6962306</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4856,11 +4831,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4887,45 +4857,50 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128110824</v>
+        <v>128102724</v>
       </c>
       <c r="B43" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533712</v>
+        <v>533659</v>
       </c>
       <c r="R43" t="n">
-        <v>6962628</v>
+        <v>6962512</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4962,7 +4937,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>20 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4989,45 +4964,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128110978</v>
+        <v>128101831</v>
       </c>
       <c r="B44" t="n">
-        <v>98504</v>
+        <v>57672</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533708</v>
+        <v>533513</v>
       </c>
       <c r="R44" t="n">
-        <v>6962645</v>
+        <v>6962442</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5060,6 +5040,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5086,32 +5071,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128110788</v>
+        <v>128110767</v>
       </c>
       <c r="B45" t="n">
-        <v>98504</v>
+        <v>57672</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5121,10 +5106,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533590</v>
+        <v>533794</v>
       </c>
       <c r="R45" t="n">
-        <v>6962592</v>
+        <v>6962411</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5157,6 +5142,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5183,32 +5173,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128110836</v>
+        <v>128110968</v>
       </c>
       <c r="B46" t="n">
-        <v>98387</v>
+        <v>57672</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5218,10 +5208,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533722</v>
+        <v>533634</v>
       </c>
       <c r="R46" t="n">
-        <v>6962426</v>
+        <v>6962526</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5254,6 +5244,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5280,32 +5275,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128099282</v>
+        <v>128110824</v>
       </c>
       <c r="B47" t="n">
-        <v>80160</v>
+        <v>98470</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5315,10 +5310,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533452</v>
+        <v>533712</v>
       </c>
       <c r="R47" t="n">
-        <v>6962232</v>
+        <v>6962628</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,6 +5346,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5377,10 +5377,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128103304</v>
+        <v>128101106</v>
       </c>
       <c r="B48" t="n">
-        <v>91124</v>
+        <v>80098</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5388,43 +5388,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3215</v>
+        <v>229748</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533594</v>
+        <v>533425</v>
       </c>
       <c r="R48" t="n">
-        <v>6962541</v>
+        <v>6962304</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5483,32 +5474,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128101106</v>
+        <v>128110812</v>
       </c>
       <c r="B49" t="n">
-        <v>80098</v>
+        <v>98470</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5518,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533425</v>
+        <v>533715</v>
       </c>
       <c r="R49" t="n">
-        <v>6962304</v>
+        <v>6962610</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5554,6 +5545,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5580,7 +5576,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128099088</v>
+        <v>128110826</v>
       </c>
       <c r="B50" t="n">
         <v>98470</v>
@@ -5608,21 +5604,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533425</v>
+        <v>533579</v>
       </c>
       <c r="R50" t="n">
-        <v>6962182</v>
+        <v>6962663</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5655,6 +5647,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5681,45 +5678,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128101702</v>
+        <v>128108922</v>
       </c>
       <c r="B51" t="n">
-        <v>91352</v>
+        <v>105508</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533529</v>
+        <v>533671</v>
       </c>
       <c r="R51" t="n">
-        <v>6962400</v>
+        <v>6962142</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5778,45 +5775,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128107546</v>
+        <v>128110804</v>
       </c>
       <c r="B52" t="n">
-        <v>80133</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533648</v>
+        <v>533532</v>
       </c>
       <c r="R52" t="n">
-        <v>6962374</v>
+        <v>6962156</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5849,6 +5846,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5875,32 +5877,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128110766</v>
+        <v>128110990</v>
       </c>
       <c r="B53" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5910,10 +5912,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533586</v>
+        <v>533873</v>
       </c>
       <c r="R53" t="n">
-        <v>6962139</v>
+        <v>6962782</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5950,7 +5952,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5977,32 +5979,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128110970</v>
+        <v>128110814</v>
       </c>
       <c r="B54" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6012,10 +6014,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>534050</v>
+        <v>533650</v>
       </c>
       <c r="R54" t="n">
-        <v>6962743</v>
+        <v>6962134</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6052,7 +6054,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>50 stycken ( några har blommat).</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6079,32 +6081,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128110812</v>
+        <v>128101702</v>
       </c>
       <c r="B55" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6114,10 +6116,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533715</v>
+        <v>533529</v>
       </c>
       <c r="R55" t="n">
-        <v>6962610</v>
+        <v>6962400</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6150,11 +6152,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6181,45 +6178,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128110826</v>
+        <v>128107546</v>
       </c>
       <c r="B56" t="n">
-        <v>98470</v>
+        <v>80133</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533579</v>
+        <v>533648</v>
       </c>
       <c r="R56" t="n">
-        <v>6962663</v>
+        <v>6962374</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6252,11 +6249,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6283,10 +6275,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128108922</v>
+        <v>128103304</v>
       </c>
       <c r="B57" t="n">
-        <v>105508</v>
+        <v>91124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6294,34 +6286,43 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221144</v>
+        <v>3215</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533671</v>
+        <v>533594</v>
       </c>
       <c r="R57" t="n">
-        <v>6962142</v>
+        <v>6962541</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6380,32 +6381,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128110804</v>
+        <v>128110766</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6415,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533532</v>
+        <v>533586</v>
       </c>
       <c r="R58" t="n">
-        <v>6962156</v>
+        <v>6962139</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6455,7 +6456,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6482,32 +6483,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128110990</v>
+        <v>128110970</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6517,10 +6518,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533873</v>
+        <v>534050</v>
       </c>
       <c r="R59" t="n">
-        <v>6962782</v>
+        <v>6962743</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6557,7 +6558,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6584,7 +6585,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128110814</v>
+        <v>128099088</v>
       </c>
       <c r="B60" t="n">
         <v>98470</v>
@@ -6612,17 +6613,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>533650</v>
+        <v>533425</v>
       </c>
       <c r="R60" t="n">
-        <v>6962134</v>
+        <v>6962182</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6655,11 +6660,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>50 stycken ( några har blommat).</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6783,54 +6783,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128099522</v>
+        <v>128099875</v>
       </c>
       <c r="B62" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533349</v>
+        <v>533445</v>
       </c>
       <c r="R62" t="n">
-        <v>6962197</v>
+        <v>6962324</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6889,45 +6880,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128099099</v>
+        <v>128099885</v>
       </c>
       <c r="B63" t="n">
-        <v>105508</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533416</v>
+        <v>533361</v>
       </c>
       <c r="R63" t="n">
-        <v>6962179</v>
+        <v>6962247</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,6 +6956,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6986,10 +6987,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128100636</v>
+        <v>128110971</v>
       </c>
       <c r="B64" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6997,21 +6998,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7021,10 +7022,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533452</v>
+        <v>534036</v>
       </c>
       <c r="R64" t="n">
-        <v>6962350</v>
+        <v>6962734</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7057,6 +7058,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7083,45 +7089,50 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128110827</v>
+        <v>128108477</v>
       </c>
       <c r="B65" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533614</v>
+        <v>533710</v>
       </c>
       <c r="R65" t="n">
-        <v>6962554</v>
+        <v>6962294</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7158,7 +7169,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7185,7 +7196,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128100184</v>
+        <v>128110827</v>
       </c>
       <c r="B66" t="n">
         <v>98470</v>
@@ -7213,21 +7224,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533509</v>
+        <v>533614</v>
       </c>
       <c r="R66" t="n">
-        <v>6962336</v>
+        <v>6962554</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7260,6 +7267,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7286,7 +7298,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128103587</v>
+        <v>128100184</v>
       </c>
       <c r="B67" t="n">
         <v>98470</v>
@@ -7316,19 +7328,19 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533650</v>
+        <v>533509</v>
       </c>
       <c r="R67" t="n">
-        <v>6962600</v>
+        <v>6962336</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7387,45 +7399,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128110971</v>
+        <v>128103587</v>
       </c>
       <c r="B68" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>534036</v>
+        <v>533650</v>
       </c>
       <c r="R68" t="n">
-        <v>6962734</v>
+        <v>6962600</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7458,11 +7474,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7489,50 +7500,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128108477</v>
+        <v>128099522</v>
       </c>
       <c r="B69" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533710</v>
+        <v>533349</v>
       </c>
       <c r="R69" t="n">
-        <v>6962294</v>
+        <v>6962197</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7565,11 +7580,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7596,32 +7606,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128099875</v>
+        <v>128099099</v>
       </c>
       <c r="B70" t="n">
-        <v>80132</v>
+        <v>105508</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7631,10 +7641,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533445</v>
+        <v>533416</v>
       </c>
       <c r="R70" t="n">
-        <v>6962324</v>
+        <v>6962179</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7693,10 +7703,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128099885</v>
+        <v>128100636</v>
       </c>
       <c r="B71" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7704,39 +7714,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533361</v>
+        <v>533452</v>
       </c>
       <c r="R71" t="n">
-        <v>6962247</v>
+        <v>6962350</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7769,11 +7774,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7800,50 +7800,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128099712</v>
+        <v>128099857</v>
       </c>
       <c r="B72" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533451</v>
+        <v>533445</v>
       </c>
       <c r="R72" t="n">
-        <v>6962307</v>
+        <v>6962324</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7876,11 +7871,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8325,7 +8315,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128101024</v>
+        <v>128110811</v>
       </c>
       <c r="B77" t="n">
         <v>98470</v>
@@ -8353,21 +8343,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533375</v>
+        <v>533706</v>
       </c>
       <c r="R77" t="n">
-        <v>6962293</v>
+        <v>6962596</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8400,6 +8386,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>24 stycken</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8426,7 +8417,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128110811</v>
+        <v>128101024</v>
       </c>
       <c r="B78" t="n">
         <v>98470</v>
@@ -8454,17 +8445,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533706</v>
+        <v>533375</v>
       </c>
       <c r="R78" t="n">
-        <v>6962596</v>
+        <v>6962293</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8497,11 +8492,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>24 stycken</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8528,45 +8518,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128099857</v>
+        <v>128099712</v>
       </c>
       <c r="B79" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533445</v>
+        <v>533451</v>
       </c>
       <c r="R79" t="n">
-        <v>6962324</v>
+        <v>6962307</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8599,6 +8594,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8625,32 +8625,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128110779</v>
+        <v>128110982</v>
       </c>
       <c r="B80" t="n">
-        <v>91124</v>
+        <v>98470</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533678</v>
+        <v>533681</v>
       </c>
       <c r="R80" t="n">
-        <v>6962542</v>
+        <v>6962434</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8696,6 +8696,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>23 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8722,32 +8727,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128102006</v>
+        <v>128110810</v>
       </c>
       <c r="B81" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8757,10 +8762,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533510</v>
+        <v>533645</v>
       </c>
       <c r="R81" t="n">
-        <v>6962462</v>
+        <v>6962593</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8819,50 +8824,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128099905</v>
+        <v>128110976</v>
       </c>
       <c r="B82" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533445</v>
+        <v>533868</v>
       </c>
       <c r="R82" t="n">
-        <v>6962324</v>
+        <v>6962692</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8926,38 +8926,37 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128101827</v>
+        <v>128101261</v>
       </c>
       <c r="B83" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -8966,10 +8965,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533594</v>
+        <v>533424</v>
       </c>
       <c r="R83" t="n">
-        <v>6962354</v>
+        <v>6962357</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9002,11 +9001,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9033,7 +9027,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128100974</v>
+        <v>128099905</v>
       </c>
       <c r="B84" t="n">
         <v>57672</v>
@@ -9073,10 +9067,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533375</v>
+        <v>533445</v>
       </c>
       <c r="R84" t="n">
-        <v>6962293</v>
+        <v>6962324</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9113,7 +9107,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9140,32 +9134,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128110969</v>
+        <v>128110779</v>
       </c>
       <c r="B85" t="n">
-        <v>57672</v>
+        <v>91124</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9175,10 +9169,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533825</v>
+        <v>533678</v>
       </c>
       <c r="R85" t="n">
-        <v>6962690</v>
+        <v>6962542</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9211,11 +9205,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9242,49 +9231,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128101261</v>
+        <v>128102006</v>
       </c>
       <c r="B86" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533424</v>
+        <v>533510</v>
       </c>
       <c r="R86" t="n">
-        <v>6962357</v>
+        <v>6962462</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9343,45 +9328,50 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128110982</v>
+        <v>128101827</v>
       </c>
       <c r="B87" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533681</v>
+        <v>533594</v>
       </c>
       <c r="R87" t="n">
-        <v>6962434</v>
+        <v>6962354</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9418,7 +9408,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>23 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9445,45 +9435,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128110810</v>
+        <v>128100974</v>
       </c>
       <c r="B88" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533645</v>
+        <v>533375</v>
       </c>
       <c r="R88" t="n">
-        <v>6962593</v>
+        <v>6962293</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9516,6 +9511,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9542,32 +9542,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128110976</v>
+        <v>128110969</v>
       </c>
       <c r="B89" t="n">
-        <v>98504</v>
+        <v>57672</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9577,10 +9577,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533868</v>
+        <v>533825</v>
       </c>
       <c r="R89" t="n">
-        <v>6962692</v>
+        <v>6962690</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Växer spritt i hela området</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10047,10 +10047,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128099401</v>
+        <v>128110834</v>
       </c>
       <c r="B94" t="n">
-        <v>92642</v>
+        <v>98387</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10058,43 +10058,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533356</v>
+        <v>533779</v>
       </c>
       <c r="R94" t="n">
-        <v>6962190</v>
+        <v>6962298</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10153,32 +10144,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128110974</v>
+        <v>128110816</v>
       </c>
       <c r="B95" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10188,10 +10179,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533937</v>
+        <v>533696</v>
       </c>
       <c r="R95" t="n">
-        <v>6962685</v>
+        <v>6962294</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10224,6 +10215,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10250,7 +10246,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128110816</v>
+        <v>128102067</v>
       </c>
       <c r="B96" t="n">
         <v>98470</v>
@@ -10278,17 +10274,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533696</v>
+        <v>533510</v>
       </c>
       <c r="R96" t="n">
-        <v>6962294</v>
+        <v>6962462</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10321,11 +10321,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10352,37 +10347,42 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128102067</v>
+        <v>128099401</v>
       </c>
       <c r="B97" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10391,10 +10391,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533510</v>
+        <v>533356</v>
       </c>
       <c r="R97" t="n">
-        <v>6962462</v>
+        <v>6962190</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10453,10 +10453,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128110834</v>
+        <v>128110974</v>
       </c>
       <c r="B98" t="n">
-        <v>98387</v>
+        <v>80161</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10464,21 +10464,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>219790</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10488,10 +10488,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>533779</v>
+        <v>533937</v>
       </c>
       <c r="R98" t="n">
-        <v>6962298</v>
+        <v>6962685</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10871,10 +10871,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128101073</v>
+        <v>128110792</v>
       </c>
       <c r="B102" t="n">
-        <v>80168</v>
+        <v>98504</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10882,21 +10882,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6464</v>
+        <v>219874</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10906,10 +10906,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>533385</v>
+        <v>533719</v>
       </c>
       <c r="R102" t="n">
-        <v>6962288</v>
+        <v>6962615</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10942,6 +10942,11 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10968,32 +10973,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128110829</v>
+        <v>128110807</v>
       </c>
       <c r="B103" t="n">
-        <v>56855</v>
+        <v>98470</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11003,10 +11008,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>533606</v>
+        <v>533664</v>
       </c>
       <c r="R103" t="n">
-        <v>6962582</v>
+        <v>6962286</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11043,7 +11048,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>1 ex. Sång</t>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11070,32 +11075,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128110785</v>
+        <v>128110983</v>
       </c>
       <c r="B104" t="n">
-        <v>97347</v>
+        <v>98470</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11105,10 +11110,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>533824</v>
+        <v>533665</v>
       </c>
       <c r="R104" t="n">
-        <v>6962352</v>
+        <v>6962459</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11141,6 +11146,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>26 ex</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11167,32 +11177,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128110807</v>
+        <v>128110829</v>
       </c>
       <c r="B105" t="n">
-        <v>98470</v>
+        <v>56855</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11202,10 +11212,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>533664</v>
+        <v>533606</v>
       </c>
       <c r="R105" t="n">
-        <v>6962286</v>
+        <v>6962582</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11242,7 +11252,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>23 stycken</t>
+          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11269,32 +11279,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128110983</v>
+        <v>128110785</v>
       </c>
       <c r="B106" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11304,10 +11314,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>533665</v>
+        <v>533824</v>
       </c>
       <c r="R106" t="n">
-        <v>6962459</v>
+        <v>6962352</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11340,11 +11350,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>26 ex</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11371,10 +11376,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128110792</v>
+        <v>128101073</v>
       </c>
       <c r="B107" t="n">
-        <v>98504</v>
+        <v>80168</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11382,21 +11387,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219874</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11406,10 +11411,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533719</v>
+        <v>533385</v>
       </c>
       <c r="R107" t="n">
-        <v>6962615</v>
+        <v>6962288</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11442,11 +11447,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11473,49 +11473,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128099487</v>
+        <v>128108028</v>
       </c>
       <c r="B108" t="n">
-        <v>98470</v>
+        <v>97353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533474</v>
+        <v>533802</v>
       </c>
       <c r="R108" t="n">
-        <v>6962267</v>
+        <v>6962332</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11574,45 +11570,50 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128110783</v>
+        <v>128108378</v>
       </c>
       <c r="B109" t="n">
-        <v>91124</v>
+        <v>57672</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533599</v>
+        <v>533750</v>
       </c>
       <c r="R109" t="n">
-        <v>6962553</v>
+        <v>6962259</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11645,6 +11646,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11671,7 +11677,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128108378</v>
+        <v>128100457</v>
       </c>
       <c r="B110" t="n">
         <v>57672</v>
@@ -11707,14 +11713,14 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533750</v>
+        <v>533556</v>
       </c>
       <c r="R110" t="n">
-        <v>6962259</v>
+        <v>6962363</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11778,10 +11784,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128100457</v>
+        <v>128110776</v>
       </c>
       <c r="B111" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11789,39 +11795,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>533556</v>
+        <v>533719</v>
       </c>
       <c r="R111" t="n">
-        <v>6962363</v>
+        <v>6962615</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11858,7 +11859,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11885,32 +11886,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128110991</v>
+        <v>128110838</v>
       </c>
       <c r="B112" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11920,10 +11921,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>533717</v>
+        <v>533708</v>
       </c>
       <c r="R112" t="n">
-        <v>6962645</v>
+        <v>6962624</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11960,7 +11961,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11987,10 +11988,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128103993</v>
+        <v>128110793</v>
       </c>
       <c r="B113" t="n">
-        <v>105508</v>
+        <v>98504</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11998,34 +11999,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221144</v>
+        <v>219874</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533664</v>
+        <v>533693</v>
       </c>
       <c r="R113" t="n">
-        <v>6962650</v>
+        <v>6962647</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12058,6 +12059,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12084,32 +12090,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128110987</v>
+        <v>128110794</v>
       </c>
       <c r="B114" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12119,10 +12125,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533999</v>
+        <v>533608</v>
       </c>
       <c r="R114" t="n">
-        <v>6962664</v>
+        <v>6962612</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12159,7 +12165,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12186,7 +12192,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103044</v>
+        <v>128110991</v>
       </c>
       <c r="B115" t="n">
         <v>98470</v>
@@ -12214,21 +12220,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533627</v>
+        <v>533717</v>
       </c>
       <c r="R115" t="n">
-        <v>6962544</v>
+        <v>6962645</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12261,6 +12263,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12287,45 +12294,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128110819</v>
+        <v>128103993</v>
       </c>
       <c r="B116" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533834</v>
+        <v>533664</v>
       </c>
       <c r="R116" t="n">
-        <v>6962298</v>
+        <v>6962650</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12358,11 +12365,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12389,45 +12391,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128108028</v>
+        <v>128110987</v>
       </c>
       <c r="B117" t="n">
-        <v>97353</v>
+        <v>98470</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533802</v>
+        <v>533999</v>
       </c>
       <c r="R117" t="n">
-        <v>6962332</v>
+        <v>6962664</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12460,6 +12462,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12486,45 +12493,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128101331</v>
+        <v>128103044</v>
       </c>
       <c r="B118" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533424</v>
+        <v>533627</v>
       </c>
       <c r="R118" t="n">
-        <v>6962357</v>
+        <v>6962544</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12583,45 +12594,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128108395</v>
+        <v>128110819</v>
       </c>
       <c r="B119" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533735</v>
+        <v>533834</v>
       </c>
       <c r="R119" t="n">
-        <v>6962274</v>
+        <v>6962298</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12654,6 +12665,11 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12680,32 +12696,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128110776</v>
+        <v>128101331</v>
       </c>
       <c r="B120" t="n">
-        <v>57832</v>
+        <v>80167</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>103021</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12715,10 +12731,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533719</v>
+        <v>533424</v>
       </c>
       <c r="R120" t="n">
-        <v>6962615</v>
+        <v>6962357</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12751,11 +12767,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12782,45 +12793,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128110838</v>
+        <v>128108395</v>
       </c>
       <c r="B121" t="n">
-        <v>98387</v>
+        <v>80132</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533708</v>
+        <v>533735</v>
       </c>
       <c r="R121" t="n">
-        <v>6962624</v>
+        <v>6962274</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12853,11 +12864,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12884,10 +12890,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128110793</v>
+        <v>128110783</v>
       </c>
       <c r="B122" t="n">
-        <v>98504</v>
+        <v>91124</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12895,21 +12901,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12919,10 +12925,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533693</v>
+        <v>533599</v>
       </c>
       <c r="R122" t="n">
-        <v>6962647</v>
+        <v>6962553</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12955,11 +12961,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12986,45 +12987,49 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128110794</v>
+        <v>128099487</v>
       </c>
       <c r="B123" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>533608</v>
+        <v>533474</v>
       </c>
       <c r="R123" t="n">
-        <v>6962612</v>
+        <v>6962267</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13057,11 +13062,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13088,50 +13088,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128099239</v>
+        <v>128110789</v>
       </c>
       <c r="B124" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>533422</v>
+        <v>533832</v>
       </c>
       <c r="R124" t="n">
-        <v>6962229</v>
+        <v>6962310</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13164,11 +13159,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13195,10 +13185,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128099811</v>
+        <v>128108119</v>
       </c>
       <c r="B125" t="n">
-        <v>105508</v>
+        <v>98504</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -13206,34 +13196,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221144</v>
+        <v>219874</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>533451</v>
+        <v>533800</v>
       </c>
       <c r="R125" t="n">
-        <v>6962307</v>
+        <v>6962306</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13292,32 +13282,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128109488</v>
+        <v>128110823</v>
       </c>
       <c r="B126" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13327,10 +13317,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>533498</v>
+        <v>533715</v>
       </c>
       <c r="R126" t="n">
-        <v>6962158</v>
+        <v>6962631</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13363,6 +13353,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13389,45 +13384,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128109254</v>
+        <v>128110825</v>
       </c>
       <c r="B127" t="n">
-        <v>80160</v>
+        <v>98470</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>533652</v>
+        <v>533583</v>
       </c>
       <c r="R127" t="n">
-        <v>6962140</v>
+        <v>6962689</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13460,6 +13455,11 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>84stycken</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13588,45 +13588,50 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128110823</v>
+        <v>128099239</v>
       </c>
       <c r="B129" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>533715</v>
+        <v>533422</v>
       </c>
       <c r="R129" t="n">
-        <v>6962631</v>
+        <v>6962229</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13663,7 +13668,7 @@
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13690,32 +13695,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128110825</v>
+        <v>128109488</v>
       </c>
       <c r="B130" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13725,10 +13730,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>533583</v>
+        <v>533498</v>
       </c>
       <c r="R130" t="n">
-        <v>6962689</v>
+        <v>6962158</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13761,11 +13766,6 @@
       <c r="AA130" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>84stycken</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -13792,10 +13792,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128110789</v>
+        <v>128109254</v>
       </c>
       <c r="B131" t="n">
-        <v>98504</v>
+        <v>80160</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13803,34 +13803,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219874</v>
+        <v>6461</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>533832</v>
+        <v>533652</v>
       </c>
       <c r="R131" t="n">
-        <v>6962310</v>
+        <v>6962140</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13889,10 +13889,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128108119</v>
+        <v>128099811</v>
       </c>
       <c r="B132" t="n">
-        <v>98504</v>
+        <v>105508</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13900,34 +13900,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>219874</v>
+        <v>221144</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>533800</v>
+        <v>533451</v>
       </c>
       <c r="R132" t="n">
-        <v>6962306</v>
+        <v>6962307</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13986,45 +13986,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103617</v>
+        <v>128110809</v>
       </c>
       <c r="B133" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>533637</v>
+        <v>533748</v>
       </c>
       <c r="R133" t="n">
-        <v>6962600</v>
+        <v>6962494</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14057,6 +14057,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14383,7 +14388,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128110809</v>
+        <v>128110984</v>
       </c>
       <c r="B137" t="n">
         <v>98470</v>
@@ -14418,10 +14423,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>533748</v>
+        <v>533734</v>
       </c>
       <c r="R137" t="n">
-        <v>6962494</v>
+        <v>6962473</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14458,7 +14463,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14485,32 +14490,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128110984</v>
+        <v>128100350</v>
       </c>
       <c r="B138" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14520,10 +14525,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>533734</v>
+        <v>533545</v>
       </c>
       <c r="R138" t="n">
-        <v>6962473</v>
+        <v>6962339</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14556,11 +14561,6 @@
       <c r="AA138" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14587,45 +14587,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128100350</v>
+        <v>128103617</v>
       </c>
       <c r="B139" t="n">
-        <v>97347</v>
+        <v>91352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>533545</v>
+        <v>533637</v>
       </c>
       <c r="R139" t="n">
-        <v>6962339</v>
+        <v>6962600</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14684,45 +14684,45 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128110801</v>
+        <v>128102955</v>
       </c>
       <c r="B140" t="n">
-        <v>98470</v>
+        <v>78787</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>533442</v>
+        <v>533659</v>
       </c>
       <c r="R140" t="n">
-        <v>6962166</v>
+        <v>6962538</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14755,11 +14755,6 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>4 stycken  ( finns möjligtvis fler I blåbärsriset)</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14786,45 +14781,50 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128110821</v>
+        <v>128108442</v>
       </c>
       <c r="B141" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>533705</v>
+        <v>533714</v>
       </c>
       <c r="R141" t="n">
-        <v>6962430</v>
+        <v>6962273</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14861,7 +14861,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>7 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -14888,45 +14888,50 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128110988</v>
+        <v>128109413</v>
       </c>
       <c r="B142" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P142" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>533959</v>
+        <v>533532</v>
       </c>
       <c r="R142" t="n">
-        <v>6962738</v>
+        <v>6962150</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14963,7 +14968,7 @@
       </c>
       <c r="AC142" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -14990,37 +14995,38 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128099760</v>
+        <v>128109827</v>
       </c>
       <c r="B143" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -15029,10 +15035,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>533451</v>
+        <v>533421</v>
       </c>
       <c r="R143" t="n">
-        <v>6962307</v>
+        <v>6962154</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15065,6 +15071,11 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15091,10 +15102,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128102955</v>
+        <v>128102524</v>
       </c>
       <c r="B144" t="n">
-        <v>78787</v>
+        <v>56855</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15102,34 +15113,39 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>533659</v>
+        <v>533640</v>
       </c>
       <c r="R144" t="n">
-        <v>6962538</v>
+        <v>6962482</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15188,50 +15204,49 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128108442</v>
+        <v>128099760</v>
       </c>
       <c r="B145" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>533714</v>
+        <v>533451</v>
       </c>
       <c r="R145" t="n">
-        <v>6962273</v>
+        <v>6962307</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15264,11 +15279,6 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15295,50 +15305,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128109413</v>
+        <v>128110801</v>
       </c>
       <c r="B146" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>533532</v>
+        <v>533442</v>
       </c>
       <c r="R146" t="n">
-        <v>6962150</v>
+        <v>6962166</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15375,7 +15380,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>4 stycken  ( finns möjligtvis fler I blåbärsriset)</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15402,50 +15407,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128109827</v>
+        <v>128110821</v>
       </c>
       <c r="B147" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>533421</v>
+        <v>533705</v>
       </c>
       <c r="R147" t="n">
-        <v>6962154</v>
+        <v>6962430</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>7 stycken</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15509,50 +15509,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128102524</v>
+        <v>128110988</v>
       </c>
       <c r="B148" t="n">
-        <v>56855</v>
+        <v>98470</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>533640</v>
+        <v>533959</v>
       </c>
       <c r="R148" t="n">
-        <v>6962482</v>
+        <v>6962738</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15585,6 +15580,11 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15611,10 +15611,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128102121</v>
+        <v>128110796</v>
       </c>
       <c r="B149" t="n">
-        <v>57832</v>
+        <v>80132</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -15622,21 +15622,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15646,10 +15646,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>533532</v>
+        <v>533655</v>
       </c>
       <c r="R149" t="n">
-        <v>6962477</v>
+        <v>6962173</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15708,10 +15708,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128110831</v>
+        <v>128109763</v>
       </c>
       <c r="B150" t="n">
-        <v>58531</v>
+        <v>80036</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15719,21 +15719,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>208249</v>
+        <v>6456</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15743,10 +15743,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>533728</v>
+        <v>533449</v>
       </c>
       <c r="R150" t="n">
-        <v>6962422</v>
+        <v>6962147</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15805,49 +15805,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128101444</v>
+        <v>128110768</v>
       </c>
       <c r="B151" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>533424</v>
+        <v>533754</v>
       </c>
       <c r="R151" t="n">
-        <v>6962351</v>
+        <v>6962450</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15880,6 +15876,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15906,32 +15907,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128110986</v>
+        <v>128102121</v>
       </c>
       <c r="B152" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15941,10 +15942,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>533957</v>
+        <v>533532</v>
       </c>
       <c r="R152" t="n">
-        <v>6962694</v>
+        <v>6962477</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15977,11 +15978,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>37 ex</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16008,10 +16004,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128102104</v>
+        <v>128099113</v>
       </c>
       <c r="B153" t="n">
-        <v>105508</v>
+        <v>92642</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16019,34 +16015,43 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>533615</v>
+        <v>533396</v>
       </c>
       <c r="R153" t="n">
-        <v>6962423</v>
+        <v>6962161</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16079,6 +16084,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16105,32 +16115,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128110768</v>
+        <v>128110831</v>
       </c>
       <c r="B154" t="n">
-        <v>57672</v>
+        <v>58531</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>208249</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16140,10 +16150,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>533754</v>
+        <v>533728</v>
       </c>
       <c r="R154" t="n">
-        <v>6962450</v>
+        <v>6962422</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16176,11 +16186,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16207,42 +16212,37 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128099113</v>
+        <v>128101444</v>
       </c>
       <c r="B155" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P155" t="inlineStr">
@@ -16251,10 +16251,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>533396</v>
+        <v>533424</v>
       </c>
       <c r="R155" t="n">
-        <v>6962161</v>
+        <v>6962351</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16287,11 +16287,6 @@
       <c r="AA155" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16318,32 +16313,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128110796</v>
+        <v>128110986</v>
       </c>
       <c r="B156" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16353,10 +16348,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>533655</v>
+        <v>533957</v>
       </c>
       <c r="R156" t="n">
-        <v>6962173</v>
+        <v>6962694</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16389,6 +16384,11 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>37 ex</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16415,10 +16415,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128109763</v>
+        <v>128102104</v>
       </c>
       <c r="B157" t="n">
-        <v>80036</v>
+        <v>105508</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16426,21 +16426,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6456</v>
+        <v>221144</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16450,10 +16450,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>533449</v>
+        <v>533615</v>
       </c>
       <c r="R157" t="n">
-        <v>6962147</v>
+        <v>6962423</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16609,10 +16609,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128110795</v>
+        <v>128110967</v>
       </c>
       <c r="B159" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16620,21 +16620,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16644,10 +16644,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>533792</v>
+        <v>533691</v>
       </c>
       <c r="R159" t="n">
-        <v>6962400</v>
+        <v>6962407</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16680,6 +16680,11 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16706,7 +16711,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128110967</v>
+        <v>128110773</v>
       </c>
       <c r="B160" t="n">
         <v>57672</v>
@@ -16741,10 +16746,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>533691</v>
+        <v>533604</v>
       </c>
       <c r="R160" t="n">
-        <v>6962407</v>
+        <v>6962650</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16781,7 +16786,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16808,7 +16813,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128110773</v>
+        <v>128110774</v>
       </c>
       <c r="B161" t="n">
         <v>57672</v>
@@ -16843,10 +16848,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>533604</v>
+        <v>533585</v>
       </c>
       <c r="R161" t="n">
-        <v>6962650</v>
+        <v>6962612</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16883,7 +16888,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>Färska ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16910,32 +16915,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128110774</v>
+        <v>128110837</v>
       </c>
       <c r="B162" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16945,10 +16950,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>533585</v>
+        <v>533617</v>
       </c>
       <c r="R162" t="n">
-        <v>6962612</v>
+        <v>6962560</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16981,11 +16986,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Färska ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17012,32 +17012,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128110805</v>
+        <v>128110791</v>
       </c>
       <c r="B163" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17047,10 +17047,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>533668</v>
+        <v>533658</v>
       </c>
       <c r="R163" t="n">
-        <v>6962160</v>
+        <v>6962570</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17083,11 +17083,6 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC163" t="inlineStr">
-        <is>
-          <t>75 stycken</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17114,7 +17109,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128109586</v>
+        <v>128110805</v>
       </c>
       <c r="B164" t="n">
         <v>98470</v>
@@ -17142,21 +17137,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>533498</v>
+        <v>533668</v>
       </c>
       <c r="R164" t="n">
-        <v>6962158</v>
+        <v>6962160</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17189,6 +17180,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>75 stycken</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17215,45 +17211,49 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128110837</v>
+        <v>128109586</v>
       </c>
       <c r="B165" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>533617</v>
+        <v>533498</v>
       </c>
       <c r="R165" t="n">
-        <v>6962560</v>
+        <v>6962158</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17312,32 +17312,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128110791</v>
+        <v>128110795</v>
       </c>
       <c r="B166" t="n">
-        <v>98504</v>
+        <v>80132</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17347,10 +17347,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>533658</v>
+        <v>533792</v>
       </c>
       <c r="R166" t="n">
-        <v>6962570</v>
+        <v>6962400</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17409,45 +17409,49 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128110782</v>
+        <v>128101672</v>
       </c>
       <c r="B167" t="n">
-        <v>91124</v>
+        <v>98470</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>533630</v>
+        <v>533534</v>
       </c>
       <c r="R167" t="n">
-        <v>6962701</v>
+        <v>6962408</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17506,45 +17510,49 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128110781</v>
+        <v>128109121</v>
       </c>
       <c r="B168" t="n">
-        <v>91124</v>
+        <v>98470</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>533700</v>
+        <v>533651</v>
       </c>
       <c r="R168" t="n">
-        <v>6962581</v>
+        <v>6962130</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17603,32 +17611,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128101262</v>
+        <v>128110813</v>
       </c>
       <c r="B169" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17638,10 +17646,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>533424</v>
+        <v>533507</v>
       </c>
       <c r="R169" t="n">
-        <v>6962357</v>
+        <v>6962168</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17674,6 +17682,11 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17700,32 +17713,32 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128110797</v>
+        <v>128110985</v>
       </c>
       <c r="B170" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17735,10 +17748,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>533832</v>
+        <v>533652</v>
       </c>
       <c r="R170" t="n">
-        <v>6962351</v>
+        <v>6962550</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17771,6 +17784,11 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17903,49 +17921,45 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128101672</v>
+        <v>128110782</v>
       </c>
       <c r="B172" t="n">
-        <v>98470</v>
+        <v>91124</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>533534</v>
+        <v>533630</v>
       </c>
       <c r="R172" t="n">
-        <v>6962408</v>
+        <v>6962701</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18004,49 +18018,45 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128109121</v>
+        <v>128110781</v>
       </c>
       <c r="B173" t="n">
-        <v>98470</v>
+        <v>91124</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>533651</v>
+        <v>533700</v>
       </c>
       <c r="R173" t="n">
-        <v>6962130</v>
+        <v>6962581</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18105,32 +18115,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128110985</v>
+        <v>128101262</v>
       </c>
       <c r="B174" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18140,10 +18150,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>533652</v>
+        <v>533424</v>
       </c>
       <c r="R174" t="n">
-        <v>6962550</v>
+        <v>6962357</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18176,11 +18186,6 @@
       <c r="AA174" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC174" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -18207,32 +18212,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128110813</v>
+        <v>128110797</v>
       </c>
       <c r="B175" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18242,10 +18247,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>533507</v>
+        <v>533832</v>
       </c>
       <c r="R175" t="n">
-        <v>6962168</v>
+        <v>6962351</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18278,11 +18283,6 @@
       <c r="AA175" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC175" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -18309,32 +18309,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128110799</v>
+        <v>128110787</v>
       </c>
       <c r="B176" t="n">
-        <v>80132</v>
+        <v>80160</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18344,10 +18344,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>533724</v>
+        <v>533785</v>
       </c>
       <c r="R176" t="n">
-        <v>6962625</v>
+        <v>6962326</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18406,32 +18406,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128110787</v>
+        <v>128101075</v>
       </c>
       <c r="B177" t="n">
-        <v>80160</v>
+        <v>80132</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18441,10 +18441,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>533785</v>
+        <v>533392</v>
       </c>
       <c r="R177" t="n">
-        <v>6962326</v>
+        <v>6962343</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18503,10 +18503,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128101075</v>
+        <v>128108439</v>
       </c>
       <c r="B178" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18514,34 +18514,39 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>533392</v>
+        <v>533711</v>
       </c>
       <c r="R178" t="n">
-        <v>6962343</v>
+        <v>6962283</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18574,6 +18579,11 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18600,7 +18610,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128108439</v>
+        <v>128101939</v>
       </c>
       <c r="B179" t="n">
         <v>57672</v>
@@ -18636,14 +18646,14 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>533711</v>
+        <v>533638</v>
       </c>
       <c r="R179" t="n">
-        <v>6962283</v>
+        <v>6962346</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18707,7 +18717,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128101939</v>
+        <v>128100413</v>
       </c>
       <c r="B180" t="n">
         <v>57672</v>
@@ -18747,10 +18757,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>533638</v>
+        <v>533545</v>
       </c>
       <c r="R180" t="n">
-        <v>6962346</v>
+        <v>6962372</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18814,50 +18824,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128100413</v>
+        <v>128110828</v>
       </c>
       <c r="B181" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>533545</v>
+        <v>533365</v>
       </c>
       <c r="R181" t="n">
-        <v>6962372</v>
+        <v>6962304</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18894,7 +18899,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18921,7 +18926,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128110828</v>
+        <v>128107826</v>
       </c>
       <c r="B182" t="n">
         <v>98470</v>
@@ -18949,17 +18954,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>533365</v>
+        <v>533723</v>
       </c>
       <c r="R182" t="n">
-        <v>6962304</v>
+        <v>6962360</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18992,11 +19001,6 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19023,7 +19027,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128107826</v>
+        <v>128110817</v>
       </c>
       <c r="B183" t="n">
         <v>98470</v>
@@ -19051,21 +19055,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>533723</v>
+        <v>533728</v>
       </c>
       <c r="R183" t="n">
-        <v>6962360</v>
+        <v>6962346</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19098,6 +19098,11 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19124,32 +19129,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128110817</v>
+        <v>128110799</v>
       </c>
       <c r="B184" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19159,10 +19164,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>533728</v>
+        <v>533724</v>
       </c>
       <c r="R184" t="n">
-        <v>6962346</v>
+        <v>6962625</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19195,11 +19200,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD184" t="b">

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -3559,45 +3559,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128110780</v>
+        <v>128099402</v>
       </c>
       <c r="B30" t="n">
-        <v>91124</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533670</v>
+        <v>533474</v>
       </c>
       <c r="R30" t="n">
-        <v>6962552</v>
+        <v>6962267</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3630,6 +3635,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3656,50 +3666,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128099402</v>
+        <v>128110780</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>91124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533474</v>
+        <v>533670</v>
       </c>
       <c r="R31" t="n">
-        <v>6962267</v>
+        <v>6962552</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3732,11 +3737,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3763,32 +3763,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128110790</v>
+        <v>128110803</v>
       </c>
       <c r="B32" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533822</v>
+        <v>533524</v>
       </c>
       <c r="R32" t="n">
-        <v>6962344</v>
+        <v>6962153</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,7 +3865,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128110803</v>
+        <v>128110981</v>
       </c>
       <c r="B33" t="n">
         <v>98470</v>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533524</v>
+        <v>533689</v>
       </c>
       <c r="R33" t="n">
-        <v>6962153</v>
+        <v>6962405</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128110981</v>
+        <v>128109875</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -3995,17 +3995,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533689</v>
+        <v>533436</v>
       </c>
       <c r="R34" t="n">
-        <v>6962405</v>
+        <v>6962158</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,11 +4042,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4069,7 +4068,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128109875</v>
+        <v>128102143</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4099,7 +4098,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4108,10 +4107,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533436</v>
+        <v>533615</v>
       </c>
       <c r="R35" t="n">
-        <v>6962158</v>
+        <v>6962423</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4170,7 +4169,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128102143</v>
+        <v>128100230</v>
       </c>
       <c r="B36" t="n">
         <v>98470</v>
@@ -4200,7 +4199,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4209,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533615</v>
+        <v>533506</v>
       </c>
       <c r="R36" t="n">
-        <v>6962423</v>
+        <v>6962358</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4271,49 +4270,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128100230</v>
+        <v>128110790</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533506</v>
+        <v>533822</v>
       </c>
       <c r="R37" t="n">
-        <v>6962358</v>
+        <v>6962344</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4346,6 +4341,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -6686,45 +6686,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128099984</v>
+        <v>128099522</v>
       </c>
       <c r="B61" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533455</v>
+        <v>533349</v>
       </c>
       <c r="R61" t="n">
-        <v>6962339</v>
+        <v>6962197</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6783,32 +6792,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128099875</v>
+        <v>128099099</v>
       </c>
       <c r="B62" t="n">
-        <v>80132</v>
+        <v>105508</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6818,10 +6827,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533445</v>
+        <v>533416</v>
       </c>
       <c r="R62" t="n">
-        <v>6962324</v>
+        <v>6962179</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6880,50 +6889,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128099885</v>
+        <v>128110827</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533361</v>
+        <v>533614</v>
       </c>
       <c r="R63" t="n">
-        <v>6962247</v>
+        <v>6962554</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,7 +6964,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6987,45 +6991,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128110971</v>
+        <v>128100184</v>
       </c>
       <c r="B64" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>534036</v>
+        <v>533509</v>
       </c>
       <c r="R64" t="n">
-        <v>6962734</v>
+        <v>6962336</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7058,11 +7066,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7089,38 +7092,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128108477</v>
+        <v>128103587</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>120</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7129,10 +7131,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533710</v>
+        <v>533650</v>
       </c>
       <c r="R65" t="n">
-        <v>6962294</v>
+        <v>6962600</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7165,11 +7167,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7196,32 +7193,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128110827</v>
+        <v>128110971</v>
       </c>
       <c r="B66" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7231,10 +7228,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533614</v>
+        <v>534036</v>
       </c>
       <c r="R66" t="n">
-        <v>6962554</v>
+        <v>6962734</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,7 +7268,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7298,49 +7295,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128100184</v>
+        <v>128108477</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533509</v>
+        <v>533710</v>
       </c>
       <c r="R67" t="n">
-        <v>6962336</v>
+        <v>6962294</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7373,6 +7371,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7399,49 +7402,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128103587</v>
+        <v>128099984</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533650</v>
+        <v>533455</v>
       </c>
       <c r="R68" t="n">
-        <v>6962600</v>
+        <v>6962339</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7500,54 +7499,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128099522</v>
+        <v>128099875</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533349</v>
+        <v>533445</v>
       </c>
       <c r="R69" t="n">
-        <v>6962197</v>
+        <v>6962324</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7606,45 +7596,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128099099</v>
+        <v>128099885</v>
       </c>
       <c r="B70" t="n">
-        <v>105508</v>
+        <v>57672</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533416</v>
+        <v>533361</v>
       </c>
       <c r="R70" t="n">
-        <v>6962179</v>
+        <v>6962247</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7677,6 +7672,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8625,32 +8625,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128110982</v>
+        <v>128110779</v>
       </c>
       <c r="B80" t="n">
-        <v>98470</v>
+        <v>91124</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533681</v>
+        <v>533678</v>
       </c>
       <c r="R80" t="n">
-        <v>6962434</v>
+        <v>6962542</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8696,11 +8696,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>23 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8727,45 +8722,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128110810</v>
+        <v>128101827</v>
       </c>
       <c r="B81" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533645</v>
+        <v>533594</v>
       </c>
       <c r="R81" t="n">
-        <v>6962593</v>
+        <v>6962354</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8798,6 +8798,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8824,45 +8829,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128110976</v>
+        <v>128100974</v>
       </c>
       <c r="B82" t="n">
-        <v>98504</v>
+        <v>57672</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533868</v>
+        <v>533375</v>
       </c>
       <c r="R82" t="n">
-        <v>6962692</v>
+        <v>6962293</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8899,7 +8909,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Växer spritt i hela området</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8926,49 +8936,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128101261</v>
+        <v>128110969</v>
       </c>
       <c r="B83" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533424</v>
+        <v>533825</v>
       </c>
       <c r="R83" t="n">
-        <v>6962357</v>
+        <v>6962690</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9001,6 +9007,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9027,10 +9038,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128099905</v>
+        <v>128102006</v>
       </c>
       <c r="B84" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9038,39 +9049,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533445</v>
+        <v>533510</v>
       </c>
       <c r="R84" t="n">
-        <v>6962324</v>
+        <v>6962462</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9103,11 +9109,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9134,45 +9135,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128110779</v>
+        <v>128099905</v>
       </c>
       <c r="B85" t="n">
-        <v>91124</v>
+        <v>57672</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533678</v>
+        <v>533445</v>
       </c>
       <c r="R85" t="n">
-        <v>6962542</v>
+        <v>6962324</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9205,6 +9211,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9231,32 +9242,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128102006</v>
+        <v>128110976</v>
       </c>
       <c r="B86" t="n">
-        <v>80132</v>
+        <v>98504</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9266,10 +9277,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533510</v>
+        <v>533868</v>
       </c>
       <c r="R86" t="n">
-        <v>6962462</v>
+        <v>6962692</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9302,6 +9313,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9328,38 +9344,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128101827</v>
+        <v>128101261</v>
       </c>
       <c r="B87" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9368,10 +9383,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533594</v>
+        <v>533424</v>
       </c>
       <c r="R87" t="n">
-        <v>6962354</v>
+        <v>6962357</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9404,11 +9419,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9435,50 +9445,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128100974</v>
+        <v>128110982</v>
       </c>
       <c r="B88" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533375</v>
+        <v>533681</v>
       </c>
       <c r="R88" t="n">
-        <v>6962293</v>
+        <v>6962434</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9515,7 +9520,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
+          <t>23 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9542,32 +9547,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128110969</v>
+        <v>128110810</v>
       </c>
       <c r="B89" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9577,10 +9582,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533825</v>
+        <v>533645</v>
       </c>
       <c r="R89" t="n">
-        <v>6962690</v>
+        <v>6962593</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9613,11 +9618,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10047,10 +10047,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128110834</v>
+        <v>128099401</v>
       </c>
       <c r="B94" t="n">
-        <v>98387</v>
+        <v>92642</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10058,34 +10058,43 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533779</v>
+        <v>533356</v>
       </c>
       <c r="R94" t="n">
-        <v>6962298</v>
+        <v>6962190</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10144,45 +10153,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128110816</v>
+        <v>128099555</v>
       </c>
       <c r="B95" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533696</v>
+        <v>533471</v>
       </c>
       <c r="R95" t="n">
-        <v>6962294</v>
+        <v>6962293</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10219,7 +10233,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>20 stycken</t>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10246,49 +10260,50 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128102067</v>
+        <v>128102878</v>
       </c>
       <c r="B96" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533510</v>
+        <v>533665</v>
       </c>
       <c r="R96" t="n">
-        <v>6962462</v>
+        <v>6962515</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10321,6 +10336,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10347,42 +10367,38 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128099401</v>
+        <v>128100043</v>
       </c>
       <c r="B97" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10391,10 +10407,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533356</v>
+        <v>533496</v>
       </c>
       <c r="R97" t="n">
-        <v>6962190</v>
+        <v>6962335</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10427,6 +10443,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10550,50 +10571,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128099555</v>
+        <v>128110834</v>
       </c>
       <c r="B99" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>533471</v>
+        <v>533779</v>
       </c>
       <c r="R99" t="n">
-        <v>6962293</v>
+        <v>6962298</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10626,11 +10642,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10657,50 +10668,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128102878</v>
+        <v>128110816</v>
       </c>
       <c r="B100" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>533665</v>
+        <v>533696</v>
       </c>
       <c r="R100" t="n">
-        <v>6962515</v>
+        <v>6962294</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10737,7 +10743,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10764,38 +10770,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128100043</v>
+        <v>128102067</v>
       </c>
       <c r="B101" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -10804,10 +10809,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533496</v>
+        <v>533510</v>
       </c>
       <c r="R101" t="n">
-        <v>6962335</v>
+        <v>6962462</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10840,11 +10845,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11473,45 +11473,49 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128108028</v>
+        <v>128099487</v>
       </c>
       <c r="B108" t="n">
-        <v>97353</v>
+        <v>98470</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533802</v>
+        <v>533474</v>
       </c>
       <c r="R108" t="n">
-        <v>6962332</v>
+        <v>6962267</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11570,10 +11574,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128108378</v>
+        <v>128110776</v>
       </c>
       <c r="B109" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11581,39 +11585,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533750</v>
+        <v>533719</v>
       </c>
       <c r="R109" t="n">
-        <v>6962259</v>
+        <v>6962615</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11650,7 +11649,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11677,50 +11676,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128100457</v>
+        <v>128110987</v>
       </c>
       <c r="B110" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533556</v>
+        <v>533999</v>
       </c>
       <c r="R110" t="n">
-        <v>6962363</v>
+        <v>6962664</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11757,7 +11751,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11784,45 +11778,49 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128110776</v>
+        <v>128103044</v>
       </c>
       <c r="B111" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>533719</v>
+        <v>533627</v>
       </c>
       <c r="R111" t="n">
-        <v>6962615</v>
+        <v>6962544</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11855,11 +11853,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11886,32 +11879,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128110838</v>
+        <v>128110819</v>
       </c>
       <c r="B112" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11921,10 +11914,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>533708</v>
+        <v>533834</v>
       </c>
       <c r="R112" t="n">
-        <v>6962624</v>
+        <v>6962298</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11961,7 +11954,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>1 stycken</t>
+          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11988,10 +11981,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128110793</v>
+        <v>128108028</v>
       </c>
       <c r="B113" t="n">
-        <v>98504</v>
+        <v>97353</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11999,34 +11992,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219874</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533693</v>
+        <v>533802</v>
       </c>
       <c r="R113" t="n">
-        <v>6962647</v>
+        <v>6962332</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12059,11 +12052,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12090,10 +12078,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128110794</v>
+        <v>128110783</v>
       </c>
       <c r="B114" t="n">
-        <v>98504</v>
+        <v>91124</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12101,21 +12089,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12125,10 +12113,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533608</v>
+        <v>533599</v>
       </c>
       <c r="R114" t="n">
-        <v>6962612</v>
+        <v>6962553</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12161,11 +12149,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12192,45 +12175,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128110991</v>
+        <v>128108378</v>
       </c>
       <c r="B115" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533717</v>
+        <v>533750</v>
       </c>
       <c r="R115" t="n">
-        <v>6962645</v>
+        <v>6962259</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12267,7 +12255,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12294,45 +12282,50 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103993</v>
+        <v>128100457</v>
       </c>
       <c r="B116" t="n">
-        <v>105508</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533664</v>
+        <v>533556</v>
       </c>
       <c r="R116" t="n">
-        <v>6962650</v>
+        <v>6962363</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12365,6 +12358,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12391,32 +12389,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128110987</v>
+        <v>128110838</v>
       </c>
       <c r="B117" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12426,10 +12424,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533999</v>
+        <v>533708</v>
       </c>
       <c r="R117" t="n">
-        <v>6962664</v>
+        <v>6962624</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12466,7 +12464,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12493,49 +12491,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103044</v>
+        <v>128110793</v>
       </c>
       <c r="B118" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533627</v>
+        <v>533693</v>
       </c>
       <c r="R118" t="n">
-        <v>6962544</v>
+        <v>6962647</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12568,6 +12562,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12594,32 +12593,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128110819</v>
+        <v>128110794</v>
       </c>
       <c r="B119" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12629,10 +12628,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533834</v>
+        <v>533608</v>
       </c>
       <c r="R119" t="n">
-        <v>6962298</v>
+        <v>6962612</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12669,7 +12668,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>10 stycken kan finnas fler runt omkring</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12696,32 +12695,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128101331</v>
+        <v>128110991</v>
       </c>
       <c r="B120" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12731,10 +12730,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533424</v>
+        <v>533717</v>
       </c>
       <c r="R120" t="n">
-        <v>6962357</v>
+        <v>6962645</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12767,6 +12766,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12793,32 +12797,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128108395</v>
+        <v>128103993</v>
       </c>
       <c r="B121" t="n">
-        <v>80132</v>
+        <v>105508</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12828,10 +12832,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533735</v>
+        <v>533664</v>
       </c>
       <c r="R121" t="n">
-        <v>6962274</v>
+        <v>6962650</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12890,10 +12894,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128110783</v>
+        <v>128101331</v>
       </c>
       <c r="B122" t="n">
-        <v>91124</v>
+        <v>80167</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12901,21 +12905,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3215</v>
+        <v>6463</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12925,10 +12929,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533599</v>
+        <v>533424</v>
       </c>
       <c r="R122" t="n">
-        <v>6962553</v>
+        <v>6962357</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12987,49 +12991,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128099487</v>
+        <v>128108395</v>
       </c>
       <c r="B123" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>533474</v>
+        <v>533735</v>
       </c>
       <c r="R123" t="n">
-        <v>6962267</v>
+        <v>6962274</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15805,45 +15805,49 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128110768</v>
+        <v>128101444</v>
       </c>
       <c r="B151" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>533754</v>
+        <v>533424</v>
       </c>
       <c r="R151" t="n">
-        <v>6962450</v>
+        <v>6962351</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15876,11 +15880,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15907,32 +15906,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128102121</v>
+        <v>128110986</v>
       </c>
       <c r="B152" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15942,10 +15941,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>533532</v>
+        <v>533957</v>
       </c>
       <c r="R152" t="n">
-        <v>6962477</v>
+        <v>6962694</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15978,6 +15977,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>37 ex</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16004,10 +16008,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128099113</v>
+        <v>128102104</v>
       </c>
       <c r="B153" t="n">
-        <v>92642</v>
+        <v>105508</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16015,43 +16019,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>533396</v>
+        <v>533615</v>
       </c>
       <c r="R153" t="n">
-        <v>6962161</v>
+        <v>6962423</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16084,11 +16079,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16115,32 +16105,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128110831</v>
+        <v>128110768</v>
       </c>
       <c r="B154" t="n">
-        <v>58531</v>
+        <v>57672</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>208249</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16150,10 +16140,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>533728</v>
+        <v>533754</v>
       </c>
       <c r="R154" t="n">
-        <v>6962422</v>
+        <v>6962450</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16186,6 +16176,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16212,49 +16207,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128101444</v>
+        <v>128110831</v>
       </c>
       <c r="B155" t="n">
-        <v>98470</v>
+        <v>58531</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>533424</v>
+        <v>533728</v>
       </c>
       <c r="R155" t="n">
-        <v>6962351</v>
+        <v>6962422</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16313,45 +16304,54 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128110986</v>
+        <v>128099113</v>
       </c>
       <c r="B156" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>533957</v>
+        <v>533396</v>
       </c>
       <c r="R156" t="n">
-        <v>6962694</v>
+        <v>6962161</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>37 ex</t>
+          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16415,32 +16415,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128102104</v>
+        <v>128102121</v>
       </c>
       <c r="B157" t="n">
-        <v>105508</v>
+        <v>57832</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16450,10 +16450,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>533615</v>
+        <v>533532</v>
       </c>
       <c r="R157" t="n">
-        <v>6962423</v>
+        <v>6962477</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -7800,45 +7800,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128099857</v>
+        <v>128099712</v>
       </c>
       <c r="B72" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533445</v>
+        <v>533451</v>
       </c>
       <c r="R72" t="n">
-        <v>6962324</v>
+        <v>6962307</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7871,6 +7876,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8315,32 +8325,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128110811</v>
+        <v>128099857</v>
       </c>
       <c r="B77" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8350,10 +8360,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533706</v>
+        <v>533445</v>
       </c>
       <c r="R77" t="n">
-        <v>6962596</v>
+        <v>6962324</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8386,11 +8396,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>24 stycken</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8417,7 +8422,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128101024</v>
+        <v>128110811</v>
       </c>
       <c r="B78" t="n">
         <v>98470</v>
@@ -8445,21 +8450,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533375</v>
+        <v>533706</v>
       </c>
       <c r="R78" t="n">
-        <v>6962293</v>
+        <v>6962596</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8492,6 +8493,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>24 stycken</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8518,38 +8524,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128099712</v>
+        <v>128101024</v>
       </c>
       <c r="B79" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8558,10 +8563,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533451</v>
+        <v>533375</v>
       </c>
       <c r="R79" t="n">
-        <v>6962307</v>
+        <v>6962293</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8594,11 +8599,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8625,32 +8625,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128110779</v>
+        <v>128110982</v>
       </c>
       <c r="B80" t="n">
-        <v>91124</v>
+        <v>98470</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533678</v>
+        <v>533681</v>
       </c>
       <c r="R80" t="n">
-        <v>6962542</v>
+        <v>6962434</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8696,6 +8696,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>23 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8722,50 +8727,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128101827</v>
+        <v>128110810</v>
       </c>
       <c r="B81" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533594</v>
+        <v>533645</v>
       </c>
       <c r="R81" t="n">
-        <v>6962354</v>
+        <v>6962593</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8798,11 +8798,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8829,50 +8824,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128100974</v>
+        <v>128110976</v>
       </c>
       <c r="B82" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533375</v>
+        <v>533868</v>
       </c>
       <c r="R82" t="n">
-        <v>6962293</v>
+        <v>6962692</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8909,7 +8899,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
+          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8936,45 +8926,49 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128110969</v>
+        <v>128101261</v>
       </c>
       <c r="B83" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533825</v>
+        <v>533424</v>
       </c>
       <c r="R83" t="n">
-        <v>6962690</v>
+        <v>6962357</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9007,11 +9001,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9038,10 +9027,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128102006</v>
+        <v>128099905</v>
       </c>
       <c r="B84" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9049,34 +9038,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533510</v>
+        <v>533445</v>
       </c>
       <c r="R84" t="n">
-        <v>6962462</v>
+        <v>6962324</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9109,6 +9103,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9135,50 +9134,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128099905</v>
+        <v>128110779</v>
       </c>
       <c r="B85" t="n">
-        <v>57672</v>
+        <v>91124</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533445</v>
+        <v>533678</v>
       </c>
       <c r="R85" t="n">
-        <v>6962324</v>
+        <v>6962542</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9211,11 +9205,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9242,32 +9231,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128110976</v>
+        <v>128102006</v>
       </c>
       <c r="B86" t="n">
-        <v>98504</v>
+        <v>80132</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9277,10 +9266,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533868</v>
+        <v>533510</v>
       </c>
       <c r="R86" t="n">
-        <v>6962692</v>
+        <v>6962462</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9313,11 +9302,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9344,37 +9328,38 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128101261</v>
+        <v>128101827</v>
       </c>
       <c r="B87" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9383,10 +9368,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533424</v>
+        <v>533594</v>
       </c>
       <c r="R87" t="n">
-        <v>6962357</v>
+        <v>6962354</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9419,6 +9404,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9445,45 +9435,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128110982</v>
+        <v>128100974</v>
       </c>
       <c r="B88" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533681</v>
+        <v>533375</v>
       </c>
       <c r="R88" t="n">
-        <v>6962434</v>
+        <v>6962293</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9520,7 +9515,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>23 ex</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9547,32 +9542,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128110810</v>
+        <v>128110969</v>
       </c>
       <c r="B89" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9582,10 +9577,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533645</v>
+        <v>533825</v>
       </c>
       <c r="R89" t="n">
-        <v>6962593</v>
+        <v>6962690</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9618,6 +9613,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11473,49 +11473,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128099487</v>
+        <v>128108028</v>
       </c>
       <c r="B108" t="n">
-        <v>98470</v>
+        <v>97353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533474</v>
+        <v>533802</v>
       </c>
       <c r="R108" t="n">
-        <v>6962267</v>
+        <v>6962332</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11574,10 +11570,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128110776</v>
+        <v>128108378</v>
       </c>
       <c r="B109" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11585,34 +11581,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533719</v>
+        <v>533750</v>
       </c>
       <c r="R109" t="n">
-        <v>6962615</v>
+        <v>6962259</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11649,7 +11650,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11676,45 +11677,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128110987</v>
+        <v>128100457</v>
       </c>
       <c r="B110" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533999</v>
+        <v>533556</v>
       </c>
       <c r="R110" t="n">
-        <v>6962664</v>
+        <v>6962363</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11751,7 +11757,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11778,49 +11784,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103044</v>
+        <v>128110776</v>
       </c>
       <c r="B111" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>533627</v>
+        <v>533719</v>
       </c>
       <c r="R111" t="n">
-        <v>6962544</v>
+        <v>6962615</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11853,6 +11855,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11879,32 +11886,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128110819</v>
+        <v>128110838</v>
       </c>
       <c r="B112" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11914,10 +11921,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>533834</v>
+        <v>533708</v>
       </c>
       <c r="R112" t="n">
-        <v>6962298</v>
+        <v>6962624</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11954,7 +11961,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>10 stycken kan finnas fler runt omkring</t>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11981,10 +11988,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128108028</v>
+        <v>128110793</v>
       </c>
       <c r="B113" t="n">
-        <v>97353</v>
+        <v>98504</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11992,34 +11999,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221941</v>
+        <v>219874</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533802</v>
+        <v>533693</v>
       </c>
       <c r="R113" t="n">
-        <v>6962332</v>
+        <v>6962647</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12052,6 +12059,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12078,10 +12090,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128110783</v>
+        <v>128110794</v>
       </c>
       <c r="B114" t="n">
-        <v>91124</v>
+        <v>98504</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12089,21 +12101,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12113,10 +12125,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533599</v>
+        <v>533608</v>
       </c>
       <c r="R114" t="n">
-        <v>6962553</v>
+        <v>6962612</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12149,6 +12161,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12175,50 +12192,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128108378</v>
+        <v>128110991</v>
       </c>
       <c r="B115" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533750</v>
+        <v>533717</v>
       </c>
       <c r="R115" t="n">
-        <v>6962259</v>
+        <v>6962645</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12255,7 +12267,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12282,50 +12294,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128100457</v>
+        <v>128103993</v>
       </c>
       <c r="B116" t="n">
-        <v>57672</v>
+        <v>105508</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533556</v>
+        <v>533664</v>
       </c>
       <c r="R116" t="n">
-        <v>6962363</v>
+        <v>6962650</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12358,11 +12365,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12389,32 +12391,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128110838</v>
+        <v>128110987</v>
       </c>
       <c r="B117" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12424,10 +12426,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533708</v>
+        <v>533999</v>
       </c>
       <c r="R117" t="n">
-        <v>6962624</v>
+        <v>6962664</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12464,7 +12466,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>1 stycken</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12491,45 +12493,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128110793</v>
+        <v>128103044</v>
       </c>
       <c r="B118" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533693</v>
+        <v>533627</v>
       </c>
       <c r="R118" t="n">
-        <v>6962647</v>
+        <v>6962544</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12562,11 +12568,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12593,32 +12594,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128110794</v>
+        <v>128110819</v>
       </c>
       <c r="B119" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12628,10 +12629,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533608</v>
+        <v>533834</v>
       </c>
       <c r="R119" t="n">
-        <v>6962612</v>
+        <v>6962298</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12668,7 +12669,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12695,32 +12696,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128110991</v>
+        <v>128101331</v>
       </c>
       <c r="B120" t="n">
-        <v>98470</v>
+        <v>80167</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12730,10 +12731,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533717</v>
+        <v>533424</v>
       </c>
       <c r="R120" t="n">
-        <v>6962645</v>
+        <v>6962357</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12766,11 +12767,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12797,32 +12793,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103993</v>
+        <v>128108395</v>
       </c>
       <c r="B121" t="n">
-        <v>105508</v>
+        <v>80132</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12832,10 +12828,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533664</v>
+        <v>533735</v>
       </c>
       <c r="R121" t="n">
-        <v>6962650</v>
+        <v>6962274</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12894,10 +12890,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128101331</v>
+        <v>128110783</v>
       </c>
       <c r="B122" t="n">
-        <v>80167</v>
+        <v>91124</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12905,21 +12901,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6463</v>
+        <v>3215</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12929,10 +12925,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533424</v>
+        <v>533599</v>
       </c>
       <c r="R122" t="n">
-        <v>6962357</v>
+        <v>6962553</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12991,45 +12987,49 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128108395</v>
+        <v>128099487</v>
       </c>
       <c r="B123" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>533735</v>
+        <v>533474</v>
       </c>
       <c r="R123" t="n">
-        <v>6962274</v>
+        <v>6962267</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13986,45 +13986,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128110809</v>
+        <v>128103617</v>
       </c>
       <c r="B133" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>533748</v>
+        <v>533637</v>
       </c>
       <c r="R133" t="n">
-        <v>6962494</v>
+        <v>6962600</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14057,11 +14057,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14088,32 +14083,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128110830</v>
+        <v>128110809</v>
       </c>
       <c r="B134" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14123,10 +14118,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>533659</v>
+        <v>533748</v>
       </c>
       <c r="R134" t="n">
-        <v>6962296</v>
+        <v>6962494</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14159,6 +14154,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14185,32 +14185,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128110808</v>
+        <v>128100350</v>
       </c>
       <c r="B135" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14220,10 +14220,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>533745</v>
+        <v>533545</v>
       </c>
       <c r="R135" t="n">
-        <v>6962429</v>
+        <v>6962339</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14256,11 +14256,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14287,49 +14282,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128107880</v>
+        <v>128110830</v>
       </c>
       <c r="B136" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>533736</v>
+        <v>533659</v>
       </c>
       <c r="R136" t="n">
-        <v>6962362</v>
+        <v>6962296</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14388,7 +14379,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128110984</v>
+        <v>128110808</v>
       </c>
       <c r="B137" t="n">
         <v>98470</v>
@@ -14423,10 +14414,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>533734</v>
+        <v>533745</v>
       </c>
       <c r="R137" t="n">
-        <v>6962473</v>
+        <v>6962429</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14463,7 +14454,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14490,45 +14481,49 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128100350</v>
+        <v>128107880</v>
       </c>
       <c r="B138" t="n">
-        <v>97347</v>
+        <v>98470</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>533545</v>
+        <v>533736</v>
       </c>
       <c r="R138" t="n">
-        <v>6962339</v>
+        <v>6962362</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14587,45 +14582,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103617</v>
+        <v>128110984</v>
       </c>
       <c r="B139" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>533637</v>
+        <v>533734</v>
       </c>
       <c r="R139" t="n">
-        <v>6962600</v>
+        <v>6962473</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14658,6 +14653,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15805,49 +15805,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128101444</v>
+        <v>128110768</v>
       </c>
       <c r="B151" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>533424</v>
+        <v>533754</v>
       </c>
       <c r="R151" t="n">
-        <v>6962351</v>
+        <v>6962450</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15880,6 +15876,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15906,32 +15907,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128110986</v>
+        <v>128102121</v>
       </c>
       <c r="B152" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15941,10 +15942,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>533957</v>
+        <v>533532</v>
       </c>
       <c r="R152" t="n">
-        <v>6962694</v>
+        <v>6962477</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15977,11 +15978,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>37 ex</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16008,10 +16004,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128102104</v>
+        <v>128099113</v>
       </c>
       <c r="B153" t="n">
-        <v>105508</v>
+        <v>92642</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16019,34 +16015,43 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P153" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>533615</v>
+        <v>533396</v>
       </c>
       <c r="R153" t="n">
-        <v>6962423</v>
+        <v>6962161</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16079,6 +16084,11 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16105,32 +16115,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128110768</v>
+        <v>128110831</v>
       </c>
       <c r="B154" t="n">
-        <v>57672</v>
+        <v>58531</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>208249</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16140,10 +16150,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>533754</v>
+        <v>533728</v>
       </c>
       <c r="R154" t="n">
-        <v>6962450</v>
+        <v>6962422</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16176,11 +16186,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16207,45 +16212,49 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128110831</v>
+        <v>128101444</v>
       </c>
       <c r="B155" t="n">
-        <v>58531</v>
+        <v>98470</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P155" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>533728</v>
+        <v>533424</v>
       </c>
       <c r="R155" t="n">
-        <v>6962422</v>
+        <v>6962351</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16304,54 +16313,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128099113</v>
+        <v>128110986</v>
       </c>
       <c r="B156" t="n">
-        <v>92642</v>
+        <v>98470</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>533396</v>
+        <v>533957</v>
       </c>
       <c r="R156" t="n">
-        <v>6962161</v>
+        <v>6962694</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Äldre ex</t>
+          <t>37 ex</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16415,32 +16415,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128102121</v>
+        <v>128102104</v>
       </c>
       <c r="B157" t="n">
-        <v>57832</v>
+        <v>105508</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16450,10 +16450,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>533532</v>
+        <v>533615</v>
       </c>
       <c r="R157" t="n">
-        <v>6962477</v>
+        <v>6962423</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17815,54 +17815,45 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128102411</v>
+        <v>128110782</v>
       </c>
       <c r="B171" t="n">
-        <v>57832</v>
+        <v>91124</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>103021</v>
+        <v>3215</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>533575</v>
+        <v>533630</v>
       </c>
       <c r="R171" t="n">
-        <v>6962520</v>
+        <v>6962701</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17921,7 +17912,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128110782</v>
+        <v>128110781</v>
       </c>
       <c r="B172" t="n">
         <v>91124</v>
@@ -17956,10 +17947,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>533630</v>
+        <v>533700</v>
       </c>
       <c r="R172" t="n">
-        <v>6962701</v>
+        <v>6962581</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18018,32 +18009,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128110781</v>
+        <v>128101262</v>
       </c>
       <c r="B173" t="n">
-        <v>91124</v>
+        <v>80132</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>3215</v>
+        <v>6458</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18053,10 +18044,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>533700</v>
+        <v>533424</v>
       </c>
       <c r="R173" t="n">
-        <v>6962581</v>
+        <v>6962357</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18115,7 +18106,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128101262</v>
+        <v>128110797</v>
       </c>
       <c r="B174" t="n">
         <v>80132</v>
@@ -18150,10 +18141,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>533424</v>
+        <v>533832</v>
       </c>
       <c r="R174" t="n">
-        <v>6962357</v>
+        <v>6962351</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18212,10 +18203,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128110797</v>
+        <v>128102411</v>
       </c>
       <c r="B175" t="n">
-        <v>80132</v>
+        <v>57832</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18223,34 +18214,43 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>533832</v>
+        <v>533575</v>
       </c>
       <c r="R175" t="n">
-        <v>6962351</v>
+        <v>6962520</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -2843,10 +2843,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128110832</v>
+        <v>128108592</v>
       </c>
       <c r="B23" t="n">
-        <v>98387</v>
+        <v>80036</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2854,34 +2854,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>219790</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533652</v>
+        <v>533675</v>
       </c>
       <c r="R23" t="n">
-        <v>6962264</v>
+        <v>6962244</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2940,49 +2940,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128101601</v>
+        <v>128110771</v>
       </c>
       <c r="B24" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533496</v>
+        <v>533583</v>
       </c>
       <c r="R24" t="n">
-        <v>6962407</v>
+        <v>6962697</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3015,6 +3011,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3041,37 +3042,38 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128108218</v>
+        <v>128109293</v>
       </c>
       <c r="B25" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3080,10 +3082,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533789</v>
+        <v>533638</v>
       </c>
       <c r="R25" t="n">
-        <v>6962263</v>
+        <v>6962157</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3116,6 +3118,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3142,10 +3149,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128108592</v>
+        <v>128110832</v>
       </c>
       <c r="B26" t="n">
-        <v>80036</v>
+        <v>98387</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3153,34 +3160,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>219790</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533675</v>
+        <v>533652</v>
       </c>
       <c r="R26" t="n">
-        <v>6962244</v>
+        <v>6962264</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3239,45 +3246,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128110771</v>
+        <v>128101601</v>
       </c>
       <c r="B27" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533583</v>
+        <v>533496</v>
       </c>
       <c r="R27" t="n">
-        <v>6962697</v>
+        <v>6962407</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3310,11 +3321,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3341,38 +3347,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128109293</v>
+        <v>128108218</v>
       </c>
       <c r="B28" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3381,10 +3386,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533638</v>
+        <v>533789</v>
       </c>
       <c r="R28" t="n">
-        <v>6962157</v>
+        <v>6962263</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3417,11 +3422,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3559,50 +3559,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128099402</v>
+        <v>128110780</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>91124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533474</v>
+        <v>533670</v>
       </c>
       <c r="R30" t="n">
-        <v>6962267</v>
+        <v>6962552</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3635,11 +3630,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3666,45 +3656,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128110780</v>
+        <v>128099402</v>
       </c>
       <c r="B31" t="n">
-        <v>91124</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533670</v>
+        <v>533474</v>
       </c>
       <c r="R31" t="n">
-        <v>6962552</v>
+        <v>6962267</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3737,6 +3732,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3763,32 +3763,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128110803</v>
+        <v>128110790</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533524</v>
+        <v>533822</v>
       </c>
       <c r="R32" t="n">
-        <v>6962153</v>
+        <v>6962344</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,7 +3865,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128110981</v>
+        <v>128110803</v>
       </c>
       <c r="B33" t="n">
         <v>98470</v>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533689</v>
+        <v>533524</v>
       </c>
       <c r="R33" t="n">
-        <v>6962405</v>
+        <v>6962153</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128109875</v>
+        <v>128110981</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -3995,21 +3995,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533436</v>
+        <v>533689</v>
       </c>
       <c r="R34" t="n">
-        <v>6962158</v>
+        <v>6962405</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4042,6 +4038,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4068,7 +4069,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128102143</v>
+        <v>128109875</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4098,7 +4099,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4107,10 +4108,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533615</v>
+        <v>533436</v>
       </c>
       <c r="R35" t="n">
-        <v>6962423</v>
+        <v>6962158</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4169,7 +4170,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128100230</v>
+        <v>128102143</v>
       </c>
       <c r="B36" t="n">
         <v>98470</v>
@@ -4199,7 +4200,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4208,10 +4209,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533506</v>
+        <v>533615</v>
       </c>
       <c r="R36" t="n">
-        <v>6962358</v>
+        <v>6962423</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,45 +4271,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128110790</v>
+        <v>128100230</v>
       </c>
       <c r="B37" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533822</v>
+        <v>533506</v>
       </c>
       <c r="R37" t="n">
-        <v>6962344</v>
+        <v>6962358</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4341,11 +4346,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5377,32 +5377,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128101106</v>
+        <v>128101702</v>
       </c>
       <c r="B48" t="n">
-        <v>80098</v>
+        <v>91352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229748</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533425</v>
+        <v>533529</v>
       </c>
       <c r="R48" t="n">
-        <v>6962304</v>
+        <v>6962400</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5474,32 +5474,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128110812</v>
+        <v>128110766</v>
       </c>
       <c r="B49" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533715</v>
+        <v>533586</v>
       </c>
       <c r="R49" t="n">
-        <v>6962610</v>
+        <v>6962139</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>60 stycken</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5576,32 +5576,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128110826</v>
+        <v>128110970</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533579</v>
+        <v>534050</v>
       </c>
       <c r="R50" t="n">
-        <v>6962663</v>
+        <v>6962743</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5678,32 +5678,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128108922</v>
+        <v>128107546</v>
       </c>
       <c r="B51" t="n">
-        <v>105508</v>
+        <v>80133</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533671</v>
+        <v>533648</v>
       </c>
       <c r="R51" t="n">
-        <v>6962142</v>
+        <v>6962374</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,45 +5775,54 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128110804</v>
+        <v>128103304</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>91124</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533532</v>
+        <v>533594</v>
       </c>
       <c r="R52" t="n">
-        <v>6962156</v>
+        <v>6962541</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5846,11 +5855,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5877,7 +5881,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128110990</v>
+        <v>128099088</v>
       </c>
       <c r="B53" t="n">
         <v>98470</v>
@@ -5905,17 +5909,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533873</v>
+        <v>533425</v>
       </c>
       <c r="R53" t="n">
-        <v>6962782</v>
+        <v>6962182</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5948,11 +5956,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5979,7 +5982,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128110814</v>
+        <v>128110812</v>
       </c>
       <c r="B54" t="n">
         <v>98470</v>
@@ -6014,10 +6017,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533650</v>
+        <v>533715</v>
       </c>
       <c r="R54" t="n">
-        <v>6962134</v>
+        <v>6962610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6054,7 +6057,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>50 stycken ( några har blommat).</t>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6081,32 +6084,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128101702</v>
+        <v>128110826</v>
       </c>
       <c r="B55" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6116,10 +6119,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533529</v>
+        <v>533579</v>
       </c>
       <c r="R55" t="n">
-        <v>6962400</v>
+        <v>6962663</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6152,6 +6155,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6178,32 +6186,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128107546</v>
+        <v>128108922</v>
       </c>
       <c r="B56" t="n">
-        <v>80133</v>
+        <v>105508</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6213,10 +6221,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533648</v>
+        <v>533671</v>
       </c>
       <c r="R56" t="n">
-        <v>6962374</v>
+        <v>6962142</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6275,54 +6283,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103304</v>
+        <v>128110804</v>
       </c>
       <c r="B57" t="n">
-        <v>91124</v>
+        <v>98470</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533594</v>
+        <v>533532</v>
       </c>
       <c r="R57" t="n">
-        <v>6962541</v>
+        <v>6962156</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6355,6 +6354,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6381,32 +6385,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128110766</v>
+        <v>128110990</v>
       </c>
       <c r="B58" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6416,10 +6420,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533586</v>
+        <v>533873</v>
       </c>
       <c r="R58" t="n">
-        <v>6962139</v>
+        <v>6962782</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6456,7 +6460,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6483,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128110970</v>
+        <v>128110814</v>
       </c>
       <c r="B59" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6518,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>534050</v>
+        <v>533650</v>
       </c>
       <c r="R59" t="n">
-        <v>6962743</v>
+        <v>6962134</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6558,7 +6562,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>50 stycken ( några har blommat).</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6585,39 +6589,35 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128099088</v>
+        <v>128101106</v>
       </c>
       <c r="B60" t="n">
-        <v>98470</v>
+        <v>80098</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>229748</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
@@ -6627,7 +6627,7 @@
         <v>533425</v>
       </c>
       <c r="R60" t="n">
-        <v>6962182</v>
+        <v>6962304</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6686,54 +6686,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128099522</v>
+        <v>128099984</v>
       </c>
       <c r="B61" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533349</v>
+        <v>533455</v>
       </c>
       <c r="R61" t="n">
-        <v>6962197</v>
+        <v>6962339</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6792,32 +6783,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128099099</v>
+        <v>128099875</v>
       </c>
       <c r="B62" t="n">
-        <v>105508</v>
+        <v>80132</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6827,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533416</v>
+        <v>533445</v>
       </c>
       <c r="R62" t="n">
-        <v>6962179</v>
+        <v>6962324</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6889,45 +6880,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128110827</v>
+        <v>128099885</v>
       </c>
       <c r="B63" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533614</v>
+        <v>533361</v>
       </c>
       <c r="R63" t="n">
-        <v>6962554</v>
+        <v>6962247</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6964,7 +6960,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6991,49 +6987,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128100184</v>
+        <v>128110971</v>
       </c>
       <c r="B64" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533509</v>
+        <v>534036</v>
       </c>
       <c r="R64" t="n">
-        <v>6962336</v>
+        <v>6962734</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7066,6 +7058,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7092,37 +7089,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128103587</v>
+        <v>128108477</v>
       </c>
       <c r="B65" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>120</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7131,10 +7129,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533650</v>
+        <v>533710</v>
       </c>
       <c r="R65" t="n">
-        <v>6962600</v>
+        <v>6962294</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7167,6 +7165,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7193,32 +7196,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128110971</v>
+        <v>128110827</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7228,10 +7231,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>534036</v>
+        <v>533614</v>
       </c>
       <c r="R66" t="n">
-        <v>6962734</v>
+        <v>6962554</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,7 +7271,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7295,50 +7298,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128108477</v>
+        <v>128100184</v>
       </c>
       <c r="B67" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533710</v>
+        <v>533509</v>
       </c>
       <c r="R67" t="n">
-        <v>6962294</v>
+        <v>6962336</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7371,11 +7373,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7402,45 +7399,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128099984</v>
+        <v>128103587</v>
       </c>
       <c r="B68" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533455</v>
+        <v>533650</v>
       </c>
       <c r="R68" t="n">
-        <v>6962339</v>
+        <v>6962600</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7499,45 +7500,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128099875</v>
+        <v>128099522</v>
       </c>
       <c r="B69" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533445</v>
+        <v>533349</v>
       </c>
       <c r="R69" t="n">
-        <v>6962324</v>
+        <v>6962197</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7596,50 +7606,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128099885</v>
+        <v>128099099</v>
       </c>
       <c r="B70" t="n">
-        <v>57672</v>
+        <v>105508</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533361</v>
+        <v>533416</v>
       </c>
       <c r="R70" t="n">
-        <v>6962247</v>
+        <v>6962179</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7672,11 +7677,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8625,32 +8625,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128110982</v>
+        <v>128110779</v>
       </c>
       <c r="B80" t="n">
-        <v>98470</v>
+        <v>91124</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533681</v>
+        <v>533678</v>
       </c>
       <c r="R80" t="n">
-        <v>6962434</v>
+        <v>6962542</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8696,11 +8696,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>23 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8727,45 +8722,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128110810</v>
+        <v>128101827</v>
       </c>
       <c r="B81" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533645</v>
+        <v>533594</v>
       </c>
       <c r="R81" t="n">
-        <v>6962593</v>
+        <v>6962354</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8798,6 +8798,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8824,45 +8829,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128110976</v>
+        <v>128100974</v>
       </c>
       <c r="B82" t="n">
-        <v>98504</v>
+        <v>57672</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533868</v>
+        <v>533375</v>
       </c>
       <c r="R82" t="n">
-        <v>6962692</v>
+        <v>6962293</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8899,7 +8909,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Växer spritt i hela området</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8926,49 +8936,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128101261</v>
+        <v>128110969</v>
       </c>
       <c r="B83" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533424</v>
+        <v>533825</v>
       </c>
       <c r="R83" t="n">
-        <v>6962357</v>
+        <v>6962690</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9001,6 +9007,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9027,10 +9038,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128099905</v>
+        <v>128102006</v>
       </c>
       <c r="B84" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9038,39 +9049,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533445</v>
+        <v>533510</v>
       </c>
       <c r="R84" t="n">
-        <v>6962324</v>
+        <v>6962462</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9103,11 +9109,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9134,45 +9135,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128110779</v>
+        <v>128099905</v>
       </c>
       <c r="B85" t="n">
-        <v>91124</v>
+        <v>57672</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533678</v>
+        <v>533445</v>
       </c>
       <c r="R85" t="n">
-        <v>6962542</v>
+        <v>6962324</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9205,6 +9211,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9231,32 +9242,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128102006</v>
+        <v>128110976</v>
       </c>
       <c r="B86" t="n">
-        <v>80132</v>
+        <v>98504</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9266,10 +9277,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533510</v>
+        <v>533868</v>
       </c>
       <c r="R86" t="n">
-        <v>6962462</v>
+        <v>6962692</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9302,6 +9313,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9328,38 +9344,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128101827</v>
+        <v>128101261</v>
       </c>
       <c r="B87" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9368,10 +9383,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533594</v>
+        <v>533424</v>
       </c>
       <c r="R87" t="n">
-        <v>6962354</v>
+        <v>6962357</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9404,11 +9419,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9435,50 +9445,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128100974</v>
+        <v>128110982</v>
       </c>
       <c r="B88" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533375</v>
+        <v>533681</v>
       </c>
       <c r="R88" t="n">
-        <v>6962293</v>
+        <v>6962434</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9515,7 +9520,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
+          <t>23 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9542,32 +9547,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128110969</v>
+        <v>128110810</v>
       </c>
       <c r="B89" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9577,10 +9582,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533825</v>
+        <v>533645</v>
       </c>
       <c r="R89" t="n">
-        <v>6962690</v>
+        <v>6962593</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9613,11 +9618,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10871,32 +10871,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128110792</v>
+        <v>128110829</v>
       </c>
       <c r="B102" t="n">
-        <v>98504</v>
+        <v>56855</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219874</v>
+        <v>102612</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10906,10 +10906,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>533719</v>
+        <v>533606</v>
       </c>
       <c r="R102" t="n">
-        <v>6962615</v>
+        <v>6962582</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11177,32 +11177,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128110829</v>
+        <v>128101073</v>
       </c>
       <c r="B105" t="n">
-        <v>56855</v>
+        <v>80168</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102612</v>
+        <v>6464</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11212,10 +11212,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>533606</v>
+        <v>533385</v>
       </c>
       <c r="R105" t="n">
-        <v>6962582</v>
+        <v>6962288</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11248,11 +11248,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11279,10 +11274,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128110785</v>
+        <v>128110792</v>
       </c>
       <c r="B106" t="n">
-        <v>97347</v>
+        <v>98504</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11290,21 +11285,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11314,10 +11309,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>533824</v>
+        <v>533719</v>
       </c>
       <c r="R106" t="n">
-        <v>6962352</v>
+        <v>6962615</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11350,6 +11345,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11376,10 +11376,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128101073</v>
+        <v>128110785</v>
       </c>
       <c r="B107" t="n">
-        <v>80168</v>
+        <v>97347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11387,21 +11387,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11411,10 +11411,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533385</v>
+        <v>533824</v>
       </c>
       <c r="R107" t="n">
-        <v>6962288</v>
+        <v>6962352</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11473,45 +11473,49 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128108028</v>
+        <v>128099487</v>
       </c>
       <c r="B108" t="n">
-        <v>97353</v>
+        <v>98470</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533802</v>
+        <v>533474</v>
       </c>
       <c r="R108" t="n">
-        <v>6962332</v>
+        <v>6962267</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11570,10 +11574,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128108378</v>
+        <v>128110776</v>
       </c>
       <c r="B109" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11581,39 +11585,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533750</v>
+        <v>533719</v>
       </c>
       <c r="R109" t="n">
-        <v>6962259</v>
+        <v>6962615</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11650,7 +11649,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11677,50 +11676,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128100457</v>
+        <v>128110987</v>
       </c>
       <c r="B110" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533556</v>
+        <v>533999</v>
       </c>
       <c r="R110" t="n">
-        <v>6962363</v>
+        <v>6962664</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11757,7 +11751,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11784,45 +11778,49 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128110776</v>
+        <v>128103044</v>
       </c>
       <c r="B111" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>533719</v>
+        <v>533627</v>
       </c>
       <c r="R111" t="n">
-        <v>6962615</v>
+        <v>6962544</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11855,11 +11853,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11886,32 +11879,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128110838</v>
+        <v>128110819</v>
       </c>
       <c r="B112" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11921,10 +11914,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>533708</v>
+        <v>533834</v>
       </c>
       <c r="R112" t="n">
-        <v>6962624</v>
+        <v>6962298</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11961,7 +11954,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>1 stycken</t>
+          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11988,10 +11981,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128110793</v>
+        <v>128108028</v>
       </c>
       <c r="B113" t="n">
-        <v>98504</v>
+        <v>97353</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11999,34 +11992,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219874</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533693</v>
+        <v>533802</v>
       </c>
       <c r="R113" t="n">
-        <v>6962647</v>
+        <v>6962332</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12059,11 +12052,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12090,10 +12078,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128110794</v>
+        <v>128110783</v>
       </c>
       <c r="B114" t="n">
-        <v>98504</v>
+        <v>91124</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12101,21 +12089,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12125,10 +12113,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533608</v>
+        <v>533599</v>
       </c>
       <c r="R114" t="n">
-        <v>6962612</v>
+        <v>6962553</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12161,11 +12149,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12192,45 +12175,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128110991</v>
+        <v>128108378</v>
       </c>
       <c r="B115" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533717</v>
+        <v>533750</v>
       </c>
       <c r="R115" t="n">
-        <v>6962645</v>
+        <v>6962259</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12267,7 +12255,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12294,45 +12282,50 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103993</v>
+        <v>128100457</v>
       </c>
       <c r="B116" t="n">
-        <v>105508</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533664</v>
+        <v>533556</v>
       </c>
       <c r="R116" t="n">
-        <v>6962650</v>
+        <v>6962363</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12365,6 +12358,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12391,32 +12389,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128110987</v>
+        <v>128110838</v>
       </c>
       <c r="B117" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12426,10 +12424,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533999</v>
+        <v>533708</v>
       </c>
       <c r="R117" t="n">
-        <v>6962664</v>
+        <v>6962624</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12466,7 +12464,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12493,49 +12491,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103044</v>
+        <v>128110793</v>
       </c>
       <c r="B118" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533627</v>
+        <v>533693</v>
       </c>
       <c r="R118" t="n">
-        <v>6962544</v>
+        <v>6962647</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12568,6 +12562,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12594,32 +12593,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128110819</v>
+        <v>128110794</v>
       </c>
       <c r="B119" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12629,10 +12628,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533834</v>
+        <v>533608</v>
       </c>
       <c r="R119" t="n">
-        <v>6962298</v>
+        <v>6962612</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12669,7 +12668,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>10 stycken kan finnas fler runt omkring</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12696,32 +12695,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128101331</v>
+        <v>128110991</v>
       </c>
       <c r="B120" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12731,10 +12730,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533424</v>
+        <v>533717</v>
       </c>
       <c r="R120" t="n">
-        <v>6962357</v>
+        <v>6962645</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12767,6 +12766,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12793,32 +12797,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128108395</v>
+        <v>128103993</v>
       </c>
       <c r="B121" t="n">
-        <v>80132</v>
+        <v>105508</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12828,10 +12832,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533735</v>
+        <v>533664</v>
       </c>
       <c r="R121" t="n">
-        <v>6962274</v>
+        <v>6962650</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12890,10 +12894,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128110783</v>
+        <v>128101331</v>
       </c>
       <c r="B122" t="n">
-        <v>91124</v>
+        <v>80167</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12901,21 +12905,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3215</v>
+        <v>6463</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12925,10 +12929,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533599</v>
+        <v>533424</v>
       </c>
       <c r="R122" t="n">
-        <v>6962553</v>
+        <v>6962357</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12987,49 +12991,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128099487</v>
+        <v>128108395</v>
       </c>
       <c r="B123" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>533474</v>
+        <v>533735</v>
       </c>
       <c r="R123" t="n">
-        <v>6962267</v>
+        <v>6962274</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13486,10 +13486,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128100396</v>
+        <v>128099239</v>
       </c>
       <c r="B128" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13497,27 +13497,27 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -13526,10 +13526,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>533537</v>
+        <v>533422</v>
       </c>
       <c r="R128" t="n">
-        <v>6962358</v>
+        <v>6962229</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13562,6 +13562,11 @@
       <c r="AA128" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13588,50 +13593,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128099239</v>
+        <v>128109488</v>
       </c>
       <c r="B129" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P129" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>533422</v>
+        <v>533498</v>
       </c>
       <c r="R129" t="n">
-        <v>6962229</v>
+        <v>6962158</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13664,11 +13664,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13695,10 +13690,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128109488</v>
+        <v>128109254</v>
       </c>
       <c r="B130" t="n">
-        <v>80161</v>
+        <v>80160</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13706,34 +13701,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>533498</v>
+        <v>533652</v>
       </c>
       <c r="R130" t="n">
-        <v>6962158</v>
+        <v>6962140</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13792,10 +13787,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128109254</v>
+        <v>128099811</v>
       </c>
       <c r="B131" t="n">
-        <v>80160</v>
+        <v>105508</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13803,34 +13798,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6461</v>
+        <v>221144</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>533652</v>
+        <v>533451</v>
       </c>
       <c r="R131" t="n">
-        <v>6962140</v>
+        <v>6962307</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13889,45 +13884,50 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128099811</v>
+        <v>128100396</v>
       </c>
       <c r="B132" t="n">
-        <v>105508</v>
+        <v>57832</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>533451</v>
+        <v>533537</v>
       </c>
       <c r="R132" t="n">
-        <v>6962307</v>
+        <v>6962358</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13986,45 +13986,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128103617</v>
+        <v>128110809</v>
       </c>
       <c r="B133" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>533637</v>
+        <v>533748</v>
       </c>
       <c r="R133" t="n">
-        <v>6962600</v>
+        <v>6962494</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14057,6 +14057,11 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14083,32 +14088,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128110809</v>
+        <v>128110830</v>
       </c>
       <c r="B134" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14118,10 +14123,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>533748</v>
+        <v>533659</v>
       </c>
       <c r="R134" t="n">
-        <v>6962494</v>
+        <v>6962296</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14154,11 +14159,6 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14185,32 +14185,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128100350</v>
+        <v>128110808</v>
       </c>
       <c r="B135" t="n">
-        <v>97347</v>
+        <v>98470</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14220,10 +14220,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>533545</v>
+        <v>533745</v>
       </c>
       <c r="R135" t="n">
-        <v>6962339</v>
+        <v>6962429</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14256,6 +14256,11 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14282,45 +14287,49 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128110830</v>
+        <v>128107880</v>
       </c>
       <c r="B136" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>533659</v>
+        <v>533736</v>
       </c>
       <c r="R136" t="n">
-        <v>6962296</v>
+        <v>6962362</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14379,7 +14388,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128110808</v>
+        <v>128110984</v>
       </c>
       <c r="B137" t="n">
         <v>98470</v>
@@ -14414,10 +14423,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>533745</v>
+        <v>533734</v>
       </c>
       <c r="R137" t="n">
-        <v>6962429</v>
+        <v>6962473</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14454,7 +14463,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>22 stycken</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14481,49 +14490,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128107880</v>
+        <v>128100350</v>
       </c>
       <c r="B138" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>533736</v>
+        <v>533545</v>
       </c>
       <c r="R138" t="n">
-        <v>6962362</v>
+        <v>6962339</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14582,45 +14587,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128110984</v>
+        <v>128103617</v>
       </c>
       <c r="B139" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>533734</v>
+        <v>533637</v>
       </c>
       <c r="R139" t="n">
-        <v>6962473</v>
+        <v>6962600</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14653,11 +14658,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -18309,32 +18309,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128110787</v>
+        <v>128110828</v>
       </c>
       <c r="B176" t="n">
-        <v>80160</v>
+        <v>98470</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18344,10 +18344,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>533785</v>
+        <v>533365</v>
       </c>
       <c r="R176" t="n">
-        <v>6962326</v>
+        <v>6962304</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18380,6 +18380,11 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18406,45 +18411,49 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128101075</v>
+        <v>128107826</v>
       </c>
       <c r="B177" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>533392</v>
+        <v>533723</v>
       </c>
       <c r="R177" t="n">
-        <v>6962343</v>
+        <v>6962360</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18503,50 +18512,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128108439</v>
+        <v>128110817</v>
       </c>
       <c r="B178" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>533711</v>
+        <v>533728</v>
       </c>
       <c r="R178" t="n">
-        <v>6962283</v>
+        <v>6962346</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18583,7 +18587,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18610,50 +18614,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128101939</v>
+        <v>128110835</v>
       </c>
       <c r="B179" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>533638</v>
+        <v>533748</v>
       </c>
       <c r="R179" t="n">
-        <v>6962346</v>
+        <v>6962431</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18686,11 +18685,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18717,50 +18711,45 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128100413</v>
+        <v>128110977</v>
       </c>
       <c r="B180" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>533545</v>
+        <v>534040</v>
       </c>
       <c r="R180" t="n">
-        <v>6962372</v>
+        <v>6962718</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18793,11 +18782,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18824,32 +18808,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128110828</v>
+        <v>128110799</v>
       </c>
       <c r="B181" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18859,10 +18843,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>533365</v>
+        <v>533724</v>
       </c>
       <c r="R181" t="n">
-        <v>6962304</v>
+        <v>6962625</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18895,11 +18879,6 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18926,49 +18905,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128107826</v>
+        <v>128110787</v>
       </c>
       <c r="B182" t="n">
-        <v>98470</v>
+        <v>80160</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>533723</v>
+        <v>533785</v>
       </c>
       <c r="R182" t="n">
-        <v>6962360</v>
+        <v>6962326</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19027,32 +19002,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128110817</v>
+        <v>128101075</v>
       </c>
       <c r="B183" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19062,10 +19037,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>533728</v>
+        <v>533392</v>
       </c>
       <c r="R183" t="n">
-        <v>6962346</v>
+        <v>6962343</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19098,11 +19073,6 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19129,10 +19099,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128110799</v>
+        <v>128108439</v>
       </c>
       <c r="B184" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19140,34 +19110,39 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>533724</v>
+        <v>533711</v>
       </c>
       <c r="R184" t="n">
-        <v>6962625</v>
+        <v>6962283</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19200,6 +19175,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19226,45 +19206,50 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128110835</v>
+        <v>128101939</v>
       </c>
       <c r="B185" t="n">
-        <v>98387</v>
+        <v>57672</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>533748</v>
+        <v>533638</v>
       </c>
       <c r="R185" t="n">
-        <v>6962431</v>
+        <v>6962346</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19297,6 +19282,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19323,45 +19313,50 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128110977</v>
+        <v>128100413</v>
       </c>
       <c r="B186" t="n">
-        <v>98504</v>
+        <v>57672</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>534040</v>
+        <v>533545</v>
       </c>
       <c r="R186" t="n">
-        <v>6962718</v>
+        <v>6962372</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19394,6 +19389,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD186" t="b">

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -3559,45 +3559,50 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128110780</v>
+        <v>128099402</v>
       </c>
       <c r="B30" t="n">
-        <v>91124</v>
+        <v>57672</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533670</v>
+        <v>533474</v>
       </c>
       <c r="R30" t="n">
-        <v>6962552</v>
+        <v>6962267</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3630,6 +3635,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3656,50 +3666,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128099402</v>
+        <v>128110780</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>91124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533474</v>
+        <v>533670</v>
       </c>
       <c r="R31" t="n">
-        <v>6962267</v>
+        <v>6962552</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3732,11 +3737,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3763,32 +3763,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128110790</v>
+        <v>128110803</v>
       </c>
       <c r="B32" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533822</v>
+        <v>533524</v>
       </c>
       <c r="R32" t="n">
-        <v>6962344</v>
+        <v>6962153</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,7 +3865,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128110803</v>
+        <v>128110981</v>
       </c>
       <c r="B33" t="n">
         <v>98470</v>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533524</v>
+        <v>533689</v>
       </c>
       <c r="R33" t="n">
-        <v>6962153</v>
+        <v>6962405</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128110981</v>
+        <v>128109875</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -3995,17 +3995,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533689</v>
+        <v>533436</v>
       </c>
       <c r="R34" t="n">
-        <v>6962405</v>
+        <v>6962158</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,11 +4042,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4069,7 +4068,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128109875</v>
+        <v>128102143</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4099,7 +4098,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4108,10 +4107,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533436</v>
+        <v>533615</v>
       </c>
       <c r="R35" t="n">
-        <v>6962158</v>
+        <v>6962423</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4170,7 +4169,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128102143</v>
+        <v>128100230</v>
       </c>
       <c r="B36" t="n">
         <v>98470</v>
@@ -4200,7 +4199,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4209,10 +4208,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533615</v>
+        <v>533506</v>
       </c>
       <c r="R36" t="n">
-        <v>6962423</v>
+        <v>6962358</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4271,49 +4270,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128100230</v>
+        <v>128110790</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533506</v>
+        <v>533822</v>
       </c>
       <c r="R37" t="n">
-        <v>6962358</v>
+        <v>6962344</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4346,6 +4341,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4372,32 +4372,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128099282</v>
+        <v>128110968</v>
       </c>
       <c r="B38" t="n">
-        <v>80160</v>
+        <v>57672</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533452</v>
+        <v>533634</v>
       </c>
       <c r="R38" t="n">
-        <v>6962232</v>
+        <v>6962526</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4443,6 +4443,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4469,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128110978</v>
+        <v>128099282</v>
       </c>
       <c r="B39" t="n">
-        <v>98504</v>
+        <v>80160</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4480,21 +4485,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219874</v>
+        <v>6461</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4504,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533708</v>
+        <v>533452</v>
       </c>
       <c r="R39" t="n">
-        <v>6962645</v>
+        <v>6962232</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4566,45 +4571,50 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128110788</v>
+        <v>128102724</v>
       </c>
       <c r="B40" t="n">
-        <v>98504</v>
+        <v>57672</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533590</v>
+        <v>533659</v>
       </c>
       <c r="R40" t="n">
-        <v>6962592</v>
+        <v>6962512</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4637,6 +4647,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4663,45 +4678,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128110836</v>
+        <v>128101831</v>
       </c>
       <c r="B41" t="n">
-        <v>98387</v>
+        <v>57672</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533722</v>
+        <v>533513</v>
       </c>
       <c r="R41" t="n">
-        <v>6962426</v>
+        <v>6962442</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4734,6 +4754,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4760,45 +4785,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128108150</v>
+        <v>128110767</v>
       </c>
       <c r="B42" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533800</v>
+        <v>533794</v>
       </c>
       <c r="R42" t="n">
-        <v>6962306</v>
+        <v>6962411</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4831,6 +4856,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4857,50 +4887,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128102724</v>
+        <v>128110978</v>
       </c>
       <c r="B43" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533659</v>
+        <v>533708</v>
       </c>
       <c r="R43" t="n">
-        <v>6962512</v>
+        <v>6962645</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4933,11 +4958,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4964,50 +4984,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128101831</v>
+        <v>128110788</v>
       </c>
       <c r="B44" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533513</v>
+        <v>533590</v>
       </c>
       <c r="R44" t="n">
-        <v>6962442</v>
+        <v>6962592</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5040,11 +5055,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5071,32 +5081,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128110767</v>
+        <v>128110824</v>
       </c>
       <c r="B45" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5106,10 +5116,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533794</v>
+        <v>533712</v>
       </c>
       <c r="R45" t="n">
-        <v>6962411</v>
+        <v>6962628</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5146,7 +5156,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5173,32 +5183,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128110968</v>
+        <v>128110836</v>
       </c>
       <c r="B46" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5208,10 +5218,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533634</v>
+        <v>533722</v>
       </c>
       <c r="R46" t="n">
-        <v>6962526</v>
+        <v>6962426</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5244,11 +5254,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5275,45 +5280,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128110824</v>
+        <v>128108150</v>
       </c>
       <c r="B47" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533712</v>
+        <v>533800</v>
       </c>
       <c r="R47" t="n">
-        <v>6962628</v>
+        <v>6962306</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5346,11 +5351,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5377,32 +5377,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128101702</v>
+        <v>128101106</v>
       </c>
       <c r="B48" t="n">
-        <v>91352</v>
+        <v>80098</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>229748</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533529</v>
+        <v>533425</v>
       </c>
       <c r="R48" t="n">
-        <v>6962400</v>
+        <v>6962304</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5474,32 +5474,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128110766</v>
+        <v>128110812</v>
       </c>
       <c r="B49" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533586</v>
+        <v>533715</v>
       </c>
       <c r="R49" t="n">
-        <v>6962139</v>
+        <v>6962610</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5576,32 +5576,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128110970</v>
+        <v>128110826</v>
       </c>
       <c r="B50" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,10 +5611,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>534050</v>
+        <v>533579</v>
       </c>
       <c r="R50" t="n">
-        <v>6962743</v>
+        <v>6962663</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5678,32 +5678,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128107546</v>
+        <v>128108922</v>
       </c>
       <c r="B51" t="n">
-        <v>80133</v>
+        <v>105508</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5713,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533648</v>
+        <v>533671</v>
       </c>
       <c r="R51" t="n">
-        <v>6962374</v>
+        <v>6962142</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,54 +5775,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128103304</v>
+        <v>128110804</v>
       </c>
       <c r="B52" t="n">
-        <v>91124</v>
+        <v>98470</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533594</v>
+        <v>533532</v>
       </c>
       <c r="R52" t="n">
-        <v>6962541</v>
+        <v>6962156</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5855,6 +5846,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5881,7 +5877,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128099088</v>
+        <v>128110990</v>
       </c>
       <c r="B53" t="n">
         <v>98470</v>
@@ -5909,21 +5905,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533425</v>
+        <v>533873</v>
       </c>
       <c r="R53" t="n">
-        <v>6962182</v>
+        <v>6962782</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5956,6 +5948,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5982,7 +5979,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128110812</v>
+        <v>128110814</v>
       </c>
       <c r="B54" t="n">
         <v>98470</v>
@@ -6017,10 +6014,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533715</v>
+        <v>533650</v>
       </c>
       <c r="R54" t="n">
-        <v>6962610</v>
+        <v>6962134</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6057,7 +6054,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>60 stycken</t>
+          <t>50 stycken ( några har blommat).</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6084,32 +6081,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128110826</v>
+        <v>128101702</v>
       </c>
       <c r="B55" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6119,10 +6116,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533579</v>
+        <v>533529</v>
       </c>
       <c r="R55" t="n">
-        <v>6962663</v>
+        <v>6962400</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6155,11 +6152,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6186,32 +6178,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128108922</v>
+        <v>128107546</v>
       </c>
       <c r="B56" t="n">
-        <v>105508</v>
+        <v>80133</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6221,10 +6213,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533671</v>
+        <v>533648</v>
       </c>
       <c r="R56" t="n">
-        <v>6962142</v>
+        <v>6962374</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6283,45 +6275,54 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128110804</v>
+        <v>128103304</v>
       </c>
       <c r="B57" t="n">
-        <v>98470</v>
+        <v>91124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533532</v>
+        <v>533594</v>
       </c>
       <c r="R57" t="n">
-        <v>6962156</v>
+        <v>6962541</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6354,11 +6355,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6385,32 +6381,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128110990</v>
+        <v>128110766</v>
       </c>
       <c r="B58" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6420,10 +6416,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533873</v>
+        <v>533586</v>
       </c>
       <c r="R58" t="n">
-        <v>6962782</v>
+        <v>6962139</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6460,7 +6456,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6487,32 +6483,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128110814</v>
+        <v>128110970</v>
       </c>
       <c r="B59" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6522,10 +6518,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533650</v>
+        <v>534050</v>
       </c>
       <c r="R59" t="n">
-        <v>6962134</v>
+        <v>6962743</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6562,7 +6558,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>50 stycken ( några har blommat).</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6589,35 +6585,39 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128101106</v>
+        <v>128099088</v>
       </c>
       <c r="B60" t="n">
-        <v>80098</v>
+        <v>98470</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229748</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
@@ -6627,7 +6627,7 @@
         <v>533425</v>
       </c>
       <c r="R60" t="n">
-        <v>6962304</v>
+        <v>6962182</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6686,45 +6686,54 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128099984</v>
+        <v>128099522</v>
       </c>
       <c r="B61" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533455</v>
+        <v>533349</v>
       </c>
       <c r="R61" t="n">
-        <v>6962339</v>
+        <v>6962197</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6783,32 +6792,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128099875</v>
+        <v>128099099</v>
       </c>
       <c r="B62" t="n">
-        <v>80132</v>
+        <v>105508</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6818,10 +6827,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533445</v>
+        <v>533416</v>
       </c>
       <c r="R62" t="n">
-        <v>6962324</v>
+        <v>6962179</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6880,50 +6889,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128099885</v>
+        <v>128110827</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533361</v>
+        <v>533614</v>
       </c>
       <c r="R63" t="n">
-        <v>6962247</v>
+        <v>6962554</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6960,7 +6964,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6987,45 +6991,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128110971</v>
+        <v>128100184</v>
       </c>
       <c r="B64" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>534036</v>
+        <v>533509</v>
       </c>
       <c r="R64" t="n">
-        <v>6962734</v>
+        <v>6962336</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7058,11 +7066,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7089,38 +7092,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128108477</v>
+        <v>128103587</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>120</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7129,10 +7131,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533710</v>
+        <v>533650</v>
       </c>
       <c r="R65" t="n">
-        <v>6962294</v>
+        <v>6962600</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7165,11 +7167,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7196,32 +7193,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128110827</v>
+        <v>128110971</v>
       </c>
       <c r="B66" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7231,10 +7228,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533614</v>
+        <v>534036</v>
       </c>
       <c r="R66" t="n">
-        <v>6962554</v>
+        <v>6962734</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,7 +7268,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7298,49 +7295,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128100184</v>
+        <v>128108477</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533509</v>
+        <v>533710</v>
       </c>
       <c r="R67" t="n">
-        <v>6962336</v>
+        <v>6962294</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7373,6 +7371,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7399,49 +7402,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128103587</v>
+        <v>128099984</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533650</v>
+        <v>533455</v>
       </c>
       <c r="R68" t="n">
-        <v>6962600</v>
+        <v>6962339</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7500,54 +7499,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128099522</v>
+        <v>128099875</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533349</v>
+        <v>533445</v>
       </c>
       <c r="R69" t="n">
-        <v>6962197</v>
+        <v>6962324</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7606,45 +7596,50 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128099099</v>
+        <v>128099885</v>
       </c>
       <c r="B70" t="n">
-        <v>105508</v>
+        <v>57672</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533416</v>
+        <v>533361</v>
       </c>
       <c r="R70" t="n">
-        <v>6962179</v>
+        <v>6962247</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7677,6 +7672,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7800,50 +7800,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128099712</v>
+        <v>128099857</v>
       </c>
       <c r="B72" t="n">
-        <v>57672</v>
+        <v>80161</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533451</v>
+        <v>533445</v>
       </c>
       <c r="R72" t="n">
-        <v>6962307</v>
+        <v>6962324</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7876,11 +7871,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8325,32 +8315,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128099857</v>
+        <v>128110811</v>
       </c>
       <c r="B77" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8360,10 +8350,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533445</v>
+        <v>533706</v>
       </c>
       <c r="R77" t="n">
-        <v>6962324</v>
+        <v>6962596</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8396,6 +8386,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>24 stycken</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8422,7 +8417,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128110811</v>
+        <v>128101024</v>
       </c>
       <c r="B78" t="n">
         <v>98470</v>
@@ -8450,17 +8445,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533706</v>
+        <v>533375</v>
       </c>
       <c r="R78" t="n">
-        <v>6962596</v>
+        <v>6962293</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8493,11 +8492,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>24 stycken</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8524,37 +8518,38 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128101024</v>
+        <v>128099712</v>
       </c>
       <c r="B79" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8563,10 +8558,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533375</v>
+        <v>533451</v>
       </c>
       <c r="R79" t="n">
-        <v>6962293</v>
+        <v>6962307</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8599,6 +8594,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8625,32 +8625,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128110779</v>
+        <v>128110982</v>
       </c>
       <c r="B80" t="n">
-        <v>91124</v>
+        <v>98470</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533678</v>
+        <v>533681</v>
       </c>
       <c r="R80" t="n">
-        <v>6962542</v>
+        <v>6962434</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8696,6 +8696,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>23 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8722,50 +8727,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128101827</v>
+        <v>128110810</v>
       </c>
       <c r="B81" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533594</v>
+        <v>533645</v>
       </c>
       <c r="R81" t="n">
-        <v>6962354</v>
+        <v>6962593</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8798,11 +8798,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8829,50 +8824,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128100974</v>
+        <v>128110976</v>
       </c>
       <c r="B82" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533375</v>
+        <v>533868</v>
       </c>
       <c r="R82" t="n">
-        <v>6962293</v>
+        <v>6962692</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8909,7 +8899,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
+          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8936,45 +8926,49 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128110969</v>
+        <v>128101261</v>
       </c>
       <c r="B83" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533825</v>
+        <v>533424</v>
       </c>
       <c r="R83" t="n">
-        <v>6962690</v>
+        <v>6962357</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9007,11 +9001,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9038,10 +9027,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128102006</v>
+        <v>128099905</v>
       </c>
       <c r="B84" t="n">
-        <v>80132</v>
+        <v>57672</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9049,34 +9038,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533510</v>
+        <v>533445</v>
       </c>
       <c r="R84" t="n">
-        <v>6962462</v>
+        <v>6962324</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9109,6 +9103,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9135,50 +9134,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128099905</v>
+        <v>128110779</v>
       </c>
       <c r="B85" t="n">
-        <v>57672</v>
+        <v>91124</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533445</v>
+        <v>533678</v>
       </c>
       <c r="R85" t="n">
-        <v>6962324</v>
+        <v>6962542</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9211,11 +9205,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9242,32 +9231,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128110976</v>
+        <v>128102006</v>
       </c>
       <c r="B86" t="n">
-        <v>98504</v>
+        <v>80132</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9277,10 +9266,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533868</v>
+        <v>533510</v>
       </c>
       <c r="R86" t="n">
-        <v>6962692</v>
+        <v>6962462</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9313,11 +9302,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9344,37 +9328,38 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128101261</v>
+        <v>128101827</v>
       </c>
       <c r="B87" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9383,10 +9368,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533424</v>
+        <v>533594</v>
       </c>
       <c r="R87" t="n">
-        <v>6962357</v>
+        <v>6962354</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9419,6 +9404,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9445,45 +9435,50 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128110982</v>
+        <v>128100974</v>
       </c>
       <c r="B88" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533681</v>
+        <v>533375</v>
       </c>
       <c r="R88" t="n">
-        <v>6962434</v>
+        <v>6962293</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9520,7 +9515,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>23 ex</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9547,32 +9542,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128110810</v>
+        <v>128110969</v>
       </c>
       <c r="B89" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9582,10 +9577,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533645</v>
+        <v>533825</v>
       </c>
       <c r="R89" t="n">
-        <v>6962593</v>
+        <v>6962690</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9618,6 +9613,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10047,10 +10047,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128099401</v>
+        <v>128110834</v>
       </c>
       <c r="B94" t="n">
-        <v>92642</v>
+        <v>98387</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10058,43 +10058,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>219790</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533356</v>
+        <v>533779</v>
       </c>
       <c r="R94" t="n">
-        <v>6962190</v>
+        <v>6962298</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10153,50 +10144,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128099555</v>
+        <v>128110816</v>
       </c>
       <c r="B95" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533471</v>
+        <v>533696</v>
       </c>
       <c r="R95" t="n">
-        <v>6962293</v>
+        <v>6962294</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10233,7 +10219,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>Både äldre och färska ringhack på tall</t>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10260,50 +10246,49 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128102878</v>
+        <v>128102067</v>
       </c>
       <c r="B96" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533665</v>
+        <v>533510</v>
       </c>
       <c r="R96" t="n">
-        <v>6962515</v>
+        <v>6962462</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10336,11 +10321,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10367,38 +10347,42 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128100043</v>
+        <v>128099401</v>
       </c>
       <c r="B97" t="n">
-        <v>57672</v>
+        <v>92642</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10407,10 +10391,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533496</v>
+        <v>533356</v>
       </c>
       <c r="R97" t="n">
-        <v>6962335</v>
+        <v>6962190</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10443,11 +10427,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10571,45 +10550,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128110834</v>
+        <v>128099555</v>
       </c>
       <c r="B99" t="n">
-        <v>98387</v>
+        <v>57672</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>533779</v>
+        <v>533471</v>
       </c>
       <c r="R99" t="n">
-        <v>6962298</v>
+        <v>6962293</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10642,6 +10626,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10668,45 +10657,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128110816</v>
+        <v>128102878</v>
       </c>
       <c r="B100" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>533696</v>
+        <v>533665</v>
       </c>
       <c r="R100" t="n">
-        <v>6962294</v>
+        <v>6962515</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10743,7 +10737,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>20 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10770,37 +10764,38 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128102067</v>
+        <v>128100043</v>
       </c>
       <c r="B101" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -10809,10 +10804,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533510</v>
+        <v>533496</v>
       </c>
       <c r="R101" t="n">
-        <v>6962462</v>
+        <v>6962335</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10845,6 +10840,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10871,32 +10871,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128110829</v>
+        <v>128110792</v>
       </c>
       <c r="B102" t="n">
-        <v>56855</v>
+        <v>98504</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>102612</v>
+        <v>219874</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10906,10 +10906,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>533606</v>
+        <v>533719</v>
       </c>
       <c r="R102" t="n">
-        <v>6962582</v>
+        <v>6962615</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>1 ex. Sång</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11177,32 +11177,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128101073</v>
+        <v>128110829</v>
       </c>
       <c r="B105" t="n">
-        <v>80168</v>
+        <v>56855</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11212,10 +11212,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>533385</v>
+        <v>533606</v>
       </c>
       <c r="R105" t="n">
-        <v>6962288</v>
+        <v>6962582</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11248,6 +11248,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11274,10 +11279,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128110792</v>
+        <v>128110785</v>
       </c>
       <c r="B106" t="n">
-        <v>98504</v>
+        <v>97347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11285,21 +11290,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11309,10 +11314,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>533719</v>
+        <v>533824</v>
       </c>
       <c r="R106" t="n">
-        <v>6962615</v>
+        <v>6962352</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11345,11 +11350,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11376,10 +11376,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128110785</v>
+        <v>128101073</v>
       </c>
       <c r="B107" t="n">
-        <v>97347</v>
+        <v>80168</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11387,21 +11387,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11411,10 +11411,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533824</v>
+        <v>533385</v>
       </c>
       <c r="R107" t="n">
-        <v>6962352</v>
+        <v>6962288</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11473,49 +11473,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128099487</v>
+        <v>128108028</v>
       </c>
       <c r="B108" t="n">
-        <v>98470</v>
+        <v>97353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533474</v>
+        <v>533802</v>
       </c>
       <c r="R108" t="n">
-        <v>6962267</v>
+        <v>6962332</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11574,10 +11570,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128110776</v>
+        <v>128108378</v>
       </c>
       <c r="B109" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11585,34 +11581,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533719</v>
+        <v>533750</v>
       </c>
       <c r="R109" t="n">
-        <v>6962615</v>
+        <v>6962259</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11649,7 +11650,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11676,45 +11677,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128110987</v>
+        <v>128100457</v>
       </c>
       <c r="B110" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533999</v>
+        <v>533556</v>
       </c>
       <c r="R110" t="n">
-        <v>6962664</v>
+        <v>6962363</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11751,7 +11757,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11778,49 +11784,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103044</v>
+        <v>128110776</v>
       </c>
       <c r="B111" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>533627</v>
+        <v>533719</v>
       </c>
       <c r="R111" t="n">
-        <v>6962544</v>
+        <v>6962615</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11853,6 +11855,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11879,32 +11886,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128110819</v>
+        <v>128110838</v>
       </c>
       <c r="B112" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11914,10 +11921,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>533834</v>
+        <v>533708</v>
       </c>
       <c r="R112" t="n">
-        <v>6962298</v>
+        <v>6962624</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11954,7 +11961,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>10 stycken kan finnas fler runt omkring</t>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11981,10 +11988,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128108028</v>
+        <v>128110793</v>
       </c>
       <c r="B113" t="n">
-        <v>97353</v>
+        <v>98504</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11992,34 +11999,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221941</v>
+        <v>219874</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533802</v>
+        <v>533693</v>
       </c>
       <c r="R113" t="n">
-        <v>6962332</v>
+        <v>6962647</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12052,6 +12059,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12078,10 +12090,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128110783</v>
+        <v>128110794</v>
       </c>
       <c r="B114" t="n">
-        <v>91124</v>
+        <v>98504</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12089,21 +12101,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12113,10 +12125,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533599</v>
+        <v>533608</v>
       </c>
       <c r="R114" t="n">
-        <v>6962553</v>
+        <v>6962612</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12149,6 +12161,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12175,50 +12192,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128108378</v>
+        <v>128110991</v>
       </c>
       <c r="B115" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533750</v>
+        <v>533717</v>
       </c>
       <c r="R115" t="n">
-        <v>6962259</v>
+        <v>6962645</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12255,7 +12267,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12282,50 +12294,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128100457</v>
+        <v>128103993</v>
       </c>
       <c r="B116" t="n">
-        <v>57672</v>
+        <v>105508</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533556</v>
+        <v>533664</v>
       </c>
       <c r="R116" t="n">
-        <v>6962363</v>
+        <v>6962650</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12358,11 +12365,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12389,32 +12391,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128110838</v>
+        <v>128110987</v>
       </c>
       <c r="B117" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12424,10 +12426,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533708</v>
+        <v>533999</v>
       </c>
       <c r="R117" t="n">
-        <v>6962624</v>
+        <v>6962664</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12464,7 +12466,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>1 stycken</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12491,45 +12493,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128110793</v>
+        <v>128103044</v>
       </c>
       <c r="B118" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533693</v>
+        <v>533627</v>
       </c>
       <c r="R118" t="n">
-        <v>6962647</v>
+        <v>6962544</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12562,11 +12568,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12593,32 +12594,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128110794</v>
+        <v>128110819</v>
       </c>
       <c r="B119" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12628,10 +12629,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533608</v>
+        <v>533834</v>
       </c>
       <c r="R119" t="n">
-        <v>6962612</v>
+        <v>6962298</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12668,7 +12669,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12695,32 +12696,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128110991</v>
+        <v>128101331</v>
       </c>
       <c r="B120" t="n">
-        <v>98470</v>
+        <v>80167</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12730,10 +12731,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533717</v>
+        <v>533424</v>
       </c>
       <c r="R120" t="n">
-        <v>6962645</v>
+        <v>6962357</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12766,11 +12767,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12797,32 +12793,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103993</v>
+        <v>128108395</v>
       </c>
       <c r="B121" t="n">
-        <v>105508</v>
+        <v>80132</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12832,10 +12828,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533664</v>
+        <v>533735</v>
       </c>
       <c r="R121" t="n">
-        <v>6962650</v>
+        <v>6962274</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12894,10 +12890,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128101331</v>
+        <v>128110783</v>
       </c>
       <c r="B122" t="n">
-        <v>80167</v>
+        <v>91124</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12905,21 +12901,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6463</v>
+        <v>3215</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12929,10 +12925,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533424</v>
+        <v>533599</v>
       </c>
       <c r="R122" t="n">
-        <v>6962357</v>
+        <v>6962553</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12991,45 +12987,49 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128108395</v>
+        <v>128099487</v>
       </c>
       <c r="B123" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>533735</v>
+        <v>533474</v>
       </c>
       <c r="R123" t="n">
-        <v>6962274</v>
+        <v>6962267</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13088,10 +13088,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128110789</v>
+        <v>128099811</v>
       </c>
       <c r="B124" t="n">
-        <v>98504</v>
+        <v>105508</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -13099,21 +13099,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>219874</v>
+        <v>221144</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13123,10 +13123,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>533832</v>
+        <v>533451</v>
       </c>
       <c r="R124" t="n">
-        <v>6962310</v>
+        <v>6962307</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13185,45 +13185,50 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128108119</v>
+        <v>128100396</v>
       </c>
       <c r="B125" t="n">
-        <v>98504</v>
+        <v>57832</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>533800</v>
+        <v>533537</v>
       </c>
       <c r="R125" t="n">
-        <v>6962306</v>
+        <v>6962358</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13282,32 +13287,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128110823</v>
+        <v>128110789</v>
       </c>
       <c r="B126" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13317,10 +13322,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>533715</v>
+        <v>533832</v>
       </c>
       <c r="R126" t="n">
-        <v>6962631</v>
+        <v>6962310</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13353,11 +13358,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13384,45 +13384,45 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128110825</v>
+        <v>128108119</v>
       </c>
       <c r="B127" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>533583</v>
+        <v>533800</v>
       </c>
       <c r="R127" t="n">
-        <v>6962689</v>
+        <v>6962306</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13455,11 +13455,6 @@
       <c r="AA127" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC127" t="inlineStr">
-        <is>
-          <t>84stycken</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13486,50 +13481,45 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128099239</v>
+        <v>128110823</v>
       </c>
       <c r="B128" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>533422</v>
+        <v>533715</v>
       </c>
       <c r="R128" t="n">
-        <v>6962229</v>
+        <v>6962631</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13566,7 +13556,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13593,32 +13583,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128109488</v>
+        <v>128110825</v>
       </c>
       <c r="B129" t="n">
-        <v>80161</v>
+        <v>98470</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13628,10 +13618,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>533498</v>
+        <v>533583</v>
       </c>
       <c r="R129" t="n">
-        <v>6962158</v>
+        <v>6962689</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13664,6 +13654,11 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>84stycken</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13690,10 +13685,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128109254</v>
+        <v>128109488</v>
       </c>
       <c r="B130" t="n">
-        <v>80160</v>
+        <v>80161</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13701,34 +13696,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6461</v>
+        <v>6462</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>533652</v>
+        <v>533498</v>
       </c>
       <c r="R130" t="n">
-        <v>6962140</v>
+        <v>6962158</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13787,10 +13782,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128099811</v>
+        <v>128109254</v>
       </c>
       <c r="B131" t="n">
-        <v>105508</v>
+        <v>80160</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -13798,34 +13793,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>221144</v>
+        <v>6461</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>533451</v>
+        <v>533652</v>
       </c>
       <c r="R131" t="n">
-        <v>6962307</v>
+        <v>6962140</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13884,10 +13879,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128100396</v>
+        <v>128099239</v>
       </c>
       <c r="B132" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -13895,27 +13890,27 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
@@ -13924,10 +13919,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>533537</v>
+        <v>533422</v>
       </c>
       <c r="R132" t="n">
-        <v>6962358</v>
+        <v>6962229</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13960,6 +13955,11 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -18309,32 +18309,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128110828</v>
+        <v>128110787</v>
       </c>
       <c r="B176" t="n">
-        <v>98470</v>
+        <v>80160</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18344,10 +18344,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>533365</v>
+        <v>533785</v>
       </c>
       <c r="R176" t="n">
-        <v>6962304</v>
+        <v>6962326</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18380,11 +18380,6 @@
       <c r="AA176" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC176" t="inlineStr">
-        <is>
-          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -18411,49 +18406,45 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128107826</v>
+        <v>128101075</v>
       </c>
       <c r="B177" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I177" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
       <c r="P177" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>533723</v>
+        <v>533392</v>
       </c>
       <c r="R177" t="n">
-        <v>6962360</v>
+        <v>6962343</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18512,45 +18503,50 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128110817</v>
+        <v>128108439</v>
       </c>
       <c r="B178" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>533728</v>
+        <v>533711</v>
       </c>
       <c r="R178" t="n">
-        <v>6962346</v>
+        <v>6962283</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18587,7 +18583,7 @@
       </c>
       <c r="AC178" t="inlineStr">
         <is>
-          <t>40 stycken i blåbärsriset</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18614,45 +18610,50 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128110835</v>
+        <v>128101939</v>
       </c>
       <c r="B179" t="n">
-        <v>98387</v>
+        <v>57672</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>533748</v>
+        <v>533638</v>
       </c>
       <c r="R179" t="n">
-        <v>6962431</v>
+        <v>6962346</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18685,6 +18686,11 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18711,45 +18717,50 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128110977</v>
+        <v>128100413</v>
       </c>
       <c r="B180" t="n">
-        <v>98504</v>
+        <v>57672</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>534040</v>
+        <v>533545</v>
       </c>
       <c r="R180" t="n">
-        <v>6962718</v>
+        <v>6962372</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18782,6 +18793,11 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18808,32 +18824,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128110799</v>
+        <v>128110828</v>
       </c>
       <c r="B181" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18843,10 +18859,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>533724</v>
+        <v>533365</v>
       </c>
       <c r="R181" t="n">
-        <v>6962625</v>
+        <v>6962304</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18879,6 +18895,11 @@
       <c r="AA181" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18905,45 +18926,49 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128110787</v>
+        <v>128107826</v>
       </c>
       <c r="B182" t="n">
-        <v>80160</v>
+        <v>98470</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>533785</v>
+        <v>533723</v>
       </c>
       <c r="R182" t="n">
-        <v>6962326</v>
+        <v>6962360</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19002,32 +19027,32 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128101075</v>
+        <v>128110817</v>
       </c>
       <c r="B183" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19037,10 +19062,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>533392</v>
+        <v>533728</v>
       </c>
       <c r="R183" t="n">
-        <v>6962343</v>
+        <v>6962346</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19073,6 +19098,11 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19099,10 +19129,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128108439</v>
+        <v>128110799</v>
       </c>
       <c r="B184" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -19110,39 +19140,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>533711</v>
+        <v>533724</v>
       </c>
       <c r="R184" t="n">
-        <v>6962283</v>
+        <v>6962625</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19175,11 +19200,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19206,50 +19226,45 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128101939</v>
+        <v>128110835</v>
       </c>
       <c r="B185" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
-      <c r="M185" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>533638</v>
+        <v>533748</v>
       </c>
       <c r="R185" t="n">
-        <v>6962346</v>
+        <v>6962431</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19282,11 +19297,6 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19313,50 +19323,45 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128100413</v>
+        <v>128110977</v>
       </c>
       <c r="B186" t="n">
-        <v>57672</v>
+        <v>98504</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
-      <c r="M186" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P186" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>533545</v>
+        <v>534040</v>
       </c>
       <c r="R186" t="n">
-        <v>6962372</v>
+        <v>6962718</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19389,11 +19394,6 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC186" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD186" t="b">

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -2736,50 +2736,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128099395</v>
+        <v>128108592</v>
       </c>
       <c r="B22" t="n">
-        <v>57672</v>
+        <v>80036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533356</v>
+        <v>533675</v>
       </c>
       <c r="R22" t="n">
-        <v>6962190</v>
+        <v>6962244</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2812,11 +2807,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2843,45 +2833,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128108592</v>
+        <v>128110771</v>
       </c>
       <c r="B23" t="n">
-        <v>80036</v>
+        <v>57672</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533675</v>
+        <v>533583</v>
       </c>
       <c r="R23" t="n">
-        <v>6962244</v>
+        <v>6962697</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2914,6 +2904,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2940,7 +2935,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128110771</v>
+        <v>128109293</v>
       </c>
       <c r="B24" t="n">
         <v>57672</v>
@@ -2969,16 +2964,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533583</v>
+        <v>533638</v>
       </c>
       <c r="R24" t="n">
-        <v>6962697</v>
+        <v>6962157</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3042,7 +3042,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128109293</v>
+        <v>128099395</v>
       </c>
       <c r="B25" t="n">
         <v>57672</v>
@@ -3078,14 +3078,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533638</v>
+        <v>533356</v>
       </c>
       <c r="R25" t="n">
-        <v>6962157</v>
+        <v>6962190</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3559,50 +3559,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128099402</v>
+        <v>128110780</v>
       </c>
       <c r="B30" t="n">
-        <v>57672</v>
+        <v>91124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533474</v>
+        <v>533670</v>
       </c>
       <c r="R30" t="n">
-        <v>6962267</v>
+        <v>6962552</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3635,11 +3630,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3666,45 +3656,50 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128110780</v>
+        <v>128099402</v>
       </c>
       <c r="B31" t="n">
-        <v>91124</v>
+        <v>57672</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533670</v>
+        <v>533474</v>
       </c>
       <c r="R31" t="n">
-        <v>6962552</v>
+        <v>6962267</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3737,6 +3732,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3763,32 +3763,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128110803</v>
+        <v>128110790</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3798,10 +3798,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533524</v>
+        <v>533822</v>
       </c>
       <c r="R32" t="n">
-        <v>6962153</v>
+        <v>6962344</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,7 +3865,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128110981</v>
+        <v>128110803</v>
       </c>
       <c r="B33" t="n">
         <v>98470</v>
@@ -3900,10 +3900,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533689</v>
+        <v>533524</v>
       </c>
       <c r="R33" t="n">
-        <v>6962405</v>
+        <v>6962153</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3967,7 +3967,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128109875</v>
+        <v>128110981</v>
       </c>
       <c r="B34" t="n">
         <v>98470</v>
@@ -3995,21 +3995,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533436</v>
+        <v>533689</v>
       </c>
       <c r="R34" t="n">
-        <v>6962158</v>
+        <v>6962405</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4042,6 +4038,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4068,7 +4069,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128102143</v>
+        <v>128109875</v>
       </c>
       <c r="B35" t="n">
         <v>98470</v>
@@ -4098,7 +4099,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4107,10 +4108,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533615</v>
+        <v>533436</v>
       </c>
       <c r="R35" t="n">
-        <v>6962423</v>
+        <v>6962158</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4169,7 +4170,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128100230</v>
+        <v>128102143</v>
       </c>
       <c r="B36" t="n">
         <v>98470</v>
@@ -4199,7 +4200,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4208,10 +4209,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533506</v>
+        <v>533615</v>
       </c>
       <c r="R36" t="n">
-        <v>6962358</v>
+        <v>6962423</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4270,45 +4271,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128110790</v>
+        <v>128100230</v>
       </c>
       <c r="B37" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533822</v>
+        <v>533506</v>
       </c>
       <c r="R37" t="n">
-        <v>6962344</v>
+        <v>6962358</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4341,11 +4346,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -8625,32 +8625,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128110982</v>
+        <v>128110779</v>
       </c>
       <c r="B80" t="n">
-        <v>98470</v>
+        <v>91124</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533681</v>
+        <v>533678</v>
       </c>
       <c r="R80" t="n">
-        <v>6962434</v>
+        <v>6962542</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8696,11 +8696,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>23 ex</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8727,45 +8722,50 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128110810</v>
+        <v>128101827</v>
       </c>
       <c r="B81" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533645</v>
+        <v>533594</v>
       </c>
       <c r="R81" t="n">
-        <v>6962593</v>
+        <v>6962354</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8798,6 +8798,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8824,45 +8829,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128110976</v>
+        <v>128100974</v>
       </c>
       <c r="B82" t="n">
-        <v>98504</v>
+        <v>57672</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533868</v>
+        <v>533375</v>
       </c>
       <c r="R82" t="n">
-        <v>6962692</v>
+        <v>6962293</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8899,7 +8909,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Växer spritt i hela området</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8926,49 +8936,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128101261</v>
+        <v>128110969</v>
       </c>
       <c r="B83" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533424</v>
+        <v>533825</v>
       </c>
       <c r="R83" t="n">
-        <v>6962357</v>
+        <v>6962690</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9001,6 +9007,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9027,10 +9038,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128099905</v>
+        <v>128102006</v>
       </c>
       <c r="B84" t="n">
-        <v>57672</v>
+        <v>80132</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9038,39 +9049,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533445</v>
+        <v>533510</v>
       </c>
       <c r="R84" t="n">
-        <v>6962324</v>
+        <v>6962462</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9103,11 +9109,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9134,45 +9135,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128110779</v>
+        <v>128099905</v>
       </c>
       <c r="B85" t="n">
-        <v>91124</v>
+        <v>57672</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533678</v>
+        <v>533445</v>
       </c>
       <c r="R85" t="n">
-        <v>6962542</v>
+        <v>6962324</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9205,6 +9211,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9231,32 +9242,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128102006</v>
+        <v>128110976</v>
       </c>
       <c r="B86" t="n">
-        <v>80132</v>
+        <v>98504</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9266,10 +9277,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533510</v>
+        <v>533868</v>
       </c>
       <c r="R86" t="n">
-        <v>6962462</v>
+        <v>6962692</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9302,6 +9313,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9328,38 +9344,37 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128101827</v>
+        <v>128101261</v>
       </c>
       <c r="B87" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9368,10 +9383,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533594</v>
+        <v>533424</v>
       </c>
       <c r="R87" t="n">
-        <v>6962354</v>
+        <v>6962357</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9404,11 +9419,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9435,50 +9445,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128100974</v>
+        <v>128110982</v>
       </c>
       <c r="B88" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533375</v>
+        <v>533681</v>
       </c>
       <c r="R88" t="n">
-        <v>6962293</v>
+        <v>6962434</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9515,7 +9520,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
+          <t>23 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9542,32 +9547,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128110969</v>
+        <v>128110810</v>
       </c>
       <c r="B89" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9577,10 +9582,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533825</v>
+        <v>533645</v>
       </c>
       <c r="R89" t="n">
-        <v>6962690</v>
+        <v>6962593</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9613,11 +9618,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11473,45 +11473,49 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128108028</v>
+        <v>128099487</v>
       </c>
       <c r="B108" t="n">
-        <v>97353</v>
+        <v>98470</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533802</v>
+        <v>533474</v>
       </c>
       <c r="R108" t="n">
-        <v>6962332</v>
+        <v>6962267</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11570,10 +11574,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128108378</v>
+        <v>128110776</v>
       </c>
       <c r="B109" t="n">
-        <v>57672</v>
+        <v>57832</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11581,39 +11585,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533750</v>
+        <v>533719</v>
       </c>
       <c r="R109" t="n">
-        <v>6962259</v>
+        <v>6962615</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11650,7 +11649,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11677,50 +11676,45 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128100457</v>
+        <v>128110987</v>
       </c>
       <c r="B110" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533556</v>
+        <v>533999</v>
       </c>
       <c r="R110" t="n">
-        <v>6962363</v>
+        <v>6962664</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11757,7 +11751,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11784,45 +11778,49 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128110776</v>
+        <v>128103044</v>
       </c>
       <c r="B111" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>533719</v>
+        <v>533627</v>
       </c>
       <c r="R111" t="n">
-        <v>6962615</v>
+        <v>6962544</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11855,11 +11853,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11886,32 +11879,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128110838</v>
+        <v>128110819</v>
       </c>
       <c r="B112" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11921,10 +11914,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>533708</v>
+        <v>533834</v>
       </c>
       <c r="R112" t="n">
-        <v>6962624</v>
+        <v>6962298</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11961,7 +11954,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>1 stycken</t>
+          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11988,10 +11981,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128110793</v>
+        <v>128108028</v>
       </c>
       <c r="B113" t="n">
-        <v>98504</v>
+        <v>97353</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11999,34 +11992,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219874</v>
+        <v>221941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533693</v>
+        <v>533802</v>
       </c>
       <c r="R113" t="n">
-        <v>6962647</v>
+        <v>6962332</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12059,11 +12052,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12090,10 +12078,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128110794</v>
+        <v>128110783</v>
       </c>
       <c r="B114" t="n">
-        <v>98504</v>
+        <v>91124</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12101,21 +12089,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12125,10 +12113,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533608</v>
+        <v>533599</v>
       </c>
       <c r="R114" t="n">
-        <v>6962612</v>
+        <v>6962553</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12161,11 +12149,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12192,45 +12175,50 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128110991</v>
+        <v>128108378</v>
       </c>
       <c r="B115" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533717</v>
+        <v>533750</v>
       </c>
       <c r="R115" t="n">
-        <v>6962645</v>
+        <v>6962259</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12267,7 +12255,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12294,45 +12282,50 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103993</v>
+        <v>128100457</v>
       </c>
       <c r="B116" t="n">
-        <v>105508</v>
+        <v>57672</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533664</v>
+        <v>533556</v>
       </c>
       <c r="R116" t="n">
-        <v>6962650</v>
+        <v>6962363</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12365,6 +12358,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12391,32 +12389,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128110987</v>
+        <v>128110838</v>
       </c>
       <c r="B117" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12426,10 +12424,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533999</v>
+        <v>533708</v>
       </c>
       <c r="R117" t="n">
-        <v>6962664</v>
+        <v>6962624</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12466,7 +12464,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12493,49 +12491,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103044</v>
+        <v>128110793</v>
       </c>
       <c r="B118" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533627</v>
+        <v>533693</v>
       </c>
       <c r="R118" t="n">
-        <v>6962544</v>
+        <v>6962647</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12568,6 +12562,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12594,32 +12593,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128110819</v>
+        <v>128110794</v>
       </c>
       <c r="B119" t="n">
-        <v>98470</v>
+        <v>98504</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12629,10 +12628,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533834</v>
+        <v>533608</v>
       </c>
       <c r="R119" t="n">
-        <v>6962298</v>
+        <v>6962612</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12669,7 +12668,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>10 stycken kan finnas fler runt omkring</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12696,32 +12695,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128101331</v>
+        <v>128110991</v>
       </c>
       <c r="B120" t="n">
-        <v>80167</v>
+        <v>98470</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12731,10 +12730,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533424</v>
+        <v>533717</v>
       </c>
       <c r="R120" t="n">
-        <v>6962357</v>
+        <v>6962645</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12767,6 +12766,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12793,32 +12797,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128108395</v>
+        <v>128103993</v>
       </c>
       <c r="B121" t="n">
-        <v>80132</v>
+        <v>105508</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12828,10 +12832,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533735</v>
+        <v>533664</v>
       </c>
       <c r="R121" t="n">
-        <v>6962274</v>
+        <v>6962650</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12890,10 +12894,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128110783</v>
+        <v>128101331</v>
       </c>
       <c r="B122" t="n">
-        <v>91124</v>
+        <v>80167</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12901,21 +12905,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3215</v>
+        <v>6463</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12925,10 +12929,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533599</v>
+        <v>533424</v>
       </c>
       <c r="R122" t="n">
-        <v>6962553</v>
+        <v>6962357</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12987,49 +12991,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128099487</v>
+        <v>128108395</v>
       </c>
       <c r="B123" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>533474</v>
+        <v>533735</v>
       </c>
       <c r="R123" t="n">
-        <v>6962267</v>
+        <v>6962274</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15805,45 +15805,49 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128110768</v>
+        <v>128101444</v>
       </c>
       <c r="B151" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>533754</v>
+        <v>533424</v>
       </c>
       <c r="R151" t="n">
-        <v>6962450</v>
+        <v>6962351</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15876,11 +15880,6 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15907,32 +15906,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128102121</v>
+        <v>128110986</v>
       </c>
       <c r="B152" t="n">
-        <v>57832</v>
+        <v>98470</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15942,10 +15941,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>533532</v>
+        <v>533957</v>
       </c>
       <c r="R152" t="n">
-        <v>6962477</v>
+        <v>6962694</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15978,6 +15977,11 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>37 ex</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16004,10 +16008,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128099113</v>
+        <v>128102104</v>
       </c>
       <c r="B153" t="n">
-        <v>92642</v>
+        <v>105508</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16015,43 +16019,34 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>533396</v>
+        <v>533615</v>
       </c>
       <c r="R153" t="n">
-        <v>6962161</v>
+        <v>6962423</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16084,11 +16079,6 @@
       <c r="AA153" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16115,32 +16105,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128110831</v>
+        <v>128110768</v>
       </c>
       <c r="B154" t="n">
-        <v>58531</v>
+        <v>57672</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>208249</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16150,10 +16140,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>533728</v>
+        <v>533754</v>
       </c>
       <c r="R154" t="n">
-        <v>6962422</v>
+        <v>6962450</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16186,6 +16176,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16212,49 +16207,45 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128101444</v>
+        <v>128110831</v>
       </c>
       <c r="B155" t="n">
-        <v>98470</v>
+        <v>58531</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>533424</v>
+        <v>533728</v>
       </c>
       <c r="R155" t="n">
-        <v>6962351</v>
+        <v>6962422</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16313,45 +16304,54 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128110986</v>
+        <v>128099113</v>
       </c>
       <c r="B156" t="n">
-        <v>98470</v>
+        <v>92642</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P156" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>533957</v>
+        <v>533396</v>
       </c>
       <c r="R156" t="n">
-        <v>6962694</v>
+        <v>6962161</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>37 ex</t>
+          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16415,32 +16415,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128102104</v>
+        <v>128102121</v>
       </c>
       <c r="B157" t="n">
-        <v>105508</v>
+        <v>57832</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16450,10 +16450,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>533615</v>
+        <v>533532</v>
       </c>
       <c r="R157" t="n">
-        <v>6962423</v>
+        <v>6962477</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -6686,54 +6686,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128099522</v>
+        <v>128099984</v>
       </c>
       <c r="B61" t="n">
-        <v>98470</v>
+        <v>80132</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533349</v>
+        <v>533455</v>
       </c>
       <c r="R61" t="n">
-        <v>6962197</v>
+        <v>6962339</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6792,32 +6783,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128099099</v>
+        <v>128099875</v>
       </c>
       <c r="B62" t="n">
-        <v>105508</v>
+        <v>80132</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6827,10 +6818,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533416</v>
+        <v>533445</v>
       </c>
       <c r="R62" t="n">
-        <v>6962179</v>
+        <v>6962324</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6889,45 +6880,50 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128110827</v>
+        <v>128099885</v>
       </c>
       <c r="B63" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533614</v>
+        <v>533361</v>
       </c>
       <c r="R63" t="n">
-        <v>6962554</v>
+        <v>6962247</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6964,7 +6960,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6991,49 +6987,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128100184</v>
+        <v>128110971</v>
       </c>
       <c r="B64" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533509</v>
+        <v>534036</v>
       </c>
       <c r="R64" t="n">
-        <v>6962336</v>
+        <v>6962734</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7066,6 +7058,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7092,37 +7089,38 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128103587</v>
+        <v>128108477</v>
       </c>
       <c r="B65" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>120</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -7131,10 +7129,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533650</v>
+        <v>533710</v>
       </c>
       <c r="R65" t="n">
-        <v>6962600</v>
+        <v>6962294</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7167,6 +7165,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7193,32 +7196,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128110971</v>
+        <v>128110827</v>
       </c>
       <c r="B66" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7228,10 +7231,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>534036</v>
+        <v>533614</v>
       </c>
       <c r="R66" t="n">
-        <v>6962734</v>
+        <v>6962554</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7268,7 +7271,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7295,50 +7298,49 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128108477</v>
+        <v>128100184</v>
       </c>
       <c r="B67" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533710</v>
+        <v>533509</v>
       </c>
       <c r="R67" t="n">
-        <v>6962294</v>
+        <v>6962336</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7371,11 +7373,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7402,45 +7399,49 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128099984</v>
+        <v>128103587</v>
       </c>
       <c r="B68" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533455</v>
+        <v>533650</v>
       </c>
       <c r="R68" t="n">
-        <v>6962339</v>
+        <v>6962600</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7499,45 +7500,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128099875</v>
+        <v>128099522</v>
       </c>
       <c r="B69" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533445</v>
+        <v>533349</v>
       </c>
       <c r="R69" t="n">
-        <v>6962324</v>
+        <v>6962197</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7596,50 +7606,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128099885</v>
+        <v>128099099</v>
       </c>
       <c r="B70" t="n">
-        <v>57672</v>
+        <v>105508</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533361</v>
+        <v>533416</v>
       </c>
       <c r="R70" t="n">
-        <v>6962247</v>
+        <v>6962179</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7672,11 +7677,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7800,45 +7800,50 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128099857</v>
+        <v>128099712</v>
       </c>
       <c r="B72" t="n">
-        <v>80161</v>
+        <v>57672</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533445</v>
+        <v>533451</v>
       </c>
       <c r="R72" t="n">
-        <v>6962324</v>
+        <v>6962307</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7871,6 +7876,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8315,32 +8325,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128110811</v>
+        <v>128099857</v>
       </c>
       <c r="B77" t="n">
-        <v>98470</v>
+        <v>80161</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8350,10 +8360,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533706</v>
+        <v>533445</v>
       </c>
       <c r="R77" t="n">
-        <v>6962596</v>
+        <v>6962324</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8386,11 +8396,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>24 stycken</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8417,7 +8422,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128101024</v>
+        <v>128110811</v>
       </c>
       <c r="B78" t="n">
         <v>98470</v>
@@ -8445,21 +8450,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533375</v>
+        <v>533706</v>
       </c>
       <c r="R78" t="n">
-        <v>6962293</v>
+        <v>6962596</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8492,6 +8493,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>24 stycken</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8518,38 +8524,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128099712</v>
+        <v>128101024</v>
       </c>
       <c r="B79" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8558,10 +8563,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533451</v>
+        <v>533375</v>
       </c>
       <c r="R79" t="n">
-        <v>6962307</v>
+        <v>6962293</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8594,11 +8599,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10047,10 +10047,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128110834</v>
+        <v>128099401</v>
       </c>
       <c r="B94" t="n">
-        <v>98387</v>
+        <v>92642</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10058,34 +10058,43 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>219790</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533779</v>
+        <v>533356</v>
       </c>
       <c r="R94" t="n">
-        <v>6962298</v>
+        <v>6962190</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10144,45 +10153,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128110816</v>
+        <v>128099555</v>
       </c>
       <c r="B95" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533696</v>
+        <v>533471</v>
       </c>
       <c r="R95" t="n">
-        <v>6962294</v>
+        <v>6962293</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10219,7 +10233,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>20 stycken</t>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10246,49 +10260,50 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128102067</v>
+        <v>128102878</v>
       </c>
       <c r="B96" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533510</v>
+        <v>533665</v>
       </c>
       <c r="R96" t="n">
-        <v>6962462</v>
+        <v>6962515</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10321,6 +10336,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10347,42 +10367,38 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128099401</v>
+        <v>128100043</v>
       </c>
       <c r="B97" t="n">
-        <v>92642</v>
+        <v>57672</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10391,10 +10407,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533356</v>
+        <v>533496</v>
       </c>
       <c r="R97" t="n">
-        <v>6962190</v>
+        <v>6962335</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10427,6 +10443,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10550,50 +10571,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128099555</v>
+        <v>128110834</v>
       </c>
       <c r="B99" t="n">
-        <v>57672</v>
+        <v>98387</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>533471</v>
+        <v>533779</v>
       </c>
       <c r="R99" t="n">
-        <v>6962293</v>
+        <v>6962298</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10626,11 +10642,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10657,50 +10668,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128102878</v>
+        <v>128110816</v>
       </c>
       <c r="B100" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>533665</v>
+        <v>533696</v>
       </c>
       <c r="R100" t="n">
-        <v>6962515</v>
+        <v>6962294</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10737,7 +10743,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10764,38 +10770,37 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128100043</v>
+        <v>128102067</v>
       </c>
       <c r="B101" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -10804,10 +10809,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533496</v>
+        <v>533510</v>
       </c>
       <c r="R101" t="n">
-        <v>6962335</v>
+        <v>6962462</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10840,11 +10845,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11473,49 +11473,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128099487</v>
+        <v>128108028</v>
       </c>
       <c r="B108" t="n">
-        <v>98470</v>
+        <v>97353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533474</v>
+        <v>533802</v>
       </c>
       <c r="R108" t="n">
-        <v>6962267</v>
+        <v>6962332</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11574,10 +11570,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128110776</v>
+        <v>128108378</v>
       </c>
       <c r="B109" t="n">
-        <v>57832</v>
+        <v>57672</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11585,34 +11581,39 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533719</v>
+        <v>533750</v>
       </c>
       <c r="R109" t="n">
-        <v>6962615</v>
+        <v>6962259</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11649,7 +11650,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11676,45 +11677,50 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128110987</v>
+        <v>128100457</v>
       </c>
       <c r="B110" t="n">
-        <v>98470</v>
+        <v>57672</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533999</v>
+        <v>533556</v>
       </c>
       <c r="R110" t="n">
-        <v>6962664</v>
+        <v>6962363</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11751,7 +11757,7 @@
       </c>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11778,49 +11784,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128103044</v>
+        <v>128110776</v>
       </c>
       <c r="B111" t="n">
-        <v>98470</v>
+        <v>57832</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>533627</v>
+        <v>533719</v>
       </c>
       <c r="R111" t="n">
-        <v>6962544</v>
+        <v>6962615</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11853,6 +11855,11 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11879,32 +11886,32 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128110819</v>
+        <v>128110838</v>
       </c>
       <c r="B112" t="n">
-        <v>98470</v>
+        <v>98387</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11914,10 +11921,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>533834</v>
+        <v>533708</v>
       </c>
       <c r="R112" t="n">
-        <v>6962298</v>
+        <v>6962624</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11954,7 +11961,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>10 stycken kan finnas fler runt omkring</t>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11981,10 +11988,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128108028</v>
+        <v>128110793</v>
       </c>
       <c r="B113" t="n">
-        <v>97353</v>
+        <v>98504</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11992,34 +11999,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>221941</v>
+        <v>219874</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533802</v>
+        <v>533693</v>
       </c>
       <c r="R113" t="n">
-        <v>6962332</v>
+        <v>6962647</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12052,6 +12059,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12078,10 +12090,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128110783</v>
+        <v>128110794</v>
       </c>
       <c r="B114" t="n">
-        <v>91124</v>
+        <v>98504</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12089,21 +12101,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12113,10 +12125,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533599</v>
+        <v>533608</v>
       </c>
       <c r="R114" t="n">
-        <v>6962553</v>
+        <v>6962612</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12149,6 +12161,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12175,50 +12192,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128108378</v>
+        <v>128110991</v>
       </c>
       <c r="B115" t="n">
-        <v>57672</v>
+        <v>98470</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533750</v>
+        <v>533717</v>
       </c>
       <c r="R115" t="n">
-        <v>6962259</v>
+        <v>6962645</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12255,7 +12267,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12282,50 +12294,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128100457</v>
+        <v>128103993</v>
       </c>
       <c r="B116" t="n">
-        <v>57672</v>
+        <v>105508</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533556</v>
+        <v>533664</v>
       </c>
       <c r="R116" t="n">
-        <v>6962363</v>
+        <v>6962650</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12358,11 +12365,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12389,32 +12391,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128110838</v>
+        <v>128110987</v>
       </c>
       <c r="B117" t="n">
-        <v>98387</v>
+        <v>98470</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12424,10 +12426,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533708</v>
+        <v>533999</v>
       </c>
       <c r="R117" t="n">
-        <v>6962624</v>
+        <v>6962664</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12464,7 +12466,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>1 stycken</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12491,45 +12493,49 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128110793</v>
+        <v>128103044</v>
       </c>
       <c r="B118" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533693</v>
+        <v>533627</v>
       </c>
       <c r="R118" t="n">
-        <v>6962647</v>
+        <v>6962544</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12562,11 +12568,6 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12593,32 +12594,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128110794</v>
+        <v>128110819</v>
       </c>
       <c r="B119" t="n">
-        <v>98504</v>
+        <v>98470</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12628,10 +12629,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533608</v>
+        <v>533834</v>
       </c>
       <c r="R119" t="n">
-        <v>6962612</v>
+        <v>6962298</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12668,7 +12669,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12695,32 +12696,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128110991</v>
+        <v>128101331</v>
       </c>
       <c r="B120" t="n">
-        <v>98470</v>
+        <v>80167</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12730,10 +12731,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533717</v>
+        <v>533424</v>
       </c>
       <c r="R120" t="n">
-        <v>6962645</v>
+        <v>6962357</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12766,11 +12767,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -12797,32 +12793,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128103993</v>
+        <v>128108395</v>
       </c>
       <c r="B121" t="n">
-        <v>105508</v>
+        <v>80132</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12832,10 +12828,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533664</v>
+        <v>533735</v>
       </c>
       <c r="R121" t="n">
-        <v>6962650</v>
+        <v>6962274</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12894,10 +12890,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128101331</v>
+        <v>128110783</v>
       </c>
       <c r="B122" t="n">
-        <v>80167</v>
+        <v>91124</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12905,21 +12901,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6463</v>
+        <v>3215</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12929,10 +12925,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533424</v>
+        <v>533599</v>
       </c>
       <c r="R122" t="n">
-        <v>6962357</v>
+        <v>6962553</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12991,45 +12987,49 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128108395</v>
+        <v>128099487</v>
       </c>
       <c r="B123" t="n">
-        <v>80132</v>
+        <v>98470</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>533735</v>
+        <v>533474</v>
       </c>
       <c r="R123" t="n">
-        <v>6962274</v>
+        <v>6962267</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13986,45 +13986,45 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128110809</v>
+        <v>128103617</v>
       </c>
       <c r="B133" t="n">
-        <v>98470</v>
+        <v>91352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>533748</v>
+        <v>533637</v>
       </c>
       <c r="R133" t="n">
-        <v>6962494</v>
+        <v>6962600</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14057,11 +14057,6 @@
       <c r="AA133" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14088,32 +14083,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128110830</v>
+        <v>128110809</v>
       </c>
       <c r="B134" t="n">
-        <v>105508</v>
+        <v>98470</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14123,10 +14118,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>533659</v>
+        <v>533748</v>
       </c>
       <c r="R134" t="n">
-        <v>6962296</v>
+        <v>6962494</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14159,6 +14154,11 @@
       <c r="AA134" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14185,32 +14185,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128110808</v>
+        <v>128100350</v>
       </c>
       <c r="B135" t="n">
-        <v>98470</v>
+        <v>97347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14220,10 +14220,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>533745</v>
+        <v>533545</v>
       </c>
       <c r="R135" t="n">
-        <v>6962429</v>
+        <v>6962339</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14256,11 +14256,6 @@
       <c r="AA135" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14287,49 +14282,45 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128107880</v>
+        <v>128110830</v>
       </c>
       <c r="B136" t="n">
-        <v>98470</v>
+        <v>105508</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>533736</v>
+        <v>533659</v>
       </c>
       <c r="R136" t="n">
-        <v>6962362</v>
+        <v>6962296</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14388,7 +14379,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128110984</v>
+        <v>128110808</v>
       </c>
       <c r="B137" t="n">
         <v>98470</v>
@@ -14423,10 +14414,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>533734</v>
+        <v>533745</v>
       </c>
       <c r="R137" t="n">
-        <v>6962473</v>
+        <v>6962429</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14463,7 +14454,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>40 ex</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14490,45 +14481,49 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128100350</v>
+        <v>128107880</v>
       </c>
       <c r="B138" t="n">
-        <v>97347</v>
+        <v>98470</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>533545</v>
+        <v>533736</v>
       </c>
       <c r="R138" t="n">
-        <v>6962339</v>
+        <v>6962362</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14587,45 +14582,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128103617</v>
+        <v>128110984</v>
       </c>
       <c r="B139" t="n">
-        <v>91352</v>
+        <v>98470</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>533637</v>
+        <v>533734</v>
       </c>
       <c r="R139" t="n">
-        <v>6962600</v>
+        <v>6962473</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14658,6 +14653,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD139" t="b">

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -1311,45 +1311,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128108655</v>
+        <v>128110802</v>
       </c>
       <c r="B8" t="n">
-        <v>92642</v>
+        <v>98478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533673</v>
+        <v>533461</v>
       </c>
       <c r="R8" t="n">
-        <v>6962211</v>
+        <v>6962171</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,6 +1382,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,45 +1413,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128109460</v>
+        <v>128100827</v>
       </c>
       <c r="B9" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533498</v>
+        <v>533406</v>
       </c>
       <c r="R9" t="n">
-        <v>6962158</v>
+        <v>6962317</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128108619</v>
+        <v>128109460</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>80135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1516,39 +1525,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533675</v>
+        <v>533498</v>
       </c>
       <c r="R10" t="n">
-        <v>6962244</v>
+        <v>6962158</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1581,11 +1585,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,10 +1611,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128110972</v>
+        <v>128108619</v>
       </c>
       <c r="B11" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,16 +1640,21 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533997</v>
+        <v>533675</v>
       </c>
       <c r="R11" t="n">
-        <v>6962746</v>
+        <v>6962244</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,7 +1691,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1714,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128101860</v>
+        <v>128110972</v>
       </c>
       <c r="B12" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,21 +1747,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533601</v>
+        <v>533997</v>
       </c>
       <c r="R12" t="n">
-        <v>6962344</v>
+        <v>6962746</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1794,7 +1793,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1821,45 +1820,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128110802</v>
+        <v>128101860</v>
       </c>
       <c r="B13" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533461</v>
+        <v>533601</v>
       </c>
       <c r="R13" t="n">
-        <v>6962171</v>
+        <v>6962344</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1896,7 +1900,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1923,49 +1927,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128100827</v>
+        <v>128108655</v>
       </c>
       <c r="B14" t="n">
-        <v>98470</v>
+        <v>92650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533406</v>
+        <v>533673</v>
       </c>
       <c r="R14" t="n">
-        <v>6962317</v>
+        <v>6962211</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,45 +2024,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128110833</v>
+        <v>128100321</v>
       </c>
       <c r="B15" t="n">
-        <v>98387</v>
+        <v>98478</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533768</v>
+        <v>533537</v>
       </c>
       <c r="R15" t="n">
-        <v>6962318</v>
+        <v>6962358</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2121,10 +2125,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128100321</v>
+        <v>128100131</v>
       </c>
       <c r="B16" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2151,7 +2155,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2160,10 +2164,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533537</v>
+        <v>533496</v>
       </c>
       <c r="R16" t="n">
-        <v>6962358</v>
+        <v>6962335</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2222,10 +2226,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128100131</v>
+        <v>128110818</v>
       </c>
       <c r="B17" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,21 +2254,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533496</v>
+        <v>533766</v>
       </c>
       <c r="R17" t="n">
-        <v>6962335</v>
+        <v>6962317</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2297,6 +2297,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>10stycken</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2323,32 +2328,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128110818</v>
+        <v>128110833</v>
       </c>
       <c r="B18" t="n">
-        <v>98470</v>
+        <v>98395</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2358,10 +2363,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>533766</v>
+        <v>533768</v>
       </c>
       <c r="R18" t="n">
-        <v>6962317</v>
+        <v>6962318</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2394,11 +2399,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>10stycken</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2425,45 +2425,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128101567</v>
+        <v>128108700</v>
       </c>
       <c r="B19" t="n">
-        <v>80036</v>
+        <v>57673</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533494</v>
+        <v>533674</v>
       </c>
       <c r="R19" t="n">
-        <v>6962425</v>
+        <v>6962199</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2496,6 +2501,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2522,10 +2532,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128108700</v>
+        <v>128109367</v>
       </c>
       <c r="B20" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,14 +2568,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533674</v>
+        <v>533550</v>
       </c>
       <c r="R20" t="n">
-        <v>6962199</v>
+        <v>6962157</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2629,50 +2639,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128109367</v>
+        <v>128101567</v>
       </c>
       <c r="B21" t="n">
-        <v>57672</v>
+        <v>80039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533550</v>
+        <v>533494</v>
       </c>
       <c r="R21" t="n">
-        <v>6962157</v>
+        <v>6962425</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,11 +2710,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2736,45 +2736,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128108592</v>
+        <v>128101601</v>
       </c>
       <c r="B22" t="n">
-        <v>80036</v>
+        <v>98478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533675</v>
+        <v>533496</v>
       </c>
       <c r="R22" t="n">
-        <v>6962244</v>
+        <v>6962407</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2833,45 +2837,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128110771</v>
+        <v>128108218</v>
       </c>
       <c r="B23" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533583</v>
+        <v>533789</v>
       </c>
       <c r="R23" t="n">
-        <v>6962697</v>
+        <v>6962263</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2904,11 +2912,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2935,10 +2938,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128109293</v>
+        <v>128099395</v>
       </c>
       <c r="B24" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2971,14 +2974,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533638</v>
+        <v>533356</v>
       </c>
       <c r="R24" t="n">
-        <v>6962157</v>
+        <v>6962190</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3015,7 +3018,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3042,50 +3045,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128099395</v>
+        <v>128108592</v>
       </c>
       <c r="B25" t="n">
-        <v>57672</v>
+        <v>80039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533356</v>
+        <v>533675</v>
       </c>
       <c r="R25" t="n">
-        <v>6962190</v>
+        <v>6962244</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3118,11 +3116,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3149,32 +3142,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128110832</v>
+        <v>128110771</v>
       </c>
       <c r="B26" t="n">
-        <v>98387</v>
+        <v>57673</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3184,10 +3177,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533652</v>
+        <v>533583</v>
       </c>
       <c r="R26" t="n">
-        <v>6962264</v>
+        <v>6962697</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3220,6 +3213,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3246,49 +3244,50 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128101601</v>
+        <v>128109293</v>
       </c>
       <c r="B27" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533496</v>
+        <v>533638</v>
       </c>
       <c r="R27" t="n">
-        <v>6962407</v>
+        <v>6962157</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,6 +3320,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3347,49 +3351,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128108218</v>
+        <v>128110832</v>
       </c>
       <c r="B28" t="n">
-        <v>98470</v>
+        <v>98395</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533789</v>
+        <v>533652</v>
       </c>
       <c r="R28" t="n">
-        <v>6962263</v>
+        <v>6962264</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,10 +3448,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128099830</v>
+        <v>128110780</v>
       </c>
       <c r="B29" t="n">
-        <v>92642</v>
+        <v>91133</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3459,43 +3459,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533353</v>
+        <v>533670</v>
       </c>
       <c r="R29" t="n">
-        <v>6962231</v>
+        <v>6962552</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3528,11 +3519,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3559,10 +3545,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128110780</v>
+        <v>128110790</v>
       </c>
       <c r="B30" t="n">
-        <v>91124</v>
+        <v>98512</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3570,21 +3556,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3215</v>
+        <v>219874</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3594,10 +3580,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533670</v>
+        <v>533822</v>
       </c>
       <c r="R30" t="n">
-        <v>6962552</v>
+        <v>6962344</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3630,6 +3616,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3656,38 +3647,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128099402</v>
+        <v>128099830</v>
       </c>
       <c r="B31" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3696,10 +3691,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>533474</v>
+        <v>533353</v>
       </c>
       <c r="R31" t="n">
-        <v>6962267</v>
+        <v>6962231</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3736,7 +3731,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre exemplar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3763,32 +3758,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128110790</v>
+        <v>128110803</v>
       </c>
       <c r="B32" t="n">
-        <v>98504</v>
+        <v>98478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3798,10 +3793,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533822</v>
+        <v>533524</v>
       </c>
       <c r="R32" t="n">
-        <v>6962344</v>
+        <v>6962153</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3838,7 +3833,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3865,10 +3860,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128110803</v>
+        <v>128110981</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3900,10 +3895,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533524</v>
+        <v>533689</v>
       </c>
       <c r="R33" t="n">
-        <v>6962153</v>
+        <v>6962405</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,7 +3935,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3967,10 +3962,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128110981</v>
+        <v>128109875</v>
       </c>
       <c r="B34" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3995,17 +3990,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533689</v>
+        <v>533436</v>
       </c>
       <c r="R34" t="n">
-        <v>6962405</v>
+        <v>6962158</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4038,11 +4037,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>15 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4069,10 +4063,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128109875</v>
+        <v>128102143</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4099,7 +4093,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4108,10 +4102,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533436</v>
+        <v>533615</v>
       </c>
       <c r="R35" t="n">
-        <v>6962158</v>
+        <v>6962423</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4170,10 +4164,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128102143</v>
+        <v>128100230</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4200,7 +4194,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>55</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4209,10 +4203,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533615</v>
+        <v>533506</v>
       </c>
       <c r="R36" t="n">
-        <v>6962423</v>
+        <v>6962358</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4271,37 +4265,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128100230</v>
+        <v>128099402</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>55</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4310,10 +4305,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533506</v>
+        <v>533474</v>
       </c>
       <c r="R37" t="n">
-        <v>6962358</v>
+        <v>6962267</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4346,6 +4341,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4372,32 +4372,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128110968</v>
+        <v>128110824</v>
       </c>
       <c r="B38" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533634</v>
+        <v>533712</v>
       </c>
       <c r="R38" t="n">
-        <v>6962526</v>
+        <v>6962628</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>En födosökande individ</t>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4474,10 +4474,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128099282</v>
+        <v>128110978</v>
       </c>
       <c r="B39" t="n">
-        <v>80160</v>
+        <v>98512</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4485,21 +4485,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6461</v>
+        <v>219874</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533452</v>
+        <v>533708</v>
       </c>
       <c r="R39" t="n">
-        <v>6962232</v>
+        <v>6962645</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,50 +4571,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128102724</v>
+        <v>128110788</v>
       </c>
       <c r="B40" t="n">
-        <v>57672</v>
+        <v>98512</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533659</v>
+        <v>533590</v>
       </c>
       <c r="R40" t="n">
-        <v>6962512</v>
+        <v>6962592</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4647,11 +4642,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4678,50 +4668,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128101831</v>
+        <v>128110836</v>
       </c>
       <c r="B41" t="n">
-        <v>57672</v>
+        <v>98395</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533513</v>
+        <v>533722</v>
       </c>
       <c r="R41" t="n">
-        <v>6962442</v>
+        <v>6962426</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4754,11 +4739,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4785,45 +4765,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128110767</v>
+        <v>128108150</v>
       </c>
       <c r="B42" t="n">
-        <v>57672</v>
+        <v>80164</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533794</v>
+        <v>533800</v>
       </c>
       <c r="R42" t="n">
-        <v>6962411</v>
+        <v>6962306</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4856,11 +4836,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4887,32 +4862,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128110978</v>
+        <v>128110968</v>
       </c>
       <c r="B43" t="n">
-        <v>98504</v>
+        <v>57673</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4922,10 +4897,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533708</v>
+        <v>533634</v>
       </c>
       <c r="R43" t="n">
-        <v>6962645</v>
+        <v>6962526</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4958,6 +4933,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4984,45 +4964,50 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128110788</v>
+        <v>128102724</v>
       </c>
       <c r="B44" t="n">
-        <v>98504</v>
+        <v>57673</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533590</v>
+        <v>533659</v>
       </c>
       <c r="R44" t="n">
-        <v>6962592</v>
+        <v>6962512</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5055,6 +5040,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5081,45 +5071,50 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128110824</v>
+        <v>128101831</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533712</v>
+        <v>533513</v>
       </c>
       <c r="R45" t="n">
-        <v>6962628</v>
+        <v>6962442</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5156,7 +5151,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>20 stycken</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5183,32 +5178,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128110836</v>
+        <v>128110767</v>
       </c>
       <c r="B46" t="n">
-        <v>98387</v>
+        <v>57673</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5218,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533722</v>
+        <v>533794</v>
       </c>
       <c r="R46" t="n">
-        <v>6962426</v>
+        <v>6962411</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5254,6 +5249,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5280,10 +5280,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128108150</v>
+        <v>128099282</v>
       </c>
       <c r="B47" t="n">
-        <v>80161</v>
+        <v>80163</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5291,34 +5291,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533800</v>
+        <v>533452</v>
       </c>
       <c r="R47" t="n">
-        <v>6962306</v>
+        <v>6962232</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5377,32 +5377,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128101106</v>
+        <v>128110766</v>
       </c>
       <c r="B48" t="n">
-        <v>80098</v>
+        <v>57673</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229748</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533425</v>
+        <v>533586</v>
       </c>
       <c r="R48" t="n">
-        <v>6962304</v>
+        <v>6962139</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5448,6 +5448,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5474,32 +5479,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128110812</v>
+        <v>128110970</v>
       </c>
       <c r="B49" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5514,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>533715</v>
+        <v>534050</v>
       </c>
       <c r="R49" t="n">
-        <v>6962610</v>
+        <v>6962743</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5549,7 +5554,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>60 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5576,32 +5581,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128110826</v>
+        <v>128101702</v>
       </c>
       <c r="B50" t="n">
-        <v>98470</v>
+        <v>91360</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,10 +5616,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533579</v>
+        <v>533529</v>
       </c>
       <c r="R50" t="n">
-        <v>6962663</v>
+        <v>6962400</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5647,11 +5652,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5678,45 +5678,49 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128108922</v>
+        <v>128099088</v>
       </c>
       <c r="B51" t="n">
-        <v>105508</v>
+        <v>98478</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533671</v>
+        <v>533425</v>
       </c>
       <c r="R51" t="n">
-        <v>6962142</v>
+        <v>6962182</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,10 +5779,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128110804</v>
+        <v>128110826</v>
       </c>
       <c r="B52" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5810,10 +5814,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533532</v>
+        <v>533579</v>
       </c>
       <c r="R52" t="n">
-        <v>6962156</v>
+        <v>6962663</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5850,7 +5854,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5877,10 +5881,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128110990</v>
+        <v>128110804</v>
       </c>
       <c r="B53" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5912,10 +5916,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533873</v>
+        <v>533532</v>
       </c>
       <c r="R53" t="n">
-        <v>6962782</v>
+        <v>6962156</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5952,7 +5956,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5979,10 +5983,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128110814</v>
+        <v>128110990</v>
       </c>
       <c r="B54" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6014,10 +6018,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533650</v>
+        <v>533873</v>
       </c>
       <c r="R54" t="n">
-        <v>6962134</v>
+        <v>6962782</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6054,7 +6058,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>50 stycken ( några har blommat).</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6081,32 +6085,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128101702</v>
+        <v>128110814</v>
       </c>
       <c r="B55" t="n">
-        <v>91352</v>
+        <v>98478</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6116,10 +6120,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533529</v>
+        <v>533650</v>
       </c>
       <c r="R55" t="n">
-        <v>6962400</v>
+        <v>6962134</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6152,6 +6156,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>50 stycken ( några har blommat).</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6178,32 +6187,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128107546</v>
+        <v>128108922</v>
       </c>
       <c r="B56" t="n">
-        <v>80133</v>
+        <v>105516</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>221144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6213,10 +6222,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533648</v>
+        <v>533671</v>
       </c>
       <c r="R56" t="n">
-        <v>6962374</v>
+        <v>6962142</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6275,54 +6284,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128103304</v>
+        <v>128107546</v>
       </c>
       <c r="B57" t="n">
-        <v>91124</v>
+        <v>80136</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3215</v>
+        <v>2081</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533594</v>
+        <v>533648</v>
       </c>
       <c r="R57" t="n">
-        <v>6962541</v>
+        <v>6962374</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6381,45 +6381,54 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128110766</v>
+        <v>128103304</v>
       </c>
       <c r="B58" t="n">
-        <v>57672</v>
+        <v>91133</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533586</v>
+        <v>533594</v>
       </c>
       <c r="R58" t="n">
-        <v>6962139</v>
+        <v>6962541</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6452,11 +6461,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6483,32 +6487,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128110970</v>
+        <v>128110812</v>
       </c>
       <c r="B59" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6518,10 +6522,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>534050</v>
+        <v>533715</v>
       </c>
       <c r="R59" t="n">
-        <v>6962743</v>
+        <v>6962610</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6558,7 +6562,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6585,39 +6589,35 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128099088</v>
+        <v>128101106</v>
       </c>
       <c r="B60" t="n">
-        <v>98470</v>
+        <v>80101</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>229748</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
@@ -6627,7 +6627,7 @@
         <v>533425</v>
       </c>
       <c r="R60" t="n">
-        <v>6962182</v>
+        <v>6962304</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6686,32 +6686,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128099984</v>
+        <v>128110827</v>
       </c>
       <c r="B61" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6721,10 +6721,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533455</v>
+        <v>533614</v>
       </c>
       <c r="R61" t="n">
-        <v>6962339</v>
+        <v>6962554</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6757,6 +6757,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6783,45 +6788,49 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128099875</v>
+        <v>128100184</v>
       </c>
       <c r="B62" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533445</v>
+        <v>533509</v>
       </c>
       <c r="R62" t="n">
-        <v>6962324</v>
+        <v>6962336</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6880,50 +6889,49 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128099885</v>
+        <v>128103587</v>
       </c>
       <c r="B63" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>120</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533361</v>
+        <v>533650</v>
       </c>
       <c r="R63" t="n">
-        <v>6962247</v>
+        <v>6962600</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6956,11 +6964,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6987,10 +6990,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128110971</v>
+        <v>128099885</v>
       </c>
       <c r="B64" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7016,16 +7019,21 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>534036</v>
+        <v>533361</v>
       </c>
       <c r="R64" t="n">
-        <v>6962734</v>
+        <v>6962247</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7062,7 +7070,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7089,10 +7097,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128108477</v>
+        <v>128110971</v>
       </c>
       <c r="B65" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7118,21 +7126,16 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533710</v>
+        <v>534036</v>
       </c>
       <c r="R65" t="n">
-        <v>6962294</v>
+        <v>6962734</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7169,7 +7172,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7196,45 +7199,50 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128110827</v>
+        <v>128108477</v>
       </c>
       <c r="B66" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533614</v>
+        <v>533710</v>
       </c>
       <c r="R66" t="n">
-        <v>6962554</v>
+        <v>6962294</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7271,7 +7279,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>25 ex</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7298,49 +7306,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128100184</v>
+        <v>128099984</v>
       </c>
       <c r="B67" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533509</v>
+        <v>533455</v>
       </c>
       <c r="R67" t="n">
-        <v>6962336</v>
+        <v>6962339</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7399,49 +7403,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128103587</v>
+        <v>128099875</v>
       </c>
       <c r="B68" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533650</v>
+        <v>533445</v>
       </c>
       <c r="R68" t="n">
-        <v>6962600</v>
+        <v>6962324</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7500,54 +7500,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128099522</v>
+        <v>128100636</v>
       </c>
       <c r="B69" t="n">
-        <v>98470</v>
+        <v>80135</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533349</v>
+        <v>533452</v>
       </c>
       <c r="R69" t="n">
-        <v>6962197</v>
+        <v>6962350</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7606,45 +7597,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128099099</v>
+        <v>128099522</v>
       </c>
       <c r="B70" t="n">
-        <v>105508</v>
+        <v>98478</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>533416</v>
+        <v>533349</v>
       </c>
       <c r="R70" t="n">
-        <v>6962179</v>
+        <v>6962197</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7703,32 +7703,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128100636</v>
+        <v>128099099</v>
       </c>
       <c r="B71" t="n">
-        <v>80132</v>
+        <v>105516</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7738,10 +7738,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>533452</v>
+        <v>533416</v>
       </c>
       <c r="R71" t="n">
-        <v>6962350</v>
+        <v>6962179</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7800,10 +7800,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128099712</v>
+        <v>128110769</v>
       </c>
       <c r="B72" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7829,21 +7829,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533451</v>
+        <v>533841</v>
       </c>
       <c r="R72" t="n">
-        <v>6962307</v>
+        <v>6962363</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7880,7 +7875,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack) spår</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7907,10 +7902,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128110769</v>
+        <v>128110775</v>
       </c>
       <c r="B73" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7942,10 +7937,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533841</v>
+        <v>533564</v>
       </c>
       <c r="R73" t="n">
-        <v>6962363</v>
+        <v>6962537</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7982,7 +7977,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack) spår</t>
+          <t>Färska och äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8009,10 +8004,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128110775</v>
+        <v>128108355</v>
       </c>
       <c r="B74" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8038,16 +8033,21 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533564</v>
+        <v>533768</v>
       </c>
       <c r="R74" t="n">
-        <v>6962537</v>
+        <v>6962269</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack på Tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8111,10 +8111,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128108355</v>
+        <v>128101911</v>
       </c>
       <c r="B75" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8142,19 +8142,19 @@
       <c r="I75" t="inlineStr"/>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533768</v>
+        <v>533510</v>
       </c>
       <c r="R75" t="n">
-        <v>6962269</v>
+        <v>6962462</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8218,38 +8218,37 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128101911</v>
+        <v>128101024</v>
       </c>
       <c r="B76" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>20</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8258,10 +8257,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533510</v>
+        <v>533375</v>
       </c>
       <c r="R76" t="n">
-        <v>6962462</v>
+        <v>6962293</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8294,11 +8293,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8328,7 +8322,7 @@
         <v>128099857</v>
       </c>
       <c r="B77" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8425,7 +8419,7 @@
         <v>128110811</v>
       </c>
       <c r="B78" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8524,37 +8518,38 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128101024</v>
+        <v>128099712</v>
       </c>
       <c r="B79" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8563,10 +8558,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533375</v>
+        <v>533451</v>
       </c>
       <c r="R79" t="n">
-        <v>6962293</v>
+        <v>6962307</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8599,6 +8594,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8625,32 +8625,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128110779</v>
+        <v>128102006</v>
       </c>
       <c r="B80" t="n">
-        <v>91124</v>
+        <v>80135</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3215</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8660,10 +8660,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>533678</v>
+        <v>533510</v>
       </c>
       <c r="R80" t="n">
-        <v>6962542</v>
+        <v>6962462</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8722,50 +8722,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128101827</v>
+        <v>128110810</v>
       </c>
       <c r="B81" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533594</v>
+        <v>533645</v>
       </c>
       <c r="R81" t="n">
-        <v>6962354</v>
+        <v>6962593</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8798,11 +8793,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8829,10 +8819,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128100974</v>
+        <v>128099905</v>
       </c>
       <c r="B82" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8869,10 +8859,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533375</v>
+        <v>533445</v>
       </c>
       <c r="R82" t="n">
-        <v>6962293</v>
+        <v>6962324</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8909,7 +8899,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8936,32 +8926,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128110969</v>
+        <v>128110779</v>
       </c>
       <c r="B83" t="n">
-        <v>57672</v>
+        <v>91133</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8971,10 +8961,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533825</v>
+        <v>533678</v>
       </c>
       <c r="R83" t="n">
-        <v>6962690</v>
+        <v>6962542</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9007,11 +8997,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9038,10 +9023,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128102006</v>
+        <v>128101827</v>
       </c>
       <c r="B84" t="n">
-        <v>80132</v>
+        <v>57673</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9049,34 +9034,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533510</v>
+        <v>533594</v>
       </c>
       <c r="R84" t="n">
-        <v>6962462</v>
+        <v>6962354</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9109,6 +9099,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9135,10 +9130,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128099905</v>
+        <v>128100974</v>
       </c>
       <c r="B85" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9175,10 +9170,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533445</v>
+        <v>533375</v>
       </c>
       <c r="R85" t="n">
-        <v>6962324</v>
+        <v>6962293</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9215,7 +9210,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9242,32 +9237,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128110976</v>
+        <v>128110969</v>
       </c>
       <c r="B86" t="n">
-        <v>98504</v>
+        <v>57673</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9277,10 +9272,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533868</v>
+        <v>533825</v>
       </c>
       <c r="R86" t="n">
-        <v>6962692</v>
+        <v>6962690</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9317,7 +9312,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Växer spritt i hela området</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9347,7 +9342,7 @@
         <v>128101261</v>
       </c>
       <c r="B87" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9448,7 +9443,7 @@
         <v>128110982</v>
       </c>
       <c r="B88" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9547,32 +9542,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128110810</v>
+        <v>128110976</v>
       </c>
       <c r="B89" t="n">
-        <v>98470</v>
+        <v>98512</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9582,10 +9577,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533645</v>
+        <v>533868</v>
       </c>
       <c r="R89" t="n">
-        <v>6962593</v>
+        <v>6962692</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9618,6 +9613,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9647,7 +9647,7 @@
         <v>128100745</v>
       </c>
       <c r="B90" t="n">
-        <v>80036</v>
+        <v>80039</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>128110973</v>
       </c>
       <c r="B91" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>128110989</v>
       </c>
       <c r="B92" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>128110806</v>
       </c>
       <c r="B93" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10047,54 +10047,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128099401</v>
+        <v>128110816</v>
       </c>
       <c r="B94" t="n">
-        <v>92642</v>
+        <v>98478</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533356</v>
+        <v>533696</v>
       </c>
       <c r="R94" t="n">
-        <v>6962190</v>
+        <v>6962294</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10127,6 +10118,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10153,38 +10149,37 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128099555</v>
+        <v>128102067</v>
       </c>
       <c r="B95" t="n">
-        <v>57672</v>
+        <v>98478</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10193,10 +10188,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533471</v>
+        <v>533510</v>
       </c>
       <c r="R95" t="n">
-        <v>6962293</v>
+        <v>6962462</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10229,11 +10224,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10260,50 +10250,54 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128102878</v>
+        <v>128099401</v>
       </c>
       <c r="B96" t="n">
-        <v>57672</v>
+        <v>92650</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533665</v>
+        <v>533356</v>
       </c>
       <c r="R96" t="n">
-        <v>6962515</v>
+        <v>6962190</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10336,11 +10330,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10367,10 +10356,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128100043</v>
+        <v>128099555</v>
       </c>
       <c r="B97" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10407,10 +10396,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533496</v>
+        <v>533471</v>
       </c>
       <c r="R97" t="n">
-        <v>6962335</v>
+        <v>6962293</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10447,7 +10436,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10477,7 +10466,7 @@
         <v>128110974</v>
       </c>
       <c r="B98" t="n">
-        <v>80161</v>
+        <v>80164</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10571,45 +10560,50 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128110834</v>
+        <v>128102878</v>
       </c>
       <c r="B99" t="n">
-        <v>98387</v>
+        <v>57673</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>533779</v>
+        <v>533665</v>
       </c>
       <c r="R99" t="n">
-        <v>6962298</v>
+        <v>6962515</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10642,6 +10636,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10668,45 +10667,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128110816</v>
+        <v>128100043</v>
       </c>
       <c r="B100" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>533696</v>
+        <v>533496</v>
       </c>
       <c r="R100" t="n">
-        <v>6962294</v>
+        <v>6962335</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10743,7 +10747,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>20 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10770,49 +10774,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128102067</v>
+        <v>128110834</v>
       </c>
       <c r="B101" t="n">
-        <v>98470</v>
+        <v>98395</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533510</v>
+        <v>533779</v>
       </c>
       <c r="R101" t="n">
-        <v>6962462</v>
+        <v>6962298</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10871,10 +10871,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128110792</v>
+        <v>128101073</v>
       </c>
       <c r="B102" t="n">
-        <v>98504</v>
+        <v>80171</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10882,21 +10882,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>219874</v>
+        <v>6464</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10906,10 +10906,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>533719</v>
+        <v>533385</v>
       </c>
       <c r="R102" t="n">
-        <v>6962615</v>
+        <v>6962288</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10942,11 +10942,6 @@
       <c r="AA102" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -10973,32 +10968,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128110807</v>
+        <v>128110829</v>
       </c>
       <c r="B103" t="n">
-        <v>98470</v>
+        <v>56855</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11008,10 +11003,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>533664</v>
+        <v>533606</v>
       </c>
       <c r="R103" t="n">
-        <v>6962286</v>
+        <v>6962582</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11048,7 +11043,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>23 stycken</t>
+          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11078,7 +11073,7 @@
         <v>128110983</v>
       </c>
       <c r="B104" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11177,32 +11172,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128110829</v>
+        <v>128110792</v>
       </c>
       <c r="B105" t="n">
-        <v>56855</v>
+        <v>98512</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>102612</v>
+        <v>219874</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11212,10 +11207,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>533606</v>
+        <v>533719</v>
       </c>
       <c r="R105" t="n">
-        <v>6962582</v>
+        <v>6962615</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11252,7 +11247,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1 ex. Sång</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11282,7 +11277,7 @@
         <v>128110785</v>
       </c>
       <c r="B106" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11376,32 +11371,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128101073</v>
+        <v>128110807</v>
       </c>
       <c r="B107" t="n">
-        <v>80168</v>
+        <v>98478</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6464</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11411,10 +11406,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533385</v>
+        <v>533664</v>
       </c>
       <c r="R107" t="n">
-        <v>6962288</v>
+        <v>6962286</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11447,6 +11442,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11473,10 +11473,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128108028</v>
+        <v>128110783</v>
       </c>
       <c r="B108" t="n">
-        <v>97353</v>
+        <v>91133</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11484,34 +11484,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221941</v>
+        <v>3215</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533802</v>
+        <v>533599</v>
       </c>
       <c r="R108" t="n">
-        <v>6962332</v>
+        <v>6962553</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11570,50 +11570,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128108378</v>
+        <v>128101331</v>
       </c>
       <c r="B109" t="n">
-        <v>57672</v>
+        <v>80170</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533750</v>
+        <v>533424</v>
       </c>
       <c r="R109" t="n">
-        <v>6962259</v>
+        <v>6962357</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11646,11 +11641,6 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11677,10 +11667,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128100457</v>
+        <v>128108395</v>
       </c>
       <c r="B110" t="n">
-        <v>57672</v>
+        <v>80135</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11688,39 +11678,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533556</v>
+        <v>533735</v>
       </c>
       <c r="R110" t="n">
-        <v>6962363</v>
+        <v>6962274</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11753,11 +11738,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11784,10 +11764,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128110776</v>
+        <v>128108378</v>
       </c>
       <c r="B111" t="n">
-        <v>57832</v>
+        <v>57673</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11795,34 +11775,39 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>533719</v>
+        <v>533750</v>
       </c>
       <c r="R111" t="n">
-        <v>6962615</v>
+        <v>6962259</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11859,7 +11844,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11886,45 +11871,50 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128110838</v>
+        <v>128100457</v>
       </c>
       <c r="B112" t="n">
-        <v>98387</v>
+        <v>57673</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>533708</v>
+        <v>533556</v>
       </c>
       <c r="R112" t="n">
-        <v>6962624</v>
+        <v>6962363</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11961,7 +11951,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>1 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11988,32 +11978,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128110793</v>
+        <v>128110776</v>
       </c>
       <c r="B113" t="n">
-        <v>98504</v>
+        <v>57833</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>219874</v>
+        <v>103021</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12023,10 +12013,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533693</v>
+        <v>533719</v>
       </c>
       <c r="R113" t="n">
-        <v>6962647</v>
+        <v>6962615</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12090,32 +12080,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128110794</v>
+        <v>128110987</v>
       </c>
       <c r="B114" t="n">
-        <v>98504</v>
+        <v>98478</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12125,10 +12115,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533608</v>
+        <v>533999</v>
       </c>
       <c r="R114" t="n">
-        <v>6962612</v>
+        <v>6962664</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12165,7 +12155,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12192,10 +12182,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128110991</v>
+        <v>128103044</v>
       </c>
       <c r="B115" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12220,17 +12210,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533717</v>
+        <v>533627</v>
       </c>
       <c r="R115" t="n">
-        <v>6962645</v>
+        <v>6962544</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12263,11 +12257,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>6 ex</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12294,45 +12283,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128103993</v>
+        <v>128110819</v>
       </c>
       <c r="B116" t="n">
-        <v>105508</v>
+        <v>98478</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533664</v>
+        <v>533834</v>
       </c>
       <c r="R116" t="n">
-        <v>6962650</v>
+        <v>6962298</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12365,6 +12354,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12391,32 +12385,32 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128110987</v>
+        <v>128110838</v>
       </c>
       <c r="B117" t="n">
-        <v>98470</v>
+        <v>98395</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12426,10 +12420,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533999</v>
+        <v>533708</v>
       </c>
       <c r="R117" t="n">
-        <v>6962664</v>
+        <v>6962624</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12466,7 +12460,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12493,49 +12487,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128103044</v>
+        <v>128110793</v>
       </c>
       <c r="B118" t="n">
-        <v>98470</v>
+        <v>98512</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533627</v>
+        <v>533693</v>
       </c>
       <c r="R118" t="n">
-        <v>6962544</v>
+        <v>6962647</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12568,6 +12558,11 @@
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12594,32 +12589,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128110819</v>
+        <v>128110794</v>
       </c>
       <c r="B119" t="n">
-        <v>98470</v>
+        <v>98512</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12629,10 +12624,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533834</v>
+        <v>533608</v>
       </c>
       <c r="R119" t="n">
-        <v>6962298</v>
+        <v>6962612</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12669,7 +12664,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>10 stycken kan finnas fler runt omkring</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12696,10 +12691,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128101331</v>
+        <v>128103993</v>
       </c>
       <c r="B120" t="n">
-        <v>80167</v>
+        <v>105516</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12707,34 +12702,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>221144</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533424</v>
+        <v>533664</v>
       </c>
       <c r="R120" t="n">
-        <v>6962357</v>
+        <v>6962650</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12793,32 +12788,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128108395</v>
+        <v>128108028</v>
       </c>
       <c r="B121" t="n">
-        <v>80132</v>
+        <v>97361</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>221941</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12828,10 +12823,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533735</v>
+        <v>533802</v>
       </c>
       <c r="R121" t="n">
-        <v>6962274</v>
+        <v>6962332</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12890,32 +12885,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128110783</v>
+        <v>128110991</v>
       </c>
       <c r="B122" t="n">
-        <v>91124</v>
+        <v>98478</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12925,10 +12920,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533599</v>
+        <v>533717</v>
       </c>
       <c r="R122" t="n">
-        <v>6962553</v>
+        <v>6962645</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12961,6 +12956,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12990,7 +12990,7 @@
         <v>128099487</v>
       </c>
       <c r="B123" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13088,32 +13088,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128099811</v>
+        <v>128110823</v>
       </c>
       <c r="B124" t="n">
-        <v>105508</v>
+        <v>98478</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13123,10 +13123,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>533451</v>
+        <v>533715</v>
       </c>
       <c r="R124" t="n">
-        <v>6962307</v>
+        <v>6962631</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13159,6 +13159,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13185,50 +13190,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128100396</v>
+        <v>128110825</v>
       </c>
       <c r="B125" t="n">
-        <v>57832</v>
+        <v>98478</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>533537</v>
+        <v>533583</v>
       </c>
       <c r="R125" t="n">
-        <v>6962358</v>
+        <v>6962689</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13261,6 +13261,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>84stycken</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13290,7 +13295,7 @@
         <v>128110789</v>
       </c>
       <c r="B126" t="n">
-        <v>98504</v>
+        <v>98512</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13387,7 +13392,7 @@
         <v>128108119</v>
       </c>
       <c r="B127" t="n">
-        <v>98504</v>
+        <v>98512</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13481,45 +13486,50 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128110823</v>
+        <v>128099239</v>
       </c>
       <c r="B128" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>533715</v>
+        <v>533422</v>
       </c>
       <c r="R128" t="n">
-        <v>6962631</v>
+        <v>6962229</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13556,7 +13566,7 @@
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13583,32 +13593,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128110825</v>
+        <v>128109488</v>
       </c>
       <c r="B129" t="n">
-        <v>98470</v>
+        <v>80164</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13618,10 +13628,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>533583</v>
+        <v>533498</v>
       </c>
       <c r="R129" t="n">
-        <v>6962689</v>
+        <v>6962158</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13654,11 +13664,6 @@
       <c r="AA129" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>84stycken</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13685,10 +13690,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128109488</v>
+        <v>128109254</v>
       </c>
       <c r="B130" t="n">
-        <v>80161</v>
+        <v>80163</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -13696,34 +13701,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>533498</v>
+        <v>533652</v>
       </c>
       <c r="R130" t="n">
-        <v>6962158</v>
+        <v>6962140</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13782,45 +13787,50 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128109254</v>
+        <v>128100396</v>
       </c>
       <c r="B131" t="n">
-        <v>80160</v>
+        <v>57833</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6461</v>
+        <v>103021</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>533652</v>
+        <v>533537</v>
       </c>
       <c r="R131" t="n">
-        <v>6962140</v>
+        <v>6962358</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13879,50 +13889,45 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128099239</v>
+        <v>128099811</v>
       </c>
       <c r="B132" t="n">
-        <v>57672</v>
+        <v>105516</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>533422</v>
+        <v>533451</v>
       </c>
       <c r="R132" t="n">
-        <v>6962229</v>
+        <v>6962307</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -13955,11 +13960,6 @@
       <c r="AA132" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -13989,7 +13989,7 @@
         <v>128103617</v>
       </c>
       <c r="B133" t="n">
-        <v>91352</v>
+        <v>91360</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14083,10 +14083,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128110809</v>
+        <v>128110808</v>
       </c>
       <c r="B134" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14118,10 +14118,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>533748</v>
+        <v>533745</v>
       </c>
       <c r="R134" t="n">
-        <v>6962494</v>
+        <v>6962429</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14158,7 +14158,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
+          <t>22 stycken</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14185,45 +14185,49 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128100350</v>
+        <v>128107880</v>
       </c>
       <c r="B135" t="n">
-        <v>97347</v>
+        <v>98478</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>533545</v>
+        <v>533736</v>
       </c>
       <c r="R135" t="n">
-        <v>6962339</v>
+        <v>6962362</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14282,32 +14286,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128110830</v>
+        <v>128110809</v>
       </c>
       <c r="B136" t="n">
-        <v>105508</v>
+        <v>98478</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14317,10 +14321,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>533659</v>
+        <v>533748</v>
       </c>
       <c r="R136" t="n">
-        <v>6962296</v>
+        <v>6962494</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14353,6 +14357,11 @@
       <c r="AA136" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>6 stycken kan möjlitvis finnas fler i blåbärsriset</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14379,10 +14388,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128110808</v>
+        <v>128110984</v>
       </c>
       <c r="B137" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -14414,10 +14423,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>533745</v>
+        <v>533734</v>
       </c>
       <c r="R137" t="n">
-        <v>6962429</v>
+        <v>6962473</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14454,7 +14463,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>22 stycken</t>
+          <t>40 ex</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14481,49 +14490,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128107880</v>
+        <v>128110830</v>
       </c>
       <c r="B138" t="n">
-        <v>98470</v>
+        <v>105516</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>533736</v>
+        <v>533659</v>
       </c>
       <c r="R138" t="n">
-        <v>6962362</v>
+        <v>6962296</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14582,32 +14587,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128110984</v>
+        <v>128100350</v>
       </c>
       <c r="B139" t="n">
-        <v>98470</v>
+        <v>97355</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14617,10 +14622,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>533734</v>
+        <v>533545</v>
       </c>
       <c r="R139" t="n">
-        <v>6962473</v>
+        <v>6962339</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14653,11 +14658,6 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>40 ex</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14684,10 +14684,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128102955</v>
+        <v>128108442</v>
       </c>
       <c r="B140" t="n">
-        <v>78787</v>
+        <v>57673</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -14695,34 +14695,39 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P140" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>533659</v>
+        <v>533714</v>
       </c>
       <c r="R140" t="n">
-        <v>6962538</v>
+        <v>6962273</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14755,6 +14760,11 @@
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -14781,10 +14791,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128108442</v>
+        <v>128109413</v>
       </c>
       <c r="B141" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -14817,14 +14827,14 @@
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>533714</v>
+        <v>533532</v>
       </c>
       <c r="R141" t="n">
-        <v>6962273</v>
+        <v>6962150</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14888,10 +14898,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128109413</v>
+        <v>128109827</v>
       </c>
       <c r="B142" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -14928,10 +14938,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>533532</v>
+        <v>533421</v>
       </c>
       <c r="R142" t="n">
-        <v>6962150</v>
+        <v>6962154</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -14995,10 +15005,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128109827</v>
+        <v>128102524</v>
       </c>
       <c r="B143" t="n">
-        <v>57672</v>
+        <v>56855</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15006,16 +15016,16 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -15026,7 +15036,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P143" t="inlineStr">
@@ -15035,10 +15045,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>533421</v>
+        <v>533640</v>
       </c>
       <c r="R143" t="n">
-        <v>6962154</v>
+        <v>6962482</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15071,11 +15081,6 @@
       <c r="AA143" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15102,38 +15107,37 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128102524</v>
+        <v>128099760</v>
       </c>
       <c r="B144" t="n">
-        <v>56855</v>
+        <v>98478</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>40</t>
         </is>
       </c>
       <c r="P144" t="inlineStr">
@@ -15142,10 +15146,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>533640</v>
+        <v>533451</v>
       </c>
       <c r="R144" t="n">
-        <v>6962482</v>
+        <v>6962307</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15204,10 +15208,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128099760</v>
+        <v>128110801</v>
       </c>
       <c r="B145" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15232,21 +15236,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>533451</v>
+        <v>533442</v>
       </c>
       <c r="R145" t="n">
-        <v>6962307</v>
+        <v>6962166</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15279,6 +15279,11 @@
       <c r="AA145" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>4 stycken  ( finns möjligtvis fler I blåbärsriset)</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15305,10 +15310,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128110801</v>
+        <v>128110821</v>
       </c>
       <c r="B146" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15340,10 +15345,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>533442</v>
+        <v>533705</v>
       </c>
       <c r="R146" t="n">
-        <v>6962166</v>
+        <v>6962430</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15380,7 +15385,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>4 stycken  ( finns möjligtvis fler I blåbärsriset)</t>
+          <t>7 stycken</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15407,10 +15412,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128110821</v>
+        <v>128110988</v>
       </c>
       <c r="B147" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -15442,10 +15447,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>533705</v>
+        <v>533959</v>
       </c>
       <c r="R147" t="n">
-        <v>6962430</v>
+        <v>6962738</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15482,7 +15487,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>7 stycken</t>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15509,45 +15514,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128110988</v>
+        <v>128102955</v>
       </c>
       <c r="B148" t="n">
-        <v>98470</v>
+        <v>78790</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>533959</v>
+        <v>533659</v>
       </c>
       <c r="R148" t="n">
-        <v>6962738</v>
+        <v>6962538</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15580,11 +15585,6 @@
       <c r="AA148" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>5 ex</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15611,45 +15611,54 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128110796</v>
+        <v>128099113</v>
       </c>
       <c r="B149" t="n">
-        <v>80132</v>
+        <v>92650</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>533655</v>
+        <v>533396</v>
       </c>
       <c r="R149" t="n">
-        <v>6962173</v>
+        <v>6962161</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15682,6 +15691,11 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15708,10 +15722,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128109763</v>
+        <v>128110831</v>
       </c>
       <c r="B150" t="n">
-        <v>80036</v>
+        <v>58532</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -15719,21 +15733,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6456</v>
+        <v>208249</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15743,10 +15757,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>533449</v>
+        <v>533728</v>
       </c>
       <c r="R150" t="n">
-        <v>6962147</v>
+        <v>6962422</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15808,7 +15822,7 @@
         <v>128101444</v>
       </c>
       <c r="B151" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -15909,7 +15923,7 @@
         <v>128110986</v>
       </c>
       <c r="B152" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16011,7 +16025,7 @@
         <v>128102104</v>
       </c>
       <c r="B153" t="n">
-        <v>105508</v>
+        <v>105516</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16105,10 +16119,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128110768</v>
+        <v>128110796</v>
       </c>
       <c r="B154" t="n">
-        <v>57672</v>
+        <v>80135</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16116,21 +16130,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16140,10 +16154,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>533754</v>
+        <v>533655</v>
       </c>
       <c r="R154" t="n">
-        <v>6962450</v>
+        <v>6962173</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16176,11 +16190,6 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16207,10 +16216,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128110831</v>
+        <v>128109763</v>
       </c>
       <c r="B155" t="n">
-        <v>58531</v>
+        <v>80039</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -16218,21 +16227,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>208249</v>
+        <v>6456</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16242,10 +16251,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>533728</v>
+        <v>533449</v>
       </c>
       <c r="R155" t="n">
-        <v>6962422</v>
+        <v>6962147</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16304,54 +16313,45 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128099113</v>
+        <v>128110768</v>
       </c>
       <c r="B156" t="n">
-        <v>92642</v>
+        <v>57673</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>533396</v>
+        <v>533754</v>
       </c>
       <c r="R156" t="n">
-        <v>6962161</v>
+        <v>6962450</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16388,7 +16388,7 @@
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Äldre ex</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16418,7 +16418,7 @@
         <v>128102121</v>
       </c>
       <c r="B157" t="n">
-        <v>57832</v>
+        <v>57833</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>128110777</v>
       </c>
       <c r="B158" t="n">
-        <v>91124</v>
+        <v>91133</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -16609,10 +16609,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128110967</v>
+        <v>128110795</v>
       </c>
       <c r="B159" t="n">
-        <v>57672</v>
+        <v>80135</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -16620,21 +16620,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16644,10 +16644,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>533691</v>
+        <v>533792</v>
       </c>
       <c r="R159" t="n">
-        <v>6962407</v>
+        <v>6962400</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16680,11 +16680,6 @@
       <c r="AA159" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -16711,10 +16706,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128110773</v>
+        <v>128110967</v>
       </c>
       <c r="B160" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -16746,10 +16741,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>533604</v>
+        <v>533691</v>
       </c>
       <c r="R160" t="n">
-        <v>6962650</v>
+        <v>6962407</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16786,7 +16781,7 @@
       </c>
       <c r="AC160" t="inlineStr">
         <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16813,10 +16808,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128110774</v>
+        <v>128110773</v>
       </c>
       <c r="B161" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -16848,10 +16843,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>533585</v>
+        <v>533604</v>
       </c>
       <c r="R161" t="n">
-        <v>6962612</v>
+        <v>6962650</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16888,7 +16883,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>Färska ringhack av tretåig hackspett på Tall</t>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16915,32 +16910,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128110837</v>
+        <v>128110774</v>
       </c>
       <c r="B162" t="n">
-        <v>98387</v>
+        <v>57673</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16950,10 +16945,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>533617</v>
+        <v>533585</v>
       </c>
       <c r="R162" t="n">
-        <v>6962560</v>
+        <v>6962612</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16986,6 +16981,11 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17012,32 +17012,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128110791</v>
+        <v>128110805</v>
       </c>
       <c r="B163" t="n">
-        <v>98504</v>
+        <v>98478</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17047,10 +17047,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>533658</v>
+        <v>533668</v>
       </c>
       <c r="R163" t="n">
-        <v>6962570</v>
+        <v>6962160</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17083,6 +17083,11 @@
       <c r="AA163" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>75 stycken</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17109,10 +17114,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128110805</v>
+        <v>128109586</v>
       </c>
       <c r="B164" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -17137,17 +17142,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>533668</v>
+        <v>533498</v>
       </c>
       <c r="R164" t="n">
-        <v>6962160</v>
+        <v>6962158</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17180,11 +17189,6 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>75 stycken</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17211,49 +17215,45 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128109586</v>
+        <v>128110837</v>
       </c>
       <c r="B165" t="n">
-        <v>98470</v>
+        <v>98395</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>533498</v>
+        <v>533617</v>
       </c>
       <c r="R165" t="n">
-        <v>6962158</v>
+        <v>6962560</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17312,32 +17312,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128110795</v>
+        <v>128110791</v>
       </c>
       <c r="B166" t="n">
-        <v>80132</v>
+        <v>98512</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17347,10 +17347,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>533792</v>
+        <v>533658</v>
       </c>
       <c r="R166" t="n">
-        <v>6962400</v>
+        <v>6962570</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17409,49 +17409,45 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128101672</v>
+        <v>128110781</v>
       </c>
       <c r="B167" t="n">
-        <v>98470</v>
+        <v>91133</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>533534</v>
+        <v>533700</v>
       </c>
       <c r="R167" t="n">
-        <v>6962408</v>
+        <v>6962581</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17510,49 +17506,45 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128109121</v>
+        <v>128110782</v>
       </c>
       <c r="B168" t="n">
-        <v>98470</v>
+        <v>91133</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>533651</v>
+        <v>533630</v>
       </c>
       <c r="R168" t="n">
-        <v>6962130</v>
+        <v>6962701</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17611,45 +17603,54 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128110813</v>
+        <v>128102411</v>
       </c>
       <c r="B169" t="n">
-        <v>98470</v>
+        <v>57833</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P169" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>533507</v>
+        <v>533575</v>
       </c>
       <c r="R169" t="n">
-        <v>6962168</v>
+        <v>6962520</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17682,11 +17683,6 @@
       <c r="AA169" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC169" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -17713,10 +17709,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128110985</v>
+        <v>128101672</v>
       </c>
       <c r="B170" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17741,17 +17737,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>533652</v>
+        <v>533534</v>
       </c>
       <c r="R170" t="n">
-        <v>6962550</v>
+        <v>6962408</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17784,11 +17784,6 @@
       <c r="AA170" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>80 ex</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17815,45 +17810,49 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128110782</v>
+        <v>128109121</v>
       </c>
       <c r="B171" t="n">
-        <v>91124</v>
+        <v>98478</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I171" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>533630</v>
+        <v>533651</v>
       </c>
       <c r="R171" t="n">
-        <v>6962701</v>
+        <v>6962130</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -17912,32 +17911,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128110781</v>
+        <v>128110985</v>
       </c>
       <c r="B172" t="n">
-        <v>91124</v>
+        <v>98478</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17947,10 +17946,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>533700</v>
+        <v>533652</v>
       </c>
       <c r="R172" t="n">
-        <v>6962581</v>
+        <v>6962550</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17983,6 +17982,11 @@
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>80 ex</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -18009,32 +18013,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128101262</v>
+        <v>128110813</v>
       </c>
       <c r="B173" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18044,10 +18048,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>533424</v>
+        <v>533507</v>
       </c>
       <c r="R173" t="n">
-        <v>6962357</v>
+        <v>6962168</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18080,6 +18084,11 @@
       <c r="AA173" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -18106,10 +18115,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128110797</v>
+        <v>128101262</v>
       </c>
       <c r="B174" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -18141,10 +18150,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>533832</v>
+        <v>533424</v>
       </c>
       <c r="R174" t="n">
-        <v>6962351</v>
+        <v>6962357</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18203,10 +18212,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128102411</v>
+        <v>128110797</v>
       </c>
       <c r="B175" t="n">
-        <v>57832</v>
+        <v>80135</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -18214,43 +18223,34 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>533575</v>
+        <v>533832</v>
       </c>
       <c r="R175" t="n">
-        <v>6962520</v>
+        <v>6962351</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18309,32 +18309,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128110787</v>
+        <v>128110799</v>
       </c>
       <c r="B176" t="n">
-        <v>80160</v>
+        <v>80135</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18344,10 +18344,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>533785</v>
+        <v>533724</v>
       </c>
       <c r="R176" t="n">
-        <v>6962326</v>
+        <v>6962625</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18406,32 +18406,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128101075</v>
+        <v>128110787</v>
       </c>
       <c r="B177" t="n">
-        <v>80132</v>
+        <v>80163</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6458</v>
+        <v>6461</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18441,10 +18441,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>533392</v>
+        <v>533785</v>
       </c>
       <c r="R177" t="n">
-        <v>6962343</v>
+        <v>6962326</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18503,10 +18503,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128108439</v>
+        <v>128101075</v>
       </c>
       <c r="B178" t="n">
-        <v>57672</v>
+        <v>80135</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -18514,39 +18514,34 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>533711</v>
+        <v>533392</v>
       </c>
       <c r="R178" t="n">
-        <v>6962283</v>
+        <v>6962343</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18579,11 +18574,6 @@
       <c r="AA178" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC178" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -18610,10 +18600,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128101939</v>
+        <v>128108439</v>
       </c>
       <c r="B179" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -18646,14 +18636,14 @@
       </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>533638</v>
+        <v>533711</v>
       </c>
       <c r="R179" t="n">
-        <v>6962346</v>
+        <v>6962283</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18717,10 +18707,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128100413</v>
+        <v>128101939</v>
       </c>
       <c r="B180" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18757,10 +18747,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>533545</v>
+        <v>533638</v>
       </c>
       <c r="R180" t="n">
-        <v>6962372</v>
+        <v>6962346</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18824,45 +18814,50 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128110828</v>
+        <v>128100413</v>
       </c>
       <c r="B181" t="n">
-        <v>98470</v>
+        <v>57673</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>533365</v>
+        <v>533545</v>
       </c>
       <c r="R181" t="n">
-        <v>6962304</v>
+        <v>6962372</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18899,7 +18894,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -18929,7 +18924,7 @@
         <v>128107826</v>
       </c>
       <c r="B182" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -19027,10 +19022,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128110817</v>
+        <v>128110828</v>
       </c>
       <c r="B183" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -19062,10 +19057,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>533728</v>
+        <v>533365</v>
       </c>
       <c r="R183" t="n">
-        <v>6962346</v>
+        <v>6962304</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19102,7 +19097,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>40 stycken i blåbärsriset</t>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19129,32 +19124,32 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128110799</v>
+        <v>128110817</v>
       </c>
       <c r="B184" t="n">
-        <v>80132</v>
+        <v>98478</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19164,10 +19159,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>533724</v>
+        <v>533728</v>
       </c>
       <c r="R184" t="n">
-        <v>6962625</v>
+        <v>6962346</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19200,6 +19195,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19229,7 +19229,7 @@
         <v>128110835</v>
       </c>
       <c r="B185" t="n">
-        <v>98387</v>
+        <v>98395</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19326,7 +19326,7 @@
         <v>128110977</v>
       </c>
       <c r="B186" t="n">
-        <v>98504</v>
+        <v>98512</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19423,7 +19423,7 @@
         <v>128269237</v>
       </c>
       <c r="B187" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>128269235</v>
       </c>
       <c r="B188" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>128269236</v>
       </c>
       <c r="B189" t="n">
-        <v>80133</v>
+        <v>80136</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -2736,37 +2736,38 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128101601</v>
+        <v>128099395</v>
       </c>
       <c r="B22" t="n">
-        <v>98478</v>
+        <v>57673</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2775,10 +2776,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533496</v>
+        <v>533356</v>
       </c>
       <c r="R22" t="n">
-        <v>6962407</v>
+        <v>6962190</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2811,6 +2812,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2837,7 +2843,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128108218</v>
+        <v>128101601</v>
       </c>
       <c r="B23" t="n">
         <v>98478</v>
@@ -2867,19 +2873,19 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533789</v>
+        <v>533496</v>
       </c>
       <c r="R23" t="n">
-        <v>6962263</v>
+        <v>6962407</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,50 +2944,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128099395</v>
+        <v>128108218</v>
       </c>
       <c r="B24" t="n">
-        <v>57673</v>
+        <v>98478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533356</v>
+        <v>533789</v>
       </c>
       <c r="R24" t="n">
-        <v>6962190</v>
+        <v>6962263</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3014,11 +3019,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -6686,32 +6686,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128110827</v>
+        <v>128100636</v>
       </c>
       <c r="B61" t="n">
-        <v>98478</v>
+        <v>80135</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6721,10 +6721,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533614</v>
+        <v>533452</v>
       </c>
       <c r="R61" t="n">
-        <v>6962554</v>
+        <v>6962350</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6757,11 +6757,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6990,10 +6985,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128099885</v>
+        <v>128099984</v>
       </c>
       <c r="B64" t="n">
-        <v>57673</v>
+        <v>80135</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7001,39 +6996,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533361</v>
+        <v>533455</v>
       </c>
       <c r="R64" t="n">
-        <v>6962247</v>
+        <v>6962339</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7066,11 +7056,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7097,10 +7082,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128110971</v>
+        <v>128099875</v>
       </c>
       <c r="B65" t="n">
-        <v>57673</v>
+        <v>80135</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7108,21 +7093,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7132,10 +7117,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>534036</v>
+        <v>533445</v>
       </c>
       <c r="R65" t="n">
-        <v>6962734</v>
+        <v>6962324</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7168,11 +7153,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7199,7 +7179,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128108477</v>
+        <v>128110971</v>
       </c>
       <c r="B66" t="n">
         <v>57673</v>
@@ -7228,21 +7208,16 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>533710</v>
+        <v>534036</v>
       </c>
       <c r="R66" t="n">
-        <v>6962294</v>
+        <v>6962734</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7279,7 +7254,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7306,10 +7281,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128099984</v>
+        <v>128108477</v>
       </c>
       <c r="B67" t="n">
-        <v>80135</v>
+        <v>57673</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7317,34 +7292,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533455</v>
+        <v>533710</v>
       </c>
       <c r="R67" t="n">
-        <v>6962339</v>
+        <v>6962294</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7377,6 +7357,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7403,32 +7388,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128099875</v>
+        <v>128110827</v>
       </c>
       <c r="B68" t="n">
-        <v>80135</v>
+        <v>98478</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7438,10 +7423,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533445</v>
+        <v>533614</v>
       </c>
       <c r="R68" t="n">
-        <v>6962324</v>
+        <v>6962554</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7474,6 +7459,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7500,10 +7490,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128100636</v>
+        <v>128099885</v>
       </c>
       <c r="B69" t="n">
-        <v>80135</v>
+        <v>57673</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7511,34 +7501,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>533452</v>
+        <v>533361</v>
       </c>
       <c r="R69" t="n">
-        <v>6962350</v>
+        <v>6962247</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7571,6 +7566,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -10047,32 +10047,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128110816</v>
+        <v>128110974</v>
       </c>
       <c r="B94" t="n">
-        <v>98478</v>
+        <v>80164</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10082,10 +10082,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>533696</v>
+        <v>533937</v>
       </c>
       <c r="R94" t="n">
-        <v>6962294</v>
+        <v>6962685</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10118,11 +10118,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10149,49 +10144,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128102067</v>
+        <v>128102878</v>
       </c>
       <c r="B95" t="n">
-        <v>98478</v>
+        <v>57673</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533510</v>
+        <v>533665</v>
       </c>
       <c r="R95" t="n">
-        <v>6962462</v>
+        <v>6962515</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10224,6 +10220,11 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10250,42 +10251,38 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128099401</v>
+        <v>128100043</v>
       </c>
       <c r="B96" t="n">
-        <v>92650</v>
+        <v>57673</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10294,10 +10291,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533356</v>
+        <v>533496</v>
       </c>
       <c r="R96" t="n">
-        <v>6962190</v>
+        <v>6962335</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10330,6 +10327,11 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10356,38 +10358,42 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128099555</v>
+        <v>128099401</v>
       </c>
       <c r="B97" t="n">
-        <v>57673</v>
+        <v>92650</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10396,10 +10402,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533471</v>
+        <v>533356</v>
       </c>
       <c r="R97" t="n">
-        <v>6962293</v>
+        <v>6962190</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10432,11 +10438,6 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10463,45 +10464,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128110974</v>
+        <v>128099555</v>
       </c>
       <c r="B98" t="n">
-        <v>80164</v>
+        <v>57673</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>533937</v>
+        <v>533471</v>
       </c>
       <c r="R98" t="n">
-        <v>6962685</v>
+        <v>6962293</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10534,6 +10540,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10560,50 +10571,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128102878</v>
+        <v>128110834</v>
       </c>
       <c r="B99" t="n">
-        <v>57673</v>
+        <v>98395</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>533665</v>
+        <v>533779</v>
       </c>
       <c r="R99" t="n">
-        <v>6962515</v>
+        <v>6962298</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10636,11 +10642,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10667,50 +10668,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128100043</v>
+        <v>128110816</v>
       </c>
       <c r="B100" t="n">
-        <v>57673</v>
+        <v>98478</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>533496</v>
+        <v>533696</v>
       </c>
       <c r="R100" t="n">
-        <v>6962335</v>
+        <v>6962294</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10747,7 +10743,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10774,45 +10770,49 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128110834</v>
+        <v>128102067</v>
       </c>
       <c r="B101" t="n">
-        <v>98395</v>
+        <v>98478</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533779</v>
+        <v>533510</v>
       </c>
       <c r="R101" t="n">
-        <v>6962298</v>
+        <v>6962462</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128110983</v>
+        <v>128110807</v>
       </c>
       <c r="B104" t="n">
         <v>98478</v>
@@ -11105,10 +11105,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>533665</v>
+        <v>533664</v>
       </c>
       <c r="R104" t="n">
-        <v>6962459</v>
+        <v>6962286</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>26 ex</t>
+          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11172,32 +11172,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128110792</v>
+        <v>128110983</v>
       </c>
       <c r="B105" t="n">
-        <v>98512</v>
+        <v>98478</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11207,10 +11207,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>533719</v>
+        <v>533665</v>
       </c>
       <c r="R105" t="n">
-        <v>6962615</v>
+        <v>6962459</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11247,7 +11247,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26 ex</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11274,10 +11274,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128110785</v>
+        <v>128110792</v>
       </c>
       <c r="B106" t="n">
-        <v>97355</v>
+        <v>98512</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11285,21 +11285,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>221945</v>
+        <v>219874</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11309,10 +11309,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>533824</v>
+        <v>533719</v>
       </c>
       <c r="R106" t="n">
-        <v>6962352</v>
+        <v>6962615</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11345,6 +11345,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11371,32 +11376,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128110807</v>
+        <v>128110785</v>
       </c>
       <c r="B107" t="n">
-        <v>98478</v>
+        <v>97355</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11406,10 +11411,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533664</v>
+        <v>533824</v>
       </c>
       <c r="R107" t="n">
-        <v>6962286</v>
+        <v>6962352</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11442,11 +11447,6 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>23 stycken</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11473,32 +11473,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128110783</v>
+        <v>128110991</v>
       </c>
       <c r="B108" t="n">
-        <v>91133</v>
+        <v>98478</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11508,10 +11508,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533599</v>
+        <v>533717</v>
       </c>
       <c r="R108" t="n">
-        <v>6962553</v>
+        <v>6962645</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11544,6 +11544,11 @@
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11570,32 +11575,32 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128101331</v>
+        <v>128110987</v>
       </c>
       <c r="B109" t="n">
-        <v>80170</v>
+        <v>98478</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11605,10 +11610,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533424</v>
+        <v>533999</v>
       </c>
       <c r="R109" t="n">
-        <v>6962357</v>
+        <v>6962664</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11641,6 +11646,11 @@
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>85 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11667,45 +11677,49 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128108395</v>
+        <v>128103044</v>
       </c>
       <c r="B110" t="n">
-        <v>80135</v>
+        <v>98478</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>533735</v>
+        <v>533627</v>
       </c>
       <c r="R110" t="n">
-        <v>6962274</v>
+        <v>6962544</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11764,50 +11778,45 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>128108378</v>
+        <v>128110819</v>
       </c>
       <c r="B111" t="n">
-        <v>57673</v>
+        <v>98478</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>533750</v>
+        <v>533834</v>
       </c>
       <c r="R111" t="n">
-        <v>6962259</v>
+        <v>6962298</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11844,7 +11853,7 @@
       </c>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11871,50 +11880,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>128100457</v>
+        <v>128110838</v>
       </c>
       <c r="B112" t="n">
-        <v>57673</v>
+        <v>98395</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>533556</v>
+        <v>533708</v>
       </c>
       <c r="R112" t="n">
-        <v>6962363</v>
+        <v>6962624</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11951,7 +11955,7 @@
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -11978,32 +11982,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128110776</v>
+        <v>128110793</v>
       </c>
       <c r="B113" t="n">
-        <v>57833</v>
+        <v>98512</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>103021</v>
+        <v>219874</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12013,10 +12017,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>533719</v>
+        <v>533693</v>
       </c>
       <c r="R113" t="n">
-        <v>6962615</v>
+        <v>6962647</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12080,32 +12084,32 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>128110987</v>
+        <v>128110794</v>
       </c>
       <c r="B114" t="n">
-        <v>98478</v>
+        <v>98512</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12115,10 +12119,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>533999</v>
+        <v>533608</v>
       </c>
       <c r="R114" t="n">
-        <v>6962664</v>
+        <v>6962612</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12155,7 +12159,7 @@
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12182,49 +12186,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128103044</v>
+        <v>128103993</v>
       </c>
       <c r="B115" t="n">
-        <v>98478</v>
+        <v>105516</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>533627</v>
+        <v>533664</v>
       </c>
       <c r="R115" t="n">
-        <v>6962544</v>
+        <v>6962650</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12283,45 +12283,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128110819</v>
+        <v>128108028</v>
       </c>
       <c r="B116" t="n">
-        <v>98478</v>
+        <v>97361</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>533834</v>
+        <v>533802</v>
       </c>
       <c r="R116" t="n">
-        <v>6962298</v>
+        <v>6962332</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12354,11 +12354,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>10 stycken kan finnas fler runt omkring</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12385,10 +12380,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128110838</v>
+        <v>128110783</v>
       </c>
       <c r="B117" t="n">
-        <v>98395</v>
+        <v>91133</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12396,21 +12391,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219790</v>
+        <v>3215</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12420,10 +12415,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>533708</v>
+        <v>533599</v>
       </c>
       <c r="R117" t="n">
-        <v>6962624</v>
+        <v>6962553</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12456,11 +12451,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>1 stycken</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12487,45 +12477,50 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128110793</v>
+        <v>128108378</v>
       </c>
       <c r="B118" t="n">
-        <v>98512</v>
+        <v>57673</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>533693</v>
+        <v>533750</v>
       </c>
       <c r="R118" t="n">
-        <v>6962647</v>
+        <v>6962259</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12562,7 +12557,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>2 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12589,45 +12584,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128110794</v>
+        <v>128100457</v>
       </c>
       <c r="B119" t="n">
-        <v>98512</v>
+        <v>57673</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>533608</v>
+        <v>533556</v>
       </c>
       <c r="R119" t="n">
-        <v>6962612</v>
+        <v>6962363</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12691,10 +12691,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128103993</v>
+        <v>128101331</v>
       </c>
       <c r="B120" t="n">
-        <v>105516</v>
+        <v>80170</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12702,34 +12702,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>221144</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>533664</v>
+        <v>533424</v>
       </c>
       <c r="R120" t="n">
-        <v>6962650</v>
+        <v>6962357</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12788,32 +12788,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128108028</v>
+        <v>128108395</v>
       </c>
       <c r="B121" t="n">
-        <v>97361</v>
+        <v>80135</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12823,10 +12823,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>533802</v>
+        <v>533735</v>
       </c>
       <c r="R121" t="n">
-        <v>6962332</v>
+        <v>6962274</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12885,32 +12885,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128110991</v>
+        <v>128110776</v>
       </c>
       <c r="B122" t="n">
-        <v>98478</v>
+        <v>57833</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12920,10 +12920,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>533717</v>
+        <v>533719</v>
       </c>
       <c r="R122" t="n">
-        <v>6962645</v>
+        <v>6962615</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="AC122" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -15611,42 +15611,37 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128099113</v>
+        <v>128101444</v>
       </c>
       <c r="B149" t="n">
-        <v>92650</v>
+        <v>98478</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>24</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -15655,10 +15650,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>533396</v>
+        <v>533424</v>
       </c>
       <c r="R149" t="n">
-        <v>6962161</v>
+        <v>6962351</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15691,11 +15686,6 @@
       <c r="AA149" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15722,32 +15712,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128110831</v>
+        <v>128110986</v>
       </c>
       <c r="B150" t="n">
-        <v>58532</v>
+        <v>98478</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>208249</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15757,10 +15747,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>533728</v>
+        <v>533957</v>
       </c>
       <c r="R150" t="n">
-        <v>6962422</v>
+        <v>6962694</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15793,6 +15783,11 @@
       <c r="AA150" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>37 ex</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -15819,37 +15814,42 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128101444</v>
+        <v>128099113</v>
       </c>
       <c r="B151" t="n">
-        <v>98478</v>
+        <v>92650</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -15858,10 +15858,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>533424</v>
+        <v>533396</v>
       </c>
       <c r="R151" t="n">
-        <v>6962351</v>
+        <v>6962161</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15894,6 +15894,11 @@
       <c r="AA151" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>Äldre ex</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -15920,32 +15925,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128110986</v>
+        <v>128110796</v>
       </c>
       <c r="B152" t="n">
-        <v>98478</v>
+        <v>80135</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -15955,10 +15960,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>533957</v>
+        <v>533655</v>
       </c>
       <c r="R152" t="n">
-        <v>6962694</v>
+        <v>6962173</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -15991,11 +15996,6 @@
       <c r="AA152" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>37 ex</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16022,10 +16022,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128102104</v>
+        <v>128109763</v>
       </c>
       <c r="B153" t="n">
-        <v>105516</v>
+        <v>80039</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -16033,21 +16033,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>221144</v>
+        <v>6456</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16057,10 +16057,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>533615</v>
+        <v>533449</v>
       </c>
       <c r="R153" t="n">
-        <v>6962423</v>
+        <v>6962147</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16119,10 +16119,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128110796</v>
+        <v>128110768</v>
       </c>
       <c r="B154" t="n">
-        <v>80135</v>
+        <v>57673</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -16130,21 +16130,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16154,10 +16154,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>533655</v>
+        <v>533754</v>
       </c>
       <c r="R154" t="n">
-        <v>6962173</v>
+        <v>6962450</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16190,6 +16190,11 @@
       <c r="AA154" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16216,32 +16221,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128109763</v>
+        <v>128102121</v>
       </c>
       <c r="B155" t="n">
-        <v>80039</v>
+        <v>57833</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6456</v>
+        <v>103021</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16251,10 +16256,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>533449</v>
+        <v>533532</v>
       </c>
       <c r="R155" t="n">
-        <v>6962147</v>
+        <v>6962477</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16313,32 +16318,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128110768</v>
+        <v>128110831</v>
       </c>
       <c r="B156" t="n">
-        <v>57673</v>
+        <v>58532</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>208249</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16348,10 +16353,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>533754</v>
+        <v>533728</v>
       </c>
       <c r="R156" t="n">
-        <v>6962450</v>
+        <v>6962422</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16384,11 +16389,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska spår)</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16415,32 +16415,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128102121</v>
+        <v>128102104</v>
       </c>
       <c r="B157" t="n">
-        <v>57833</v>
+        <v>105516</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16450,10 +16450,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>533532</v>
+        <v>533615</v>
       </c>
       <c r="R157" t="n">
-        <v>6962477</v>
+        <v>6962423</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16512,32 +16512,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128110777</v>
+        <v>128110805</v>
       </c>
       <c r="B158" t="n">
-        <v>91133</v>
+        <v>98478</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16547,10 +16547,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>533841</v>
+        <v>533668</v>
       </c>
       <c r="R158" t="n">
-        <v>6962306</v>
+        <v>6962160</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16583,6 +16583,11 @@
       <c r="AA158" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>75 stycken</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16609,45 +16614,49 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128110795</v>
+        <v>128109586</v>
       </c>
       <c r="B159" t="n">
-        <v>80135</v>
+        <v>98478</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>533792</v>
+        <v>533498</v>
       </c>
       <c r="R159" t="n">
-        <v>6962400</v>
+        <v>6962158</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16706,32 +16715,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128110967</v>
+        <v>128110837</v>
       </c>
       <c r="B160" t="n">
-        <v>57673</v>
+        <v>98395</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16741,10 +16750,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>533691</v>
+        <v>533617</v>
       </c>
       <c r="R160" t="n">
-        <v>6962407</v>
+        <v>6962560</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16777,11 +16786,6 @@
       <c r="AA160" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -16808,32 +16812,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128110773</v>
+        <v>128110791</v>
       </c>
       <c r="B161" t="n">
-        <v>57673</v>
+        <v>98512</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16843,10 +16847,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>533604</v>
+        <v>533658</v>
       </c>
       <c r="R161" t="n">
-        <v>6962650</v>
+        <v>6962570</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -16879,11 +16883,6 @@
       <c r="AA161" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -16910,10 +16909,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128110774</v>
+        <v>128110795</v>
       </c>
       <c r="B162" t="n">
-        <v>57673</v>
+        <v>80135</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -16921,21 +16920,21 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -16945,10 +16944,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>533585</v>
+        <v>533792</v>
       </c>
       <c r="R162" t="n">
-        <v>6962612</v>
+        <v>6962400</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -16981,11 +16980,6 @@
       <c r="AA162" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC162" t="inlineStr">
-        <is>
-          <t>Färska ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -17012,32 +17006,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128110805</v>
+        <v>128110967</v>
       </c>
       <c r="B163" t="n">
-        <v>98478</v>
+        <v>57673</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17047,10 +17041,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>533668</v>
+        <v>533691</v>
       </c>
       <c r="R163" t="n">
-        <v>6962160</v>
+        <v>6962407</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17087,7 +17081,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>75 stycken</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -17114,49 +17108,45 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128109586</v>
+        <v>128110773</v>
       </c>
       <c r="B164" t="n">
-        <v>98478</v>
+        <v>57673</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>533498</v>
+        <v>533604</v>
       </c>
       <c r="R164" t="n">
-        <v>6962158</v>
+        <v>6962650</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17189,6 +17179,11 @@
       <c r="AA164" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -17215,32 +17210,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128110837</v>
+        <v>128110774</v>
       </c>
       <c r="B165" t="n">
-        <v>98395</v>
+        <v>57673</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17250,10 +17245,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>533617</v>
+        <v>533585</v>
       </c>
       <c r="R165" t="n">
-        <v>6962560</v>
+        <v>6962612</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17286,6 +17281,11 @@
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>Färska ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -17312,10 +17312,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128110791</v>
+        <v>128110777</v>
       </c>
       <c r="B166" t="n">
-        <v>98512</v>
+        <v>91133</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -17323,21 +17323,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17347,10 +17347,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>533658</v>
+        <v>533841</v>
       </c>
       <c r="R166" t="n">
-        <v>6962570</v>
+        <v>6962306</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18309,32 +18309,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128110799</v>
+        <v>128110835</v>
       </c>
       <c r="B176" t="n">
-        <v>80135</v>
+        <v>98395</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18344,10 +18344,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>533724</v>
+        <v>533748</v>
       </c>
       <c r="R176" t="n">
-        <v>6962625</v>
+        <v>6962431</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18406,10 +18406,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128110787</v>
+        <v>128110977</v>
       </c>
       <c r="B177" t="n">
-        <v>80163</v>
+        <v>98512</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -18417,21 +18417,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6461</v>
+        <v>219874</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18441,10 +18441,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>533785</v>
+        <v>534040</v>
       </c>
       <c r="R177" t="n">
-        <v>6962326</v>
+        <v>6962718</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18503,7 +18503,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128101075</v>
+        <v>128110799</v>
       </c>
       <c r="B178" t="n">
         <v>80135</v>
@@ -18538,10 +18538,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>533392</v>
+        <v>533724</v>
       </c>
       <c r="R178" t="n">
-        <v>6962343</v>
+        <v>6962625</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18600,50 +18600,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128108439</v>
+        <v>128110787</v>
       </c>
       <c r="B179" t="n">
-        <v>57673</v>
+        <v>80163</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>533711</v>
+        <v>533785</v>
       </c>
       <c r="R179" t="n">
-        <v>6962283</v>
+        <v>6962326</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18676,11 +18671,6 @@
       <c r="AA179" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18707,10 +18697,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128101939</v>
+        <v>128101075</v>
       </c>
       <c r="B180" t="n">
-        <v>57673</v>
+        <v>80135</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -18718,39 +18708,34 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>533638</v>
+        <v>533392</v>
       </c>
       <c r="R180" t="n">
-        <v>6962346</v>
+        <v>6962343</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18783,11 +18768,6 @@
       <c r="AA180" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -18814,7 +18794,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128100413</v>
+        <v>128108439</v>
       </c>
       <c r="B181" t="n">
         <v>57673</v>
@@ -18850,14 +18830,14 @@
       </c>
       <c r="P181" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>533545</v>
+        <v>533711</v>
       </c>
       <c r="R181" t="n">
-        <v>6962372</v>
+        <v>6962283</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -18921,49 +18901,50 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128107826</v>
+        <v>128101939</v>
       </c>
       <c r="B182" t="n">
-        <v>98478</v>
+        <v>57673</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>533723</v>
+        <v>533638</v>
       </c>
       <c r="R182" t="n">
-        <v>6962360</v>
+        <v>6962346</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -18996,6 +18977,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19022,45 +19008,50 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>128110828</v>
+        <v>128100413</v>
       </c>
       <c r="B183" t="n">
-        <v>98478</v>
+        <v>57673</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>533365</v>
+        <v>533545</v>
       </c>
       <c r="R183" t="n">
-        <v>6962304</v>
+        <v>6962372</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19097,7 +19088,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>30 stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19124,7 +19115,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128110817</v>
+        <v>128107826</v>
       </c>
       <c r="B184" t="n">
         <v>98478</v>
@@ -19152,17 +19143,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>533728</v>
+        <v>533723</v>
       </c>
       <c r="R184" t="n">
-        <v>6962346</v>
+        <v>6962360</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19195,11 +19190,6 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19226,32 +19216,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>128110835</v>
+        <v>128110828</v>
       </c>
       <c r="B185" t="n">
-        <v>98395</v>
+        <v>98478</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19261,10 +19251,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>533748</v>
+        <v>533365</v>
       </c>
       <c r="R185" t="n">
-        <v>6962431</v>
+        <v>6962304</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19297,6 +19287,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>30 stycken</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19323,32 +19318,32 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>128110977</v>
+        <v>128110817</v>
       </c>
       <c r="B186" t="n">
-        <v>98512</v>
+        <v>98478</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>219874</v>
+        <v>220787</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19358,10 +19353,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>534040</v>
+        <v>533728</v>
       </c>
       <c r="R186" t="n">
-        <v>6962718</v>
+        <v>6962346</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19394,6 +19389,11 @@
       <c r="AA186" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>40 stycken i blåbärsriset</t>
         </is>
       </c>
       <c r="AD186" t="b">

--- a/artfynd/A 36183-2025 artfynd.xlsx
+++ b/artfynd/A 36183-2025 artfynd.xlsx
@@ -1311,32 +1311,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128110802</v>
+        <v>128109460</v>
       </c>
       <c r="B8" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1346,10 +1346,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>533461</v>
+        <v>533498</v>
       </c>
       <c r="R8" t="n">
-        <v>6962171</v>
+        <v>6962158</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1382,11 +1382,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,49 +1408,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128100827</v>
+        <v>128108655</v>
       </c>
       <c r="B9" t="n">
-        <v>98478</v>
+        <v>92742</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>533406</v>
+        <v>533673</v>
       </c>
       <c r="R9" t="n">
-        <v>6962317</v>
+        <v>6962211</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,32 +1505,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128109460</v>
+        <v>128110802</v>
       </c>
       <c r="B10" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>533498</v>
+        <v>533461</v>
       </c>
       <c r="R10" t="n">
-        <v>6962158</v>
+        <v>6962171</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1585,6 +1576,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,50 +1607,49 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128108619</v>
+        <v>128100827</v>
       </c>
       <c r="B11" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>533675</v>
+        <v>533406</v>
       </c>
       <c r="R11" t="n">
-        <v>6962244</v>
+        <v>6962317</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,11 +1682,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1718,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128110972</v>
+        <v>128108619</v>
       </c>
       <c r="B12" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,16 +1737,21 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>533997</v>
+        <v>533675</v>
       </c>
       <c r="R12" t="n">
-        <v>6962746</v>
+        <v>6962244</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1793,7 +1788,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1820,10 +1815,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128101860</v>
+        <v>128110972</v>
       </c>
       <c r="B13" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1849,21 +1844,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>533601</v>
+        <v>533997</v>
       </c>
       <c r="R13" t="n">
-        <v>6962344</v>
+        <v>6962746</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,7 +1890,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,45 +1917,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128108655</v>
+        <v>128101860</v>
       </c>
       <c r="B14" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>533673</v>
+        <v>533601</v>
       </c>
       <c r="R14" t="n">
-        <v>6962211</v>
+        <v>6962344</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1998,6 +1993,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2024,49 +2024,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128100321</v>
+        <v>128101567</v>
       </c>
       <c r="B15" t="n">
-        <v>98478</v>
+        <v>80092</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>533537</v>
+        <v>533494</v>
       </c>
       <c r="R15" t="n">
-        <v>6962358</v>
+        <v>6962425</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2125,49 +2121,50 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128100131</v>
+        <v>128108700</v>
       </c>
       <c r="B16" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>533496</v>
+        <v>533674</v>
       </c>
       <c r="R16" t="n">
-        <v>6962335</v>
+        <v>6962199</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2200,6 +2197,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2226,45 +2228,50 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128110818</v>
+        <v>128109367</v>
       </c>
       <c r="B17" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>533766</v>
+        <v>533550</v>
       </c>
       <c r="R17" t="n">
-        <v>6962317</v>
+        <v>6962157</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,7 +2308,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>10stycken</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2331,7 +2338,7 @@
         <v>128110833</v>
       </c>
       <c r="B18" t="n">
-        <v>98395</v>
+        <v>98488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2425,50 +2432,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128108700</v>
+        <v>128100321</v>
       </c>
       <c r="B19" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>533674</v>
+        <v>533537</v>
       </c>
       <c r="R19" t="n">
-        <v>6962199</v>
+        <v>6962358</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2501,11 +2507,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2532,38 +2533,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128109367</v>
+        <v>128100131</v>
       </c>
       <c r="B20" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2572,10 +2572,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>533550</v>
+        <v>533496</v>
       </c>
       <c r="R20" t="n">
-        <v>6962157</v>
+        <v>6962335</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2608,11 +2608,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2639,32 +2634,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128101567</v>
+        <v>128110818</v>
       </c>
       <c r="B21" t="n">
-        <v>80039</v>
+        <v>98571</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2674,10 +2669,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>533494</v>
+        <v>533766</v>
       </c>
       <c r="R21" t="n">
-        <v>6962425</v>
+        <v>6962317</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,6 +2705,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>10stycken</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2736,10 +2736,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128099395</v>
+        <v>128110771</v>
       </c>
       <c r="B22" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2765,21 +2765,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>533356</v>
+        <v>533583</v>
       </c>
       <c r="R22" t="n">
-        <v>6962190</v>
+        <v>6962697</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2816,7 +2811,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
+          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2843,49 +2838,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128101601</v>
+        <v>128109293</v>
       </c>
       <c r="B23" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>533496</v>
+        <v>533638</v>
       </c>
       <c r="R23" t="n">
-        <v>6962407</v>
+        <v>6962157</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2918,6 +2914,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2944,49 +2945,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128108218</v>
+        <v>128110832</v>
       </c>
       <c r="B24" t="n">
-        <v>98478</v>
+        <v>98488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>533789</v>
+        <v>533652</v>
       </c>
       <c r="R24" t="n">
-        <v>6962263</v>
+        <v>6962264</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3045,45 +3042,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128108592</v>
+        <v>128101601</v>
       </c>
       <c r="B25" t="n">
-        <v>80039</v>
+        <v>98571</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>533675</v>
+        <v>533496</v>
       </c>
       <c r="R25" t="n">
-        <v>6962244</v>
+        <v>6962407</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3142,45 +3143,49 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128110771</v>
+        <v>128108218</v>
       </c>
       <c r="B26" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>533583</v>
+        <v>533789</v>
       </c>
       <c r="R26" t="n">
-        <v>6962697</v>
+        <v>6962263</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3213,11 +3218,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Träd nr 2, ringhack av tretåig hackspett på gran. Färska spår</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3244,50 +3244,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128109293</v>
+        <v>128108592</v>
       </c>
       <c r="B27" t="n">
-        <v>57673</v>
+        <v>80092</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>533638</v>
+        <v>533675</v>
       </c>
       <c r="R27" t="n">
-        <v>6962157</v>
+        <v>6962244</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3320,11 +3315,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3351,45 +3341,50 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128110832</v>
+        <v>128099395</v>
       </c>
       <c r="B28" t="n">
-        <v>98395</v>
+        <v>57685</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>533652</v>
+        <v>533356</v>
       </c>
       <c r="R28" t="n">
-        <v>6962264</v>
+        <v>6962190</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3422,6 +3417,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall (äldre, färska, och helt nya)! Visar på lång användning av området.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3448,45 +3448,50 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128110780</v>
+        <v>128099402</v>
       </c>
       <c r="B29" t="n">
-        <v>91133</v>
+        <v>57685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>533670</v>
+        <v>533474</v>
       </c>
       <c r="R29" t="n">
-        <v>6962552</v>
+        <v>6962267</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3519,6 +3524,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3545,10 +3555,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128110790</v>
+        <v>128110780</v>
       </c>
       <c r="B30" t="n">
-        <v>98512</v>
+        <v>91225</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3556,21 +3566,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>219874</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3580,10 +3590,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>533822</v>
+        <v>533670</v>
       </c>
       <c r="R30" t="n">
-        <v>6962344</v>
+        <v>6962552</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3616,11 +3626,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3650,7 +3655,7 @@
         <v>128099830</v>
       </c>
       <c r="B31" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3758,32 +3763,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128110803</v>
+        <v>128110790</v>
       </c>
       <c r="B32" t="n">
-        <v>98478</v>
+        <v>98605</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3793,10 +3798,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>533524</v>
+        <v>533822</v>
       </c>
       <c r="R32" t="n">
-        <v>6962153</v>
+        <v>6962344</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3833,7 +3838,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>50 stycken</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3860,10 +3865,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128110981</v>
+        <v>128110803</v>
       </c>
       <c r="B33" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3895,10 +3900,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>533689</v>
+        <v>533524</v>
       </c>
       <c r="R33" t="n">
-        <v>6962405</v>
+        <v>6962153</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3935,7 +3940,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>15 ex</t>
+          <t>50 stycken</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3962,10 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128109875</v>
+        <v>128110981</v>
       </c>
       <c r="B34" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3990,21 +3995,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>533436</v>
+        <v>533689</v>
       </c>
       <c r="R34" t="n">
-        <v>6962158</v>
+        <v>6962405</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4037,6 +4038,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>15 ex</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4063,10 +4069,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128102143</v>
+        <v>128109875</v>
       </c>
       <c r="B35" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4093,7 +4099,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4102,10 +4108,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>533615</v>
+        <v>533436</v>
       </c>
       <c r="R35" t="n">
-        <v>6962423</v>
+        <v>6962158</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4164,10 +4170,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128100230</v>
+        <v>128102143</v>
       </c>
       <c r="B36" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4194,7 +4200,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>45</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4203,10 +4209,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>533506</v>
+        <v>533615</v>
       </c>
       <c r="R36" t="n">
-        <v>6962358</v>
+        <v>6962423</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4265,38 +4271,37 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128099402</v>
+        <v>128100230</v>
       </c>
       <c r="B37" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>55</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4305,10 +4310,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>533474</v>
+        <v>533506</v>
       </c>
       <c r="R37" t="n">
-        <v>6962267</v>
+        <v>6962358</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4341,11 +4346,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4372,32 +4372,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128110824</v>
+        <v>128099282</v>
       </c>
       <c r="B38" t="n">
-        <v>98478</v>
+        <v>80216</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4407,10 +4407,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>533712</v>
+        <v>533452</v>
       </c>
       <c r="R38" t="n">
-        <v>6962628</v>
+        <v>6962232</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4443,11 +4443,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4474,10 +4469,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128110978</v>
+        <v>128108150</v>
       </c>
       <c r="B39" t="n">
-        <v>98512</v>
+        <v>80217</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4485,34 +4480,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219874</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>533708</v>
+        <v>533800</v>
       </c>
       <c r="R39" t="n">
-        <v>6962645</v>
+        <v>6962306</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4571,32 +4566,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128110788</v>
+        <v>128110968</v>
       </c>
       <c r="B40" t="n">
-        <v>98512</v>
+        <v>57685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4606,10 +4601,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>533590</v>
+        <v>533634</v>
       </c>
       <c r="R40" t="n">
-        <v>6962592</v>
+        <v>6962526</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4642,6 +4637,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>En födosökande individ</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4668,45 +4668,50 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128110836</v>
+        <v>128102724</v>
       </c>
       <c r="B41" t="n">
-        <v>98395</v>
+        <v>57685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>533722</v>
+        <v>533659</v>
       </c>
       <c r="R41" t="n">
-        <v>6962426</v>
+        <v>6962512</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4739,6 +4744,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4765,45 +4775,50 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128108150</v>
+        <v>128101831</v>
       </c>
       <c r="B42" t="n">
-        <v>80164</v>
+        <v>57685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>533800</v>
+        <v>533513</v>
       </c>
       <c r="R42" t="n">
-        <v>6962306</v>
+        <v>6962442</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4836,6 +4851,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4862,10 +4882,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128110968</v>
+        <v>128110767</v>
       </c>
       <c r="B43" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4897,10 +4917,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>533634</v>
+        <v>533794</v>
       </c>
       <c r="R43" t="n">
-        <v>6962526</v>
+        <v>6962411</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4937,7 +4957,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>En födosökande individ</t>
+          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4964,50 +4984,45 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128102724</v>
+        <v>128110978</v>
       </c>
       <c r="B44" t="n">
-        <v>57673</v>
+        <v>98605</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>533659</v>
+        <v>533708</v>
       </c>
       <c r="R44" t="n">
-        <v>6962512</v>
+        <v>6962645</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5040,11 +5055,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5071,50 +5081,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128101831</v>
+        <v>128110788</v>
       </c>
       <c r="B45" t="n">
-        <v>57673</v>
+        <v>98605</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>533513</v>
+        <v>533590</v>
       </c>
       <c r="R45" t="n">
-        <v>6962442</v>
+        <v>6962592</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5147,11 +5152,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5178,32 +5178,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128110767</v>
+        <v>128110836</v>
       </c>
       <c r="B46" t="n">
-        <v>57673</v>
+        <v>98488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5213,10 +5213,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>533794</v>
+        <v>533722</v>
       </c>
       <c r="R46" t="n">
-        <v>6962411</v>
+        <v>6962426</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,11 +5249,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5280,32 +5275,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128099282</v>
+        <v>128110824</v>
       </c>
       <c r="B47" t="n">
-        <v>80163</v>
+        <v>98571</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5315,10 +5310,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>533452</v>
+        <v>533712</v>
       </c>
       <c r="R47" t="n">
-        <v>6962232</v>
+        <v>6962628</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5351,6 +5346,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5377,10 +5377,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128110766</v>
+        <v>128101702</v>
       </c>
       <c r="B48" t="n">
-        <v>57673</v>
+        <v>91452</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5388,21 +5388,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>533586</v>
+        <v>533529</v>
       </c>
       <c r="R48" t="n">
-        <v>6962139</v>
+        <v>6962400</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5448,11 +5448,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5479,10 +5474,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128110970</v>
+        <v>128107546</v>
       </c>
       <c r="B49" t="n">
-        <v>57673</v>
+        <v>80189</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5490,34 +5485,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>534050</v>
+        <v>533648</v>
       </c>
       <c r="R49" t="n">
-        <v>6962743</v>
+        <v>6962374</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5550,11 +5545,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5581,10 +5571,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128101702</v>
+        <v>128110766</v>
       </c>
       <c r="B50" t="n">
-        <v>91360</v>
+        <v>57685</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5592,21 +5582,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5616,10 +5606,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>533529</v>
+        <v>533586</v>
       </c>
       <c r="R50" t="n">
-        <v>6962400</v>
+        <v>6962139</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5652,6 +5642,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Färska ringhack på Tall av tretåig hackspett</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5678,49 +5673,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128099088</v>
+        <v>128110970</v>
       </c>
       <c r="B51" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>533425</v>
+        <v>534050</v>
       </c>
       <c r="R51" t="n">
-        <v>6962182</v>
+        <v>6962743</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5753,6 +5744,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5779,10 +5775,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128110826</v>
+        <v>128099088</v>
       </c>
       <c r="B52" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5807,17 +5803,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>533579</v>
+        <v>533425</v>
       </c>
       <c r="R52" t="n">
-        <v>6962663</v>
+        <v>6962182</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5850,11 +5850,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5881,45 +5876,54 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128110804</v>
+        <v>128103304</v>
       </c>
       <c r="B53" t="n">
-        <v>98478</v>
+        <v>91225</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>533532</v>
+        <v>533594</v>
       </c>
       <c r="R53" t="n">
-        <v>6962156</v>
+        <v>6962541</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5952,11 +5956,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5983,10 +5982,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128110990</v>
+        <v>128110812</v>
       </c>
       <c r="B54" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6018,10 +6017,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>533873</v>
+        <v>533715</v>
       </c>
       <c r="R54" t="n">
-        <v>6962782</v>
+        <v>6962610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6058,7 +6057,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>5 ex</t>
+          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6085,10 +6084,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128110814</v>
+        <v>128110826</v>
       </c>
       <c r="B55" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6120,10 +6119,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>533650</v>
+        <v>533579</v>
       </c>
       <c r="R55" t="n">
-        <v>6962134</v>
+        <v>6962663</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6160,7 +6159,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>50 stycken ( några har blommat).</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6187,45 +6186,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128108922</v>
+        <v>128110804</v>
       </c>
       <c r="B56" t="n">
-        <v>105516</v>
+        <v>98571</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>533671</v>
+        <v>533532</v>
       </c>
       <c r="R56" t="n">
-        <v>6962142</v>
+        <v>6962156</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6258,6 +6257,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>12 stycken, kan möjlitvis finnas fler I blåbärsriset</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6284,45 +6288,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128107546</v>
+        <v>128110990</v>
       </c>
       <c r="B57" t="n">
-        <v>80136</v>
+        <v>98571</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>533648</v>
+        <v>533873</v>
       </c>
       <c r="R57" t="n">
-        <v>6962374</v>
+        <v>6962782</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6355,6 +6359,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>5 ex</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6381,54 +6390,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128103304</v>
+        <v>128110814</v>
       </c>
       <c r="B58" t="n">
-        <v>91133</v>
+        <v>98571</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3215</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>533594</v>
+        <v>533650</v>
       </c>
       <c r="R58" t="n">
-        <v>6962541</v>
+        <v>6962134</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6461,6 +6461,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>50 stycken ( några har blommat).</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6487,45 +6492,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128110812</v>
+        <v>128108922</v>
       </c>
       <c r="B59" t="n">
-        <v>98478</v>
+        <v>105609</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>533715</v>
+        <v>533671</v>
       </c>
       <c r="R59" t="n">
-        <v>6962610</v>
+        <v>6962142</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6558,11 +6563,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>60 stycken</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6592,7 +6592,7 @@
         <v>128101106</v>
       </c>
       <c r="B60" t="n">
-        <v>80101</v>
+        <v>80154</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6686,10 +6686,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128100636</v>
+        <v>128110971</v>
       </c>
       <c r="B61" t="n">
-        <v>80135</v>
+        <v>57685</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6697,21 +6697,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6721,10 +6721,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>533452</v>
+        <v>534036</v>
       </c>
       <c r="R61" t="n">
-        <v>6962350</v>
+        <v>6962734</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6757,6 +6757,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6783,49 +6788,50 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128100184</v>
+        <v>128108477</v>
       </c>
       <c r="B62" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>40</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>533509</v>
+        <v>533710</v>
       </c>
       <c r="R62" t="n">
-        <v>6962336</v>
+        <v>6962294</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6858,6 +6864,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6884,10 +6895,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128103587</v>
+        <v>128110827</v>
       </c>
       <c r="B63" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6912,21 +6923,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>533650</v>
+        <v>533614</v>
       </c>
       <c r="R63" t="n">
-        <v>6962600</v>
+        <v>6962554</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6959,6 +6966,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>25 ex</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6985,45 +6997,49 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128099984</v>
+        <v>128100184</v>
       </c>
       <c r="B64" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>533455</v>
+        <v>533509</v>
       </c>
       <c r="R64" t="n">
-        <v>6962339</v>
+        <v>6962336</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7082,45 +7098,49 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128099875</v>
+        <v>128103587</v>
       </c>
       <c r="B65" t="n">
-        <v>80135</v>
+        <v>98571</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>533445</v>
+        <v>533650</v>
       </c>
       <c r="R65" t="n">
-        <v>6962324</v>
+        <v>6962600</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7179,10 +7199,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128110971</v>
+        <v>128099984</v>
       </c>
       <c r="B66" t="n">
-        <v>57673</v>
+        <v>80188</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7190,21 +7210,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7214,10 +7234,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>534036</v>
+        <v>533455</v>
       </c>
       <c r="R66" t="n">
-        <v>6962734</v>
+        <v>6962339</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7250,11 +7270,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7281,10 +7296,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128108477</v>
+        <v>128099875</v>
       </c>
       <c r="B67" t="n">
-        <v>57673</v>
+        <v>80188</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7292,39 +7307,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>533710</v>
+        <v>533445</v>
       </c>
       <c r="R67" t="n">
-        <v>6962294</v>
+        <v>6962324</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7357,11 +7367,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7388,32 +7393,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128110827</v>
+        <v>128100636</v>
       </c>
       <c r="B68" t="n">
-        <v>98478</v>
+        <v>80188</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7423,10 +7428,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>533614</v>
+        <v>533452</v>
       </c>
       <c r="R68" t="n">
-        <v>6962554</v>
+        <v>6962350</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7459,11 +7464,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>25 ex</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7493,7 +7493,7 @@
         <v>128099885</v>
       </c>
       <c r="B69" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>128099522</v>
       </c>
       <c r="B70" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>128099099</v>
       </c>
       <c r="B71" t="n">
-        <v>105516</v>
+        <v>105609</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7800,10 +7800,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128110769</v>
+        <v>128099712</v>
       </c>
       <c r="B72" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7829,16 +7829,21 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>533841</v>
+        <v>533451</v>
       </c>
       <c r="R72" t="n">
-        <v>6962363</v>
+        <v>6962307</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7875,7 +7880,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack) spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7902,32 +7907,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128110775</v>
+        <v>128099857</v>
       </c>
       <c r="B73" t="n">
-        <v>57673</v>
+        <v>80217</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7937,10 +7942,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>533564</v>
+        <v>533445</v>
       </c>
       <c r="R73" t="n">
-        <v>6962537</v>
+        <v>6962324</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7973,11 +7978,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8004,10 +8004,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128108355</v>
+        <v>128110769</v>
       </c>
       <c r="B74" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8033,21 +8033,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>533768</v>
+        <v>533841</v>
       </c>
       <c r="R74" t="n">
-        <v>6962269</v>
+        <v>6962363</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8084,7 +8079,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall ( färska ringhack) spår</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8111,10 +8106,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128101911</v>
+        <v>128110775</v>
       </c>
       <c r="B75" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8140,21 +8135,16 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>533510</v>
+        <v>533564</v>
       </c>
       <c r="R75" t="n">
-        <v>6962462</v>
+        <v>6962537</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8191,7 +8181,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Färska och äldre ringhack på Tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8218,49 +8208,50 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128101024</v>
+        <v>128108355</v>
       </c>
       <c r="B76" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>533375</v>
+        <v>533768</v>
       </c>
       <c r="R76" t="n">
-        <v>6962293</v>
+        <v>6962269</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8293,6 +8284,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8319,45 +8315,50 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128099857</v>
+        <v>128101911</v>
       </c>
       <c r="B77" t="n">
-        <v>80164</v>
+        <v>57685</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>533445</v>
+        <v>533510</v>
       </c>
       <c r="R77" t="n">
-        <v>6962324</v>
+        <v>6962462</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8390,6 +8391,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8416,10 +8422,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128110811</v>
+        <v>128101024</v>
       </c>
       <c r="B78" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8444,17 +8450,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>533706</v>
+        <v>533375</v>
       </c>
       <c r="R78" t="n">
-        <v>6962596</v>
+        <v>6962293</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8487,11 +8497,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>24 stycken</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8518,50 +8523,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128099712</v>
+        <v>128110811</v>
       </c>
       <c r="B79" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>533451</v>
+        <v>533706</v>
       </c>
       <c r="R79" t="n">
-        <v>6962307</v>
+        <v>6962596</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>24 stycken</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8628,7 +8628,7 @@
         <v>128102006</v>
       </c>
       <c r="B80" t="n">
-        <v>80135</v>
+        <v>80188</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8722,32 +8722,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128110810</v>
+        <v>128110779</v>
       </c>
       <c r="B81" t="n">
-        <v>98478</v>
+        <v>91225</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8757,10 +8757,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>533645</v>
+        <v>533678</v>
       </c>
       <c r="R81" t="n">
-        <v>6962593</v>
+        <v>6962542</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8819,10 +8819,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128099905</v>
+        <v>128101827</v>
       </c>
       <c r="B82" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8859,10 +8859,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>533445</v>
+        <v>533594</v>
       </c>
       <c r="R82" t="n">
-        <v>6962324</v>
+        <v>6962354</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8926,45 +8926,50 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128110779</v>
+        <v>128100974</v>
       </c>
       <c r="B83" t="n">
-        <v>91133</v>
+        <v>57685</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3215</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>533678</v>
+        <v>533375</v>
       </c>
       <c r="R83" t="n">
-        <v>6962542</v>
+        <v>6962293</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8997,6 +9002,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9023,10 +9033,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128101827</v>
+        <v>128110969</v>
       </c>
       <c r="B84" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9052,21 +9062,16 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>533594</v>
+        <v>533825</v>
       </c>
       <c r="R84" t="n">
-        <v>6962354</v>
+        <v>6962690</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9103,7 +9108,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9130,50 +9135,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128100974</v>
+        <v>128110976</v>
       </c>
       <c r="B85" t="n">
-        <v>57673</v>
+        <v>98605</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>219874</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>533375</v>
+        <v>533868</v>
       </c>
       <c r="R85" t="n">
-        <v>6962293</v>
+        <v>6962692</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall ( färska) och äldre</t>
+          <t>Växer spritt i hela området</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9237,45 +9237,49 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128110969</v>
+        <v>128101261</v>
       </c>
       <c r="B86" t="n">
-        <v>57673</v>
+        <v>98571</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>533825</v>
+        <v>533424</v>
       </c>
       <c r="R86" t="n">
-        <v>6962690</v>
+        <v>6962357</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9308,11 +9312,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9339,10 +9338,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128101261</v>
+        <v>128110982</v>
       </c>
       <c r="B87" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9367,21 +9366,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>533424</v>
+        <v>533681</v>
       </c>
       <c r="R87" t="n">
-        <v>6962357</v>
+        <v>6962434</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9414,6 +9409,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>23 ex</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9440,10 +9440,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128110982</v>
+        <v>128110810</v>
       </c>
       <c r="B88" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9475,10 +9475,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>533681</v>
+        <v>533645</v>
       </c>
       <c r="R88" t="n">
-        <v>6962434</v>
+        <v>6962593</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9511,11 +9511,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>23 ex</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9542,45 +9537,50 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128110976</v>
+        <v>128099905</v>
       </c>
       <c r="B89" t="n">
-        <v>98512</v>
+        <v>57685</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>219874</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>533868</v>
+        <v>533445</v>
       </c>
       <c r="R89" t="n">
-        <v>6962692</v>
+        <v>6962324</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9617,7 +9617,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Växer spritt i hela området</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9647,7 +9647,7 @@
         <v>128100745</v>
       </c>
       <c r="B90" t="n">
-        <v>80039</v>
+        <v>80092</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9744,7 +9744,7 @@
         <v>128110973</v>
       </c>
       <c r="B91" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9846,7 +9846,7 @@
         <v>128110989</v>
       </c>
       <c r="B92" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9948,7 +9948,7 @@
         <v>128110806</v>
       </c>
       <c r="B93" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>128110974</v>
       </c>
       <c r="B94" t="n">
-        <v>80164</v>
+        <v>80217</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10144,50 +10144,54 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128102878</v>
+        <v>128099401</v>
       </c>
       <c r="B95" t="n">
-        <v>57673</v>
+        <v>92742</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>533665</v>
+        <v>533356</v>
       </c>
       <c r="R95" t="n">
-        <v>6962515</v>
+        <v>6962190</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10220,11 +10224,6 @@
       <c r="AA95" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10251,10 +10250,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128100043</v>
+        <v>128102878</v>
       </c>
       <c r="B96" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10287,14 +10286,14 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Mörttjärnbäcken, Jmt</t>
+          <t>Gravtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>533496</v>
+        <v>533665</v>
       </c>
       <c r="R96" t="n">
-        <v>6962335</v>
+        <v>6962515</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10358,42 +10357,38 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128099401</v>
+        <v>128100043</v>
       </c>
       <c r="B97" t="n">
-        <v>92650</v>
+        <v>57685</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -10402,10 +10397,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>533356</v>
+        <v>533496</v>
       </c>
       <c r="R97" t="n">
-        <v>6962190</v>
+        <v>6962335</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10438,6 +10433,11 @@
       <c r="AA97" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10464,50 +10464,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128099555</v>
+        <v>128110834</v>
       </c>
       <c r="B98" t="n">
-        <v>57673</v>
+        <v>98488</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>533471</v>
+        <v>533779</v>
       </c>
       <c r="R98" t="n">
-        <v>6962293</v>
+        <v>6962298</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10540,11 +10535,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10571,32 +10561,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128110834</v>
+        <v>128110816</v>
       </c>
       <c r="B99" t="n">
-        <v>98395</v>
+        <v>98571</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10606,10 +10596,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>533779</v>
+        <v>533696</v>
       </c>
       <c r="R99" t="n">
-        <v>6962298</v>
+        <v>6962294</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10642,6 +10632,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10668,10 +10663,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128110816</v>
+        <v>128102067</v>
       </c>
       <c r="B100" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10696,17 +10691,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>533696</v>
+        <v>533510</v>
       </c>
       <c r="R100" t="n">
-        <v>6962294</v>
+        <v>6962462</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10739,11 +10738,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>20 stycken</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10770,37 +10764,38 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128102067</v>
+        <v>128099555</v>
       </c>
       <c r="B101" t="n">
-        <v>98478</v>
+        <v>57685</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -10809,10 +10804,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>533510</v>
+        <v>533471</v>
       </c>
       <c r="R101" t="n">
-        <v>6962462</v>
+        <v>6962293</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10845,6 +10840,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Både äldre och färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10874,7 +10874,7 @@
         <v>128101073</v>
       </c>
       <c r="B102" t="n">
-        <v>80171</v>
+        <v>80224</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10968,32 +10968,32 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128110829</v>
+        <v>128110792</v>
       </c>
       <c r="B103" t="n">
-        <v>56855</v>
+        <v>98605</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>102612</v>
+        <v>219874</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11003,10 +11003,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>533606</v>
+        <v>533719</v>
       </c>
       <c r="R103" t="n">
-        <v>6962582</v>
+        <v>6962615</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>1 ex. Sång</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11073,7 +11073,7 @@
         <v>128110807</v>
       </c>
       <c r="B104" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>128110983</v>
       </c>
       <c r="B105" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11274,10 +11274,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128110792</v>
+        <v>128110785</v>
       </c>
       <c r="B106" t="n">
-        <v>98512</v>
+        <v>97448</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11285,21 +11285,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219874</v>
+        <v>221945</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11309,10 +11309,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>533719</v>
+        <v>533824</v>
       </c>
       <c r="R106" t="n">
-        <v>6962615</v>
+        <v>6962352</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11345,11 +11345,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2025-08-31</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11376,32 +11371,32 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>128110785</v>
+        <v>128110829</v>
       </c>
       <c r="B107" t="n">
-        <v>97355</v>
+        <v>56867</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11411,10 +11406,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>533824</v>
+        <v>533606</v>
       </c>
       <c r="R107" t="n">
-        <v>6962352</v>
+        <v>6962582</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11447,6 +11442,11 @@
       <c r="AA107" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>1 ex. Sång</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11473,32 +11473,32 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128110991</v>
+        <v>128110776</v>
       </c>
       <c r="B108" t="n">
-        <v>98478</v>
+        <v>57845</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11508,10 +11508,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>533717</v>
+        <v>533719</v>
       </c>
       <c r="R108" t="n">
-        <v>6962645</v>
+        <v>6962615</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11548,7 +11548,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>6 ex</t>
+          <t>2 stycken</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11575,10 +11575,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128110987</v>
+        <v>128110991</v>
       </c>
       <c r="B109" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11610,10 +11610,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>533999</v>
+        <v>533717</v>
       </c>
       <c r="R109" t="n">
-        <v>6962664</v>
+        <v>6962645</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11650,7 +11650,7 @@
       </c>
       <c r="AC109" t="inlineStr">
         <is>
-          <t>85 ex</t>
+          <t>6 ex</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11677,10 +11677,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128103044</v>
+        <v>128110987</v>
       </c>
       <c r="B110" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11705,21 +11705,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Gravtjärnen, Jmt</t>
+          <t>Mörttjärnbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">